--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -343,6 +343,18 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>UPSON INTERNATIONAL CORP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2nd floor SM Cyberzone SM City Sta. Rosa, Tagapo, City Of Santa Rosa, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-03-03-0771</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1174-419</x:t>
+  </x:si>
+  <x:si>
     <x:t>INNOVASIA MARKETING</x:t>
   </x:si>
   <x:si>
@@ -353,6 +365,33 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1146-031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2106</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1176-385</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1175-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-17-03-2015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1173-016</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -673,7 +712,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -745,9 +784,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -3227,7 +3263,7 @@
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>55</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
         <x:v>106</x:v>
@@ -3245,19 +3281,19 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="H6" s="12">
-        <x:v>46083.0787962963</x:v>
+        <x:v>46086.1064814815</x:v>
       </x:c>
       <x:c r="I6" s="32">
-        <x:v>46084</x:v>
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J6" s="11" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K6" s="13" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L6" s="12">
-        <x:v>46083.104224537</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
         <x:v>50</x:v>
@@ -3265,70 +3301,215 @@
       <x:c r="N6" s="7" t="s"/>
       <x:c r="O6" s="9" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
+      <x:c r="B7" s="11" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H7" s="12">
+        <x:v>46083.0787962963</x:v>
+      </x:c>
+      <x:c r="I7" s="32">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J7" s="11" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K7" s="13" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L7" s="12">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M7" s="11" t="s">
+        <x:v>50</x:v>
+      </x:c>
       <x:c r="N7" s="7" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="20" t="s">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B8" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I8" s="19">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="18">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I9" s="19">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L9" s="18">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I10" s="19">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="18">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="20" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C9" s="21" t="s"/>
-      <x:c r="D9" s="21" t="s"/>
-      <x:c r="E9" s="22" t="s"/>
-      <x:c r="F9" s="22" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="23" t="s">
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="C10" s="24" t="s"/>
-      <x:c r="D10" s="24" t="s"/>
-      <x:c r="E10" s="24" t="s"/>
-      <x:c r="F10" s="25" t="s">
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
         <x:v>104</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="26" t="s">
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="26" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="C11" s="27" t="s"/>
-      <x:c r="D11" s="27" t="s"/>
-      <x:c r="E11" s="27" t="s"/>
-      <x:c r="F11" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="29" t="s">
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B17" s="29" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C12" s="30" t="s"/>
-      <x:c r="D12" s="30" t="s"/>
-      <x:c r="E12" s="30" t="s"/>
-      <x:c r="F12" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C17" s="30" t="s"/>
+      <x:c r="D17" s="30" t="s"/>
+      <x:c r="E17" s="30" t="s"/>
+      <x:c r="F17" s="31" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4306,13 +4487,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
+  <x:mergeCells count="7">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
-    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -353,6 +353,30 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1174-419</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2518</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1172-434</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ricardo Natividad</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2519</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1171-081</x:t>
   </x:si>
   <x:si>
     <x:t>INNOVASIA MARKETING</x:t>
@@ -3304,13 +3328,13 @@
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="7" t="s"/>
       <x:c r="B7" s="11" t="s">
-        <x:v>55</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C7" s="11" t="s">
         <x:v>110</x:v>
       </x:c>
       <x:c r="D7" s="11" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E7" s="11" t="s">
         <x:v>111</x:v>
@@ -3322,61 +3346,61 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="H7" s="12">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I7" s="32">
-        <x:v>46084</x:v>
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I7" s="12">
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K7" s="13" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L7" s="12">
-        <x:v>46083.104224537</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M7" s="11" t="s">
-        <x:v>50</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="N7" s="7" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B8" s="14" t="s">
-        <x:v>55</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>106</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D8" s="15" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46085.1662615741</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L8" s="18">
+        <x:v>46090.3437268519</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46087.1643287037</x:v>
-      </x:c>
-      <x:c r="I8" s="19">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="n">
-        <x:v>1511760</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46090.2727777778</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -3384,34 +3408,34 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>106</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I9" s="19">
-        <x:v>46097</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J9" s="15" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1511639</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46083.104224537</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>50</x:v>
@@ -3428,91 +3452,175 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G10" s="14" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46087.1643287037</x:v>
       </x:c>
       <x:c r="I10" s="19">
-        <x:v>46098</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J10" s="15" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511760</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46090.2727777778</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I12" s="19">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="20" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
+      <x:c r="C15" s="21" t="s"/>
+      <x:c r="D15" s="21" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="22" t="s"/>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B16" s="23" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
+      <x:c r="C16" s="24" t="s"/>
+      <x:c r="D16" s="24" t="s"/>
+      <x:c r="E16" s="24" t="s"/>
+      <x:c r="F16" s="25" t="s">
         <x:v>104</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="26" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="26" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="26" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="29" t="s">
+    <x:row r="20" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B20" s="29" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C17" s="30" t="s"/>
-      <x:c r="D17" s="30" t="s"/>
-      <x:c r="E17" s="30" t="s"/>
-      <x:c r="F17" s="31" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C20" s="30" t="s"/>
+      <x:c r="D20" s="30" t="s"/>
+      <x:c r="E20" s="30" t="s"/>
+      <x:c r="F20" s="31" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4487,14 +4595,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
+  <x:mergeCells count="8">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B13:F13"/>
-    <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B15:F15"/>
     <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -341,6 +341,18 @@
   </x:si>
   <x:si>
     <x:t>TOTAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERALD BEBIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>94 Magsaysay, Poblacion, Cavinti, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03009-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1189-403</x:t>
   </x:si>
   <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
@@ -3287,14 +3299,12 @@
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>30</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>32</x:v>
-      </x:c>
+      <x:c r="D6" s="11" t="s"/>
       <x:c r="E6" s="11" t="s">
         <x:v>107</x:v>
       </x:c>
@@ -3305,19 +3315,19 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="H6" s="12">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I6" s="32">
-        <x:v>46095</x:v>
+        <x:v>46091.306099537</x:v>
+      </x:c>
+      <x:c r="I6" s="12">
+        <x:v>46091.3107986111</x:v>
       </x:c>
       <x:c r="J6" s="11" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511778</x:v>
       </x:c>
       <x:c r="K6" s="13" t="n">
-        <x:v>3030</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L6" s="12">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46091.3131828704</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
         <x:v>50</x:v>
@@ -3328,13 +3338,13 @@
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="7" t="s"/>
       <x:c r="B7" s="11" t="s">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C7" s="11" t="s">
         <x:v>110</x:v>
       </x:c>
       <x:c r="D7" s="11" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E7" s="11" t="s">
         <x:v>111</x:v>
@@ -3346,22 +3356,22 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="H7" s="12">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I7" s="12">
-        <x:v>46085.1709375</x:v>
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I7" s="32">
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K7" s="13" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L7" s="12">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M7" s="11" t="s">
-        <x:v>114</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="N7" s="7" t="s"/>
     </x:row>
@@ -3370,7 +3380,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>110</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D8" s="15" t="s">
         <x:v>25</x:v>
@@ -3385,33 +3395,33 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46085.16625</x:v>
+        <x:v>46085.1709143519</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J8" s="15" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>114</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>55</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>118</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
         <x:v>119</x:v>
@@ -3423,22 +3433,22 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I9" s="19">
-        <x:v>46084</x:v>
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J9" s="15" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46083.104224537</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>50</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
@@ -3446,34 +3456,34 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>106</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G10" s="14" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I10" s="19">
-        <x:v>46104</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J10" s="15" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511639</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46083.104224537</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>50</x:v>
@@ -3484,34 +3494,34 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>106</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="E11" s="14" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F11" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G11" s="14" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46087.1643287037</x:v>
       </x:c>
       <x:c r="I11" s="19">
-        <x:v>46097</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J11" s="15" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1511760</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46090.2727777778</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>50</x:v>
@@ -3522,107 +3532,154 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>106</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F12" s="14" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G12" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46086.1144444444</x:v>
       </x:c>
       <x:c r="I12" s="19">
-        <x:v>46098</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="J12" s="15" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511759</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46090.2703703704</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I13" s="19">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="18">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="20" t="s">
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="20" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C15" s="21" t="s"/>
-      <x:c r="D15" s="21" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="22" t="s"/>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="23" t="s">
+      <x:c r="C16" s="21" t="s"/>
+      <x:c r="D16" s="21" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="22" t="s"/>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B17" s="23" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="C16" s="24" t="s"/>
-      <x:c r="D16" s="24" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="25" t="s">
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="s">
         <x:v>104</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
       <x:c r="B18" s="26" t="s">
-        <x:v>45</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C18" s="27" t="s"/>
       <x:c r="D18" s="27" t="s"/>
       <x:c r="E18" s="27" t="s"/>
       <x:c r="F18" s="28" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
       <x:c r="B19" s="26" t="s">
-        <x:v>55</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C19" s="27" t="s"/>
       <x:c r="D19" s="27" t="s"/>
       <x:c r="E19" s="27" t="s"/>
       <x:c r="F19" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="26" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="26" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="29" t="s">
+    <x:row r="22" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B22" s="29" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C20" s="30" t="s"/>
-      <x:c r="D20" s="30" t="s"/>
-      <x:c r="E20" s="30" t="s"/>
-      <x:c r="F20" s="31" t="n">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C22" s="30" t="s"/>
+      <x:c r="D22" s="30" t="s"/>
+      <x:c r="E22" s="30" t="s"/>
+      <x:c r="F22" s="31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4595,15 +4652,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
+  <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B15:F15"/>
-    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B16:F16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -353,6 +353,18 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1189-403</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JAKE C. PASILAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>103, Banlic, Cabuyao City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03010-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1198-002</x:t>
   </x:si>
   <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
@@ -748,7 +760,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -819,11 +831,8 @@
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -940,10 +949,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -3338,14 +3343,12 @@
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="7" t="s"/>
       <x:c r="B7" s="11" t="s">
-        <x:v>30</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C7" s="11" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>32</x:v>
-      </x:c>
+      <x:c r="D7" s="11" t="s"/>
       <x:c r="E7" s="11" t="s">
         <x:v>111</x:v>
       </x:c>
@@ -3356,19 +3359,19 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="H7" s="12">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I7" s="32">
-        <x:v>46095</x:v>
+        <x:v>46093.1459375</x:v>
+      </x:c>
+      <x:c r="I7" s="12">
+        <x:v>46093.1585185185</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511815</x:v>
       </x:c>
       <x:c r="K7" s="13" t="n">
-        <x:v>3030</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L7" s="12">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46093.159537037</x:v>
       </x:c>
       <x:c r="M7" s="11" t="s">
         <x:v>50</x:v>
@@ -3377,13 +3380,13 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B8" s="14" t="s">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
         <x:v>114</x:v>
       </x:c>
       <x:c r="D8" s="15" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
         <x:v>115</x:v>
@@ -3395,22 +3398,22 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46085.1709375</x:v>
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I8" s="19">
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J8" s="15" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>118</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -3418,7 +3421,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>114</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
         <x:v>25</x:v>
@@ -3433,33 +3436,33 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46085.16625</x:v>
+        <x:v>46085.1709143519</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J9" s="15" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>118</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="14" t="s">
-        <x:v>55</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>122</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
         <x:v>123</x:v>
@@ -3471,22 +3474,22 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>46084</x:v>
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J10" s="15" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46083.104224537</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
-        <x:v>50</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
@@ -3494,34 +3497,34 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>110</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="E11" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="F11" s="14" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G11" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I11" s="19">
-        <x:v>46104</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J11" s="15" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511639</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46083.104224537</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>50</x:v>
@@ -3532,34 +3535,34 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>110</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F12" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G12" s="14" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46087.1643287037</x:v>
       </x:c>
       <x:c r="I12" s="19">
-        <x:v>46097</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J12" s="15" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1511760</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46090.2727777778</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>50</x:v>
@@ -3570,117 +3573,154 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>110</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G13" s="14" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46086.1144444444</x:v>
       </x:c>
       <x:c r="I13" s="19">
-        <x:v>46098</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="J13" s="15" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511759</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46090.2703703704</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I14" s="19">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="18">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="20" t="s">
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="20" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C16" s="21" t="s"/>
-      <x:c r="D16" s="21" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="22" t="s"/>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="23" t="s">
+      <x:c r="C17" s="21" t="s"/>
+      <x:c r="D17" s="21" t="s"/>
+      <x:c r="E17" s="22" t="s"/>
+      <x:c r="F17" s="22" t="s"/>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B18" s="23" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="s">
+      <x:c r="C18" s="24" t="s"/>
+      <x:c r="D18" s="24" t="s"/>
+      <x:c r="E18" s="24" t="s"/>
+      <x:c r="F18" s="25" t="s">
         <x:v>104</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
       <x:c r="B19" s="26" t="s">
-        <x:v>30</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C19" s="27" t="s"/>
       <x:c r="D19" s="27" t="s"/>
       <x:c r="E19" s="27" t="s"/>
       <x:c r="F19" s="28" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
       <x:c r="B20" s="26" t="s">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C20" s="27" t="s"/>
       <x:c r="D20" s="27" t="s"/>
       <x:c r="E20" s="27" t="s"/>
       <x:c r="F20" s="28" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
       <x:c r="B21" s="26" t="s">
-        <x:v>55</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C21" s="27" t="s"/>
       <x:c r="D21" s="27" t="s"/>
       <x:c r="E21" s="27" t="s"/>
       <x:c r="F21" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="26" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C22" s="27" t="s"/>
+      <x:c r="D22" s="27" t="s"/>
+      <x:c r="E22" s="27" t="s"/>
+      <x:c r="F22" s="28" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="29" t="s">
+    <x:row r="23" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B23" s="29" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C22" s="30" t="s"/>
-      <x:c r="D22" s="30" t="s"/>
-      <x:c r="E22" s="30" t="s"/>
-      <x:c r="F22" s="31" t="n">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C23" s="30" t="s"/>
+      <x:c r="D23" s="30" t="s"/>
+      <x:c r="E23" s="30" t="s"/>
+      <x:c r="F23" s="31" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4655,13 +4695,13 @@
   <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B16:F16"/>
-    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B17:F17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B23:E23"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -365,6 +365,21 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1198-002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELLTY MOBILE INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SM CITY BACOOR CZ430, HABAY II, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0762</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1155-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cesar Allen Centeno</x:t>
   </x:si>
   <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
@@ -3398,60 +3413,60 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46086.1064814815</x:v>
+        <x:v>46084.0854513889</x:v>
       </x:c>
       <x:c r="I8" s="19">
-        <x:v>46095</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J8" s="15" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511225</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46093.3956365741</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>50</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46085.1709375</x:v>
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I9" s="19">
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J9" s="15" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>122</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
@@ -3459,75 +3474,75 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>118</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G10" s="14" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46085.16625</x:v>
+        <x:v>46085.1709143519</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J10" s="15" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
-        <x:v>122</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>55</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E11" s="14" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46085.1662615741</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>46090.3437268519</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
         <x:v>127</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1511639</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46083.104224537</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
@@ -3535,34 +3550,34 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F12" s="14" t="s">
-        <x:v>131</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G12" s="14" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I12" s="19">
-        <x:v>46104</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J12" s="15" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511639</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46083.104224537</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>50</x:v>
@@ -3573,34 +3588,34 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>114</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>134</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G13" s="14" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46087.1643287037</x:v>
       </x:c>
       <x:c r="I13" s="19">
-        <x:v>46097</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J13" s="15" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1511760</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46090.2727777778</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>50</x:v>
@@ -3611,86 +3626,113 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>114</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F14" s="14" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G14" s="14" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46086.1144444444</x:v>
       </x:c>
       <x:c r="I14" s="19">
-        <x:v>46098</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="J14" s="15" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511759</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46090.2703703704</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I15" s="19">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="18">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="20" t="s">
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="20" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C17" s="21" t="s"/>
-      <x:c r="D17" s="21" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="22" t="s"/>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B18" s="23" t="s">
+      <x:c r="C18" s="21" t="s"/>
+      <x:c r="D18" s="21" t="s"/>
+      <x:c r="E18" s="22" t="s"/>
+      <x:c r="F18" s="22" t="s"/>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B19" s="23" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="C18" s="24" t="s"/>
-      <x:c r="D18" s="24" t="s"/>
-      <x:c r="E18" s="24" t="s"/>
-      <x:c r="F18" s="25" t="s">
+      <x:c r="C19" s="24" t="s"/>
+      <x:c r="D19" s="24" t="s"/>
+      <x:c r="E19" s="24" t="s"/>
+      <x:c r="F19" s="25" t="s">
         <x:v>104</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
       <x:c r="B20" s="26" t="s">
-        <x:v>30</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C20" s="27" t="s"/>
       <x:c r="D20" s="27" t="s"/>
       <x:c r="E20" s="27" t="s"/>
       <x:c r="F20" s="28" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
       <x:c r="B21" s="26" t="s">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C21" s="27" t="s"/>
       <x:c r="D21" s="27" t="s"/>
@@ -3701,27 +3743,37 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
       <x:c r="B22" s="26" t="s">
-        <x:v>55</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C22" s="27" t="s"/>
       <x:c r="D22" s="27" t="s"/>
       <x:c r="E22" s="27" t="s"/>
       <x:c r="F22" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="26" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C23" s="27" t="s"/>
+      <x:c r="D23" s="27" t="s"/>
+      <x:c r="E23" s="27" t="s"/>
+      <x:c r="F23" s="28" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="29" t="s">
+    <x:row r="24" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B24" s="29" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C23" s="30" t="s"/>
-      <x:c r="D23" s="30" t="s"/>
-      <x:c r="E23" s="30" t="s"/>
-      <x:c r="F23" s="31" t="n">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C24" s="30" t="s"/>
+      <x:c r="D24" s="30" t="s"/>
+      <x:c r="E24" s="30" t="s"/>
+      <x:c r="F24" s="31" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4695,13 +4747,13 @@
   <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B17:F17"/>
-    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B18:F18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B24:E24"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -10,58 +10,22 @@
     <x:sheet name="March 2026" sheetId="8" r:id="rId8"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
-  <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
+  <x:si>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -367,6 +331,42 @@
     <x:t>43A-3-2026-1198-002</x:t>
   </x:si>
   <x:si>
+    <x:t>BSD INTERNATIONAL MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C-24 SM City Rosario, Gen. Trias Dr.,, Tejeros Convention,, Rosario, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0781 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1144-933</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ 248-3 SM City San Pablo, Brgy. San Rafael, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0780 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1151-716</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELL EVER MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ 424 Cyberzone 4th flr., SM City Bacoor, Habay II, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-456b-22R (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1154-964</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELLTY MOBILE INC</x:t>
   </x:si>
   <x:si>
@@ -379,7 +379,61 @@
     <x:t>43A-3-2026-1155-834</x:t>
   </x:si>
   <x:si>
-    <x:t>Cesar Allen Centeno</x:t>
+    <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-020R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1156-896</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELLTY MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-01-25-453R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1085-453</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLIXTEC INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3/F BLDG. D DAANG HARI ROAD, PASONG BUAYA I, Imus City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-01-25-456R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1086-471</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTO GADGETS TOO INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ 440 SM City Bacoor, Habay II,, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0773 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1152-831</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONE DOTCOM CELL INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ SM City Bacoor, Habay II,, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0778 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1153-796</x:t>
   </x:si>
   <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
@@ -397,6 +451,18 @@
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
+    <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2519</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1171-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ricardo Natividad</x:t>
+  </x:si>
+  <x:si>
     <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
   </x:si>
   <x:si>
@@ -406,16 +472,13 @@
     <x:t>43A-3-2026-1172-434</x:t>
   </x:si>
   <x:si>
-    <x:t>Ricardo Natividad</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-2519</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1171-081</x:t>
+    <x:t>WALTERMART TANAUAN 225 WALTERMART JPL-HWAY, DARASA, City Of Tanauan, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-21-03-2265</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1157-256</x:t>
   </x:si>
   <x:si>
     <x:t>INNOVASIA MARKETING</x:t>
@@ -430,6 +493,24 @@
     <x:t>43A-3-2026-1146-031</x:t>
   </x:si>
   <x:si>
+    <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-17-03-2015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1173-016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1175-710</x:t>
+  </x:si>
+  <x:si>
     <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
   </x:si>
   <x:si>
@@ -437,24 +518,6 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1176-385</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-18-02-2017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1175-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-17-03-2015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1173-016</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -464,7 +527,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -491,12 +554,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -504,6 +561,27 @@
       <x:sz val="11.0"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -518,13 +596,6 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -569,12 +640,12 @@
   <x:borders count="14">
     <x:border/>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF000000"/>
-      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
@@ -586,14 +657,14 @@
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -775,7 +846,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -786,183 +857,208 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1226,961 +1322,937 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
+      <x:c r="C6" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="D6" s="12" t="s"/>
+      <x:c r="E6" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
+      <x:c r="F6" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F5" s="10" t="s">
+      <x:c r="G6" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G5" s="10" t="s">
+      <x:c r="H6" s="13">
+        <x:v>46069.0835185185</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>46069.1006712963</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1506161</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L6" s="15">
+        <x:v>46069.1133333333</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J5" s="10" t="s">
+      <x:c r="F7" s="16" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K5" s="10" t="s">
+      <x:c r="G7" s="16" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L5" s="10" t="s">
+      <x:c r="H7" s="17">
+        <x:v>46069.0835648148</x:v>
+      </x:c>
+      <x:c r="I7" s="17">
+        <x:v>46069.1000231481</x:v>
+      </x:c>
+      <x:c r="J7" s="16" t="n">
+        <x:v>1506159</x:v>
+      </x:c>
+      <x:c r="K7" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L7" s="17">
+        <x:v>46069.1128587963</x:v>
+      </x:c>
+      <x:c r="M7" s="16" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="19" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M5" s="10" t="s">
+      <x:c r="C8" s="19" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
+      <x:c r="D8" s="19" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="s">
+      <x:c r="E8" s="19" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s"/>
-      <x:c r="E6" s="11" t="s">
+      <x:c r="F8" s="19" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="s">
+      <x:c r="G8" s="19" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G6" s="11" t="s">
+      <x:c r="H8" s="20">
+        <x:v>46067.3600231481</x:v>
+      </x:c>
+      <x:c r="I8" s="20">
+        <x:v>46067.3600462963</x:v>
+      </x:c>
+      <x:c r="J8" s="19" t="n">
+        <x:v>1505803</x:v>
+      </x:c>
+      <x:c r="K8" s="21" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L8" s="20">
+        <x:v>46079.2730092593</x:v>
+      </x:c>
+      <x:c r="M8" s="19" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46069.0835185185</x:v>
-      </x:c>
-      <x:c r="I6" s="12">
-        <x:v>46069.1006712963</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1506161</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46069.1133333333</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="19" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
+      <x:c r="C9" s="19" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D9" s="19" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E9" s="19" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F9" s="19" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G9" s="19" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H9" s="20">
+        <x:v>46067.1596643518</x:v>
+      </x:c>
+      <x:c r="I9" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J9" s="19" t="n">
+        <x:v>1505804</x:v>
+      </x:c>
+      <x:c r="K9" s="21" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L9" s="20">
+        <x:v>46079.2772569444</x:v>
+      </x:c>
+      <x:c r="M9" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H10" s="13">
+        <x:v>46067.2222106481</x:v>
+      </x:c>
+      <x:c r="I10" s="23">
+        <x:v>46089</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1505805</x:v>
+      </x:c>
+      <x:c r="K10" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="15">
+        <x:v>46079.2763078704</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H11" s="13">
+        <x:v>46063.1352777778</x:v>
+      </x:c>
+      <x:c r="I11" s="23">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:v>1511010</x:v>
+      </x:c>
+      <x:c r="K11" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="15">
+        <x:v>46063.2367708333</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s"/>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="E12" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H12" s="13">
+        <x:v>46079.3584722222</x:v>
+      </x:c>
+      <x:c r="I12" s="13">
+        <x:v>46079.3584953704</x:v>
+      </x:c>
+      <x:c r="J12" s="12" t="n">
+        <x:v>1511622</x:v>
+      </x:c>
+      <x:c r="K12" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L12" s="15">
+        <x:v>46080.2311226852</x:v>
+      </x:c>
+      <x:c r="M12" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H13" s="13">
+        <x:v>46079.3539699074</x:v>
+      </x:c>
+      <x:c r="I13" s="13">
+        <x:v>46079.3539814815</x:v>
+      </x:c>
+      <x:c r="J13" s="12" t="n">
+        <x:v>1511627</x:v>
+      </x:c>
+      <x:c r="K13" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L13" s="15">
+        <x:v>46080.2440856481</x:v>
+      </x:c>
+      <x:c r="M13" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D14" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46069.0835648148</x:v>
-      </x:c>
-      <x:c r="I7" s="12">
-        <x:v>46069.1000231481</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1506159</x:v>
-      </x:c>
-      <x:c r="K7" s="13" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46069.1128587963</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46067.3600231481</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46067.3600462963</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46079.2730092593</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46067.1596643518</x:v>
-      </x:c>
-      <x:c r="I9" s="19">
+      <x:c r="E14" s="11" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H14" s="13">
+        <x:v>46079.3873148148</x:v>
+      </x:c>
+      <x:c r="I14" s="23">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J9" s="15" t="n">
-        <x:v>1505804</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="J14" s="12" t="n">
+        <x:v>1511623</x:v>
+      </x:c>
+      <x:c r="K14" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46079.2772569444</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="L14" s="15">
+        <x:v>46080.2360763889</x:v>
+      </x:c>
+      <x:c r="M14" s="11" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46067.2222106481</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>46089</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="n">
-        <x:v>1505805</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H15" s="13">
+        <x:v>46079.2523032407</x:v>
+      </x:c>
+      <x:c r="I15" s="23">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="n">
+        <x:v>1511631</x:v>
+      </x:c>
+      <x:c r="K15" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46079.2763078704</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="L15" s="15">
+        <x:v>46080.2925810185</x:v>
+      </x:c>
+      <x:c r="M15" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="11" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46063.1352777778</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1511010</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="C16" s="11" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H16" s="13">
+        <x:v>46079.2430555556</x:v>
+      </x:c>
+      <x:c r="I16" s="23">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J16" s="12" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K16" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46063.2367708333</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46079.3584722222</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46079.3584953704</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1511622</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46080.2311226852</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46079.3539699074</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46079.3539814815</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="n">
-        <x:v>1511627</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46080.2440856481</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
+      <x:c r="L16" s="15">
+        <x:v>46080.2801273148</x:v>
+      </x:c>
+      <x:c r="M16" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
+      <x:c r="D17" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="F17" s="11" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
+      <x:c r="G17" s="11" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46079.3873148148</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
+      <x:c r="H17" s="13">
+        <x:v>46079.3651967593</x:v>
+      </x:c>
+      <x:c r="I17" s="23">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J14" s="15" t="n">
-        <x:v>1511623</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
+      <x:c r="J17" s="12" t="n">
+        <x:v>1511626</x:v>
+      </x:c>
+      <x:c r="K17" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46080.2360763889</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
+      <x:c r="L17" s="15">
+        <x:v>46080.2425462963</x:v>
+      </x:c>
+      <x:c r="M17" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
+      <x:c r="D18" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="F18" s="11" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="G18" s="11" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46079.2523032407</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
+      <x:c r="H18" s="13">
+        <x:v>46080.2923611111</x:v>
+      </x:c>
+      <x:c r="I18" s="23">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J15" s="15" t="n">
-        <x:v>1511631</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
+      <x:c r="J18" s="12" t="n">
+        <x:v>1511635</x:v>
+      </x:c>
+      <x:c r="K18" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46080.2925810185</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
+      <x:c r="L18" s="15">
+        <x:v>46080.3208564815</x:v>
+      </x:c>
+      <x:c r="M18" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
+      <x:c r="D19" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="s">
+      <x:c r="G19" s="11" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G16" s="14" t="s">
+      <x:c r="H19" s="13">
+        <x:v>46079.31625</x:v>
+      </x:c>
+      <x:c r="I19" s="23">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J19" s="12" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K19" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="15">
+        <x:v>46080.2883680556</x:v>
+      </x:c>
+      <x:c r="M19" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C20" s="11" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46079.2430555556</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
+      <x:c r="D20" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H20" s="13">
+        <x:v>46079.3059375</x:v>
+      </x:c>
+      <x:c r="I20" s="23">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J16" s="15" t="n">
+      <x:c r="J20" s="12" t="n">
         <x:v>1511630</x:v>
       </x:c>
-      <x:c r="K16" s="17" t="n">
+      <x:c r="K20" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="18">
-        <x:v>46080.2801273148</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
+      <x:c r="L20" s="15">
+        <x:v>46080.2896875</x:v>
+      </x:c>
+      <x:c r="M20" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C21" s="11" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G17" s="14" t="s">
+      <x:c r="D21" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46079.3651967593</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
+      <x:c r="G21" s="11" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H21" s="13">
+        <x:v>46079.2943981482</x:v>
+      </x:c>
+      <x:c r="I21" s="23">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J17" s="15" t="n">
-        <x:v>1511626</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
+      <x:c r="J21" s="12" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K21" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46080.2425462963</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
+      <x:c r="L21" s="15">
+        <x:v>46080.2916782407</x:v>
+      </x:c>
+      <x:c r="M21" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C22" s="11" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="s">
+      <x:c r="D22" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E22" s="11" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="G18" s="14" t="s">
+      <x:c r="F22" s="11" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46080.2923611111</x:v>
-      </x:c>
-      <x:c r="I18" s="19">
+      <x:c r="G22" s="11" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H22" s="13">
+        <x:v>46079.378900463</x:v>
+      </x:c>
+      <x:c r="I22" s="23">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J18" s="15" t="n">
-        <x:v>1511635</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
+      <x:c r="J22" s="12" t="n">
+        <x:v>1511624</x:v>
+      </x:c>
+      <x:c r="K22" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="18">
-        <x:v>46080.3208564815</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
+      <x:c r="L22" s="15">
+        <x:v>46080.2376041667</x:v>
+      </x:c>
+      <x:c r="M22" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C23" s="11" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="G19" s="14" t="s">
+      <x:c r="D23" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F23" s="11" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46079.31625</x:v>
-      </x:c>
-      <x:c r="I19" s="19">
+      <x:c r="G23" s="11" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H23" s="13">
+        <x:v>46079.3728240741</x:v>
+      </x:c>
+      <x:c r="I23" s="23">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J19" s="15" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
+      <x:c r="J23" s="12" t="n">
+        <x:v>1511625</x:v>
+      </x:c>
+      <x:c r="K23" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L19" s="18">
-        <x:v>46080.2883680556</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
+      <x:c r="L23" s="15">
+        <x:v>46080.2394328704</x:v>
+      </x:c>
+      <x:c r="M23" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="11" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="G20" s="14" t="s">
+      <x:c r="C24" s="11" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46079.3059375</x:v>
-      </x:c>
-      <x:c r="I20" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="18">
-        <x:v>46080.2896875</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
+      <x:c r="D24" s="12" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E24" s="11" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
+      <x:c r="F24" s="11" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G21" s="14" t="s">
+      <x:c r="G24" s="11" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46079.2943981482</x:v>
-      </x:c>
-      <x:c r="I21" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K21" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="18">
-        <x:v>46080.2916782407</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
+      <x:c r="H24" s="13">
+        <x:v>46062.1590162037</x:v>
+      </x:c>
+      <x:c r="I24" s="13">
+        <x:v>46062.1590277778</x:v>
+      </x:c>
+      <x:c r="J24" s="12" t="n">
+        <x:v>1510925</x:v>
+      </x:c>
+      <x:c r="K24" s="14" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L24" s="15">
+        <x:v>46062.1863194444</x:v>
+      </x:c>
+      <x:c r="M24" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="11" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
+      <x:c r="C25" s="11" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="F22" s="14" t="s">
+      <x:c r="D25" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="G22" s="14" t="s">
+      <x:c r="F25" s="11" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46079.378900463</x:v>
-      </x:c>
-      <x:c r="I22" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="n">
-        <x:v>1511624</x:v>
-      </x:c>
-      <x:c r="K22" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="18">
-        <x:v>46080.2376041667</x:v>
-      </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
+      <x:c r="G25" s="11" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46079.3728240741</x:v>
-      </x:c>
-      <x:c r="I23" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="n">
-        <x:v>1511625</x:v>
-      </x:c>
-      <x:c r="K23" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="18">
-        <x:v>46080.2394328704</x:v>
-      </x:c>
-      <x:c r="M23" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="H24" s="16">
-        <x:v>46062.1590162037</x:v>
-      </x:c>
-      <x:c r="I24" s="16">
-        <x:v>46062.1590277778</x:v>
-      </x:c>
-      <x:c r="J24" s="15" t="n">
-        <x:v>1510925</x:v>
-      </x:c>
-      <x:c r="K24" s="17" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L24" s="18">
-        <x:v>46062.1863194444</x:v>
-      </x:c>
-      <x:c r="M24" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="14" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C25" s="14" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D25" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E25" s="14" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="F25" s="14" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G25" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="H25" s="16">
+      <x:c r="H25" s="13">
         <x:v>46071.0492476852</x:v>
       </x:c>
-      <x:c r="I25" s="19">
+      <x:c r="I25" s="23">
         <x:v>46052</x:v>
       </x:c>
-      <x:c r="J25" s="15" t="n">
+      <x:c r="J25" s="12" t="n">
         <x:v>1511502</x:v>
       </x:c>
-      <x:c r="K25" s="17" t="n">
+      <x:c r="K25" s="14" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L25" s="18">
+      <x:c r="L25" s="15">
         <x:v>46071.0606134259</x:v>
       </x:c>
-      <x:c r="M25" s="14" t="s">
-        <x:v>50</x:v>
+      <x:c r="M25" s="11" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="20" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C28" s="21" t="s"/>
-      <x:c r="D28" s="21" t="s"/>
-      <x:c r="E28" s="22" t="s"/>
-      <x:c r="F28" s="22" t="s"/>
+      <x:c r="B28" s="24" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C28" s="25" t="s"/>
+      <x:c r="D28" s="25" t="s"/>
+      <x:c r="E28" s="26" t="s"/>
+      <x:c r="F28" s="26" t="s"/>
     </x:row>
     <x:row r="29" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B29" s="23" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C29" s="24" t="s"/>
-      <x:c r="D29" s="24" t="s"/>
-      <x:c r="E29" s="24" t="s"/>
-      <x:c r="F29" s="25" t="s">
-        <x:v>104</x:v>
+      <x:c r="B29" s="27" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C29" s="28" t="s"/>
+      <x:c r="D29" s="28" t="s"/>
+      <x:c r="E29" s="28" t="s"/>
+      <x:c r="F29" s="29" t="s">
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="26" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C30" s="27" t="s"/>
-      <x:c r="D30" s="27" t="s"/>
-      <x:c r="E30" s="27" t="s"/>
-      <x:c r="F30" s="28" t="n">
+      <x:c r="B30" s="30" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C30" s="31" t="s"/>
+      <x:c r="D30" s="31" t="s"/>
+      <x:c r="E30" s="31" t="s"/>
+      <x:c r="F30" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="26" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C31" s="27" t="s"/>
-      <x:c r="D31" s="27" t="s"/>
-      <x:c r="E31" s="27" t="s"/>
-      <x:c r="F31" s="28" t="n">
+      <x:c r="B31" s="30" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C31" s="31" t="s"/>
+      <x:c r="D31" s="31" t="s"/>
+      <x:c r="E31" s="31" t="s"/>
+      <x:c r="F31" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C32" s="27" t="s"/>
-      <x:c r="D32" s="27" t="s"/>
-      <x:c r="E32" s="27" t="s"/>
-      <x:c r="F32" s="28" t="n">
+      <x:c r="B32" s="30" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C32" s="31" t="s"/>
+      <x:c r="D32" s="31" t="s"/>
+      <x:c r="E32" s="31" t="s"/>
+      <x:c r="F32" s="32" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="26" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C33" s="27" t="s"/>
-      <x:c r="D33" s="27" t="s"/>
-      <x:c r="E33" s="27" t="s"/>
-      <x:c r="F33" s="28" t="n">
+      <x:c r="B33" s="30" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C33" s="31" t="s"/>
+      <x:c r="D33" s="31" t="s"/>
+      <x:c r="E33" s="31" t="s"/>
+      <x:c r="F33" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="26" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C34" s="27" t="s"/>
-      <x:c r="D34" s="27" t="s"/>
-      <x:c r="E34" s="27" t="s"/>
-      <x:c r="F34" s="28" t="n">
+      <x:c r="B34" s="30" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C34" s="31" t="s"/>
+      <x:c r="D34" s="31" t="s"/>
+      <x:c r="E34" s="31" t="s"/>
+      <x:c r="F34" s="32" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="26" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C35" s="27" t="s"/>
-      <x:c r="D35" s="27" t="s"/>
-      <x:c r="E35" s="27" t="s"/>
-      <x:c r="F35" s="28" t="n">
+      <x:c r="B35" s="30" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C35" s="31" t="s"/>
+      <x:c r="D35" s="31" t="s"/>
+      <x:c r="E35" s="31" t="s"/>
+      <x:c r="F35" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="26" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C36" s="27" t="s"/>
-      <x:c r="D36" s="27" t="s"/>
-      <x:c r="E36" s="27" t="s"/>
-      <x:c r="F36" s="28" t="n">
+      <x:c r="B36" s="30" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C36" s="31" t="s"/>
+      <x:c r="D36" s="31" t="s"/>
+      <x:c r="E36" s="31" t="s"/>
+      <x:c r="F36" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B37" s="29" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C37" s="30" t="s"/>
-      <x:c r="D37" s="30" t="s"/>
-      <x:c r="E37" s="30" t="s"/>
-      <x:c r="F37" s="31" t="n">
+      <x:c r="B37" s="33" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C37" s="34" t="s"/>
+      <x:c r="D37" s="34" t="s"/>
+      <x:c r="E37" s="34" t="s"/>
+      <x:c r="F37" s="35" t="n">
         <x:v>20</x:v>
       </x:c>
     </x:row>
@@ -3229,560 +3301,869 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
+      <x:c r="C6" s="11" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s"/>
+      <x:c r="E6" s="11" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>46091.306099537</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>46091.3107986111</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1511778</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L6" s="15">
+        <x:v>46091.3131828704</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F7" s="16" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G7" s="16" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H7" s="17">
+        <x:v>46093.1459375</x:v>
+      </x:c>
+      <x:c r="I7" s="17">
+        <x:v>46093.1585185185</x:v>
+      </x:c>
+      <x:c r="J7" s="16" t="n">
+        <x:v>1511815</x:v>
+      </x:c>
+      <x:c r="K7" s="18" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L7" s="17">
+        <x:v>46093.159537037</x:v>
+      </x:c>
+      <x:c r="M7" s="16" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="19" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C8" s="19" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D8" s="19" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E8" s="19" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F8" s="19" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G8" s="19" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H8" s="20">
+        <x:v>46080.4532523148</x:v>
+      </x:c>
+      <x:c r="I8" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J8" s="19" t="n">
+        <x:v>1511232</x:v>
+      </x:c>
+      <x:c r="K8" s="21" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="20">
+        <x:v>46097.1461689815</x:v>
+      </x:c>
+      <x:c r="M8" s="19" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="19" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C9" s="19" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D9" s="19" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E9" s="19" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F9" s="19" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G9" s="19" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H9" s="20">
+        <x:v>46083.2380439815</x:v>
+      </x:c>
+      <x:c r="I9" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J9" s="19" t="n">
+        <x:v>1511234</x:v>
+      </x:c>
+      <x:c r="K9" s="21" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L9" s="20">
+        <x:v>46097.1564351852</x:v>
+      </x:c>
+      <x:c r="M9" s="19" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H10" s="13">
+        <x:v>46083.2599189815</x:v>
+      </x:c>
+      <x:c r="I10" s="23">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1511237</x:v>
+      </x:c>
+      <x:c r="K10" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="15">
+        <x:v>46097.1652314815</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H11" s="13">
+        <x:v>46084.0854513889</x:v>
+      </x:c>
+      <x:c r="I11" s="23">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:v>1511225</x:v>
+      </x:c>
+      <x:c r="K11" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="15">
+        <x:v>46093.3956365741</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H12" s="13">
+        <x:v>46084.0996759259</x:v>
+      </x:c>
+      <x:c r="I12" s="23">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J12" s="12" t="n">
+        <x:v>1511192</x:v>
+      </x:c>
+      <x:c r="K12" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="15">
+        <x:v>46097.2414583333</x:v>
+      </x:c>
+      <x:c r="M12" s="11" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="H13" s="13">
+        <x:v>46069.1542013889</x:v>
+      </x:c>
+      <x:c r="I13" s="23">
+        <x:v>46035</x:v>
+      </x:c>
+      <x:c r="J13" s="12" t="n">
+        <x:v>1511206</x:v>
+      </x:c>
+      <x:c r="K13" s="14" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L13" s="15">
+        <x:v>46097.2466550926</x:v>
+      </x:c>
+      <x:c r="M13" s="11" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D14" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="H14" s="13">
+        <x:v>46069.2178703704</x:v>
+      </x:c>
+      <x:c r="I14" s="23">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J14" s="12" t="n">
+        <x:v>1511196</x:v>
+      </x:c>
+      <x:c r="K14" s="14" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L14" s="15">
+        <x:v>46097.2456365741</x:v>
+      </x:c>
+      <x:c r="M14" s="11" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H15" s="13">
+        <x:v>46083.2443865741</x:v>
+      </x:c>
+      <x:c r="I15" s="23">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="n">
+        <x:v>1511235</x:v>
+      </x:c>
+      <x:c r="K15" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="15">
+        <x:v>46097.1600115741</x:v>
+      </x:c>
+      <x:c r="M15" s="11" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="H16" s="13">
+        <x:v>46083.2521064815</x:v>
+      </x:c>
+      <x:c r="I16" s="23">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J16" s="12" t="n">
+        <x:v>1511236</x:v>
+      </x:c>
+      <x:c r="K16" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="15">
+        <x:v>46097.1628935185</x:v>
+      </x:c>
+      <x:c r="M16" s="11" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D17" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="H17" s="13">
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I17" s="23">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="J17" s="12" t="n">
+        <x:v>1511761</x:v>
+      </x:c>
+      <x:c r="K17" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="15">
+        <x:v>46090.2765740741</x:v>
+      </x:c>
+      <x:c r="M17" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D18" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="s">
+      <x:c r="E18" s="11" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="G18" s="11" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="H18" s="13">
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I18" s="13">
+        <x:v>46085.1662615741</x:v>
+      </x:c>
+      <x:c r="J18" s="12" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K18" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L18" s="15">
+        <x:v>46090.3437268519</x:v>
+      </x:c>
+      <x:c r="M18" s="11" t="s">
+        <x:v>145</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D19" s="12" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="H19" s="13">
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I19" s="13">
+        <x:v>46085.1709375</x:v>
+      </x:c>
+      <x:c r="J19" s="12" t="n">
+        <x:v>1507965</x:v>
+      </x:c>
+      <x:c r="K19" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L19" s="15">
+        <x:v>46090.3336921296</x:v>
+      </x:c>
+      <x:c r="M19" s="11" t="s">
+        <x:v>145</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C20" s="11" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D20" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="H20" s="13">
+        <x:v>46084.1080324074</x:v>
+      </x:c>
+      <x:c r="I20" s="23">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J20" s="12" t="n">
+        <x:v>1511208</x:v>
+      </x:c>
+      <x:c r="K20" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="15">
+        <x:v>46097.2478125</x:v>
+      </x:c>
+      <x:c r="M20" s="11" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46091.306099537</x:v>
-      </x:c>
-      <x:c r="I6" s="12">
-        <x:v>46091.3107986111</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1511778</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46091.3131828704</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s"/>
-      <x:c r="E7" s="11" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46093.1459375</x:v>
-      </x:c>
-      <x:c r="I7" s="12">
-        <x:v>46093.1585185185</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1511815</x:v>
-      </x:c>
-      <x:c r="K7" s="13" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46093.159537037</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46084.0854513889</x:v>
-      </x:c>
-      <x:c r="I8" s="19">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="n">
-        <x:v>1511225</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C21" s="11" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D21" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H21" s="13">
+        <x:v>46083.0787962963</x:v>
+      </x:c>
+      <x:c r="I21" s="23">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J21" s="12" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K21" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46093.3956365741</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>118</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I9" s="19">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="n">
-        <x:v>1511761</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="L21" s="15">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M21" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C22" s="11" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D22" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E22" s="11" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="F22" s="11" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G22" s="11" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="H22" s="13">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I22" s="23">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J22" s="12" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K22" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46090.2765740741</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46085.1709375</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="n">
-        <x:v>1507965</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46090.3336921296</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>127</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46085.1662615741</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46090.3437268519</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>127</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1511639</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="L22" s="15">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M22" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C23" s="11" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D23" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="F23" s="11" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G23" s="11" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="H23" s="13">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I23" s="23">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J23" s="12" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K23" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46083.104224537</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="L23" s="15">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M23" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C24" s="11" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="H13" s="16">
+      <x:c r="D24" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E24" s="11" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="F24" s="11" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G24" s="11" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="H24" s="13">
         <x:v>46087.1643287037</x:v>
       </x:c>
-      <x:c r="I13" s="19">
+      <x:c r="I24" s="23">
         <x:v>46104</x:v>
       </x:c>
-      <x:c r="J13" s="15" t="n">
+      <x:c r="J24" s="12" t="n">
         <x:v>1511760</x:v>
       </x:c>
-      <x:c r="K13" s="17" t="n">
+      <x:c r="K24" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="18">
+      <x:c r="L24" s="15">
         <x:v>46090.2727777778</x:v>
       </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="n">
-        <x:v>1511759</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46090.2703703704</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="n">
-        <x:v>1511758</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46090.2691087963</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="20" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C18" s="21" t="s"/>
-      <x:c r="D18" s="21" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="22" t="s"/>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="23" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="s"/>
-      <x:c r="D19" s="24" t="s"/>
-      <x:c r="E19" s="24" t="s"/>
-      <x:c r="F19" s="25" t="s">
-        <x:v>104</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B24" s="29" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C24" s="30" t="s"/>
-      <x:c r="D24" s="30" t="s"/>
-      <x:c r="E24" s="30" t="s"/>
-      <x:c r="F24" s="31" t="n">
-        <x:v>10</x:v>
+      <x:c r="M24" s="11" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B27" s="24" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C27" s="25" t="s"/>
+      <x:c r="D27" s="25" t="s"/>
+      <x:c r="E27" s="26" t="s"/>
+      <x:c r="F27" s="26" t="s"/>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B28" s="27" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C28" s="28" t="s"/>
+      <x:c r="D28" s="28" t="s"/>
+      <x:c r="E28" s="28" t="s"/>
+      <x:c r="F28" s="29" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="30" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C29" s="31" t="s"/>
+      <x:c r="D29" s="31" t="s"/>
+      <x:c r="E29" s="31" t="s"/>
+      <x:c r="F29" s="32" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="30" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C30" s="31" t="s"/>
+      <x:c r="D30" s="31" t="s"/>
+      <x:c r="E30" s="31" t="s"/>
+      <x:c r="F30" s="32" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="30" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C31" s="31" t="s"/>
+      <x:c r="D31" s="31" t="s"/>
+      <x:c r="E31" s="31" t="s"/>
+      <x:c r="F31" s="32" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="30" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C32" s="31" t="s"/>
+      <x:c r="D32" s="31" t="s"/>
+      <x:c r="E32" s="31" t="s"/>
+      <x:c r="F32" s="32" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B33" s="33" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C33" s="34" t="s"/>
+      <x:c r="D33" s="34" t="s"/>
+      <x:c r="E33" s="34" t="s"/>
+      <x:c r="F33" s="35" t="n">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
     <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4747,13 +5128,13 @@
   <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B18:F18"/>
-    <x:mergeCell ref="B19:E19"/>
-    <x:mergeCell ref="B20:E20"/>
-    <x:mergeCell ref="B21:E21"/>
-    <x:mergeCell ref="B22:E22"/>
-    <x:mergeCell ref="B23:E23"/>
-    <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B27:F27"/>
+    <x:mergeCell ref="B28:E28"/>
+    <x:mergeCell ref="B29:E29"/>
+    <x:mergeCell ref="B30:E30"/>
+    <x:mergeCell ref="B31:E31"/>
+    <x:mergeCell ref="B32:E32"/>
+    <x:mergeCell ref="B33:E33"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -23,9 +23,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
-  <x:si>
-    <x:t>{{Name}}</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
+  <x:si>
+    <x:t>EVALUATOR SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENGR. GALELEO MENDOZA</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -927,7 +930,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="36">
+  <x:cellXfs count="42">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -963,6 +966,54 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -974,6 +1025,10 @@
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -982,36 +1037,8 @@
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1307,7 +1334,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -1324,7 +1353,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>46054</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -1385,22 +1414,22 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s"/>
       <x:c r="E6" s="11" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H6" s="13">
         <x:v>46069.0835185185</x:v>
@@ -1418,28 +1447,28 @@
         <x:v>46069.1133333333</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="16" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D7" s="16" t="s"/>
       <x:c r="E7" s="16" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F7" s="16" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G7" s="16" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H7" s="17">
         <x:v>46069.0835648148</x:v>
@@ -1457,29 +1486,29 @@
         <x:v>46069.1128587963</x:v>
       </x:c>
       <x:c r="M7" s="16" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="19" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C8" s="19" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D8" s="19" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E8" s="19" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F8" s="19" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G8" s="19" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H8" s="20">
         <x:v>46067.3600231481</x:v>
@@ -1497,27 +1526,27 @@
         <x:v>46079.2730092593</x:v>
       </x:c>
       <x:c r="M8" s="19" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="19" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="19" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D9" s="19" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E9" s="19" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F9" s="19" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G9" s="19" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H9" s="20">
         <x:v>46067.1596643518</x:v>
@@ -1535,729 +1564,755 @@
         <x:v>46079.2772569444</x:v>
       </x:c>
       <x:c r="M9" s="19" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="11" t="s">
+      <x:c r="B10" s="23" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C10" s="23" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D10" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E10" s="23" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F10" s="23" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G10" s="23" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H10" s="25">
+        <x:v>46067.2222106481</x:v>
+      </x:c>
+      <x:c r="I10" s="26">
+        <x:v>46089</x:v>
+      </x:c>
+      <x:c r="J10" s="24" t="n">
+        <x:v>1505805</x:v>
+      </x:c>
+      <x:c r="K10" s="27" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="28">
+        <x:v>46079.2763078704</x:v>
+      </x:c>
+      <x:c r="M10" s="23" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D10" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E10" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F10" s="11" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G10" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H10" s="13">
-        <x:v>46067.2222106481</x:v>
-      </x:c>
-      <x:c r="I10" s="23">
-        <x:v>46089</x:v>
-      </x:c>
-      <x:c r="J10" s="12" t="n">
-        <x:v>1505805</x:v>
-      </x:c>
-      <x:c r="K10" s="14" t="n">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="23" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C11" s="23" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D11" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E11" s="23" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F11" s="23" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G11" s="23" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H11" s="25">
+        <x:v>46063.1352777778</x:v>
+      </x:c>
+      <x:c r="I11" s="26">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J11" s="24" t="n">
+        <x:v>1511010</x:v>
+      </x:c>
+      <x:c r="K11" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="15">
-        <x:v>46079.2763078704</x:v>
-      </x:c>
-      <x:c r="M10" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C11" s="11" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D11" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E11" s="11" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F11" s="11" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G11" s="11" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H11" s="13">
-        <x:v>46063.1352777778</x:v>
-      </x:c>
-      <x:c r="I11" s="23">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J11" s="12" t="n">
-        <x:v>1511010</x:v>
-      </x:c>
-      <x:c r="K11" s="14" t="n">
+      <x:c r="L11" s="28">
+        <x:v>46063.2367708333</x:v>
+      </x:c>
+      <x:c r="M11" s="23" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="23" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C12" s="23" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D12" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E12" s="23" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F12" s="23" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G12" s="23" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H12" s="25">
+        <x:v>46079.3584722222</x:v>
+      </x:c>
+      <x:c r="I12" s="25">
+        <x:v>46079.3584953704</x:v>
+      </x:c>
+      <x:c r="J12" s="24" t="n">
+        <x:v>1511622</x:v>
+      </x:c>
+      <x:c r="K12" s="27" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L12" s="28">
+        <x:v>46080.2311226852</x:v>
+      </x:c>
+      <x:c r="M12" s="23" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="23" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C13" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D13" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E13" s="23" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F13" s="23" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G13" s="23" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H13" s="25">
+        <x:v>46079.3539699074</x:v>
+      </x:c>
+      <x:c r="I13" s="25">
+        <x:v>46079.3539814815</x:v>
+      </x:c>
+      <x:c r="J13" s="24" t="n">
+        <x:v>1511627</x:v>
+      </x:c>
+      <x:c r="K13" s="27" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L13" s="28">
+        <x:v>46080.2440856481</x:v>
+      </x:c>
+      <x:c r="M13" s="23" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="23" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C14" s="23" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D14" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E14" s="23" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F14" s="23" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G14" s="23" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H14" s="25">
+        <x:v>46079.3873148148</x:v>
+      </x:c>
+      <x:c r="I14" s="26">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J14" s="24" t="n">
+        <x:v>1511623</x:v>
+      </x:c>
+      <x:c r="K14" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="15">
-        <x:v>46063.2367708333</x:v>
-      </x:c>
-      <x:c r="M11" s="11" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="11" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C12" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D12" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E12" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F12" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G12" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H12" s="13">
-        <x:v>46079.3584722222</x:v>
-      </x:c>
-      <x:c r="I12" s="13">
-        <x:v>46079.3584953704</x:v>
-      </x:c>
-      <x:c r="J12" s="12" t="n">
-        <x:v>1511622</x:v>
-      </x:c>
-      <x:c r="K12" s="14" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L12" s="15">
-        <x:v>46080.2311226852</x:v>
-      </x:c>
-      <x:c r="M12" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="11" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C13" s="11" t="s">
+      <x:c r="L14" s="28">
+        <x:v>46080.2360763889</x:v>
+      </x:c>
+      <x:c r="M14" s="23" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D13" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E13" s="11" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F13" s="11" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G13" s="11" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H13" s="13">
-        <x:v>46079.3539699074</x:v>
-      </x:c>
-      <x:c r="I13" s="13">
-        <x:v>46079.3539814815</x:v>
-      </x:c>
-      <x:c r="J13" s="12" t="n">
-        <x:v>1511627</x:v>
-      </x:c>
-      <x:c r="K13" s="14" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L13" s="15">
-        <x:v>46080.2440856481</x:v>
-      </x:c>
-      <x:c r="M13" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C14" s="11" t="s">
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="23" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D14" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F14" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="G14" s="11" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H14" s="13">
-        <x:v>46079.3873148148</x:v>
-      </x:c>
-      <x:c r="I14" s="23">
+      <x:c r="C15" s="23" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D15" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E15" s="23" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F15" s="23" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G15" s="23" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H15" s="25">
+        <x:v>46079.2523032407</x:v>
+      </x:c>
+      <x:c r="I15" s="26">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J14" s="12" t="n">
-        <x:v>1511623</x:v>
-      </x:c>
-      <x:c r="K14" s="14" t="n">
+      <x:c r="J15" s="24" t="n">
+        <x:v>1511631</x:v>
+      </x:c>
+      <x:c r="K15" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L14" s="15">
-        <x:v>46080.2360763889</x:v>
-      </x:c>
-      <x:c r="M14" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C15" s="11" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D15" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E15" s="11" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F15" s="11" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G15" s="11" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H15" s="13">
-        <x:v>46079.2523032407</x:v>
-      </x:c>
-      <x:c r="I15" s="23">
+      <x:c r="L15" s="28">
+        <x:v>46080.2925810185</x:v>
+      </x:c>
+      <x:c r="M15" s="23" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="23" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C16" s="23" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D16" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E16" s="23" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F16" s="23" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G16" s="23" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H16" s="25">
+        <x:v>46079.2430555556</x:v>
+      </x:c>
+      <x:c r="I16" s="26">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J15" s="12" t="n">
-        <x:v>1511631</x:v>
-      </x:c>
-      <x:c r="K15" s="14" t="n">
+      <x:c r="J16" s="24" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K16" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L15" s="15">
-        <x:v>46080.2925810185</x:v>
-      </x:c>
-      <x:c r="M15" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C16" s="11" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D16" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E16" s="11" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F16" s="11" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G16" s="11" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H16" s="13">
-        <x:v>46079.2430555556</x:v>
-      </x:c>
-      <x:c r="I16" s="23">
+      <x:c r="L16" s="28">
+        <x:v>46080.2801273148</x:v>
+      </x:c>
+      <x:c r="M16" s="23" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="23" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C17" s="23" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D17" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E17" s="23" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F17" s="23" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G17" s="23" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H17" s="25">
+        <x:v>46079.3651967593</x:v>
+      </x:c>
+      <x:c r="I17" s="26">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J16" s="12" t="n">
+      <x:c r="J17" s="24" t="n">
+        <x:v>1511626</x:v>
+      </x:c>
+      <x:c r="K17" s="27" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="28">
+        <x:v>46080.2425462963</x:v>
+      </x:c>
+      <x:c r="M17" s="23" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="23" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C18" s="23" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D18" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E18" s="23" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F18" s="23" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G18" s="23" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H18" s="25">
+        <x:v>46080.2923611111</x:v>
+      </x:c>
+      <x:c r="I18" s="26">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J18" s="24" t="n">
+        <x:v>1511635</x:v>
+      </x:c>
+      <x:c r="K18" s="27" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="28">
+        <x:v>46080.3208564815</x:v>
+      </x:c>
+      <x:c r="M18" s="23" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="23" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C19" s="23" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D19" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E19" s="23" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F19" s="23" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G19" s="23" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H19" s="25">
+        <x:v>46079.31625</x:v>
+      </x:c>
+      <x:c r="I19" s="26">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J19" s="24" t="n">
         <x:v>1511630</x:v>
       </x:c>
-      <x:c r="K16" s="14" t="n">
+      <x:c r="K19" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="15">
-        <x:v>46080.2801273148</x:v>
-      </x:c>
-      <x:c r="M16" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C17" s="11" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D17" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E17" s="11" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F17" s="11" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G17" s="11" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H17" s="13">
-        <x:v>46079.3651967593</x:v>
-      </x:c>
-      <x:c r="I17" s="23">
+      <x:c r="L19" s="28">
+        <x:v>46080.2883680556</x:v>
+      </x:c>
+      <x:c r="M19" s="23" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="23" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C20" s="23" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D20" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E20" s="23" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F20" s="23" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G20" s="23" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H20" s="25">
+        <x:v>46079.3059375</x:v>
+      </x:c>
+      <x:c r="I20" s="26">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J17" s="12" t="n">
-        <x:v>1511626</x:v>
-      </x:c>
-      <x:c r="K17" s="14" t="n">
+      <x:c r="J20" s="24" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K20" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="15">
-        <x:v>46080.2425462963</x:v>
-      </x:c>
-      <x:c r="M17" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C18" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D18" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E18" s="11" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F18" s="11" t="s">
+      <x:c r="L20" s="28">
+        <x:v>46080.2896875</x:v>
+      </x:c>
+      <x:c r="M20" s="23" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="23" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C21" s="23" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D21" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E21" s="23" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G18" s="11" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H18" s="13">
-        <x:v>46080.2923611111</x:v>
-      </x:c>
-      <x:c r="I18" s="23">
+      <x:c r="F21" s="23" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G21" s="23" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H21" s="25">
+        <x:v>46079.2943981482</x:v>
+      </x:c>
+      <x:c r="I21" s="26">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J18" s="12" t="n">
-        <x:v>1511635</x:v>
-      </x:c>
-      <x:c r="K18" s="14" t="n">
+      <x:c r="J21" s="24" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K21" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="15">
-        <x:v>46080.3208564815</x:v>
-      </x:c>
-      <x:c r="M18" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C19" s="11" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D19" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E19" s="11" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F19" s="11" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="G19" s="11" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H19" s="13">
-        <x:v>46079.31625</x:v>
-      </x:c>
-      <x:c r="I19" s="23">
+      <x:c r="L21" s="28">
+        <x:v>46080.2916782407</x:v>
+      </x:c>
+      <x:c r="M21" s="23" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="23" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C22" s="23" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D22" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E22" s="23" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F22" s="23" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G22" s="23" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H22" s="25">
+        <x:v>46079.378900463</x:v>
+      </x:c>
+      <x:c r="I22" s="26">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J19" s="12" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K19" s="14" t="n">
+      <x:c r="J22" s="24" t="n">
+        <x:v>1511624</x:v>
+      </x:c>
+      <x:c r="K22" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L19" s="15">
-        <x:v>46080.2883680556</x:v>
-      </x:c>
-      <x:c r="M19" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C20" s="11" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D20" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E20" s="11" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F20" s="11" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G20" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H20" s="13">
-        <x:v>46079.3059375</x:v>
-      </x:c>
-      <x:c r="I20" s="23">
+      <x:c r="L22" s="28">
+        <x:v>46080.2376041667</x:v>
+      </x:c>
+      <x:c r="M22" s="23" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="23" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C23" s="23" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D23" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E23" s="23" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F23" s="23" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G23" s="23" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H23" s="25">
+        <x:v>46079.3728240741</x:v>
+      </x:c>
+      <x:c r="I23" s="26">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J20" s="12" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K20" s="14" t="n">
+      <x:c r="J23" s="24" t="n">
+        <x:v>1511625</x:v>
+      </x:c>
+      <x:c r="K23" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L20" s="15">
-        <x:v>46080.2896875</x:v>
-      </x:c>
-      <x:c r="M20" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C21" s="11" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D21" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E21" s="11" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F21" s="11" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G21" s="11" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H21" s="13">
-        <x:v>46079.2943981482</x:v>
-      </x:c>
-      <x:c r="I21" s="23">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J21" s="12" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K21" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="15">
-        <x:v>46080.2916782407</x:v>
-      </x:c>
-      <x:c r="M21" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C22" s="11" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D22" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E22" s="11" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F22" s="11" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G22" s="11" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H22" s="13">
-        <x:v>46079.378900463</x:v>
-      </x:c>
-      <x:c r="I22" s="23">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J22" s="12" t="n">
-        <x:v>1511624</x:v>
-      </x:c>
-      <x:c r="K22" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="15">
-        <x:v>46080.2376041667</x:v>
-      </x:c>
-      <x:c r="M22" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C23" s="11" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D23" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E23" s="11" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F23" s="11" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="G23" s="11" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="H23" s="13">
-        <x:v>46079.3728240741</x:v>
-      </x:c>
-      <x:c r="I23" s="23">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J23" s="12" t="n">
-        <x:v>1511625</x:v>
-      </x:c>
-      <x:c r="K23" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="15">
+      <x:c r="L23" s="28">
         <x:v>46080.2394328704</x:v>
       </x:c>
-      <x:c r="M23" s="11" t="s">
-        <x:v>38</x:v>
+      <x:c r="M23" s="23" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="11" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C24" s="11" t="s">
+      <x:c r="B24" s="23" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="D24" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E24" s="11" t="s">
+      <x:c r="C24" s="23" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="F24" s="11" t="s">
+      <x:c r="D24" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E24" s="23" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G24" s="11" t="s">
+      <x:c r="F24" s="23" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H24" s="13">
+      <x:c r="G24" s="23" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H24" s="25">
         <x:v>46062.1590162037</x:v>
       </x:c>
-      <x:c r="I24" s="13">
+      <x:c r="I24" s="25">
         <x:v>46062.1590277778</x:v>
       </x:c>
-      <x:c r="J24" s="12" t="n">
+      <x:c r="J24" s="24" t="n">
         <x:v>1510925</x:v>
       </x:c>
-      <x:c r="K24" s="14" t="n">
+      <x:c r="K24" s="27" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L24" s="15">
+      <x:c r="L24" s="28">
         <x:v>46062.1863194444</x:v>
       </x:c>
-      <x:c r="M24" s="11" t="s">
-        <x:v>38</x:v>
+      <x:c r="M24" s="23" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="11" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C25" s="11" t="s">
+      <x:c r="B25" s="23" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="D25" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E25" s="11" t="s">
+      <x:c r="C25" s="23" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="F25" s="11" t="s">
+      <x:c r="D25" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E25" s="23" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="G25" s="11" t="s">
+      <x:c r="F25" s="23" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="H25" s="13">
+      <x:c r="G25" s="23" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H25" s="25">
         <x:v>46071.0492476852</x:v>
       </x:c>
-      <x:c r="I25" s="23">
+      <x:c r="I25" s="26">
         <x:v>46052</x:v>
       </x:c>
-      <x:c r="J25" s="12" t="n">
+      <x:c r="J25" s="24" t="n">
         <x:v>1511502</x:v>
       </x:c>
-      <x:c r="K25" s="14" t="n">
+      <x:c r="K25" s="27" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L25" s="15">
+      <x:c r="L25" s="28">
         <x:v>46071.0606134259</x:v>
       </x:c>
-      <x:c r="M25" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="24" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C28" s="25" t="s"/>
-      <x:c r="D28" s="25" t="s"/>
-      <x:c r="E28" s="26" t="s"/>
-      <x:c r="F28" s="26" t="s"/>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B29" s="27" t="s">
+      <x:c r="M25" s="23" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B26" s="29" t="s"/>
+      <x:c r="C26" s="29" t="s"/>
+      <x:c r="D26" s="29" t="s"/>
+      <x:c r="E26" s="29" t="s"/>
+      <x:c r="F26" s="29" t="s"/>
+      <x:c r="G26" s="29" t="s"/>
+      <x:c r="H26" s="29" t="s"/>
+      <x:c r="I26" s="29" t="s"/>
+      <x:c r="J26" s="29" t="s"/>
+      <x:c r="K26" s="29" t="s"/>
+      <x:c r="L26" s="29" t="s"/>
+      <x:c r="M26" s="29" t="s"/>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B27" s="29" t="s"/>
+      <x:c r="C27" s="29" t="s"/>
+      <x:c r="D27" s="29" t="s"/>
+      <x:c r="E27" s="29" t="s"/>
+      <x:c r="F27" s="29" t="s"/>
+      <x:c r="G27" s="29" t="s"/>
+      <x:c r="H27" s="29" t="s"/>
+      <x:c r="I27" s="29" t="s"/>
+      <x:c r="J27" s="29" t="s"/>
+      <x:c r="K27" s="29" t="s"/>
+      <x:c r="L27" s="29" t="s"/>
+      <x:c r="M27" s="29" t="s"/>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B30" s="30" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="C29" s="28" t="s"/>
-      <x:c r="D29" s="28" t="s"/>
-      <x:c r="E29" s="28" t="s"/>
-      <x:c r="F29" s="29" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="30" t="s">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="C30" s="31" t="s"/>
       <x:c r="D30" s="31" t="s"/>
-      <x:c r="E30" s="31" t="s"/>
-      <x:c r="F30" s="32" t="n">
+      <x:c r="E30" s="32" t="s"/>
+      <x:c r="F30" s="32" t="s"/>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B31" s="33" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C31" s="34" t="s"/>
+      <x:c r="D31" s="34" t="s"/>
+      <x:c r="E31" s="34" t="s"/>
+      <x:c r="F31" s="35" t="s">
+        <x:v>93</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="36" t="s">
         <x:v>2</x:v>
       </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="30" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C31" s="31" t="s"/>
-      <x:c r="D31" s="31" t="s"/>
-      <x:c r="E31" s="31" t="s"/>
-      <x:c r="F31" s="32" t="n">
+      <x:c r="C32" s="37" t="s"/>
+      <x:c r="D32" s="37" t="s"/>
+      <x:c r="E32" s="37" t="s"/>
+      <x:c r="F32" s="38" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="36" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C33" s="37" t="s"/>
+      <x:c r="D33" s="37" t="s"/>
+      <x:c r="E33" s="37" t="s"/>
+      <x:c r="F33" s="38" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="30" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C32" s="31" t="s"/>
-      <x:c r="D32" s="31" t="s"/>
-      <x:c r="E32" s="31" t="s"/>
-      <x:c r="F32" s="32" t="n">
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="36" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C34" s="37" t="s"/>
+      <x:c r="D34" s="37" t="s"/>
+      <x:c r="E34" s="37" t="s"/>
+      <x:c r="F34" s="38" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="30" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C33" s="31" t="s"/>
-      <x:c r="D33" s="31" t="s"/>
-      <x:c r="E33" s="31" t="s"/>
-      <x:c r="F33" s="32" t="n">
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="36" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C35" s="37" t="s"/>
+      <x:c r="D35" s="37" t="s"/>
+      <x:c r="E35" s="37" t="s"/>
+      <x:c r="F35" s="38" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="30" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C34" s="31" t="s"/>
-      <x:c r="D34" s="31" t="s"/>
-      <x:c r="E34" s="31" t="s"/>
-      <x:c r="F34" s="32" t="n">
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="36" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C36" s="37" t="s"/>
+      <x:c r="D36" s="37" t="s"/>
+      <x:c r="E36" s="37" t="s"/>
+      <x:c r="F36" s="38" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="30" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C35" s="31" t="s"/>
-      <x:c r="D35" s="31" t="s"/>
-      <x:c r="E35" s="31" t="s"/>
-      <x:c r="F35" s="32" t="n">
+    <x:row r="37" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B37" s="36" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C37" s="37" t="s"/>
+      <x:c r="D37" s="37" t="s"/>
+      <x:c r="E37" s="37" t="s"/>
+      <x:c r="F37" s="38" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="30" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C36" s="31" t="s"/>
-      <x:c r="D36" s="31" t="s"/>
-      <x:c r="E36" s="31" t="s"/>
-      <x:c r="F36" s="32" t="n">
+    <x:row r="38" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B38" s="36" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C38" s="37" t="s"/>
+      <x:c r="D38" s="37" t="s"/>
+      <x:c r="E38" s="37" t="s"/>
+      <x:c r="F38" s="38" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B37" s="33" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C37" s="34" t="s"/>
-      <x:c r="D37" s="34" t="s"/>
-      <x:c r="E37" s="34" t="s"/>
-      <x:c r="F37" s="35" t="n">
+    <x:row r="39" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B39" s="39" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C39" s="40" t="s"/>
+      <x:c r="D39" s="40" t="s"/>
+      <x:c r="E39" s="40" t="s"/>
+      <x:c r="F39" s="41" t="n">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3213,12 +3268,11 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="12">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B28:F28"/>
-    <x:mergeCell ref="B29:E29"/>
-    <x:mergeCell ref="B30:E30"/>
+  <x:mergeCells count="13">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B30:F30"/>
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
     <x:mergeCell ref="B33:E33"/>
@@ -3226,6 +3280,8 @@
     <x:mergeCell ref="B35:E35"/>
     <x:mergeCell ref="B36:E36"/>
     <x:mergeCell ref="B37:E37"/>
+    <x:mergeCell ref="B38:E38"/>
+    <x:mergeCell ref="B39:E39"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -3286,7 +3342,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -3364,22 +3422,22 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s"/>
       <x:c r="E6" s="11" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H6" s="13">
         <x:v>46091.306099537</x:v>
@@ -3397,28 +3455,28 @@
         <x:v>46091.3131828704</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="16" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D7" s="16" t="s"/>
       <x:c r="E7" s="16" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F7" s="16" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G7" s="16" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H7" s="17">
         <x:v>46093.1459375</x:v>
@@ -3436,29 +3494,29 @@
         <x:v>46093.159537037</x:v>
       </x:c>
       <x:c r="M7" s="16" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="19" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C8" s="19" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D8" s="19" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E8" s="19" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F8" s="19" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G8" s="19" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H8" s="20">
         <x:v>46080.4532523148</x:v>
@@ -3476,27 +3534,27 @@
         <x:v>46097.1461689815</x:v>
       </x:c>
       <x:c r="M8" s="19" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="19" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="19" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D9" s="19" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E9" s="19" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F9" s="19" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G9" s="19" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H9" s="20">
         <x:v>46083.2380439815</x:v>
@@ -3514,658 +3572,684 @@
         <x:v>46097.1564351852</x:v>
       </x:c>
       <x:c r="M9" s="19" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C10" s="11" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D10" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E10" s="11" t="s">
+      <x:c r="B10" s="23" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C10" s="23" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="F10" s="11" t="s">
+      <x:c r="D10" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E10" s="23" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G10" s="11" t="s">
+      <x:c r="F10" s="23" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="H10" s="13">
+      <x:c r="G10" s="23" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H10" s="25">
         <x:v>46083.2599189815</x:v>
       </x:c>
-      <x:c r="I10" s="23">
+      <x:c r="I10" s="26">
         <x:v>46101</x:v>
       </x:c>
-      <x:c r="J10" s="12" t="n">
+      <x:c r="J10" s="24" t="n">
         <x:v>1511237</x:v>
       </x:c>
-      <x:c r="K10" s="14" t="n">
+      <x:c r="K10" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="15">
+      <x:c r="L10" s="28">
         <x:v>46097.1652314815</x:v>
       </x:c>
-      <x:c r="M10" s="11" t="s">
-        <x:v>106</x:v>
+      <x:c r="M10" s="23" t="s">
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C11" s="11" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="D11" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E11" s="11" t="s">
+      <x:c r="B11" s="23" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C11" s="23" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="F11" s="11" t="s">
+      <x:c r="D11" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E11" s="23" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="G11" s="11" t="s">
+      <x:c r="F11" s="23" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="H11" s="13">
+      <x:c r="G11" s="23" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="H11" s="25">
         <x:v>46084.0854513889</x:v>
       </x:c>
-      <x:c r="I11" s="23">
+      <x:c r="I11" s="26">
         <x:v>46144</x:v>
       </x:c>
-      <x:c r="J11" s="12" t="n">
+      <x:c r="J11" s="24" t="n">
         <x:v>1511225</x:v>
       </x:c>
-      <x:c r="K11" s="14" t="n">
+      <x:c r="K11" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="15">
+      <x:c r="L11" s="28">
         <x:v>46093.3956365741</x:v>
       </x:c>
-      <x:c r="M11" s="11" t="s">
-        <x:v>106</x:v>
+      <x:c r="M11" s="23" t="s">
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C12" s="11" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="D12" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E12" s="11" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="F12" s="11" t="s">
+      <x:c r="B12" s="23" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C12" s="23" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D12" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E12" s="23" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="G12" s="11" t="s">
+      <x:c r="F12" s="23" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H12" s="13">
+      <x:c r="G12" s="23" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H12" s="25">
         <x:v>46084.0996759259</x:v>
       </x:c>
-      <x:c r="I12" s="23">
+      <x:c r="I12" s="26">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J12" s="12" t="n">
+      <x:c r="J12" s="24" t="n">
         <x:v>1511192</x:v>
       </x:c>
-      <x:c r="K12" s="14" t="n">
+      <x:c r="K12" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="15">
+      <x:c r="L12" s="28">
         <x:v>46097.2414583333</x:v>
       </x:c>
-      <x:c r="M12" s="11" t="s">
-        <x:v>106</x:v>
+      <x:c r="M12" s="23" t="s">
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C13" s="11" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D13" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E13" s="11" t="s">
+      <x:c r="B13" s="23" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C13" s="23" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="F13" s="11" t="s">
+      <x:c r="D13" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E13" s="23" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="G13" s="11" t="s">
+      <x:c r="F13" s="23" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="H13" s="13">
+      <x:c r="G13" s="23" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H13" s="25">
         <x:v>46069.1542013889</x:v>
       </x:c>
-      <x:c r="I13" s="23">
+      <x:c r="I13" s="26">
         <x:v>46035</x:v>
       </x:c>
-      <x:c r="J13" s="12" t="n">
+      <x:c r="J13" s="24" t="n">
         <x:v>1511206</x:v>
       </x:c>
-      <x:c r="K13" s="14" t="n">
+      <x:c r="K13" s="27" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L13" s="15">
+      <x:c r="L13" s="28">
         <x:v>46097.2466550926</x:v>
       </x:c>
-      <x:c r="M13" s="11" t="s">
-        <x:v>106</x:v>
+      <x:c r="M13" s="23" t="s">
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C14" s="11" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="D14" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="s">
+      <x:c r="B14" s="23" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C14" s="23" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="F14" s="11" t="s">
+      <x:c r="D14" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E14" s="23" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="G14" s="11" t="s">
+      <x:c r="F14" s="23" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="H14" s="13">
+      <x:c r="G14" s="23" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H14" s="25">
         <x:v>46069.2178703704</x:v>
       </x:c>
-      <x:c r="I14" s="23">
+      <x:c r="I14" s="26">
         <x:v>46051</x:v>
       </x:c>
-      <x:c r="J14" s="12" t="n">
+      <x:c r="J14" s="24" t="n">
         <x:v>1511196</x:v>
       </x:c>
-      <x:c r="K14" s="14" t="n">
+      <x:c r="K14" s="27" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L14" s="15">
+      <x:c r="L14" s="28">
         <x:v>46097.2456365741</x:v>
       </x:c>
-      <x:c r="M14" s="11" t="s">
-        <x:v>106</x:v>
+      <x:c r="M14" s="23" t="s">
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C15" s="11" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="D15" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E15" s="11" t="s">
+      <x:c r="B15" s="23" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C15" s="23" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="F15" s="11" t="s">
+      <x:c r="D15" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E15" s="23" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="G15" s="11" t="s">
+      <x:c r="F15" s="23" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="H15" s="13">
+      <x:c r="G15" s="23" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="H15" s="25">
         <x:v>46083.2443865741</x:v>
       </x:c>
-      <x:c r="I15" s="23">
+      <x:c r="I15" s="26">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J15" s="12" t="n">
+      <x:c r="J15" s="24" t="n">
         <x:v>1511235</x:v>
       </x:c>
-      <x:c r="K15" s="14" t="n">
+      <x:c r="K15" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L15" s="15">
+      <x:c r="L15" s="28">
         <x:v>46097.1600115741</x:v>
       </x:c>
-      <x:c r="M15" s="11" t="s">
-        <x:v>106</x:v>
+      <x:c r="M15" s="23" t="s">
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C16" s="11" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="D16" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E16" s="11" t="s">
+      <x:c r="B16" s="23" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C16" s="23" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="F16" s="11" t="s">
+      <x:c r="D16" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E16" s="23" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="G16" s="11" t="s">
+      <x:c r="F16" s="23" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="H16" s="13">
+      <x:c r="G16" s="23" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="H16" s="25">
         <x:v>46083.2521064815</x:v>
       </x:c>
-      <x:c r="I16" s="23">
+      <x:c r="I16" s="26">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J16" s="12" t="n">
+      <x:c r="J16" s="24" t="n">
         <x:v>1511236</x:v>
       </x:c>
-      <x:c r="K16" s="14" t="n">
+      <x:c r="K16" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="15">
+      <x:c r="L16" s="28">
         <x:v>46097.1628935185</x:v>
       </x:c>
-      <x:c r="M16" s="11" t="s">
-        <x:v>106</x:v>
+      <x:c r="M16" s="23" t="s">
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C17" s="11" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="D17" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E17" s="11" t="s">
+      <x:c r="B17" s="23" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C17" s="23" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="F17" s="11" t="s">
+      <x:c r="D17" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E17" s="23" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="G17" s="11" t="s">
+      <x:c r="F17" s="23" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="H17" s="13">
+      <x:c r="G17" s="23" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="H17" s="25">
         <x:v>46086.1064814815</x:v>
       </x:c>
-      <x:c r="I17" s="23">
+      <x:c r="I17" s="26">
         <x:v>46095</x:v>
       </x:c>
-      <x:c r="J17" s="12" t="n">
+      <x:c r="J17" s="24" t="n">
         <x:v>1511761</x:v>
       </x:c>
-      <x:c r="K17" s="14" t="n">
+      <x:c r="K17" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="15">
+      <x:c r="L17" s="28">
         <x:v>46090.2765740741</x:v>
       </x:c>
-      <x:c r="M17" s="11" t="s">
-        <x:v>38</x:v>
+      <x:c r="M17" s="23" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="11" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C18" s="11" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="D18" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E18" s="11" t="s">
+      <x:c r="B18" s="23" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C18" s="23" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="F18" s="11" t="s">
+      <x:c r="D18" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E18" s="23" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="G18" s="11" t="s">
+      <x:c r="F18" s="23" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="H18" s="13">
+      <x:c r="G18" s="23" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="H18" s="25">
         <x:v>46085.16625</x:v>
       </x:c>
-      <x:c r="I18" s="13">
+      <x:c r="I18" s="25">
         <x:v>46085.1662615741</x:v>
       </x:c>
-      <x:c r="J18" s="12" t="n">
+      <x:c r="J18" s="24" t="n">
         <x:v>1507966</x:v>
       </x:c>
-      <x:c r="K18" s="14" t="n">
+      <x:c r="K18" s="27" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L18" s="15">
+      <x:c r="L18" s="28">
         <x:v>46090.3437268519</x:v>
       </x:c>
-      <x:c r="M18" s="11" t="s">
-        <x:v>145</x:v>
+      <x:c r="M18" s="23" t="s">
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="11" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C19" s="11" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="D19" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E19" s="11" t="s">
+      <x:c r="B19" s="23" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C19" s="23" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D19" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E19" s="23" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="F19" s="23" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G19" s="23" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H19" s="25">
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I19" s="25">
+        <x:v>46085.1709375</x:v>
+      </x:c>
+      <x:c r="J19" s="24" t="n">
+        <x:v>1507965</x:v>
+      </x:c>
+      <x:c r="K19" s="27" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L19" s="28">
+        <x:v>46090.3336921296</x:v>
+      </x:c>
+      <x:c r="M19" s="23" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="F19" s="11" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="G19" s="11" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="H19" s="13">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I19" s="13">
-        <x:v>46085.1709375</x:v>
-      </x:c>
-      <x:c r="J19" s="12" t="n">
-        <x:v>1507965</x:v>
-      </x:c>
-      <x:c r="K19" s="14" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L19" s="15">
-        <x:v>46090.3336921296</x:v>
-      </x:c>
-      <x:c r="M19" s="11" t="s">
-        <x:v>145</x:v>
-      </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C20" s="11" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="D20" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E20" s="11" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="F20" s="11" t="s">
+      <x:c r="B20" s="23" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C20" s="23" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D20" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E20" s="23" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="G20" s="11" t="s">
+      <x:c r="F20" s="23" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="H20" s="13">
+      <x:c r="G20" s="23" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H20" s="25">
         <x:v>46084.1080324074</x:v>
       </x:c>
-      <x:c r="I20" s="23">
+      <x:c r="I20" s="26">
         <x:v>46103</x:v>
       </x:c>
-      <x:c r="J20" s="12" t="n">
+      <x:c r="J20" s="24" t="n">
         <x:v>1511208</x:v>
       </x:c>
-      <x:c r="K20" s="14" t="n">
+      <x:c r="K20" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L20" s="15">
+      <x:c r="L20" s="28">
         <x:v>46097.2478125</x:v>
       </x:c>
-      <x:c r="M20" s="11" t="s">
-        <x:v>106</x:v>
+      <x:c r="M20" s="23" t="s">
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C21" s="11" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="D21" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E21" s="11" t="s">
+      <x:c r="B21" s="23" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C21" s="23" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="F21" s="11" t="s">
+      <x:c r="D21" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E21" s="23" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="G21" s="11" t="s">
+      <x:c r="F21" s="23" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="H21" s="13">
+      <x:c r="G21" s="23" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="H21" s="25">
         <x:v>46083.0787962963</x:v>
       </x:c>
-      <x:c r="I21" s="23">
+      <x:c r="I21" s="26">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J21" s="12" t="n">
+      <x:c r="J21" s="24" t="n">
         <x:v>1511639</x:v>
       </x:c>
-      <x:c r="K21" s="14" t="n">
+      <x:c r="K21" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L21" s="15">
+      <x:c r="L21" s="28">
         <x:v>46083.104224537</x:v>
       </x:c>
-      <x:c r="M21" s="11" t="s">
-        <x:v>38</x:v>
+      <x:c r="M21" s="23" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C22" s="11" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="D22" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E22" s="11" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="F22" s="11" t="s">
+      <x:c r="B22" s="23" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C22" s="23" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="D22" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E22" s="23" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="G22" s="11" t="s">
+      <x:c r="F22" s="23" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="H22" s="13">
+      <x:c r="G22" s="23" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="H22" s="25">
         <x:v>46086.0997916667</x:v>
       </x:c>
-      <x:c r="I22" s="23">
+      <x:c r="I22" s="26">
         <x:v>46098</x:v>
       </x:c>
-      <x:c r="J22" s="12" t="n">
+      <x:c r="J22" s="24" t="n">
         <x:v>1511758</x:v>
       </x:c>
-      <x:c r="K22" s="14" t="n">
+      <x:c r="K22" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L22" s="15">
+      <x:c r="L22" s="28">
         <x:v>46090.2691087963</x:v>
       </x:c>
-      <x:c r="M22" s="11" t="s">
-        <x:v>38</x:v>
+      <x:c r="M22" s="23" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C23" s="11" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="D23" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E23" s="11" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="F23" s="11" t="s">
+      <x:c r="B23" s="23" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C23" s="23" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="D23" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E23" s="23" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="G23" s="11" t="s">
+      <x:c r="F23" s="23" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="H23" s="13">
+      <x:c r="G23" s="23" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="H23" s="25">
         <x:v>46086.1144444444</x:v>
       </x:c>
-      <x:c r="I23" s="23">
+      <x:c r="I23" s="26">
         <x:v>46097</x:v>
       </x:c>
-      <x:c r="J23" s="12" t="n">
+      <x:c r="J23" s="24" t="n">
         <x:v>1511759</x:v>
       </x:c>
-      <x:c r="K23" s="14" t="n">
+      <x:c r="K23" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L23" s="15">
+      <x:c r="L23" s="28">
         <x:v>46090.2703703704</x:v>
       </x:c>
-      <x:c r="M23" s="11" t="s">
-        <x:v>38</x:v>
+      <x:c r="M23" s="23" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C24" s="11" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="D24" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E24" s="11" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="F24" s="11" t="s">
+      <x:c r="B24" s="23" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C24" s="23" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="D24" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E24" s="23" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="G24" s="11" t="s">
+      <x:c r="F24" s="23" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="H24" s="13">
+      <x:c r="G24" s="23" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="H24" s="25">
         <x:v>46087.1643287037</x:v>
       </x:c>
-      <x:c r="I24" s="23">
+      <x:c r="I24" s="26">
         <x:v>46104</x:v>
       </x:c>
-      <x:c r="J24" s="12" t="n">
+      <x:c r="J24" s="24" t="n">
         <x:v>1511760</x:v>
       </x:c>
-      <x:c r="K24" s="14" t="n">
+      <x:c r="K24" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L24" s="15">
+      <x:c r="L24" s="28">
         <x:v>46090.2727777778</x:v>
       </x:c>
-      <x:c r="M24" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="24" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C27" s="25" t="s"/>
-      <x:c r="D27" s="25" t="s"/>
-      <x:c r="E27" s="26" t="s"/>
-      <x:c r="F27" s="26" t="s"/>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="27" t="s">
+      <x:c r="M24" s="23" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B25" s="29" t="s"/>
+      <x:c r="C25" s="29" t="s"/>
+      <x:c r="D25" s="29" t="s"/>
+      <x:c r="E25" s="29" t="s"/>
+      <x:c r="F25" s="29" t="s"/>
+      <x:c r="G25" s="29" t="s"/>
+      <x:c r="H25" s="29" t="s"/>
+      <x:c r="I25" s="29" t="s"/>
+      <x:c r="J25" s="29" t="s"/>
+      <x:c r="K25" s="29" t="s"/>
+      <x:c r="L25" s="29" t="s"/>
+      <x:c r="M25" s="29" t="s"/>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B26" s="29" t="s"/>
+      <x:c r="C26" s="29" t="s"/>
+      <x:c r="D26" s="29" t="s"/>
+      <x:c r="E26" s="29" t="s"/>
+      <x:c r="F26" s="29" t="s"/>
+      <x:c r="G26" s="29" t="s"/>
+      <x:c r="H26" s="29" t="s"/>
+      <x:c r="I26" s="29" t="s"/>
+      <x:c r="J26" s="29" t="s"/>
+      <x:c r="K26" s="29" t="s"/>
+      <x:c r="L26" s="29" t="s"/>
+      <x:c r="M26" s="29" t="s"/>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B29" s="30" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="C28" s="28" t="s"/>
-      <x:c r="D28" s="28" t="s"/>
-      <x:c r="E28" s="28" t="s"/>
-      <x:c r="F28" s="29" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="30" t="s">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="C29" s="31" t="s"/>
       <x:c r="D29" s="31" t="s"/>
-      <x:c r="E29" s="31" t="s"/>
-      <x:c r="F29" s="32" t="n">
+      <x:c r="E29" s="32" t="s"/>
+      <x:c r="F29" s="32" t="s"/>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B30" s="33" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C30" s="34" t="s"/>
+      <x:c r="D30" s="34" t="s"/>
+      <x:c r="E30" s="34" t="s"/>
+      <x:c r="F30" s="35" t="s">
+        <x:v>93</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="36" t="s">
         <x:v>2</x:v>
       </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="30" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C30" s="31" t="s"/>
-      <x:c r="D30" s="31" t="s"/>
-      <x:c r="E30" s="31" t="s"/>
-      <x:c r="F30" s="32" t="n">
+      <x:c r="C31" s="37" t="s"/>
+      <x:c r="D31" s="37" t="s"/>
+      <x:c r="E31" s="37" t="s"/>
+      <x:c r="F31" s="38" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="36" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C32" s="37" t="s"/>
+      <x:c r="D32" s="37" t="s"/>
+      <x:c r="E32" s="37" t="s"/>
+      <x:c r="F32" s="38" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="30" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C31" s="31" t="s"/>
-      <x:c r="D31" s="31" t="s"/>
-      <x:c r="E31" s="31" t="s"/>
-      <x:c r="F31" s="32" t="n">
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="36" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C33" s="37" t="s"/>
+      <x:c r="D33" s="37" t="s"/>
+      <x:c r="E33" s="37" t="s"/>
+      <x:c r="F33" s="38" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="30" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C32" s="31" t="s"/>
-      <x:c r="D32" s="31" t="s"/>
-      <x:c r="E32" s="31" t="s"/>
-      <x:c r="F32" s="32" t="n">
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="36" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C34" s="37" t="s"/>
+      <x:c r="D34" s="37" t="s"/>
+      <x:c r="E34" s="37" t="s"/>
+      <x:c r="F34" s="38" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B33" s="33" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C33" s="34" t="s"/>
-      <x:c r="D33" s="34" t="s"/>
-      <x:c r="E33" s="34" t="s"/>
-      <x:c r="F33" s="35" t="n">
+    <x:row r="35" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B35" s="39" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C35" s="40" t="s"/>
+      <x:c r="D35" s="40" t="s"/>
+      <x:c r="E35" s="40" t="s"/>
+      <x:c r="F35" s="41" t="n">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5125,16 +5209,17 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="9">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B27:F27"/>
-    <x:mergeCell ref="B28:E28"/>
-    <x:mergeCell ref="B29:E29"/>
+  <x:mergeCells count="10">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B29:F29"/>
     <x:mergeCell ref="B30:E30"/>
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
     <x:mergeCell ref="B33:E33"/>
+    <x:mergeCell ref="B34:E34"/>
+    <x:mergeCell ref="B35:E35"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="174">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -427,6 +427,18 @@
     <x:t>43A-3-2026-1152-831</x:t>
   </x:si>
   <x:si>
+    <x:t>MOBILECRAZE TELECOM INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLA MALL PAGSANJAN NATIONAL ROAD, PAGSANJAN, City Of Biñan, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-06-0809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1159-651</x:t>
+  </x:si>
+  <x:si>
     <x:t>ONE DOTCOM CELL INC.</x:t>
   </x:si>
   <x:si>
@@ -437,6 +449,18 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1153-796</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYNCNETIC INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LEVEL 3 0118, SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-18-05-0718</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1083-282</x:t>
   </x:si>
   <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
@@ -1384,7 +1408,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -1452,7 +1476,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>2</x:v>
@@ -3392,7 +3416,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -3460,7 +3484,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>2</x:v>
@@ -3823,19 +3847,19 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="H16" s="25">
-        <x:v>46083.2521064815</x:v>
+        <x:v>46084.1225115741</x:v>
       </x:c>
       <x:c r="I16" s="26">
-        <x:v>46100</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J16" s="24" t="n">
-        <x:v>1511236</x:v>
+        <x:v>1511242</x:v>
       </x:c>
       <x:c r="K16" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="28">
-        <x:v>46097.1628935185</x:v>
+        <x:v>46097.3505092593</x:v>
       </x:c>
       <x:c r="M16" s="23" t="s">
         <x:v>107</x:v>
@@ -3861,33 +3885,33 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="H17" s="25">
-        <x:v>46086.1064814815</x:v>
+        <x:v>46083.2521064815</x:v>
       </x:c>
       <x:c r="I17" s="26">
-        <x:v>46095</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J17" s="24" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511236</x:v>
       </x:c>
       <x:c r="K17" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L17" s="28">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46097.1628935185</x:v>
       </x:c>
       <x:c r="M17" s="23" t="s">
-        <x:v>39</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B18" s="23" t="s">
-        <x:v>34</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C18" s="23" t="s">
         <x:v>142</x:v>
       </x:c>
       <x:c r="D18" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E18" s="23" t="s">
         <x:v>143</x:v>
@@ -3899,33 +3923,33 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="H18" s="25">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I18" s="25">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46069.115150463</x:v>
+      </x:c>
+      <x:c r="I18" s="26">
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J18" s="24" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1511241</x:v>
       </x:c>
       <x:c r="K18" s="27" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L18" s="28">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46097.3433796296</x:v>
       </x:c>
       <x:c r="M18" s="23" t="s">
-        <x:v>146</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B19" s="23" t="s">
-        <x:v>34</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C19" s="23" t="s">
-        <x:v>142</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D19" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E19" s="23" t="s">
         <x:v>147</x:v>
@@ -3937,98 +3961,98 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="H19" s="25">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I19" s="25">
-        <x:v>46085.1709375</x:v>
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I19" s="26">
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J19" s="24" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K19" s="27" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="28">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M19" s="23" t="s">
-        <x:v>146</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B20" s="23" t="s">
-        <x:v>44</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C20" s="23" t="s">
-        <x:v>115</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D20" s="24" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E20" s="23" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="F20" s="23" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G20" s="23" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="H20" s="25">
-        <x:v>46084.1080324074</x:v>
-      </x:c>
-      <x:c r="I20" s="26">
-        <x:v>46103</x:v>
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I20" s="25">
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J20" s="24" t="n">
-        <x:v>1511208</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K20" s="27" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L20" s="28">
-        <x:v>46097.2478125</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M20" s="23" t="s">
-        <x:v>107</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B21" s="23" t="s">
-        <x:v>44</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C21" s="23" t="s">
-        <x:v>153</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D21" s="24" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E21" s="23" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="F21" s="23" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="G21" s="23" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="H21" s="25">
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I21" s="25">
+        <x:v>46085.1709375</x:v>
+      </x:c>
+      <x:c r="J21" s="24" t="n">
+        <x:v>1507965</x:v>
+      </x:c>
+      <x:c r="K21" s="27" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L21" s="28">
+        <x:v>46090.3336921296</x:v>
+      </x:c>
+      <x:c r="M21" s="23" t="s">
         <x:v>154</x:v>
-      </x:c>
-      <x:c r="F21" s="23" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="G21" s="23" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="H21" s="25">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I21" s="26">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J21" s="24" t="n">
-        <x:v>1511639</x:v>
-      </x:c>
-      <x:c r="K21" s="27" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="28">
-        <x:v>46083.104224537</x:v>
-      </x:c>
-      <x:c r="M21" s="23" t="s">
-        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
@@ -4036,37 +4060,37 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="C22" s="23" t="s">
-        <x:v>138</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D22" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="E22" s="23" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="F22" s="23" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="G22" s="23" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="H22" s="25">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46084.1080324074</x:v>
       </x:c>
       <x:c r="I22" s="26">
-        <x:v>46098</x:v>
+        <x:v>46103</x:v>
       </x:c>
       <x:c r="J22" s="24" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511208</x:v>
       </x:c>
       <x:c r="K22" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="28">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46097.2478125</x:v>
       </x:c>
       <x:c r="M22" s="23" t="s">
-        <x:v>39</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
@@ -4074,34 +4098,34 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="C23" s="23" t="s">
-        <x:v>138</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D23" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="E23" s="23" t="s">
-        <x:v>160</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="F23" s="23" t="s">
-        <x:v>161</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G23" s="23" t="s">
-        <x:v>162</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="H23" s="25">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I23" s="26">
-        <x:v>46097</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J23" s="24" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1511639</x:v>
       </x:c>
       <x:c r="K23" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="28">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46083.104224537</x:v>
       </x:c>
       <x:c r="M23" s="23" t="s">
         <x:v>39</x:v>
@@ -4112,114 +4136,168 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="C24" s="23" t="s">
-        <x:v>138</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D24" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="E24" s="23" t="s">
-        <x:v>163</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="F24" s="23" t="s">
-        <x:v>164</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G24" s="23" t="s">
-        <x:v>165</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="H24" s="25">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46086.0997916667</x:v>
       </x:c>
       <x:c r="I24" s="26">
-        <x:v>46104</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="J24" s="24" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511758</x:v>
       </x:c>
       <x:c r="K24" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="28">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46090.2691087963</x:v>
       </x:c>
       <x:c r="M24" s="23" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B25" s="29" t="s"/>
-      <x:c r="C25" s="29" t="s"/>
-      <x:c r="D25" s="29" t="s"/>
-      <x:c r="E25" s="29" t="s"/>
-      <x:c r="F25" s="29" t="s"/>
-      <x:c r="G25" s="29" t="s"/>
-      <x:c r="H25" s="29" t="s"/>
-      <x:c r="I25" s="29" t="s"/>
-      <x:c r="J25" s="29" t="s"/>
-      <x:c r="K25" s="29" t="s"/>
-      <x:c r="L25" s="29" t="s"/>
-      <x:c r="M25" s="29" t="s"/>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B26" s="29" t="s"/>
-      <x:c r="C26" s="29" t="s"/>
-      <x:c r="D26" s="29" t="s"/>
-      <x:c r="E26" s="29" t="s"/>
-      <x:c r="F26" s="29" t="s"/>
-      <x:c r="G26" s="29" t="s"/>
-      <x:c r="H26" s="29" t="s"/>
-      <x:c r="I26" s="29" t="s"/>
-      <x:c r="J26" s="29" t="s"/>
-      <x:c r="K26" s="29" t="s"/>
-      <x:c r="L26" s="29" t="s"/>
-      <x:c r="M26" s="29" t="s"/>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B29" s="30" t="s">
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="23" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C25" s="23" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D25" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E25" s="23" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="F25" s="23" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="G25" s="23" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="H25" s="25">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I25" s="26">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J25" s="24" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K25" s="27" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="28">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M25" s="23" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="23" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C26" s="23" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D26" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E26" s="23" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="F26" s="23" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="G26" s="23" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="H26" s="25">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I26" s="26">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J26" s="24" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K26" s="27" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="28">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M26" s="23" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B27" s="29" t="s"/>
+      <x:c r="C27" s="29" t="s"/>
+      <x:c r="D27" s="29" t="s"/>
+      <x:c r="E27" s="29" t="s"/>
+      <x:c r="F27" s="29" t="s"/>
+      <x:c r="G27" s="29" t="s"/>
+      <x:c r="H27" s="29" t="s"/>
+      <x:c r="I27" s="29" t="s"/>
+      <x:c r="J27" s="29" t="s"/>
+      <x:c r="K27" s="29" t="s"/>
+      <x:c r="L27" s="29" t="s"/>
+      <x:c r="M27" s="29" t="s"/>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B28" s="29" t="s"/>
+      <x:c r="C28" s="29" t="s"/>
+      <x:c r="D28" s="29" t="s"/>
+      <x:c r="E28" s="29" t="s"/>
+      <x:c r="F28" s="29" t="s"/>
+      <x:c r="G28" s="29" t="s"/>
+      <x:c r="H28" s="29" t="s"/>
+      <x:c r="I28" s="29" t="s"/>
+      <x:c r="J28" s="29" t="s"/>
+      <x:c r="K28" s="29" t="s"/>
+      <x:c r="L28" s="29" t="s"/>
+      <x:c r="M28" s="29" t="s"/>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B31" s="30" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C29" s="31" t="s"/>
-      <x:c r="D29" s="31" t="s"/>
-      <x:c r="E29" s="32" t="s"/>
-      <x:c r="F29" s="32" t="s"/>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B30" s="33" t="s">
+      <x:c r="C31" s="31" t="s"/>
+      <x:c r="D31" s="31" t="s"/>
+      <x:c r="E31" s="32" t="s"/>
+      <x:c r="F31" s="32" t="s"/>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B32" s="33" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C30" s="34" t="s"/>
-      <x:c r="D30" s="34" t="s"/>
-      <x:c r="E30" s="34" t="s"/>
-      <x:c r="F30" s="35" t="s">
+      <x:c r="C32" s="34" t="s"/>
+      <x:c r="D32" s="34" t="s"/>
+      <x:c r="E32" s="34" t="s"/>
+      <x:c r="F32" s="35" t="s">
         <x:v>93</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="36" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C31" s="37" t="s"/>
-      <x:c r="D31" s="37" t="s"/>
-      <x:c r="E31" s="37" t="s"/>
-      <x:c r="F31" s="38" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="36" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C32" s="37" t="s"/>
-      <x:c r="D32" s="37" t="s"/>
-      <x:c r="E32" s="37" t="s"/>
-      <x:c r="F32" s="38" t="n">
-        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
       <x:c r="B33" s="36" t="s">
-        <x:v>34</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C33" s="37" t="s"/>
       <x:c r="D33" s="37" t="s"/>
@@ -4230,28 +4308,48 @@
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
       <x:c r="B34" s="36" t="s">
-        <x:v>44</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C34" s="37" t="s"/>
       <x:c r="D34" s="37" t="s"/>
       <x:c r="E34" s="37" t="s"/>
       <x:c r="F34" s="38" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="36" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C35" s="37" t="s"/>
+      <x:c r="D35" s="37" t="s"/>
+      <x:c r="E35" s="37" t="s"/>
+      <x:c r="F35" s="38" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="36" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C36" s="37" t="s"/>
+      <x:c r="D36" s="37" t="s"/>
+      <x:c r="E36" s="37" t="s"/>
+      <x:c r="F36" s="38" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B35" s="39" t="s">
+    <x:row r="37" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B37" s="39" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="C35" s="40" t="s"/>
-      <x:c r="D35" s="40" t="s"/>
-      <x:c r="E35" s="40" t="s"/>
-      <x:c r="F35" s="41" t="n">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C37" s="40" t="s"/>
+      <x:c r="D37" s="40" t="s"/>
+      <x:c r="E37" s="40" t="s"/>
+      <x:c r="F37" s="41" t="n">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5213,13 +5311,13 @@
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
     <x:mergeCell ref="B3:M4"/>
-    <x:mergeCell ref="B29:F29"/>
-    <x:mergeCell ref="B30:E30"/>
-    <x:mergeCell ref="B31:E31"/>
+    <x:mergeCell ref="B31:F31"/>
     <x:mergeCell ref="B32:E32"/>
     <x:mergeCell ref="B33:E33"/>
     <x:mergeCell ref="B34:E34"/>
     <x:mergeCell ref="B35:E35"/>
+    <x:mergeCell ref="B36:E36"/>
+    <x:mergeCell ref="B37:E37"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -23,12 +23,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="174">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="186">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>ENGR. GALELEO MENDOZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -554,7 +590,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -599,21 +635,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
@@ -623,6 +644,13 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -873,7 +901,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -884,77 +912,68 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="42">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -985,60 +1004,8 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1049,67 +1016,79 @@
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1410,18 +1389,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1439,901 +1406,913 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46069.0835185185</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46069.1006712963</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1506161</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46069.1133333333</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="s">
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s">
+      <x:c r="I7" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F7" s="16" t="s">
+      <x:c r="J7" s="10" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G7" s="16" t="s">
+      <x:c r="K7" s="10" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="H7" s="17">
-        <x:v>46069.0835648148</x:v>
-      </x:c>
-      <x:c r="I7" s="17">
-        <x:v>46069.1000231481</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>1506159</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>46069.1128587963</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
-        <x:v>7</x:v>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="19" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="E8" s="19" t="s">
+      <x:c r="C8" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F8" s="19" t="s">
+      <x:c r="D8" s="11" t="s"/>
+      <x:c r="E8" s="11" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G8" s="19" t="s">
+      <x:c r="F8" s="11" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="H8" s="20">
+      <x:c r="G8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46069.0835185185</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46069.1006712963</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1506161</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46069.1133333333</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s"/>
+      <x:c r="E9" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46069.0835648148</x:v>
+      </x:c>
+      <x:c r="I9" s="12">
+        <x:v>46069.1000231481</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1506159</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46069.1128587963</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
         <x:v>46067.3600231481</x:v>
       </x:c>
-      <x:c r="I8" s="20">
+      <x:c r="I10" s="16">
         <x:v>46067.3600462963</x:v>
       </x:c>
-      <x:c r="J8" s="19" t="n">
+      <x:c r="J10" s="15" t="n">
         <x:v>1505803</x:v>
       </x:c>
-      <x:c r="K8" s="21" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L8" s="20">
+      <x:c r="L10" s="18">
         <x:v>46079.2730092593</x:v>
       </x:c>
-      <x:c r="M8" s="19" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="19" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E9" s="19" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F9" s="19" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G9" s="19" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H9" s="20">
+      <x:c r="M10" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
         <x:v>46067.1596643518</x:v>
       </x:c>
-      <x:c r="I9" s="22">
+      <x:c r="I11" s="19">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J9" s="19" t="n">
+      <x:c r="J11" s="15" t="n">
         <x:v>1505804</x:v>
       </x:c>
-      <x:c r="K9" s="21" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="L11" s="18">
         <x:v>46079.2772569444</x:v>
       </x:c>
-      <x:c r="M9" s="19" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="23" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C10" s="23" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D10" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E10" s="23" t="s">
+      <x:c r="M11" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46067.2222106481</x:v>
+      </x:c>
+      <x:c r="I12" s="19">
+        <x:v>46089</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="n">
+        <x:v>1505805</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>46079.2763078704</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>46063.1352777778</x:v>
+      </x:c>
+      <x:c r="I13" s="19">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="n">
+        <x:v>1511010</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="18">
+        <x:v>46063.2367708333</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="F10" s="23" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G10" s="23" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H10" s="25">
-        <x:v>46067.2222106481</x:v>
-      </x:c>
-      <x:c r="I10" s="26">
-        <x:v>46089</x:v>
-      </x:c>
-      <x:c r="J10" s="24" t="n">
-        <x:v>1505805</x:v>
-      </x:c>
-      <x:c r="K10" s="27" t="n">
+      <x:c r="E14" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46079.3584722222</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46079.3584953704</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="n">
+        <x:v>1511622</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L14" s="18">
+        <x:v>46080.2311226852</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>46079.3539699074</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46079.3539814815</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="n">
+        <x:v>1511627</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L15" s="18">
+        <x:v>46080.2440856481</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>46079.3873148148</x:v>
+      </x:c>
+      <x:c r="I16" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="n">
+        <x:v>1511623</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="28">
-        <x:v>46079.2763078704</x:v>
-      </x:c>
-      <x:c r="M10" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="23" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C11" s="23" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D11" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E11" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F11" s="23" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G11" s="23" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H11" s="25">
-        <x:v>46063.1352777778</x:v>
-      </x:c>
-      <x:c r="I11" s="26">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J11" s="24" t="n">
-        <x:v>1511010</x:v>
-      </x:c>
-      <x:c r="K11" s="27" t="n">
+      <x:c r="L16" s="18">
+        <x:v>46080.2360763889</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>46079.2523032407</x:v>
+      </x:c>
+      <x:c r="I17" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="n">
+        <x:v>1511631</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="28">
-        <x:v>46063.2367708333</x:v>
-      </x:c>
-      <x:c r="M11" s="23" t="s">
+      <x:c r="L17" s="18">
+        <x:v>46080.2925810185</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
         <x:v>33</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C12" s="23" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D12" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E12" s="23" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F12" s="23" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G12" s="23" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H12" s="25">
-        <x:v>46079.3584722222</x:v>
-      </x:c>
-      <x:c r="I12" s="25">
-        <x:v>46079.3584953704</x:v>
-      </x:c>
-      <x:c r="J12" s="24" t="n">
-        <x:v>1511622</x:v>
-      </x:c>
-      <x:c r="K12" s="27" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L12" s="28">
-        <x:v>46080.2311226852</x:v>
-      </x:c>
-      <x:c r="M12" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D13" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E13" s="23" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F13" s="23" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G13" s="23" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H13" s="25">
-        <x:v>46079.3539699074</x:v>
-      </x:c>
-      <x:c r="I13" s="25">
-        <x:v>46079.3539814815</x:v>
-      </x:c>
-      <x:c r="J13" s="24" t="n">
-        <x:v>1511627</x:v>
-      </x:c>
-      <x:c r="K13" s="27" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L13" s="28">
-        <x:v>46080.2440856481</x:v>
-      </x:c>
-      <x:c r="M13" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D14" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E14" s="23" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F14" s="23" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G14" s="23" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H14" s="25">
-        <x:v>46079.3873148148</x:v>
-      </x:c>
-      <x:c r="I14" s="26">
+      <x:c r="E18" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46079.2430555556</x:v>
+      </x:c>
+      <x:c r="I18" s="19">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J14" s="24" t="n">
-        <x:v>1511623</x:v>
-      </x:c>
-      <x:c r="K14" s="27" t="n">
+      <x:c r="J18" s="15" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L14" s="28">
-        <x:v>46080.2360763889</x:v>
-      </x:c>
-      <x:c r="M14" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="23" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D15" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E15" s="23" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F15" s="23" t="s">
+      <x:c r="L18" s="18">
+        <x:v>46080.2801273148</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="G15" s="23" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H15" s="25">
-        <x:v>46079.2523032407</x:v>
-      </x:c>
-      <x:c r="I15" s="26">
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46079.3651967593</x:v>
+      </x:c>
+      <x:c r="I19" s="19">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J15" s="24" t="n">
-        <x:v>1511631</x:v>
-      </x:c>
-      <x:c r="K15" s="27" t="n">
+      <x:c r="J19" s="15" t="n">
+        <x:v>1511626</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L15" s="28">
-        <x:v>46080.2925810185</x:v>
-      </x:c>
-      <x:c r="M15" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="23" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C16" s="23" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D16" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E16" s="23" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F16" s="23" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G16" s="23" t="s">
+      <x:c r="L19" s="18">
+        <x:v>46080.2425462963</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="H16" s="25">
-        <x:v>46079.2430555556</x:v>
-      </x:c>
-      <x:c r="I16" s="26">
+      <x:c r="C20" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46080.2923611111</x:v>
+      </x:c>
+      <x:c r="I20" s="19">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J16" s="24" t="n">
+      <x:c r="J20" s="15" t="n">
+        <x:v>1511635</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="18">
+        <x:v>46080.3208564815</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46079.31625</x:v>
+      </x:c>
+      <x:c r="I21" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="n">
         <x:v>1511630</x:v>
       </x:c>
-      <x:c r="K16" s="27" t="n">
+      <x:c r="K21" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="28">
-        <x:v>46080.2801273148</x:v>
-      </x:c>
-      <x:c r="M16" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="23" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C17" s="23" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D17" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E17" s="23" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F17" s="23" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G17" s="23" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H17" s="25">
-        <x:v>46079.3651967593</x:v>
-      </x:c>
-      <x:c r="I17" s="26">
+      <x:c r="L21" s="18">
+        <x:v>46080.2883680556</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46079.3059375</x:v>
+      </x:c>
+      <x:c r="I22" s="19">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J17" s="24" t="n">
-        <x:v>1511626</x:v>
-      </x:c>
-      <x:c r="K17" s="27" t="n">
+      <x:c r="J22" s="15" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="28">
-        <x:v>46080.2425462963</x:v>
-      </x:c>
-      <x:c r="M17" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="23" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C18" s="23" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E18" s="23" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F18" s="23" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G18" s="23" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H18" s="25">
-        <x:v>46080.2923611111</x:v>
-      </x:c>
-      <x:c r="I18" s="26">
+      <x:c r="L22" s="18">
+        <x:v>46080.2896875</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46079.2943981482</x:v>
+      </x:c>
+      <x:c r="I23" s="19">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J18" s="24" t="n">
-        <x:v>1511635</x:v>
-      </x:c>
-      <x:c r="K18" s="27" t="n">
+      <x:c r="J23" s="15" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="28">
-        <x:v>46080.3208564815</x:v>
-      </x:c>
-      <x:c r="M18" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="23" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C19" s="23" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E19" s="23" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F19" s="23" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="G19" s="23" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="H19" s="25">
-        <x:v>46079.31625</x:v>
-      </x:c>
-      <x:c r="I19" s="26">
+      <x:c r="L23" s="18">
+        <x:v>46080.2916782407</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>46079.378900463</x:v>
+      </x:c>
+      <x:c r="I24" s="19">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J19" s="24" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K19" s="27" t="n">
+      <x:c r="J24" s="15" t="n">
+        <x:v>1511624</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L19" s="28">
-        <x:v>46080.2883680556</x:v>
-      </x:c>
-      <x:c r="M19" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="23" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C20" s="23" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D20" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E20" s="23" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F20" s="23" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="G20" s="23" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="H20" s="25">
-        <x:v>46079.3059375</x:v>
-      </x:c>
-      <x:c r="I20" s="26">
+      <x:c r="L24" s="18">
+        <x:v>46080.2376041667</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H25" s="16">
+        <x:v>46079.3728240741</x:v>
+      </x:c>
+      <x:c r="I25" s="19">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J20" s="24" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K20" s="27" t="n">
+      <x:c r="J25" s="15" t="n">
+        <x:v>1511625</x:v>
+      </x:c>
+      <x:c r="K25" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L20" s="28">
-        <x:v>46080.2896875</x:v>
-      </x:c>
-      <x:c r="M20" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="23" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C21" s="23" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D21" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E21" s="23" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F21" s="23" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G21" s="23" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H21" s="25">
-        <x:v>46079.2943981482</x:v>
-      </x:c>
-      <x:c r="I21" s="26">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J21" s="24" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K21" s="27" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="28">
-        <x:v>46080.2916782407</x:v>
-      </x:c>
-      <x:c r="M21" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="23" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C22" s="23" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D22" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E22" s="23" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F22" s="23" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G22" s="23" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="H22" s="25">
-        <x:v>46079.378900463</x:v>
-      </x:c>
-      <x:c r="I22" s="26">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J22" s="24" t="n">
-        <x:v>1511624</x:v>
-      </x:c>
-      <x:c r="K22" s="27" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="28">
-        <x:v>46080.2376041667</x:v>
-      </x:c>
-      <x:c r="M22" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="23" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C23" s="23" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D23" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E23" s="23" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F23" s="23" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="G23" s="23" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="H23" s="25">
-        <x:v>46079.3728240741</x:v>
-      </x:c>
-      <x:c r="I23" s="26">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J23" s="24" t="n">
-        <x:v>1511625</x:v>
-      </x:c>
-      <x:c r="K23" s="27" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="28">
+      <x:c r="L25" s="18">
         <x:v>46080.2394328704</x:v>
       </x:c>
-      <x:c r="M23" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="23" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C24" s="23" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D24" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E24" s="23" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="F24" s="23" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="G24" s="23" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="H24" s="25">
+      <x:c r="M25" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H26" s="16">
         <x:v>46062.1590162037</x:v>
       </x:c>
-      <x:c r="I24" s="25">
+      <x:c r="I26" s="16">
         <x:v>46062.1590277778</x:v>
       </x:c>
-      <x:c r="J24" s="24" t="n">
+      <x:c r="J26" s="15" t="n">
         <x:v>1510925</x:v>
       </x:c>
-      <x:c r="K24" s="27" t="n">
+      <x:c r="K26" s="17" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L24" s="28">
+      <x:c r="L26" s="18">
         <x:v>46062.1863194444</x:v>
       </x:c>
-      <x:c r="M24" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="23" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C25" s="23" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="D25" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E25" s="23" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="F25" s="23" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="G25" s="23" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H25" s="25">
+      <x:c r="M26" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="14" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H27" s="16">
         <x:v>46071.0492476852</x:v>
       </x:c>
-      <x:c r="I25" s="26">
+      <x:c r="I27" s="19">
         <x:v>46052</x:v>
       </x:c>
-      <x:c r="J25" s="24" t="n">
+      <x:c r="J27" s="15" t="n">
         <x:v>1511502</x:v>
       </x:c>
-      <x:c r="K25" s="27" t="n">
+      <x:c r="K27" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L25" s="28">
+      <x:c r="L27" s="18">
         <x:v>46071.0606134259</x:v>
       </x:c>
-      <x:c r="M25" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B26" s="29" t="s"/>
-      <x:c r="C26" s="29" t="s"/>
-      <x:c r="D26" s="29" t="s"/>
-      <x:c r="E26" s="29" t="s"/>
-      <x:c r="F26" s="29" t="s"/>
-      <x:c r="G26" s="29" t="s"/>
-      <x:c r="H26" s="29" t="s"/>
-      <x:c r="I26" s="29" t="s"/>
-      <x:c r="J26" s="29" t="s"/>
-      <x:c r="K26" s="29" t="s"/>
-      <x:c r="L26" s="29" t="s"/>
-      <x:c r="M26" s="29" t="s"/>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B27" s="29" t="s"/>
-      <x:c r="C27" s="29" t="s"/>
-      <x:c r="D27" s="29" t="s"/>
-      <x:c r="E27" s="29" t="s"/>
-      <x:c r="F27" s="29" t="s"/>
-      <x:c r="G27" s="29" t="s"/>
-      <x:c r="H27" s="29" t="s"/>
-      <x:c r="I27" s="29" t="s"/>
-      <x:c r="J27" s="29" t="s"/>
-      <x:c r="K27" s="29" t="s"/>
-      <x:c r="L27" s="29" t="s"/>
-      <x:c r="M27" s="29" t="s"/>
+      <x:c r="M27" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B30" s="30" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C30" s="31" t="s"/>
-      <x:c r="D30" s="31" t="s"/>
-      <x:c r="E30" s="32" t="s"/>
-      <x:c r="F30" s="32" t="s"/>
+      <x:c r="B30" s="20" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C30" s="21" t="s"/>
+      <x:c r="D30" s="21" t="s"/>
+      <x:c r="E30" s="22" t="s"/>
+      <x:c r="F30" s="22" t="s"/>
     </x:row>
     <x:row r="31" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B31" s="33" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C31" s="34" t="s"/>
-      <x:c r="D31" s="34" t="s"/>
-      <x:c r="E31" s="34" t="s"/>
-      <x:c r="F31" s="35" t="s">
+      <x:c r="B31" s="23" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C31" s="24" t="s"/>
+      <x:c r="D31" s="24" t="s"/>
+      <x:c r="E31" s="24" t="s"/>
+      <x:c r="F31" s="25" t="s">
+        <x:v>105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C32" s="27" t="s"/>
+      <x:c r="D32" s="27" t="s"/>
+      <x:c r="E32" s="27" t="s"/>
+      <x:c r="F32" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="26" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C33" s="27" t="s"/>
+      <x:c r="D33" s="27" t="s"/>
+      <x:c r="E33" s="27" t="s"/>
+      <x:c r="F33" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="26" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C34" s="27" t="s"/>
+      <x:c r="D34" s="27" t="s"/>
+      <x:c r="E34" s="27" t="s"/>
+      <x:c r="F34" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="26" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C35" s="27" t="s"/>
+      <x:c r="D35" s="27" t="s"/>
+      <x:c r="E35" s="27" t="s"/>
+      <x:c r="F35" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="26" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C36" s="27" t="s"/>
+      <x:c r="D36" s="27" t="s"/>
+      <x:c r="E36" s="27" t="s"/>
+      <x:c r="F36" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B37" s="26" t="s">
         <x:v>93</x:v>
       </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="36" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C32" s="37" t="s"/>
-      <x:c r="D32" s="37" t="s"/>
-      <x:c r="E32" s="37" t="s"/>
-      <x:c r="F32" s="38" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="36" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C33" s="37" t="s"/>
-      <x:c r="D33" s="37" t="s"/>
-      <x:c r="E33" s="37" t="s"/>
-      <x:c r="F33" s="38" t="n">
+      <x:c r="C37" s="27" t="s"/>
+      <x:c r="D37" s="27" t="s"/>
+      <x:c r="E37" s="27" t="s"/>
+      <x:c r="F37" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="36" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C34" s="37" t="s"/>
-      <x:c r="D34" s="37" t="s"/>
-      <x:c r="E34" s="37" t="s"/>
-      <x:c r="F34" s="38" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="36" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C35" s="37" t="s"/>
-      <x:c r="D35" s="37" t="s"/>
-      <x:c r="E35" s="37" t="s"/>
-      <x:c r="F35" s="38" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="36" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C36" s="37" t="s"/>
-      <x:c r="D36" s="37" t="s"/>
-      <x:c r="E36" s="37" t="s"/>
-      <x:c r="F36" s="38" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B37" s="36" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C37" s="37" t="s"/>
-      <x:c r="D37" s="37" t="s"/>
-      <x:c r="E37" s="37" t="s"/>
-      <x:c r="F37" s="38" t="n">
+    <x:row r="38" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B38" s="26" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C38" s="27" t="s"/>
+      <x:c r="D38" s="27" t="s"/>
+      <x:c r="E38" s="27" t="s"/>
+      <x:c r="F38" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B38" s="36" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C38" s="37" t="s"/>
-      <x:c r="D38" s="37" t="s"/>
-      <x:c r="E38" s="37" t="s"/>
-      <x:c r="F38" s="38" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
     <x:row r="39" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B39" s="39" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C39" s="40" t="s"/>
-      <x:c r="D39" s="40" t="s"/>
-      <x:c r="E39" s="40" t="s"/>
-      <x:c r="F39" s="41" t="n">
+      <x:c r="B39" s="29" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C39" s="30" t="s"/>
+      <x:c r="D39" s="30" t="s"/>
+      <x:c r="E39" s="30" t="s"/>
+      <x:c r="F39" s="31" t="n">
         <x:v>20</x:v>
       </x:c>
     </x:row>
@@ -3418,18 +3397,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3447,906 +3414,918 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46091.306099537</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46091.3107986111</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1511778</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46091.3131828704</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="F7" s="16" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="G7" s="16" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="H7" s="17">
-        <x:v>46093.1459375</x:v>
-      </x:c>
-      <x:c r="I7" s="17">
-        <x:v>46093.1585185185</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>1511815</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>46093.159537037</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
-        <x:v>39</x:v>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="19" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="F8" s="19" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="G8" s="19" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="H8" s="20">
+      <x:c r="B8" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s"/>
+      <x:c r="E8" s="11" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46091.306099537</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46091.3107986111</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1511778</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46091.3131828704</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s"/>
+      <x:c r="E9" s="11" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46093.1459375</x:v>
+      </x:c>
+      <x:c r="I9" s="12">
+        <x:v>46093.1585185185</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1511815</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46093.159537037</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
         <x:v>46080.4532523148</x:v>
       </x:c>
-      <x:c r="I8" s="22">
+      <x:c r="I10" s="19">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J8" s="19" t="n">
+      <x:c r="J10" s="15" t="n">
         <x:v>1511232</x:v>
       </x:c>
-      <x:c r="K8" s="21" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="20">
+      <x:c r="L10" s="18">
         <x:v>46097.1461689815</x:v>
       </x:c>
-      <x:c r="M8" s="19" t="s">
-        <x:v>107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="19" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E9" s="19" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="F9" s="19" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="G9" s="19" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="H9" s="20">
+      <x:c r="M10" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
         <x:v>46083.2380439815</x:v>
       </x:c>
-      <x:c r="I9" s="22">
+      <x:c r="I11" s="19">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J9" s="19" t="n">
+      <x:c r="J11" s="15" t="n">
         <x:v>1511234</x:v>
       </x:c>
-      <x:c r="K9" s="21" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="L11" s="18">
         <x:v>46097.1564351852</x:v>
       </x:c>
-      <x:c r="M9" s="19" t="s">
-        <x:v>107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="23" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C10" s="23" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="D10" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E10" s="23" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="F10" s="23" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="G10" s="23" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="H10" s="25">
+      <x:c r="M11" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
         <x:v>46083.2599189815</x:v>
       </x:c>
-      <x:c r="I10" s="26">
+      <x:c r="I12" s="19">
         <x:v>46101</x:v>
       </x:c>
-      <x:c r="J10" s="24" t="n">
+      <x:c r="J12" s="15" t="n">
         <x:v>1511237</x:v>
       </x:c>
-      <x:c r="K10" s="27" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="28">
+      <x:c r="L12" s="18">
         <x:v>46097.1652314815</x:v>
       </x:c>
-      <x:c r="M10" s="23" t="s">
-        <x:v>107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="23" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C11" s="23" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="D11" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E11" s="23" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="F11" s="23" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="G11" s="23" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="H11" s="25">
+      <x:c r="M12" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
         <x:v>46084.0854513889</x:v>
       </x:c>
-      <x:c r="I11" s="26">
+      <x:c r="I13" s="19">
         <x:v>46144</x:v>
       </x:c>
-      <x:c r="J11" s="24" t="n">
+      <x:c r="J13" s="15" t="n">
         <x:v>1511225</x:v>
       </x:c>
-      <x:c r="K11" s="27" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="28">
+      <x:c r="L13" s="18">
         <x:v>46093.3956365741</x:v>
       </x:c>
-      <x:c r="M11" s="23" t="s">
-        <x:v>107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C12" s="23" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="D12" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E12" s="23" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="F12" s="23" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="G12" s="23" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="H12" s="25">
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
         <x:v>46084.0996759259</x:v>
       </x:c>
-      <x:c r="I12" s="26">
+      <x:c r="I14" s="19">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J12" s="24" t="n">
+      <x:c r="J14" s="15" t="n">
         <x:v>1511192</x:v>
       </x:c>
-      <x:c r="K12" s="27" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="28">
+      <x:c r="L14" s="18">
         <x:v>46097.2414583333</x:v>
       </x:c>
-      <x:c r="M12" s="23" t="s">
-        <x:v>107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="D13" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E13" s="23" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="F13" s="23" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="G13" s="23" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="H13" s="25">
+      <x:c r="M14" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
         <x:v>46069.1542013889</x:v>
       </x:c>
-      <x:c r="I13" s="26">
+      <x:c r="I15" s="19">
         <x:v>46035</x:v>
       </x:c>
-      <x:c r="J13" s="24" t="n">
+      <x:c r="J15" s="15" t="n">
         <x:v>1511206</x:v>
       </x:c>
-      <x:c r="K13" s="27" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L13" s="28">
+      <x:c r="L15" s="18">
         <x:v>46097.2466550926</x:v>
       </x:c>
-      <x:c r="M13" s="23" t="s">
-        <x:v>107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="D14" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E14" s="23" t="s">
+      <x:c r="M15" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>46069.2178703704</x:v>
+      </x:c>
+      <x:c r="I16" s="19">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="n">
+        <x:v>1511196</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L16" s="18">
+        <x:v>46097.2456365741</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>46083.2443865741</x:v>
+      </x:c>
+      <x:c r="I17" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="n">
+        <x:v>1511235</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="18">
+        <x:v>46097.1600115741</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46084.1225115741</x:v>
+      </x:c>
+      <x:c r="I18" s="19">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="n">
+        <x:v>1511242</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="18">
+        <x:v>46097.3505092593</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46083.2521064815</x:v>
+      </x:c>
+      <x:c r="I19" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="n">
+        <x:v>1511236</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="18">
+        <x:v>46097.1628935185</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46069.115150463</x:v>
+      </x:c>
+      <x:c r="I20" s="19">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="n">
+        <x:v>1511241</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="18">
+        <x:v>46097.3433796296</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I21" s="19">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="n">
+        <x:v>1511761</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="18">
+        <x:v>46090.2765740741</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
+        <x:v>46085.1662615741</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L22" s="18">
+        <x:v>46090.3437268519</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>166</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I23" s="16">
+        <x:v>46085.1709375</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="n">
+        <x:v>1507965</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L23" s="18">
+        <x:v>46090.3336921296</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>166</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="F14" s="23" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="G14" s="23" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="H14" s="25">
-        <x:v>46069.2178703704</x:v>
-      </x:c>
-      <x:c r="I14" s="26">
-        <x:v>46051</x:v>
-      </x:c>
-      <x:c r="J14" s="24" t="n">
-        <x:v>1511196</x:v>
-      </x:c>
-      <x:c r="K14" s="27" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L14" s="28">
-        <x:v>46097.2456365741</x:v>
-      </x:c>
-      <x:c r="M14" s="23" t="s">
-        <x:v>107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="23" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D15" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E15" s="23" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="F15" s="23" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="G15" s="23" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="H15" s="25">
-        <x:v>46083.2443865741</x:v>
-      </x:c>
-      <x:c r="I15" s="26">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J15" s="24" t="n">
-        <x:v>1511235</x:v>
-      </x:c>
-      <x:c r="K15" s="27" t="n">
+      <x:c r="D24" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>46084.1080324074</x:v>
+      </x:c>
+      <x:c r="I24" s="19">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J24" s="15" t="n">
+        <x:v>1511208</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L15" s="28">
-        <x:v>46097.1600115741</x:v>
-      </x:c>
-      <x:c r="M15" s="23" t="s">
-        <x:v>107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="23" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C16" s="23" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D16" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E16" s="23" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="F16" s="23" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="G16" s="23" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="H16" s="25">
-        <x:v>46084.1225115741</x:v>
-      </x:c>
-      <x:c r="I16" s="26">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J16" s="24" t="n">
-        <x:v>1511242</x:v>
-      </x:c>
-      <x:c r="K16" s="27" t="n">
+      <x:c r="L24" s="18">
+        <x:v>46097.2478125</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="H25" s="16">
+        <x:v>46083.0787962963</x:v>
+      </x:c>
+      <x:c r="I25" s="19">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J25" s="15" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K25" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="28">
-        <x:v>46097.3505092593</x:v>
-      </x:c>
-      <x:c r="M16" s="23" t="s">
-        <x:v>107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="23" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C17" s="23" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="D17" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E17" s="23" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="F17" s="23" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="G17" s="23" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="H17" s="25">
-        <x:v>46083.2521064815</x:v>
-      </x:c>
-      <x:c r="I17" s="26">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J17" s="24" t="n">
-        <x:v>1511236</x:v>
-      </x:c>
-      <x:c r="K17" s="27" t="n">
+      <x:c r="L25" s="18">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="H26" s="16">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I26" s="19">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J26" s="15" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K26" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="28">
-        <x:v>46097.1628935185</x:v>
-      </x:c>
-      <x:c r="M17" s="23" t="s">
-        <x:v>107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="23" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C18" s="23" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E18" s="23" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="F18" s="23" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="G18" s="23" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="H18" s="25">
-        <x:v>46069.115150463</x:v>
-      </x:c>
-      <x:c r="I18" s="26">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J18" s="24" t="n">
-        <x:v>1511241</x:v>
-      </x:c>
-      <x:c r="K18" s="27" t="n">
+      <x:c r="L26" s="18">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M26" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="H27" s="16">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I27" s="19">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J27" s="15" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K27" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="28">
-        <x:v>46097.3433796296</x:v>
-      </x:c>
-      <x:c r="M18" s="23" t="s">
-        <x:v>107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="23" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C19" s="23" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E19" s="23" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="F19" s="23" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="G19" s="23" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="H19" s="25">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I19" s="26">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="J19" s="24" t="n">
-        <x:v>1511761</x:v>
-      </x:c>
-      <x:c r="K19" s="27" t="n">
+      <x:c r="L27" s="18">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M27" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D28" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E28" s="14" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G28" s="14" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H28" s="16">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I28" s="19">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J28" s="15" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K28" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L19" s="28">
-        <x:v>46090.2765740741</x:v>
-      </x:c>
-      <x:c r="M19" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="23" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C20" s="23" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="D20" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E20" s="23" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="F20" s="23" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="G20" s="23" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="H20" s="25">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I20" s="25">
-        <x:v>46085.1662615741</x:v>
-      </x:c>
-      <x:c r="J20" s="24" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K20" s="27" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L20" s="28">
-        <x:v>46090.3437268519</x:v>
-      </x:c>
-      <x:c r="M20" s="23" t="s">
-        <x:v>154</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="23" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C21" s="23" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="D21" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E21" s="23" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="F21" s="23" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="G21" s="23" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="H21" s="25">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I21" s="25">
-        <x:v>46085.1709375</x:v>
-      </x:c>
-      <x:c r="J21" s="24" t="n">
-        <x:v>1507965</x:v>
-      </x:c>
-      <x:c r="K21" s="27" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L21" s="28">
-        <x:v>46090.3336921296</x:v>
-      </x:c>
-      <x:c r="M21" s="23" t="s">
-        <x:v>154</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="23" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C22" s="23" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="D22" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E22" s="23" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="F22" s="23" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="G22" s="23" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="H22" s="25">
-        <x:v>46084.1080324074</x:v>
-      </x:c>
-      <x:c r="I22" s="26">
-        <x:v>46103</x:v>
-      </x:c>
-      <x:c r="J22" s="24" t="n">
-        <x:v>1511208</x:v>
-      </x:c>
-      <x:c r="K22" s="27" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="28">
-        <x:v>46097.2478125</x:v>
-      </x:c>
-      <x:c r="M22" s="23" t="s">
-        <x:v>107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="23" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C23" s="23" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="D23" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E23" s="23" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="F23" s="23" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="G23" s="23" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="H23" s="25">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I23" s="26">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J23" s="24" t="n">
-        <x:v>1511639</x:v>
-      </x:c>
-      <x:c r="K23" s="27" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="28">
-        <x:v>46083.104224537</x:v>
-      </x:c>
-      <x:c r="M23" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="23" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C24" s="23" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="D24" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E24" s="23" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="F24" s="23" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="G24" s="23" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="H24" s="25">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I24" s="26">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="J24" s="24" t="n">
-        <x:v>1511758</x:v>
-      </x:c>
-      <x:c r="K24" s="27" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L24" s="28">
-        <x:v>46090.2691087963</x:v>
-      </x:c>
-      <x:c r="M24" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="23" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C25" s="23" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="D25" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E25" s="23" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="F25" s="23" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="G25" s="23" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="H25" s="25">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I25" s="26">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J25" s="24" t="n">
-        <x:v>1511759</x:v>
-      </x:c>
-      <x:c r="K25" s="27" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L25" s="28">
-        <x:v>46090.2703703704</x:v>
-      </x:c>
-      <x:c r="M25" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="23" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C26" s="23" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="D26" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E26" s="23" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="F26" s="23" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="G26" s="23" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="H26" s="25">
-        <x:v>46087.1643287037</x:v>
-      </x:c>
-      <x:c r="I26" s="26">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="J26" s="24" t="n">
-        <x:v>1511760</x:v>
-      </x:c>
-      <x:c r="K26" s="27" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="28">
+      <x:c r="L28" s="18">
         <x:v>46090.2727777778</x:v>
       </x:c>
-      <x:c r="M26" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B27" s="29" t="s"/>
-      <x:c r="C27" s="29" t="s"/>
-      <x:c r="D27" s="29" t="s"/>
-      <x:c r="E27" s="29" t="s"/>
-      <x:c r="F27" s="29" t="s"/>
-      <x:c r="G27" s="29" t="s"/>
-      <x:c r="H27" s="29" t="s"/>
-      <x:c r="I27" s="29" t="s"/>
-      <x:c r="J27" s="29" t="s"/>
-      <x:c r="K27" s="29" t="s"/>
-      <x:c r="L27" s="29" t="s"/>
-      <x:c r="M27" s="29" t="s"/>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B28" s="29" t="s"/>
-      <x:c r="C28" s="29" t="s"/>
-      <x:c r="D28" s="29" t="s"/>
-      <x:c r="E28" s="29" t="s"/>
-      <x:c r="F28" s="29" t="s"/>
-      <x:c r="G28" s="29" t="s"/>
-      <x:c r="H28" s="29" t="s"/>
-      <x:c r="I28" s="29" t="s"/>
-      <x:c r="J28" s="29" t="s"/>
-      <x:c r="K28" s="29" t="s"/>
-      <x:c r="L28" s="29" t="s"/>
-      <x:c r="M28" s="29" t="s"/>
+      <x:c r="M28" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="31" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B31" s="30" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C31" s="31" t="s"/>
-      <x:c r="D31" s="31" t="s"/>
-      <x:c r="E31" s="32" t="s"/>
-      <x:c r="F31" s="32" t="s"/>
+      <x:c r="B31" s="20" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C31" s="21" t="s"/>
+      <x:c r="D31" s="21" t="s"/>
+      <x:c r="E31" s="22" t="s"/>
+      <x:c r="F31" s="22" t="s"/>
     </x:row>
     <x:row r="32" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B32" s="33" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C32" s="34" t="s"/>
-      <x:c r="D32" s="34" t="s"/>
-      <x:c r="E32" s="34" t="s"/>
-      <x:c r="F32" s="35" t="s">
-        <x:v>93</x:v>
+      <x:c r="B32" s="23" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C32" s="24" t="s"/>
+      <x:c r="D32" s="24" t="s"/>
+      <x:c r="E32" s="24" t="s"/>
+      <x:c r="F32" s="25" t="s">
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="36" t="s">
+      <x:c r="B33" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C33" s="27" t="s"/>
+      <x:c r="D33" s="27" t="s"/>
+      <x:c r="E33" s="27" t="s"/>
+      <x:c r="F33" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C33" s="37" t="s"/>
-      <x:c r="D33" s="37" t="s"/>
-      <x:c r="E33" s="37" t="s"/>
-      <x:c r="F33" s="38" t="n">
+    </x:row>
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="26" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C34" s="27" t="s"/>
+      <x:c r="D34" s="27" t="s"/>
+      <x:c r="E34" s="27" t="s"/>
+      <x:c r="F34" s="28" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="26" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C35" s="27" t="s"/>
+      <x:c r="D35" s="27" t="s"/>
+      <x:c r="E35" s="27" t="s"/>
+      <x:c r="F35" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="36" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C34" s="37" t="s"/>
-      <x:c r="D34" s="37" t="s"/>
-      <x:c r="E34" s="37" t="s"/>
-      <x:c r="F34" s="38" t="n">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="36" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C35" s="37" t="s"/>
-      <x:c r="D35" s="37" t="s"/>
-      <x:c r="E35" s="37" t="s"/>
-      <x:c r="F35" s="38" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
     <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="36" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C36" s="37" t="s"/>
-      <x:c r="D36" s="37" t="s"/>
-      <x:c r="E36" s="37" t="s"/>
-      <x:c r="F36" s="38" t="n">
+      <x:c r="B36" s="26" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C36" s="27" t="s"/>
+      <x:c r="D36" s="27" t="s"/>
+      <x:c r="E36" s="27" t="s"/>
+      <x:c r="F36" s="28" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B37" s="39" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C37" s="40" t="s"/>
-      <x:c r="D37" s="40" t="s"/>
-      <x:c r="E37" s="40" t="s"/>
-      <x:c r="F37" s="41" t="n">
+      <x:c r="B37" s="29" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C37" s="30" t="s"/>
+      <x:c r="D37" s="30" t="s"/>
+      <x:c r="E37" s="30" t="s"/>
+      <x:c r="F37" s="31" t="n">
         <x:v>21</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="186">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -31,6 +31,9 @@
     <x:t>ENGR. GALELEO MENDOZA</x:t>
   </x:si>
   <x:si>
+    <x:t>IV-A | February 2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>Application Type</x:t>
   </x:si>
   <x:si>
@@ -344,6 +347,9 @@
   </x:si>
   <x:si>
     <x:t>TOTAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IV-A | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>HERALD BEBIS</x:t>
@@ -590,7 +596,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -630,6 +636,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -901,14 +931,23 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -921,59 +960,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1004,91 +1043,103 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1317,58 +1368,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -1411,908 +1462,908 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s"/>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="G8" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46069.0835185185</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="15">
         <x:v>46069.1006712963</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1506161</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>46069.1133333333</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>19</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46069.0835648148</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46069.1000231481</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1506159</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46069.1128587963</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s"/>
-      <x:c r="E9" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H9" s="12">
-        <x:v>46069.0835648148</x:v>
-      </x:c>
-      <x:c r="I9" s="12">
-        <x:v>46069.1000231481</x:v>
-      </x:c>
-      <x:c r="J9" s="11" t="n">
-        <x:v>1506159</x:v>
-      </x:c>
-      <x:c r="K9" s="13" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L9" s="12">
-        <x:v>46069.1128587963</x:v>
-      </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="B10" s="17" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
+      <x:c r="C10" s="17" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="D10" s="18" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="E10" s="17" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="F10" s="17" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="G10" s="17" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
         <x:v>46067.3600231481</x:v>
       </x:c>
-      <x:c r="I10" s="16">
+      <x:c r="I10" s="19">
         <x:v>46067.3600462963</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="n">
+      <x:c r="J10" s="18" t="n">
         <x:v>1505803</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K10" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="21">
         <x:v>46079.2730092593</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>30</x:v>
+      <x:c r="M10" s="17" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
+      <x:c r="B11" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
+        <x:v>46067.1596643518</x:v>
+      </x:c>
+      <x:c r="I11" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1505804</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="21">
+        <x:v>46079.2772569444</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C11" s="14" t="s">
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="17" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
+      <x:c r="C12" s="17" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46067.1596643518</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="E12" s="17" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
+        <x:v>46067.2222106481</x:v>
+      </x:c>
+      <x:c r="I12" s="22">
+        <x:v>46089</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="n">
+        <x:v>1505805</x:v>
+      </x:c>
+      <x:c r="K12" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="21">
+        <x:v>46079.2763078704</x:v>
+      </x:c>
+      <x:c r="M12" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E13" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H13" s="19">
+        <x:v>46063.1352777778</x:v>
+      </x:c>
+      <x:c r="I13" s="22">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="n">
+        <x:v>1511010</x:v>
+      </x:c>
+      <x:c r="K13" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="21">
+        <x:v>46063.2367708333</x:v>
+      </x:c>
+      <x:c r="M13" s="17" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="17" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E14" s="17" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H14" s="19">
+        <x:v>46079.3584722222</x:v>
+      </x:c>
+      <x:c r="I14" s="19">
+        <x:v>46079.3584953704</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="n">
+        <x:v>1511622</x:v>
+      </x:c>
+      <x:c r="K14" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L14" s="21">
+        <x:v>46080.2311226852</x:v>
+      </x:c>
+      <x:c r="M14" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="17" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E15" s="17" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F15" s="17" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H15" s="19">
+        <x:v>46079.3539699074</x:v>
+      </x:c>
+      <x:c r="I15" s="19">
+        <x:v>46079.3539814815</x:v>
+      </x:c>
+      <x:c r="J15" s="18" t="n">
+        <x:v>1511627</x:v>
+      </x:c>
+      <x:c r="K15" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L15" s="21">
+        <x:v>46080.2440856481</x:v>
+      </x:c>
+      <x:c r="M15" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D16" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E16" s="17" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G16" s="17" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H16" s="19">
+        <x:v>46079.3873148148</x:v>
+      </x:c>
+      <x:c r="I16" s="22">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1505804</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="J16" s="18" t="n">
+        <x:v>1511623</x:v>
+      </x:c>
+      <x:c r="K16" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46079.2772569444</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46067.2222106481</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>46089</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1505805</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="L16" s="21">
+        <x:v>46080.2360763889</x:v>
+      </x:c>
+      <x:c r="M16" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C17" s="17" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D17" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E17" s="17" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F17" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G17" s="17" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H17" s="19">
+        <x:v>46079.2523032407</x:v>
+      </x:c>
+      <x:c r="I17" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J17" s="18" t="n">
+        <x:v>1511631</x:v>
+      </x:c>
+      <x:c r="K17" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46079.2763078704</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46063.1352777778</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="n">
-        <x:v>1511010</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
+      <x:c r="L17" s="21">
+        <x:v>46080.2925810185</x:v>
+      </x:c>
+      <x:c r="M17" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C18" s="17" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E18" s="17" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F18" s="17" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G18" s="17" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H18" s="19">
+        <x:v>46079.2430555556</x:v>
+      </x:c>
+      <x:c r="I18" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J18" s="18" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K18" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46063.2367708333</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46079.3584722222</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46079.3584953704</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="n">
-        <x:v>1511622</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46080.2311226852</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
+      <x:c r="L18" s="21">
+        <x:v>46080.2801273148</x:v>
+      </x:c>
+      <x:c r="M18" s="17" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46079.3539699074</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46079.3539814815</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="n">
-        <x:v>1511627</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46080.2440856481</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="17" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46079.3873148148</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
+      <x:c r="C19" s="17" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D19" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E19" s="17" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F19" s="17" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G19" s="17" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H19" s="19">
+        <x:v>46079.3651967593</x:v>
+      </x:c>
+      <x:c r="I19" s="22">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J16" s="15" t="n">
-        <x:v>1511623</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
+      <x:c r="J19" s="18" t="n">
+        <x:v>1511626</x:v>
+      </x:c>
+      <x:c r="K19" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="18">
-        <x:v>46080.2360763889</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46079.2523032407</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
+      <x:c r="L19" s="21">
+        <x:v>46080.2425462963</x:v>
+      </x:c>
+      <x:c r="M19" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C20" s="17" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D20" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E20" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F20" s="17" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G20" s="17" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H20" s="19">
+        <x:v>46080.2923611111</x:v>
+      </x:c>
+      <x:c r="I20" s="22">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J17" s="15" t="n">
-        <x:v>1511631</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
+      <x:c r="J20" s="18" t="n">
+        <x:v>1511635</x:v>
+      </x:c>
+      <x:c r="K20" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46080.2925810185</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46079.2430555556</x:v>
-      </x:c>
-      <x:c r="I18" s="19">
+      <x:c r="L20" s="21">
+        <x:v>46080.3208564815</x:v>
+      </x:c>
+      <x:c r="M20" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C21" s="17" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D21" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E21" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F21" s="17" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G21" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H21" s="19">
+        <x:v>46079.31625</x:v>
+      </x:c>
+      <x:c r="I21" s="22">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J18" s="15" t="n">
+      <x:c r="J21" s="18" t="n">
         <x:v>1511630</x:v>
       </x:c>
-      <x:c r="K18" s="17" t="n">
+      <x:c r="K21" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="18">
-        <x:v>46080.2801273148</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46079.3651967593</x:v>
-      </x:c>
-      <x:c r="I19" s="19">
+      <x:c r="L21" s="21">
+        <x:v>46080.2883680556</x:v>
+      </x:c>
+      <x:c r="M21" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C22" s="17" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D22" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E22" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F22" s="17" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G22" s="17" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H22" s="19">
+        <x:v>46079.3059375</x:v>
+      </x:c>
+      <x:c r="I22" s="22">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J19" s="15" t="n">
-        <x:v>1511626</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
+      <x:c r="J22" s="18" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K22" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L19" s="18">
-        <x:v>46080.2425462963</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
+      <x:c r="L22" s="21">
+        <x:v>46080.2896875</x:v>
+      </x:c>
+      <x:c r="M22" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C23" s="17" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D23" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E23" s="17" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46080.2923611111</x:v>
-      </x:c>
-      <x:c r="I20" s="19">
+      <x:c r="F23" s="17" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G23" s="17" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H23" s="19">
+        <x:v>46079.2943981482</x:v>
+      </x:c>
+      <x:c r="I23" s="22">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J20" s="15" t="n">
-        <x:v>1511635</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="n">
+      <x:c r="J23" s="18" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K23" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L20" s="18">
-        <x:v>46080.3208564815</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46079.31625</x:v>
-      </x:c>
-      <x:c r="I21" s="19">
+      <x:c r="L23" s="21">
+        <x:v>46080.2916782407</x:v>
+      </x:c>
+      <x:c r="M23" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C24" s="17" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D24" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E24" s="17" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F24" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G24" s="17" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H24" s="19">
+        <x:v>46079.378900463</x:v>
+      </x:c>
+      <x:c r="I24" s="22">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J21" s="15" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K21" s="17" t="n">
+      <x:c r="J24" s="18" t="n">
+        <x:v>1511624</x:v>
+      </x:c>
+      <x:c r="K24" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L21" s="18">
-        <x:v>46080.2883680556</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46079.3059375</x:v>
-      </x:c>
-      <x:c r="I22" s="19">
+      <x:c r="L24" s="21">
+        <x:v>46080.2376041667</x:v>
+      </x:c>
+      <x:c r="M24" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C25" s="17" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D25" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E25" s="17" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F25" s="17" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G25" s="17" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H25" s="19">
+        <x:v>46079.3728240741</x:v>
+      </x:c>
+      <x:c r="I25" s="22">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J22" s="15" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K22" s="17" t="n">
+      <x:c r="J25" s="18" t="n">
+        <x:v>1511625</x:v>
+      </x:c>
+      <x:c r="K25" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L22" s="18">
-        <x:v>46080.2896875</x:v>
-      </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46079.2943981482</x:v>
-      </x:c>
-      <x:c r="I23" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K23" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="18">
-        <x:v>46080.2916782407</x:v>
-      </x:c>
-      <x:c r="M23" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="H24" s="16">
-        <x:v>46079.378900463</x:v>
-      </x:c>
-      <x:c r="I24" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J24" s="15" t="n">
-        <x:v>1511624</x:v>
-      </x:c>
-      <x:c r="K24" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L24" s="18">
-        <x:v>46080.2376041667</x:v>
-      </x:c>
-      <x:c r="M24" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C25" s="14" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D25" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E25" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F25" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G25" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="H25" s="16">
-        <x:v>46079.3728240741</x:v>
-      </x:c>
-      <x:c r="I25" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J25" s="15" t="n">
-        <x:v>1511625</x:v>
-      </x:c>
-      <x:c r="K25" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L25" s="18">
+      <x:c r="L25" s="21">
         <x:v>46080.2394328704</x:v>
       </x:c>
-      <x:c r="M25" s="14" t="s">
-        <x:v>51</x:v>
+      <x:c r="M25" s="17" t="s">
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="14" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C26" s="14" t="s">
+      <x:c r="B26" s="17" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="D26" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E26" s="14" t="s">
+      <x:c r="C26" s="17" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="F26" s="14" t="s">
+      <x:c r="D26" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E26" s="17" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="G26" s="14" t="s">
+      <x:c r="F26" s="17" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="H26" s="16">
+      <x:c r="G26" s="17" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H26" s="19">
         <x:v>46062.1590162037</x:v>
       </x:c>
-      <x:c r="I26" s="16">
+      <x:c r="I26" s="19">
         <x:v>46062.1590277778</x:v>
       </x:c>
-      <x:c r="J26" s="15" t="n">
+      <x:c r="J26" s="18" t="n">
         <x:v>1510925</x:v>
       </x:c>
-      <x:c r="K26" s="17" t="n">
+      <x:c r="K26" s="20" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L26" s="18">
+      <x:c r="L26" s="21">
         <x:v>46062.1863194444</x:v>
       </x:c>
-      <x:c r="M26" s="14" t="s">
-        <x:v>51</x:v>
+      <x:c r="M26" s="17" t="s">
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="14" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C27" s="14" t="s">
+      <x:c r="B27" s="17" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="D27" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E27" s="14" t="s">
+      <x:c r="C27" s="17" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F27" s="14" t="s">
+      <x:c r="D27" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E27" s="17" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="G27" s="14" t="s">
+      <x:c r="F27" s="17" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="H27" s="16">
+      <x:c r="G27" s="17" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H27" s="19">
         <x:v>46071.0492476852</x:v>
       </x:c>
-      <x:c r="I27" s="19">
+      <x:c r="I27" s="22">
         <x:v>46052</x:v>
       </x:c>
-      <x:c r="J27" s="15" t="n">
+      <x:c r="J27" s="18" t="n">
         <x:v>1511502</x:v>
       </x:c>
-      <x:c r="K27" s="17" t="n">
+      <x:c r="K27" s="20" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L27" s="18">
+      <x:c r="L27" s="21">
         <x:v>46071.0606134259</x:v>
       </x:c>
-      <x:c r="M27" s="14" t="s">
-        <x:v>51</x:v>
+      <x:c r="M27" s="17" t="s">
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B30" s="20" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C30" s="21" t="s"/>
-      <x:c r="D30" s="21" t="s"/>
-      <x:c r="E30" s="22" t="s"/>
-      <x:c r="F30" s="22" t="s"/>
+      <x:c r="B30" s="23" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C30" s="24" t="s"/>
+      <x:c r="D30" s="24" t="s"/>
+      <x:c r="E30" s="25" t="s"/>
+      <x:c r="F30" s="25" t="s"/>
     </x:row>
     <x:row r="31" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B31" s="23" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="C31" s="24" t="s"/>
-      <x:c r="D31" s="24" t="s"/>
-      <x:c r="E31" s="24" t="s"/>
-      <x:c r="F31" s="25" t="s">
+      <x:c r="B31" s="26" t="s">
         <x:v>105</x:v>
       </x:c>
+      <x:c r="C31" s="27" t="s"/>
+      <x:c r="D31" s="27" t="s"/>
+      <x:c r="E31" s="27" t="s"/>
+      <x:c r="F31" s="28" t="s">
+        <x:v>106</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="26" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C32" s="27" t="s"/>
-      <x:c r="D32" s="27" t="s"/>
-      <x:c r="E32" s="27" t="s"/>
-      <x:c r="F32" s="28" t="n">
+      <x:c r="B32" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C32" s="30" t="s"/>
+      <x:c r="D32" s="30" t="s"/>
+      <x:c r="E32" s="30" t="s"/>
+      <x:c r="F32" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="26" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C33" s="27" t="s"/>
-      <x:c r="D33" s="27" t="s"/>
-      <x:c r="E33" s="27" t="s"/>
-      <x:c r="F33" s="28" t="n">
+      <x:c r="B33" s="29" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C33" s="30" t="s"/>
+      <x:c r="D33" s="30" t="s"/>
+      <x:c r="E33" s="30" t="s"/>
+      <x:c r="F33" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="26" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C34" s="27" t="s"/>
-      <x:c r="D34" s="27" t="s"/>
-      <x:c r="E34" s="27" t="s"/>
-      <x:c r="F34" s="28" t="n">
+      <x:c r="B34" s="29" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C34" s="30" t="s"/>
+      <x:c r="D34" s="30" t="s"/>
+      <x:c r="E34" s="30" t="s"/>
+      <x:c r="F34" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="26" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C35" s="27" t="s"/>
-      <x:c r="D35" s="27" t="s"/>
-      <x:c r="E35" s="27" t="s"/>
-      <x:c r="F35" s="28" t="n">
+      <x:c r="B35" s="29" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C35" s="30" t="s"/>
+      <x:c r="D35" s="30" t="s"/>
+      <x:c r="E35" s="30" t="s"/>
+      <x:c r="F35" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="26" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C36" s="27" t="s"/>
-      <x:c r="D36" s="27" t="s"/>
-      <x:c r="E36" s="27" t="s"/>
-      <x:c r="F36" s="28" t="n">
+      <x:c r="B36" s="29" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C36" s="30" t="s"/>
+      <x:c r="D36" s="30" t="s"/>
+      <x:c r="E36" s="30" t="s"/>
+      <x:c r="F36" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B37" s="26" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C37" s="27" t="s"/>
-      <x:c r="D37" s="27" t="s"/>
-      <x:c r="E37" s="27" t="s"/>
-      <x:c r="F37" s="28" t="n">
+      <x:c r="B37" s="29" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C37" s="30" t="s"/>
+      <x:c r="D37" s="30" t="s"/>
+      <x:c r="E37" s="30" t="s"/>
+      <x:c r="F37" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B38" s="26" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C38" s="27" t="s"/>
-      <x:c r="D38" s="27" t="s"/>
-      <x:c r="E38" s="27" t="s"/>
-      <x:c r="F38" s="28" t="n">
+      <x:c r="B38" s="29" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C38" s="30" t="s"/>
+      <x:c r="D38" s="30" t="s"/>
+      <x:c r="E38" s="30" t="s"/>
+      <x:c r="F38" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B39" s="29" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="C39" s="30" t="s"/>
-      <x:c r="D39" s="30" t="s"/>
-      <x:c r="E39" s="30" t="s"/>
-      <x:c r="F39" s="31" t="n">
+      <x:c r="B39" s="32" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C39" s="33" t="s"/>
+      <x:c r="D39" s="33" t="s"/>
+      <x:c r="E39" s="33" t="s"/>
+      <x:c r="F39" s="34" t="n">
         <x:v>20</x:v>
       </x:c>
     </x:row>
@@ -3274,7 +3325,7 @@
   <x:mergeCells count="13">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B30:F30"/>
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
@@ -3325,58 +3376,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -3419,913 +3470,913 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s"/>
-      <x:c r="E8" s="11" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="F8" s="14" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46091.306099537</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="15">
         <x:v>46091.3107986111</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1511778</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>46091.3131828704</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>51</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s"/>
-      <x:c r="E9" s="11" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="F9" s="14" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>46093.1459375</x:v>
       </x:c>
-      <x:c r="I9" s="12">
+      <x:c r="I9" s="15">
         <x:v>46093.1585185185</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1511815</x:v>
       </x:c>
-      <x:c r="K9" s="13" t="n">
+      <x:c r="K9" s="16" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="15">
         <x:v>46093.159537037</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>51</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="B10" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="D10" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E10" s="17" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="F10" s="17" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
         <x:v>46080.4532523148</x:v>
       </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="I10" s="22">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="n">
+      <x:c r="J10" s="18" t="n">
         <x:v>1511232</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K10" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="21">
         <x:v>46097.1461689815</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>119</x:v>
+      <x:c r="M10" s="17" t="s">
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="B11" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
+        <x:v>46083.2380439815</x:v>
+      </x:c>
+      <x:c r="I11" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1511234</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="21">
+        <x:v>46097.1564351852</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46083.2380439815</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
+        <x:v>46083.2599189815</x:v>
+      </x:c>
+      <x:c r="I12" s="22">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="n">
+        <x:v>1511237</x:v>
+      </x:c>
+      <x:c r="K12" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="21">
+        <x:v>46097.1652314815</x:v>
+      </x:c>
+      <x:c r="M12" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E13" s="17" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H13" s="19">
+        <x:v>46084.0854513889</x:v>
+      </x:c>
+      <x:c r="I13" s="22">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="n">
+        <x:v>1511225</x:v>
+      </x:c>
+      <x:c r="K13" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="21">
+        <x:v>46093.3956365741</x:v>
+      </x:c>
+      <x:c r="M13" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E14" s="17" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H14" s="19">
+        <x:v>46084.0996759259</x:v>
+      </x:c>
+      <x:c r="I14" s="22">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="n">
+        <x:v>1511192</x:v>
+      </x:c>
+      <x:c r="K14" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="21">
+        <x:v>46097.2414583333</x:v>
+      </x:c>
+      <x:c r="M14" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E15" s="17" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="F15" s="17" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="H15" s="19">
+        <x:v>46069.1542013889</x:v>
+      </x:c>
+      <x:c r="I15" s="22">
+        <x:v>46035</x:v>
+      </x:c>
+      <x:c r="J15" s="18" t="n">
+        <x:v>1511206</x:v>
+      </x:c>
+      <x:c r="K15" s="20" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L15" s="21">
+        <x:v>46097.2466550926</x:v>
+      </x:c>
+      <x:c r="M15" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D16" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E16" s="17" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G16" s="17" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="H16" s="19">
+        <x:v>46069.2178703704</x:v>
+      </x:c>
+      <x:c r="I16" s="22">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J16" s="18" t="n">
+        <x:v>1511196</x:v>
+      </x:c>
+      <x:c r="K16" s="20" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L16" s="21">
+        <x:v>46097.2456365741</x:v>
+      </x:c>
+      <x:c r="M16" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C17" s="17" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D17" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E17" s="17" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="F17" s="17" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="G17" s="17" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H17" s="19">
+        <x:v>46083.2443865741</x:v>
+      </x:c>
+      <x:c r="I17" s="22">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1511234</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="J17" s="18" t="n">
+        <x:v>1511235</x:v>
+      </x:c>
+      <x:c r="K17" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46097.1564351852</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>119</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46083.2599189815</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>46101</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1511237</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="L17" s="21">
+        <x:v>46097.1600115741</x:v>
+      </x:c>
+      <x:c r="M17" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C18" s="17" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E18" s="17" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="F18" s="17" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="G18" s="17" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="H18" s="19">
+        <x:v>46084.1225115741</x:v>
+      </x:c>
+      <x:c r="I18" s="22">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J18" s="18" t="n">
+        <x:v>1511242</x:v>
+      </x:c>
+      <x:c r="K18" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46097.1652314815</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>119</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="L18" s="21">
+        <x:v>46097.3505092593</x:v>
+      </x:c>
+      <x:c r="M18" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C19" s="17" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D19" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E19" s="17" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F19" s="17" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G19" s="17" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H19" s="19">
+        <x:v>46083.2521064815</x:v>
+      </x:c>
+      <x:c r="I19" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J19" s="18" t="n">
+        <x:v>1511236</x:v>
+      </x:c>
+      <x:c r="K19" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="21">
+        <x:v>46097.1628935185</x:v>
+      </x:c>
+      <x:c r="M19" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C20" s="17" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D20" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E20" s="17" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="F20" s="17" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="G20" s="17" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="H20" s="19">
+        <x:v>46069.115150463</x:v>
+      </x:c>
+      <x:c r="I20" s="22">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J20" s="18" t="n">
+        <x:v>1511241</x:v>
+      </x:c>
+      <x:c r="K20" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="21">
+        <x:v>46097.3433796296</x:v>
+      </x:c>
+      <x:c r="M20" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C21" s="17" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D21" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E21" s="17" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="F21" s="17" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="G21" s="17" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H21" s="19">
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I21" s="22">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="J21" s="18" t="n">
+        <x:v>1511761</x:v>
+      </x:c>
+      <x:c r="K21" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="21">
+        <x:v>46090.2765740741</x:v>
+      </x:c>
+      <x:c r="M21" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="17" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C22" s="17" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D22" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E22" s="17" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F22" s="17" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G22" s="17" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="H22" s="19">
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I22" s="19">
+        <x:v>46085.1662615741</x:v>
+      </x:c>
+      <x:c r="J22" s="18" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K22" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L22" s="21">
+        <x:v>46090.3437268519</x:v>
+      </x:c>
+      <x:c r="M22" s="17" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="17" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C23" s="17" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D23" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E23" s="17" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="F23" s="17" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G23" s="17" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="H23" s="19">
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I23" s="19">
+        <x:v>46085.1709375</x:v>
+      </x:c>
+      <x:c r="J23" s="18" t="n">
+        <x:v>1507965</x:v>
+      </x:c>
+      <x:c r="K23" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L23" s="21">
+        <x:v>46090.3336921296</x:v>
+      </x:c>
+      <x:c r="M23" s="17" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C24" s="17" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46084.0854513889</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="n">
-        <x:v>1511225</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
+      <x:c r="D24" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E24" s="17" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F24" s="17" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G24" s="17" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H24" s="19">
+        <x:v>46084.1080324074</x:v>
+      </x:c>
+      <x:c r="I24" s="22">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J24" s="18" t="n">
+        <x:v>1511208</x:v>
+      </x:c>
+      <x:c r="K24" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46093.3956365741</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>119</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46084.0996759259</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="n">
-        <x:v>1511192</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
+      <x:c r="L24" s="21">
+        <x:v>46097.2478125</x:v>
+      </x:c>
+      <x:c r="M24" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C25" s="17" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D25" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E25" s="17" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="F25" s="17" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="G25" s="17" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="H25" s="19">
+        <x:v>46083.0787962963</x:v>
+      </x:c>
+      <x:c r="I25" s="22">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J25" s="18" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K25" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46097.2414583333</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>119</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46069.1542013889</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
-        <x:v>46035</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="n">
-        <x:v>1511206</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46097.2466550926</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>119</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46069.2178703704</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
-        <x:v>46051</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="n">
-        <x:v>1511196</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L16" s="18">
-        <x:v>46097.2456365741</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>119</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46083.2443865741</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="n">
-        <x:v>1511235</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
+      <x:c r="L25" s="21">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M25" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C26" s="17" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D26" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E26" s="17" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="F26" s="17" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G26" s="17" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="H26" s="19">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I26" s="22">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J26" s="18" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K26" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46097.1600115741</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>119</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46084.1225115741</x:v>
-      </x:c>
-      <x:c r="I18" s="19">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="n">
-        <x:v>1511242</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
+      <x:c r="L26" s="21">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M26" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C27" s="17" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D27" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E27" s="17" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="F27" s="17" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="G27" s="17" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="H27" s="19">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I27" s="22">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J27" s="18" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K27" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="18">
-        <x:v>46097.3505092593</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>119</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46083.2521064815</x:v>
-      </x:c>
-      <x:c r="I19" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="n">
-        <x:v>1511236</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
+      <x:c r="L27" s="21">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M27" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C28" s="17" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D28" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E28" s="17" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="F28" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="G28" s="17" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="H28" s="19">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I28" s="22">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J28" s="18" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K28" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L19" s="18">
-        <x:v>46097.1628935185</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>119</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46069.115150463</x:v>
-      </x:c>
-      <x:c r="I20" s="19">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="n">
-        <x:v>1511241</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="18">
-        <x:v>46097.3433796296</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>119</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I21" s="19">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="n">
-        <x:v>1511761</x:v>
-      </x:c>
-      <x:c r="K21" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="18">
-        <x:v>46090.2765740741</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I22" s="16">
-        <x:v>46085.1662615741</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K22" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L22" s="18">
-        <x:v>46090.3437268519</x:v>
-      </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>166</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I23" s="16">
-        <x:v>46085.1709375</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="n">
-        <x:v>1507965</x:v>
-      </x:c>
-      <x:c r="K23" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L23" s="18">
-        <x:v>46090.3336921296</x:v>
-      </x:c>
-      <x:c r="M23" s="14" t="s">
-        <x:v>166</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="H24" s="16">
-        <x:v>46084.1080324074</x:v>
-      </x:c>
-      <x:c r="I24" s="19">
-        <x:v>46103</x:v>
-      </x:c>
-      <x:c r="J24" s="15" t="n">
-        <x:v>1511208</x:v>
-      </x:c>
-      <x:c r="K24" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L24" s="18">
-        <x:v>46097.2478125</x:v>
-      </x:c>
-      <x:c r="M24" s="14" t="s">
-        <x:v>119</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C25" s="14" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="D25" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E25" s="14" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="F25" s="14" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="G25" s="14" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="H25" s="16">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I25" s="19">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J25" s="15" t="n">
-        <x:v>1511639</x:v>
-      </x:c>
-      <x:c r="K25" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L25" s="18">
-        <x:v>46083.104224537</x:v>
-      </x:c>
-      <x:c r="M25" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C26" s="14" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="D26" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E26" s="14" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="F26" s="14" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="G26" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="H26" s="16">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I26" s="19">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="J26" s="15" t="n">
-        <x:v>1511758</x:v>
-      </x:c>
-      <x:c r="K26" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="18">
-        <x:v>46090.2691087963</x:v>
-      </x:c>
-      <x:c r="M26" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C27" s="14" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="D27" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E27" s="14" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="F27" s="14" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="G27" s="14" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="H27" s="16">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I27" s="19">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J27" s="15" t="n">
-        <x:v>1511759</x:v>
-      </x:c>
-      <x:c r="K27" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="18">
-        <x:v>46090.2703703704</x:v>
-      </x:c>
-      <x:c r="M27" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C28" s="14" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="D28" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E28" s="14" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="F28" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="G28" s="14" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="H28" s="16">
-        <x:v>46087.1643287037</x:v>
-      </x:c>
-      <x:c r="I28" s="19">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="J28" s="15" t="n">
-        <x:v>1511760</x:v>
-      </x:c>
-      <x:c r="K28" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="18">
+      <x:c r="L28" s="21">
         <x:v>46090.2727777778</x:v>
       </x:c>
-      <x:c r="M28" s="14" t="s">
-        <x:v>51</x:v>
+      <x:c r="M28" s="17" t="s">
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="31" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B31" s="20" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C31" s="21" t="s"/>
-      <x:c r="D31" s="21" t="s"/>
-      <x:c r="E31" s="22" t="s"/>
-      <x:c r="F31" s="22" t="s"/>
+      <x:c r="B31" s="23" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C31" s="24" t="s"/>
+      <x:c r="D31" s="24" t="s"/>
+      <x:c r="E31" s="25" t="s"/>
+      <x:c r="F31" s="25" t="s"/>
     </x:row>
     <x:row r="32" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B32" s="23" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="C32" s="24" t="s"/>
-      <x:c r="D32" s="24" t="s"/>
-      <x:c r="E32" s="24" t="s"/>
-      <x:c r="F32" s="25" t="s">
+      <x:c r="B32" s="26" t="s">
         <x:v>105</x:v>
       </x:c>
+      <x:c r="C32" s="27" t="s"/>
+      <x:c r="D32" s="27" t="s"/>
+      <x:c r="E32" s="27" t="s"/>
+      <x:c r="F32" s="28" t="s">
+        <x:v>106</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="26" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C33" s="27" t="s"/>
-      <x:c r="D33" s="27" t="s"/>
-      <x:c r="E33" s="27" t="s"/>
-      <x:c r="F33" s="28" t="n">
+      <x:c r="B33" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C33" s="30" t="s"/>
+      <x:c r="D33" s="30" t="s"/>
+      <x:c r="E33" s="30" t="s"/>
+      <x:c r="F33" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="26" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C34" s="27" t="s"/>
-      <x:c r="D34" s="27" t="s"/>
-      <x:c r="E34" s="27" t="s"/>
-      <x:c r="F34" s="28" t="n">
+      <x:c r="B34" s="29" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C34" s="30" t="s"/>
+      <x:c r="D34" s="30" t="s"/>
+      <x:c r="E34" s="30" t="s"/>
+      <x:c r="F34" s="31" t="n">
         <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="26" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C35" s="27" t="s"/>
-      <x:c r="D35" s="27" t="s"/>
-      <x:c r="E35" s="27" t="s"/>
-      <x:c r="F35" s="28" t="n">
+      <x:c r="B35" s="29" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C35" s="30" t="s"/>
+      <x:c r="D35" s="30" t="s"/>
+      <x:c r="E35" s="30" t="s"/>
+      <x:c r="F35" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="26" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C36" s="27" t="s"/>
-      <x:c r="D36" s="27" t="s"/>
-      <x:c r="E36" s="27" t="s"/>
-      <x:c r="F36" s="28" t="n">
+      <x:c r="B36" s="29" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C36" s="30" t="s"/>
+      <x:c r="D36" s="30" t="s"/>
+      <x:c r="E36" s="30" t="s"/>
+      <x:c r="F36" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B37" s="29" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="C37" s="30" t="s"/>
-      <x:c r="D37" s="30" t="s"/>
-      <x:c r="E37" s="30" t="s"/>
-      <x:c r="F37" s="31" t="n">
+      <x:c r="B37" s="32" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C37" s="33" t="s"/>
+      <x:c r="D37" s="33" t="s"/>
+      <x:c r="E37" s="33" t="s"/>
+      <x:c r="F37" s="34" t="n">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -5289,7 +5340,7 @@
   <x:mergeCells count="10">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B31:F31"/>
     <x:mergeCell ref="B32:E32"/>
     <x:mergeCell ref="B33:E33"/>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -68,42 +68,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -634,7 +598,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -678,14 +642,6 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
@@ -697,6 +653,21 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -954,7 +925,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -962,16 +933,16 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -983,13 +954,7 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1001,41 +966,50 @@
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1066,28 +1040,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1102,55 +1068,71 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1483,7 +1465,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1523,925 +1505,875 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="H8" s="15">
+        <x:v>46069.0835185185</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46069.1006712963</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1506161</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46069.1133333333</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
+      <x:c r="H9" s="15">
+        <x:v>46069.0835648148</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46069.1000231481</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1506159</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46069.1128587963</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="17" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="M8" s="9" t="s">
+      <x:c r="C10" s="17" t="s">
         <x:v>26</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="D10" s="18" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="E10" s="17" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="F10" s="17" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="G10" s="17" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="H10" s="19">
+        <x:v>46067.3600231481</x:v>
+      </x:c>
+      <x:c r="I10" s="19">
+        <x:v>46067.3600462963</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="n">
+        <x:v>1505803</x:v>
+      </x:c>
+      <x:c r="K10" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L10" s="21">
+        <x:v>46079.2730092593</x:v>
+      </x:c>
+      <x:c r="M10" s="17" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46069.0835185185</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46069.1006712963</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1506161</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46069.1133333333</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="17" t="s">
         <x:v>32</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="C11" s="17" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
+        <x:v>46067.1596643518</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1505804</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="21">
+        <x:v>46079.2772569444</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
+        <x:v>46067.2222106481</x:v>
+      </x:c>
+      <x:c r="I12" s="19">
+        <x:v>46089</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="n">
+        <x:v>1505805</x:v>
+      </x:c>
+      <x:c r="K12" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="21">
+        <x:v>46079.2763078704</x:v>
+      </x:c>
+      <x:c r="M12" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E13" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H13" s="19">
+        <x:v>46063.1352777778</x:v>
+      </x:c>
+      <x:c r="I13" s="19">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="n">
+        <x:v>1511010</x:v>
+      </x:c>
+      <x:c r="K13" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="21">
+        <x:v>46063.2367708333</x:v>
+      </x:c>
+      <x:c r="M13" s="17" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="17" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E14" s="17" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H14" s="19">
+        <x:v>46079.3584722222</x:v>
+      </x:c>
+      <x:c r="I14" s="19">
+        <x:v>46079.3584953704</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="n">
+        <x:v>1511622</x:v>
+      </x:c>
+      <x:c r="K14" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L14" s="21">
+        <x:v>46080.2311226852</x:v>
+      </x:c>
+      <x:c r="M14" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="17" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E15" s="17" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F15" s="17" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H15" s="19">
+        <x:v>46079.3539699074</x:v>
+      </x:c>
+      <x:c r="I15" s="19">
+        <x:v>46079.3539814815</x:v>
+      </x:c>
+      <x:c r="J15" s="18" t="n">
+        <x:v>1511627</x:v>
+      </x:c>
+      <x:c r="K15" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L15" s="21">
+        <x:v>46080.2440856481</x:v>
+      </x:c>
+      <x:c r="M15" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D16" s="18" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>46069.0835648148</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>46069.1000231481</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1506159</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>46069.1128587963</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="E16" s="17" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G16" s="17" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H16" s="19">
+        <x:v>46079.3873148148</x:v>
+      </x:c>
+      <x:c r="I16" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J16" s="18" t="n">
+        <x:v>1511623</x:v>
+      </x:c>
+      <x:c r="K16" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="21">
+        <x:v>46080.2360763889</x:v>
+      </x:c>
+      <x:c r="M16" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C17" s="17" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D17" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E17" s="17" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F17" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G17" s="17" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H17" s="19">
+        <x:v>46079.2523032407</x:v>
+      </x:c>
+      <x:c r="I17" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J17" s="18" t="n">
+        <x:v>1511631</x:v>
+      </x:c>
+      <x:c r="K17" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="21">
+        <x:v>46080.2925810185</x:v>
+      </x:c>
+      <x:c r="M17" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C18" s="17" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E18" s="17" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F18" s="17" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G18" s="17" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H18" s="19">
+        <x:v>46079.2430555556</x:v>
+      </x:c>
+      <x:c r="I18" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J18" s="18" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K18" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="21">
+        <x:v>46080.2801273148</x:v>
+      </x:c>
+      <x:c r="M18" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C19" s="17" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D19" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E19" s="17" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F19" s="17" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G19" s="17" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H19" s="19">
+        <x:v>46079.3651967593</x:v>
+      </x:c>
+      <x:c r="I19" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J19" s="18" t="n">
+        <x:v>1511626</x:v>
+      </x:c>
+      <x:c r="K19" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="21">
+        <x:v>46080.2425462963</x:v>
+      </x:c>
+      <x:c r="M19" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C20" s="17" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D20" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E20" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F20" s="17" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G20" s="17" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H20" s="19">
+        <x:v>46080.2923611111</x:v>
+      </x:c>
+      <x:c r="I20" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J20" s="18" t="n">
+        <x:v>1511635</x:v>
+      </x:c>
+      <x:c r="K20" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="21">
+        <x:v>46080.3208564815</x:v>
+      </x:c>
+      <x:c r="M20" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C21" s="17" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D21" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E21" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F21" s="17" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G21" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H21" s="19">
+        <x:v>46079.31625</x:v>
+      </x:c>
+      <x:c r="I21" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J21" s="18" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K21" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="21">
+        <x:v>46080.2883680556</x:v>
+      </x:c>
+      <x:c r="M21" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C22" s="17" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D22" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E22" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F22" s="17" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G22" s="17" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H22" s="19">
+        <x:v>46079.3059375</x:v>
+      </x:c>
+      <x:c r="I22" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J22" s="18" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K22" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L22" s="21">
+        <x:v>46080.2896875</x:v>
+      </x:c>
+      <x:c r="M22" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C23" s="17" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D23" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E23" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F23" s="17" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G23" s="17" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H23" s="19">
+        <x:v>46079.2943981482</x:v>
+      </x:c>
+      <x:c r="I23" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J23" s="18" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K23" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="21">
+        <x:v>46080.2916782407</x:v>
+      </x:c>
+      <x:c r="M23" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C24" s="17" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D24" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E24" s="17" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F24" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G24" s="17" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H24" s="19">
+        <x:v>46079.378900463</x:v>
+      </x:c>
+      <x:c r="I24" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J24" s="18" t="n">
+        <x:v>1511624</x:v>
+      </x:c>
+      <x:c r="K24" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L24" s="21">
+        <x:v>46080.2376041667</x:v>
+      </x:c>
+      <x:c r="M24" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C25" s="17" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D25" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E25" s="17" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F25" s="17" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G25" s="17" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H25" s="19">
+        <x:v>46079.3728240741</x:v>
+      </x:c>
+      <x:c r="I25" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J25" s="18" t="n">
+        <x:v>1511625</x:v>
+      </x:c>
+      <x:c r="K25" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="21">
+        <x:v>46080.2394328704</x:v>
+      </x:c>
+      <x:c r="M25" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="17" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C26" s="17" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D26" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E26" s="17" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F26" s="17" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G26" s="17" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H26" s="19">
+        <x:v>46062.1590162037</x:v>
+      </x:c>
+      <x:c r="I26" s="19">
+        <x:v>46062.1590277778</x:v>
+      </x:c>
+      <x:c r="J26" s="18" t="n">
+        <x:v>1510925</x:v>
+      </x:c>
+      <x:c r="K26" s="20" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L26" s="21">
+        <x:v>46062.1863194444</x:v>
+      </x:c>
+      <x:c r="M26" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="17" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C27" s="17" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D27" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E27" s="17" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F27" s="17" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G27" s="17" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H27" s="19">
+        <x:v>46071.0492476852</x:v>
+      </x:c>
+      <x:c r="I27" s="19">
+        <x:v>46052</x:v>
+      </x:c>
+      <x:c r="J27" s="18" t="n">
+        <x:v>1511502</x:v>
+      </x:c>
+      <x:c r="K27" s="20" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L27" s="21">
+        <x:v>46071.0606134259</x:v>
+      </x:c>
+      <x:c r="M27" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B30" s="22" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C30" s="23" t="s"/>
+      <x:c r="D30" s="23" t="s"/>
+      <x:c r="E30" s="24" t="s"/>
+      <x:c r="F30" s="24" t="s"/>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B31" s="25" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C31" s="26" t="s"/>
+      <x:c r="D31" s="26" t="s"/>
+      <x:c r="E31" s="26" t="s"/>
+      <x:c r="F31" s="27" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C32" s="29" t="s"/>
+      <x:c r="D32" s="29" t="s"/>
+      <x:c r="E32" s="29" t="s"/>
+      <x:c r="F32" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="28" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C33" s="29" t="s"/>
+      <x:c r="D33" s="29" t="s"/>
+      <x:c r="E33" s="29" t="s"/>
+      <x:c r="F33" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="28" t="s">
         <x:v>32</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>46067.3600231481</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>46067.3600462963</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L12" s="19">
-        <x:v>46079.2730092593</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="C34" s="29" t="s"/>
+      <x:c r="D34" s="29" t="s"/>
+      <x:c r="E34" s="29" t="s"/>
+      <x:c r="F34" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="28" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>46067.1596643518</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1505804</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="19">
-        <x:v>46079.2772569444</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>46067.2222106481</x:v>
-      </x:c>
-      <x:c r="I14" s="17">
-        <x:v>46089</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1505805</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L14" s="19">
-        <x:v>46079.2763078704</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E15" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="C35" s="29" t="s"/>
+      <x:c r="D35" s="29" t="s"/>
+      <x:c r="E35" s="29" t="s"/>
+      <x:c r="F35" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="28" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="H15" s="17">
-        <x:v>46063.1352777778</x:v>
-      </x:c>
-      <x:c r="I15" s="17">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="n">
-        <x:v>1511010</x:v>
-      </x:c>
-      <x:c r="K15" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L15" s="19">
-        <x:v>46063.2367708333</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C16" s="15" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D16" s="16" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E16" s="15" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F16" s="15" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G16" s="15" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H16" s="17">
-        <x:v>46079.3584722222</x:v>
-      </x:c>
-      <x:c r="I16" s="17">
-        <x:v>46079.3584953704</x:v>
-      </x:c>
-      <x:c r="J16" s="16" t="n">
-        <x:v>1511622</x:v>
-      </x:c>
-      <x:c r="K16" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L16" s="19">
-        <x:v>46080.2311226852</x:v>
-      </x:c>
-      <x:c r="M16" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C17" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D17" s="16" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E17" s="15" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F17" s="15" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G17" s="15" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H17" s="17">
-        <x:v>46079.3539699074</x:v>
-      </x:c>
-      <x:c r="I17" s="17">
-        <x:v>46079.3539814815</x:v>
-      </x:c>
-      <x:c r="J17" s="16" t="n">
-        <x:v>1511627</x:v>
-      </x:c>
-      <x:c r="K17" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L17" s="19">
-        <x:v>46080.2440856481</x:v>
-      </x:c>
-      <x:c r="M17" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C18" s="15" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D18" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E18" s="15" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="F18" s="15" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G18" s="15" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H18" s="17">
-        <x:v>46079.3873148148</x:v>
-      </x:c>
-      <x:c r="I18" s="17">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J18" s="16" t="n">
-        <x:v>1511623</x:v>
-      </x:c>
-      <x:c r="K18" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="19">
-        <x:v>46080.2360763889</x:v>
-      </x:c>
-      <x:c r="M18" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C19" s="15" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D19" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E19" s="15" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F19" s="15" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G19" s="15" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="H19" s="17">
-        <x:v>46079.2523032407</x:v>
-      </x:c>
-      <x:c r="I19" s="17">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J19" s="16" t="n">
-        <x:v>1511631</x:v>
-      </x:c>
-      <x:c r="K19" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="19">
-        <x:v>46080.2925810185</x:v>
-      </x:c>
-      <x:c r="M19" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C20" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D20" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E20" s="15" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F20" s="15" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="G20" s="15" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="H20" s="17">
-        <x:v>46079.2430555556</x:v>
-      </x:c>
-      <x:c r="I20" s="17">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J20" s="16" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K20" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="19">
-        <x:v>46080.2801273148</x:v>
-      </x:c>
-      <x:c r="M20" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C21" s="15" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D21" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E21" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="F21" s="15" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="G21" s="15" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="H21" s="17">
-        <x:v>46079.3651967593</x:v>
-      </x:c>
-      <x:c r="I21" s="17">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J21" s="16" t="n">
-        <x:v>1511626</x:v>
-      </x:c>
-      <x:c r="K21" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="19">
-        <x:v>46080.2425462963</x:v>
-      </x:c>
-      <x:c r="M21" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C22" s="15" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D22" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E22" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F22" s="15" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="G22" s="15" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="H22" s="17">
-        <x:v>46080.2923611111</x:v>
-      </x:c>
-      <x:c r="I22" s="17">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J22" s="16" t="n">
-        <x:v>1511635</x:v>
-      </x:c>
-      <x:c r="K22" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="19">
-        <x:v>46080.3208564815</x:v>
-      </x:c>
-      <x:c r="M22" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C23" s="15" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D23" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E23" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F23" s="15" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G23" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="H23" s="17">
-        <x:v>46079.31625</x:v>
-      </x:c>
-      <x:c r="I23" s="17">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J23" s="16" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K23" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="19">
-        <x:v>46080.2883680556</x:v>
-      </x:c>
-      <x:c r="M23" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C24" s="15" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D24" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E24" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F24" s="15" t="s">
+      <x:c r="C36" s="29" t="s"/>
+      <x:c r="D36" s="29" t="s"/>
+      <x:c r="E36" s="29" t="s"/>
+      <x:c r="F36" s="30" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B37" s="28" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G24" s="15" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="H24" s="17">
-        <x:v>46079.3059375</x:v>
-      </x:c>
-      <x:c r="I24" s="17">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J24" s="16" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K24" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L24" s="19">
-        <x:v>46080.2896875</x:v>
-      </x:c>
-      <x:c r="M24" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C25" s="15" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D25" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E25" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F25" s="15" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="G25" s="15" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="H25" s="17">
-        <x:v>46079.2943981482</x:v>
-      </x:c>
-      <x:c r="I25" s="17">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J25" s="16" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K25" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L25" s="19">
-        <x:v>46080.2916782407</x:v>
-      </x:c>
-      <x:c r="M25" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C26" s="15" t="s">
+      <x:c r="C37" s="29" t="s"/>
+      <x:c r="D37" s="29" t="s"/>
+      <x:c r="E37" s="29" t="s"/>
+      <x:c r="F37" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B38" s="28" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="D26" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E26" s="15" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="F26" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="G26" s="15" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="H26" s="17">
-        <x:v>46079.378900463</x:v>
-      </x:c>
-      <x:c r="I26" s="17">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J26" s="16" t="n">
-        <x:v>1511624</x:v>
-      </x:c>
-      <x:c r="K26" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="19">
-        <x:v>46080.2376041667</x:v>
-      </x:c>
-      <x:c r="M26" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C27" s="15" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D27" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E27" s="15" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="F27" s="15" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="G27" s="15" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="H27" s="17">
-        <x:v>46079.3728240741</x:v>
-      </x:c>
-      <x:c r="I27" s="17">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J27" s="16" t="n">
-        <x:v>1511625</x:v>
-      </x:c>
-      <x:c r="K27" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="19">
-        <x:v>46080.2394328704</x:v>
-      </x:c>
-      <x:c r="M27" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="15" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="C28" s="15" t="s">
+      <x:c r="C38" s="29" t="s"/>
+      <x:c r="D38" s="29" t="s"/>
+      <x:c r="E38" s="29" t="s"/>
+      <x:c r="F38" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B39" s="31" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="D28" s="16" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E28" s="15" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="F28" s="15" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="G28" s="15" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="H28" s="17">
-        <x:v>46062.1590162037</x:v>
-      </x:c>
-      <x:c r="I28" s="17">
-        <x:v>46062.1590277778</x:v>
-      </x:c>
-      <x:c r="J28" s="16" t="n">
-        <x:v>1510925</x:v>
-      </x:c>
-      <x:c r="K28" s="18" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L28" s="19">
-        <x:v>46062.1863194444</x:v>
-      </x:c>
-      <x:c r="M28" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="15" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C29" s="15" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="D29" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E29" s="15" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="F29" s="15" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="G29" s="15" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="H29" s="17">
-        <x:v>46071.0492476852</x:v>
-      </x:c>
-      <x:c r="I29" s="17">
-        <x:v>46052</x:v>
-      </x:c>
-      <x:c r="J29" s="16" t="n">
-        <x:v>1511502</x:v>
-      </x:c>
-      <x:c r="K29" s="18" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L29" s="19">
-        <x:v>46071.0606134259</x:v>
-      </x:c>
-      <x:c r="M29" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="32" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B32" s="20" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="C32" s="21" t="s"/>
-      <x:c r="D32" s="21" t="s"/>
-      <x:c r="E32" s="22" t="s"/>
-      <x:c r="F32" s="22" t="s"/>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B33" s="23" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="C33" s="24" t="s"/>
-      <x:c r="D33" s="24" t="s"/>
-      <x:c r="E33" s="24" t="s"/>
-      <x:c r="F33" s="25" t="s">
-        <x:v>118</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C34" s="27" t="s"/>
-      <x:c r="D34" s="27" t="s"/>
-      <x:c r="E34" s="27" t="s"/>
-      <x:c r="F34" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="26" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C35" s="27" t="s"/>
-      <x:c r="D35" s="27" t="s"/>
-      <x:c r="E35" s="27" t="s"/>
-      <x:c r="F35" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="26" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C36" s="27" t="s"/>
-      <x:c r="D36" s="27" t="s"/>
-      <x:c r="E36" s="27" t="s"/>
-      <x:c r="F36" s="28" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B37" s="26" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C37" s="27" t="s"/>
-      <x:c r="D37" s="27" t="s"/>
-      <x:c r="E37" s="27" t="s"/>
-      <x:c r="F37" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B38" s="26" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C38" s="27" t="s"/>
-      <x:c r="D38" s="27" t="s"/>
-      <x:c r="E38" s="27" t="s"/>
-      <x:c r="F38" s="28" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B39" s="26" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="C39" s="27" t="s"/>
-      <x:c r="D39" s="27" t="s"/>
-      <x:c r="E39" s="27" t="s"/>
-      <x:c r="F39" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B40" s="26" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C40" s="27" t="s"/>
-      <x:c r="D40" s="27" t="s"/>
-      <x:c r="E40" s="27" t="s"/>
-      <x:c r="F40" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B41" s="29" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="C41" s="30" t="s"/>
-      <x:c r="D41" s="30" t="s"/>
-      <x:c r="E41" s="30" t="s"/>
-      <x:c r="F41" s="31" t="n">
+      <x:c r="C39" s="32" t="s"/>
+      <x:c r="D39" s="32" t="s"/>
+      <x:c r="E39" s="32" t="s"/>
+      <x:c r="F39" s="33" t="n">
         <x:v>20</x:v>
       </x:c>
     </x:row>
+    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3400,7 +3332,9 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B32:F32"/>
+    <x:mergeCell ref="B30:F30"/>
+    <x:mergeCell ref="B31:E31"/>
+    <x:mergeCell ref="B32:E32"/>
     <x:mergeCell ref="B33:E33"/>
     <x:mergeCell ref="B34:E34"/>
     <x:mergeCell ref="B35:E35"/>
@@ -3408,8 +3342,6 @@
     <x:mergeCell ref="B37:E37"/>
     <x:mergeCell ref="B38:E38"/>
     <x:mergeCell ref="B39:E39"/>
-    <x:mergeCell ref="B40:E40"/>
-    <x:mergeCell ref="B41:E41"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -3521,7 +3453,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>120</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -3554,7 +3486,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -3594,930 +3526,880 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46091.306099537</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46091.3107986111</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1511778</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46091.3131828704</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46093.1459375</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46093.1585185185</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1511815</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46093.159537037</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E10" s="17" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
+        <x:v>46080.4532523148</x:v>
+      </x:c>
+      <x:c r="I10" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="n">
+        <x:v>1511232</x:v>
+      </x:c>
+      <x:c r="K10" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="21">
+        <x:v>46097.1461689815</x:v>
+      </x:c>
+      <x:c r="M10" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
+        <x:v>46083.2380439815</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1511234</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="21">
+        <x:v>46097.1564351852</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
+        <x:v>46083.2599189815</x:v>
+      </x:c>
+      <x:c r="I12" s="19">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="n">
+        <x:v>1511237</x:v>
+      </x:c>
+      <x:c r="K12" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="21">
+        <x:v>46097.1652314815</x:v>
+      </x:c>
+      <x:c r="M12" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E13" s="17" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H13" s="19">
+        <x:v>46084.0854513889</x:v>
+      </x:c>
+      <x:c r="I13" s="19">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="n">
+        <x:v>1511225</x:v>
+      </x:c>
+      <x:c r="K13" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="21">
+        <x:v>46093.3956365741</x:v>
+      </x:c>
+      <x:c r="M13" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E14" s="17" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H14" s="19">
+        <x:v>46084.0996759259</x:v>
+      </x:c>
+      <x:c r="I14" s="19">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="n">
+        <x:v>1511192</x:v>
+      </x:c>
+      <x:c r="K14" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="21">
+        <x:v>46097.2414583333</x:v>
+      </x:c>
+      <x:c r="M14" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E15" s="17" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="F15" s="17" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="H15" s="19">
+        <x:v>46069.1542013889</x:v>
+      </x:c>
+      <x:c r="I15" s="19">
+        <x:v>46035</x:v>
+      </x:c>
+      <x:c r="J15" s="18" t="n">
+        <x:v>1511206</x:v>
+      </x:c>
+      <x:c r="K15" s="20" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L15" s="21">
+        <x:v>46097.2466550926</x:v>
+      </x:c>
+      <x:c r="M15" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D16" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E16" s="17" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G16" s="17" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="H16" s="19">
+        <x:v>46069.2178703704</x:v>
+      </x:c>
+      <x:c r="I16" s="19">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J16" s="18" t="n">
+        <x:v>1511196</x:v>
+      </x:c>
+      <x:c r="K16" s="20" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L16" s="21">
+        <x:v>46097.2456365741</x:v>
+      </x:c>
+      <x:c r="M16" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C17" s="17" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D17" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E17" s="17" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="F17" s="17" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="G17" s="17" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H17" s="19">
+        <x:v>46083.2443865741</x:v>
+      </x:c>
+      <x:c r="I17" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J17" s="18" t="n">
+        <x:v>1511235</x:v>
+      </x:c>
+      <x:c r="K17" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="21">
+        <x:v>46097.1600115741</x:v>
+      </x:c>
+      <x:c r="M17" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C18" s="17" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E18" s="17" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="F18" s="17" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="G18" s="17" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="H18" s="19">
+        <x:v>46084.1225115741</x:v>
+      </x:c>
+      <x:c r="I18" s="19">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J18" s="18" t="n">
+        <x:v>1511242</x:v>
+      </x:c>
+      <x:c r="K18" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="21">
+        <x:v>46097.3505092593</x:v>
+      </x:c>
+      <x:c r="M18" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C19" s="17" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D19" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E19" s="17" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F19" s="17" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G19" s="17" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H19" s="19">
+        <x:v>46083.2521064815</x:v>
+      </x:c>
+      <x:c r="I19" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J19" s="18" t="n">
+        <x:v>1511236</x:v>
+      </x:c>
+      <x:c r="K19" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="21">
+        <x:v>46097.1628935185</x:v>
+      </x:c>
+      <x:c r="M19" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C20" s="17" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D20" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E20" s="17" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="F20" s="17" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="G20" s="17" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="H20" s="19">
+        <x:v>46069.115150463</x:v>
+      </x:c>
+      <x:c r="I20" s="19">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J20" s="18" t="n">
+        <x:v>1511241</x:v>
+      </x:c>
+      <x:c r="K20" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="21">
+        <x:v>46097.3433796296</x:v>
+      </x:c>
+      <x:c r="M20" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C21" s="17" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D21" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E21" s="17" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="F21" s="17" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="G21" s="17" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H21" s="19">
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I21" s="19">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="J21" s="18" t="n">
+        <x:v>1511761</x:v>
+      </x:c>
+      <x:c r="K21" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="21">
+        <x:v>46090.2765740741</x:v>
+      </x:c>
+      <x:c r="M21" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="17" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C22" s="17" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D22" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E22" s="17" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F22" s="17" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G22" s="17" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="H22" s="19">
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I22" s="19">
+        <x:v>46085.1662615741</x:v>
+      </x:c>
+      <x:c r="J22" s="18" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K22" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L22" s="21">
+        <x:v>46090.3437268519</x:v>
+      </x:c>
+      <x:c r="M22" s="17" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="17" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C23" s="17" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D23" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E23" s="17" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="F23" s="17" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G23" s="17" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="H23" s="19">
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I23" s="19">
+        <x:v>46085.1709375</x:v>
+      </x:c>
+      <x:c r="J23" s="18" t="n">
+        <x:v>1507965</x:v>
+      </x:c>
+      <x:c r="K23" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L23" s="21">
+        <x:v>46090.3336921296</x:v>
+      </x:c>
+      <x:c r="M23" s="17" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C24" s="17" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D24" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E24" s="17" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F24" s="17" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G24" s="17" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H24" s="19">
+        <x:v>46084.1080324074</x:v>
+      </x:c>
+      <x:c r="I24" s="19">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J24" s="18" t="n">
+        <x:v>1511208</x:v>
+      </x:c>
+      <x:c r="K24" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L24" s="21">
+        <x:v>46097.2478125</x:v>
+      </x:c>
+      <x:c r="M24" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C25" s="17" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D25" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E25" s="17" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="F25" s="17" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="G25" s="17" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="H25" s="19">
+        <x:v>46083.0787962963</x:v>
+      </x:c>
+      <x:c r="I25" s="19">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J25" s="18" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K25" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="21">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M25" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C26" s="17" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D26" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E26" s="17" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="F26" s="17" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G26" s="17" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="H26" s="19">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I26" s="19">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J26" s="18" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K26" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="21">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M26" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C27" s="17" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D27" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E27" s="17" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="F27" s="17" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="G27" s="17" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="H27" s="19">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I27" s="19">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J27" s="18" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K27" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L27" s="21">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M27" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C28" s="17" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D28" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E28" s="17" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="F28" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="G28" s="17" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="H28" s="19">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I28" s="19">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J28" s="18" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K28" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="21">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M28" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B31" s="22" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C31" s="23" t="s"/>
+      <x:c r="D31" s="23" t="s"/>
+      <x:c r="E31" s="24" t="s"/>
+      <x:c r="F31" s="24" t="s"/>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B32" s="25" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C32" s="26" t="s"/>
+      <x:c r="D32" s="26" t="s"/>
+      <x:c r="E32" s="26" t="s"/>
+      <x:c r="F32" s="27" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C33" s="29" t="s"/>
+      <x:c r="D33" s="29" t="s"/>
+      <x:c r="E33" s="29" t="s"/>
+      <x:c r="F33" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="28" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C34" s="29" t="s"/>
+      <x:c r="D34" s="29" t="s"/>
+      <x:c r="E34" s="29" t="s"/>
+      <x:c r="F34" s="30" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="28" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C35" s="29" t="s"/>
+      <x:c r="D35" s="29" t="s"/>
+      <x:c r="E35" s="29" t="s"/>
+      <x:c r="F35" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="28" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C36" s="29" t="s"/>
+      <x:c r="D36" s="29" t="s"/>
+      <x:c r="E36" s="29" t="s"/>
+      <x:c r="F36" s="30" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B37" s="31" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C37" s="32" t="s"/>
+      <x:c r="D37" s="32" t="s"/>
+      <x:c r="E37" s="32" t="s"/>
+      <x:c r="F37" s="33" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46091.306099537</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46091.3107986111</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1511778</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46091.3131828704</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="15" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>46093.1459375</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>46093.1585185185</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1511815</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>46093.159537037</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>46080.4532523148</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1511232</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L12" s="19">
-        <x:v>46097.1461689815</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>133</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>46083.2380439815</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1511234</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="19">
-        <x:v>46097.1564351852</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>133</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>46083.2599189815</x:v>
-      </x:c>
-      <x:c r="I14" s="17">
-        <x:v>46101</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1511237</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L14" s="19">
-        <x:v>46097.1652314815</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>133</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E15" s="15" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="G15" s="15" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="H15" s="17">
-        <x:v>46084.0854513889</x:v>
-      </x:c>
-      <x:c r="I15" s="17">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="n">
-        <x:v>1511225</x:v>
-      </x:c>
-      <x:c r="K15" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L15" s="19">
-        <x:v>46093.3956365741</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>133</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C16" s="15" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="D16" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E16" s="15" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="F16" s="15" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="G16" s="15" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="H16" s="17">
-        <x:v>46084.0996759259</x:v>
-      </x:c>
-      <x:c r="I16" s="17">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J16" s="16" t="n">
-        <x:v>1511192</x:v>
-      </x:c>
-      <x:c r="K16" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L16" s="19">
-        <x:v>46097.2414583333</x:v>
-      </x:c>
-      <x:c r="M16" s="15" t="s">
-        <x:v>133</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C17" s="15" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="D17" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E17" s="15" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="F17" s="15" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="G17" s="15" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="H17" s="17">
-        <x:v>46069.1542013889</x:v>
-      </x:c>
-      <x:c r="I17" s="17">
-        <x:v>46035</x:v>
-      </x:c>
-      <x:c r="J17" s="16" t="n">
-        <x:v>1511206</x:v>
-      </x:c>
-      <x:c r="K17" s="18" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L17" s="19">
-        <x:v>46097.2466550926</x:v>
-      </x:c>
-      <x:c r="M17" s="15" t="s">
-        <x:v>133</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C18" s="15" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="D18" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E18" s="15" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="F18" s="15" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="G18" s="15" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="H18" s="17">
-        <x:v>46069.2178703704</x:v>
-      </x:c>
-      <x:c r="I18" s="17">
-        <x:v>46051</x:v>
-      </x:c>
-      <x:c r="J18" s="16" t="n">
-        <x:v>1511196</x:v>
-      </x:c>
-      <x:c r="K18" s="18" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L18" s="19">
-        <x:v>46097.2456365741</x:v>
-      </x:c>
-      <x:c r="M18" s="15" t="s">
-        <x:v>133</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C19" s="15" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="D19" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E19" s="15" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="F19" s="15" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="G19" s="15" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="H19" s="17">
-        <x:v>46083.2443865741</x:v>
-      </x:c>
-      <x:c r="I19" s="17">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J19" s="16" t="n">
-        <x:v>1511235</x:v>
-      </x:c>
-      <x:c r="K19" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="19">
-        <x:v>46097.1600115741</x:v>
-      </x:c>
-      <x:c r="M19" s="15" t="s">
-        <x:v>133</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C20" s="15" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="D20" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E20" s="15" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="F20" s="15" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="G20" s="15" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="H20" s="17">
-        <x:v>46084.1225115741</x:v>
-      </x:c>
-      <x:c r="I20" s="17">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J20" s="16" t="n">
-        <x:v>1511242</x:v>
-      </x:c>
-      <x:c r="K20" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="19">
-        <x:v>46097.3505092593</x:v>
-      </x:c>
-      <x:c r="M20" s="15" t="s">
-        <x:v>133</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C21" s="15" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="D21" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E21" s="15" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="F21" s="15" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="G21" s="15" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="H21" s="17">
-        <x:v>46083.2521064815</x:v>
-      </x:c>
-      <x:c r="I21" s="17">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J21" s="16" t="n">
-        <x:v>1511236</x:v>
-      </x:c>
-      <x:c r="K21" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="19">
-        <x:v>46097.1628935185</x:v>
-      </x:c>
-      <x:c r="M21" s="15" t="s">
-        <x:v>133</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C22" s="15" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="D22" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E22" s="15" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="F22" s="15" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="G22" s="15" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="H22" s="17">
-        <x:v>46069.115150463</x:v>
-      </x:c>
-      <x:c r="I22" s="17">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J22" s="16" t="n">
-        <x:v>1511241</x:v>
-      </x:c>
-      <x:c r="K22" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="19">
-        <x:v>46097.3433796296</x:v>
-      </x:c>
-      <x:c r="M22" s="15" t="s">
-        <x:v>133</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C23" s="15" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="D23" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E23" s="15" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="F23" s="15" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="G23" s="15" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="H23" s="17">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I23" s="17">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="J23" s="16" t="n">
-        <x:v>1511761</x:v>
-      </x:c>
-      <x:c r="K23" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="19">
-        <x:v>46090.2765740741</x:v>
-      </x:c>
-      <x:c r="M23" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C24" s="15" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="D24" s="16" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E24" s="15" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="F24" s="15" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="G24" s="15" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="H24" s="17">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I24" s="17">
-        <x:v>46085.1662615741</x:v>
-      </x:c>
-      <x:c r="J24" s="16" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K24" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L24" s="19">
-        <x:v>46090.3437268519</x:v>
-      </x:c>
-      <x:c r="M24" s="15" t="s">
-        <x:v>180</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C25" s="15" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="D25" s="16" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E25" s="15" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="F25" s="15" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="G25" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="H25" s="17">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I25" s="17">
-        <x:v>46085.1709375</x:v>
-      </x:c>
-      <x:c r="J25" s="16" t="n">
-        <x:v>1507965</x:v>
-      </x:c>
-      <x:c r="K25" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L25" s="19">
-        <x:v>46090.3336921296</x:v>
-      </x:c>
-      <x:c r="M25" s="15" t="s">
-        <x:v>180</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C26" s="15" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="D26" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E26" s="15" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="F26" s="15" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="G26" s="15" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="H26" s="17">
-        <x:v>46084.1080324074</x:v>
-      </x:c>
-      <x:c r="I26" s="17">
-        <x:v>46103</x:v>
-      </x:c>
-      <x:c r="J26" s="16" t="n">
-        <x:v>1511208</x:v>
-      </x:c>
-      <x:c r="K26" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="19">
-        <x:v>46097.2478125</x:v>
-      </x:c>
-      <x:c r="M26" s="15" t="s">
-        <x:v>133</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C27" s="15" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="D27" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E27" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="F27" s="15" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="G27" s="15" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="H27" s="17">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I27" s="17">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J27" s="16" t="n">
-        <x:v>1511639</x:v>
-      </x:c>
-      <x:c r="K27" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="19">
-        <x:v>46083.104224537</x:v>
-      </x:c>
-      <x:c r="M27" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C28" s="15" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="D28" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E28" s="15" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="F28" s="15" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G28" s="15" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="H28" s="17">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I28" s="17">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="J28" s="16" t="n">
-        <x:v>1511758</x:v>
-      </x:c>
-      <x:c r="K28" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="19">
-        <x:v>46090.2691087963</x:v>
-      </x:c>
-      <x:c r="M28" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C29" s="15" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="D29" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E29" s="15" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="F29" s="15" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="G29" s="15" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="H29" s="17">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I29" s="17">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J29" s="16" t="n">
-        <x:v>1511759</x:v>
-      </x:c>
-      <x:c r="K29" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="19">
-        <x:v>46090.2703703704</x:v>
-      </x:c>
-      <x:c r="M29" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C30" s="15" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="D30" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E30" s="15" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="F30" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="G30" s="15" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="H30" s="17">
-        <x:v>46087.1643287037</x:v>
-      </x:c>
-      <x:c r="I30" s="17">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="J30" s="16" t="n">
-        <x:v>1511760</x:v>
-      </x:c>
-      <x:c r="K30" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="19">
-        <x:v>46090.2727777778</x:v>
-      </x:c>
-      <x:c r="M30" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="33" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B33" s="20" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="C33" s="21" t="s"/>
-      <x:c r="D33" s="21" t="s"/>
-      <x:c r="E33" s="22" t="s"/>
-      <x:c r="F33" s="22" t="s"/>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B34" s="23" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="C34" s="24" t="s"/>
-      <x:c r="D34" s="24" t="s"/>
-      <x:c r="E34" s="24" t="s"/>
-      <x:c r="F34" s="25" t="s">
-        <x:v>118</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C35" s="27" t="s"/>
-      <x:c r="D35" s="27" t="s"/>
-      <x:c r="E35" s="27" t="s"/>
-      <x:c r="F35" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="26" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C36" s="27" t="s"/>
-      <x:c r="D36" s="27" t="s"/>
-      <x:c r="E36" s="27" t="s"/>
-      <x:c r="F36" s="28" t="n">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B37" s="26" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C37" s="27" t="s"/>
-      <x:c r="D37" s="27" t="s"/>
-      <x:c r="E37" s="27" t="s"/>
-      <x:c r="F37" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B38" s="26" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C38" s="27" t="s"/>
-      <x:c r="D38" s="27" t="s"/>
-      <x:c r="E38" s="27" t="s"/>
-      <x:c r="F38" s="28" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B39" s="29" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="C39" s="30" t="s"/>
-      <x:c r="D39" s="30" t="s"/>
-      <x:c r="E39" s="30" t="s"/>
-      <x:c r="F39" s="31" t="n">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5478,13 +5360,13 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B33:F33"/>
+    <x:mergeCell ref="B31:F31"/>
+    <x:mergeCell ref="B32:E32"/>
+    <x:mergeCell ref="B33:E33"/>
     <x:mergeCell ref="B34:E34"/>
     <x:mergeCell ref="B35:E35"/>
     <x:mergeCell ref="B36:E36"/>
     <x:mergeCell ref="B37:E37"/>
-    <x:mergeCell ref="B38:E38"/>
-    <x:mergeCell ref="B39:E39"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="192">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -415,6 +415,15 @@
     <x:t>CELLTY MOBILE INC</x:t>
   </x:si>
   <x:si>
+    <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-020R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1156-896</x:t>
+  </x:si>
+  <x:si>
     <x:t>SM CITY BACOOR CZ430, HABAY II, Bacoor City, Cavite</x:t>
   </x:si>
   <x:si>
@@ -424,15 +433,6 @@
     <x:t>43A-3-2026-1155-834</x:t>
   </x:si>
   <x:si>
-    <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-020R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1156-896</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -520,6 +520,18 @@
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
+    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2518</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1172-434</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ricardo Natividad</x:t>
+  </x:si>
+  <x:si>
     <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
   </x:si>
   <x:si>
@@ -529,18 +541,6 @@
     <x:t>43A-3-2026-1171-081</x:t>
   </x:si>
   <x:si>
-    <x:t>Ricardo Natividad</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-2518</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1172-434</x:t>
-  </x:si>
-  <x:si>
     <x:t>WALTERMART TANAUAN 225 WALTERMART JPL-HWAY, DARASA, City Of Tanauan, Batangas</x:t>
   </x:si>
   <x:si>
@@ -562,6 +562,24 @@
     <x:t>43A-3-2026-1146-031</x:t>
   </x:si>
   <x:si>
+    <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1175-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2106</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1176-385</x:t>
+  </x:si>
+  <x:si>
     <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -571,22 +589,16 @@
     <x:t>43A-3-2026-1173-016</x:t>
   </x:si>
   <x:si>
-    <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-18-02-2017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1175-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-18-02-2106</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1176-385</x:t>
+    <x:t>CELLBOY INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLOOR CYBERZONE SM CALAMBA NATIONAL HIGHWAY, REAL, City Of Calamba, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-16-12-0951</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1205-403</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3733,19 +3745,19 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="H13" s="19">
-        <x:v>46084.0854513889</x:v>
+        <x:v>46084.0996759259</x:v>
       </x:c>
       <x:c r="I13" s="19">
-        <x:v>46144</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J13" s="18" t="n">
-        <x:v>1511225</x:v>
+        <x:v>1511192</x:v>
       </x:c>
       <x:c r="K13" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="21">
-        <x:v>46093.3956365741</x:v>
+        <x:v>46097.2414583333</x:v>
       </x:c>
       <x:c r="M13" s="17" t="s">
         <x:v>121</x:v>
@@ -3771,19 +3783,19 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="H14" s="19">
-        <x:v>46084.0996759259</x:v>
+        <x:v>46084.0854513889</x:v>
       </x:c>
       <x:c r="I14" s="19">
-        <x:v>46094</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J14" s="18" t="n">
-        <x:v>1511192</x:v>
+        <x:v>1511225</x:v>
       </x:c>
       <x:c r="K14" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="21">
-        <x:v>46097.2414583333</x:v>
+        <x:v>46093.3956365741</x:v>
       </x:c>
       <x:c r="M14" s="17" t="s">
         <x:v>121</x:v>
@@ -4075,19 +4087,19 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="H22" s="19">
-        <x:v>46085.16625</x:v>
+        <x:v>46085.1709143519</x:v>
       </x:c>
       <x:c r="I22" s="19">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J22" s="18" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K22" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L22" s="21">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M22" s="17" t="s">
         <x:v>168</x:v>
@@ -4113,19 +4125,19 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="H23" s="19">
-        <x:v>46085.1709143519</x:v>
+        <x:v>46085.16625</x:v>
       </x:c>
       <x:c r="I23" s="19">
-        <x:v>46085.1709375</x:v>
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J23" s="18" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K23" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L23" s="21">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M23" s="17" t="s">
         <x:v>168</x:v>
@@ -4227,19 +4239,19 @@
         <x:v>181</x:v>
       </x:c>
       <x:c r="H26" s="19">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46086.1144444444</x:v>
       </x:c>
       <x:c r="I26" s="19">
-        <x:v>46098</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="J26" s="18" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511759</x:v>
       </x:c>
       <x:c r="K26" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L26" s="21">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46090.2703703704</x:v>
       </x:c>
       <x:c r="M26" s="17" t="s">
         <x:v>52</x:v>
@@ -4265,19 +4277,19 @@
         <x:v>184</x:v>
       </x:c>
       <x:c r="H27" s="19">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46087.1643287037</x:v>
       </x:c>
       <x:c r="I27" s="19">
-        <x:v>46097</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J27" s="18" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1511760</x:v>
       </x:c>
       <x:c r="K27" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L27" s="21">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46090.2727777778</x:v>
       </x:c>
       <x:c r="M27" s="17" t="s">
         <x:v>52</x:v>
@@ -4303,103 +4315,150 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="H28" s="19">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46086.0997916667</x:v>
       </x:c>
       <x:c r="I28" s="19">
-        <x:v>46104</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="J28" s="18" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511758</x:v>
       </x:c>
       <x:c r="K28" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L28" s="21">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46090.2691087963</x:v>
       </x:c>
       <x:c r="M28" s="17" t="s">
         <x:v>52</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="17" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C29" s="17" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="D29" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E29" s="17" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="F29" s="17" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="G29" s="17" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="H29" s="19">
+        <x:v>46098.2908796296</x:v>
+      </x:c>
+      <x:c r="I29" s="19">
+        <x:v>45997</x:v>
+      </x:c>
+      <x:c r="J29" s="18" t="n">
+        <x:v>1511858</x:v>
+      </x:c>
+      <x:c r="K29" s="20" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L29" s="21">
+        <x:v>46098.3188657407</x:v>
+      </x:c>
+      <x:c r="M29" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="31" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B31" s="22" t="s">
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B32" s="22" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="C31" s="23" t="s"/>
-      <x:c r="D31" s="23" t="s"/>
-      <x:c r="E31" s="24" t="s"/>
-      <x:c r="F31" s="24" t="s"/>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B32" s="25" t="s">
+      <x:c r="C32" s="23" t="s"/>
+      <x:c r="D32" s="23" t="s"/>
+      <x:c r="E32" s="24" t="s"/>
+      <x:c r="F32" s="24" t="s"/>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B33" s="25" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C32" s="26" t="s"/>
-      <x:c r="D32" s="26" t="s"/>
-      <x:c r="E32" s="26" t="s"/>
-      <x:c r="F32" s="27" t="s">
+      <x:c r="C33" s="26" t="s"/>
+      <x:c r="D33" s="26" t="s"/>
+      <x:c r="E33" s="26" t="s"/>
+      <x:c r="F33" s="27" t="s">
         <x:v>106</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C33" s="29" t="s"/>
-      <x:c r="D33" s="29" t="s"/>
-      <x:c r="E33" s="29" t="s"/>
-      <x:c r="F33" s="30" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
       <x:c r="B34" s="28" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C34" s="29" t="s"/>
       <x:c r="D34" s="29" t="s"/>
       <x:c r="E34" s="29" t="s"/>
       <x:c r="F34" s="30" t="n">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
       <x:c r="B35" s="28" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C35" s="29" t="s"/>
       <x:c r="D35" s="29" t="s"/>
       <x:c r="E35" s="29" t="s"/>
       <x:c r="F35" s="30" t="n">
-        <x:v>2</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="18" customHeight="1">
       <x:c r="B36" s="28" t="s">
-        <x:v>57</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C36" s="29" t="s"/>
       <x:c r="D36" s="29" t="s"/>
       <x:c r="E36" s="29" t="s"/>
       <x:c r="F36" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B37" s="28" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C37" s="29" t="s"/>
+      <x:c r="D37" s="29" t="s"/>
+      <x:c r="E37" s="29" t="s"/>
+      <x:c r="F37" s="30" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B37" s="31" t="s">
+    <x:row r="38" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B38" s="28" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C38" s="29" t="s"/>
+      <x:c r="D38" s="29" t="s"/>
+      <x:c r="E38" s="29" t="s"/>
+      <x:c r="F38" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B39" s="31" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="C37" s="32" t="s"/>
-      <x:c r="D37" s="32" t="s"/>
-      <x:c r="E37" s="32" t="s"/>
-      <x:c r="F37" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C39" s="32" t="s"/>
+      <x:c r="D39" s="32" t="s"/>
+      <x:c r="E39" s="32" t="s"/>
+      <x:c r="F39" s="33" t="n">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5355,18 +5414,19 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="11">
+  <x:mergeCells count="12">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B31:F31"/>
-    <x:mergeCell ref="B32:E32"/>
+    <x:mergeCell ref="B32:F32"/>
     <x:mergeCell ref="B33:E33"/>
     <x:mergeCell ref="B34:E34"/>
     <x:mergeCell ref="B35:E35"/>
     <x:mergeCell ref="B36:E36"/>
     <x:mergeCell ref="B37:E37"/>
+    <x:mergeCell ref="B38:E38"/>
+    <x:mergeCell ref="B39:E39"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="192">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -352,6 +352,18 @@
     <x:t>IV-A | March 2026</x:t>
   </x:si>
   <x:si>
+    <x:t>ALCALA, GLENN GUIBAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Block 2 Lot 9 Sunridge Ville Phase 1 Isarog Street, Barangay Isabang, City Of Tayabas, Quezon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03011-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1207-652</x:t>
+  </x:si>
+  <x:si>
     <x:t>HERALD BEBIS</x:t>
   </x:si>
   <x:si>
@@ -415,6 +427,15 @@
     <x:t>CELLTY MOBILE INC</x:t>
   </x:si>
   <x:si>
+    <x:t>SM CITY BACOOR CZ430, HABAY II, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0762</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1155-834</x:t>
+  </x:si>
+  <x:si>
     <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
   </x:si>
   <x:si>
@@ -424,15 +445,6 @@
     <x:t>43A-3-2026-1156-896</x:t>
   </x:si>
   <x:si>
-    <x:t>SM CITY BACOOR CZ430, HABAY II, Bacoor City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-03-0762</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1155-834</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -562,6 +574,15 @@
     <x:t>43A-3-2026-1146-031</x:t>
   </x:si>
   <x:si>
+    <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-17-03-2015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1173-016</x:t>
+  </x:si>
+  <x:si>
     <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
   </x:si>
   <x:si>
@@ -578,15 +599,6 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1176-385</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-17-03-2015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1173-016</x:t>
   </x:si>
   <x:si>
     <x:t>CELLBOY INC.</x:t>
@@ -3557,19 +3569,19 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="H8" s="15">
-        <x:v>46091.306099537</x:v>
+        <x:v>46100.1144675926</x:v>
       </x:c>
       <x:c r="I8" s="15">
-        <x:v>46091.3107986111</x:v>
+        <x:v>46100.1505092593</x:v>
       </x:c>
       <x:c r="J8" s="14" t="n">
-        <x:v>1511778</x:v>
+        <x:v>1511906</x:v>
       </x:c>
       <x:c r="K8" s="16" t="n">
         <x:v>230</x:v>
       </x:c>
       <x:c r="L8" s="15">
-        <x:v>46091.3131828704</x:v>
+        <x:v>46100.1652777778</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>52</x:v>
@@ -3593,19 +3605,19 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="H9" s="15">
-        <x:v>46093.1459375</x:v>
+        <x:v>46091.306099537</x:v>
       </x:c>
       <x:c r="I9" s="15">
-        <x:v>46093.1585185185</x:v>
+        <x:v>46091.3107986111</x:v>
       </x:c>
       <x:c r="J9" s="14" t="n">
-        <x:v>1511815</x:v>
+        <x:v>1511778</x:v>
       </x:c>
       <x:c r="K9" s="16" t="n">
         <x:v>230</x:v>
       </x:c>
       <x:c r="L9" s="15">
-        <x:v>46093.159537037</x:v>
+        <x:v>46091.3131828704</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>52</x:v>
@@ -3613,14 +3625,12 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="17" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C10" s="17" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="D10" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
+      <x:c r="D10" s="18" t="s"/>
       <x:c r="E10" s="17" t="s">
         <x:v>118</x:v>
       </x:c>
@@ -3631,22 +3641,22 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="H10" s="19">
-        <x:v>46080.4532523148</x:v>
+        <x:v>46093.1459375</x:v>
       </x:c>
       <x:c r="I10" s="19">
-        <x:v>46100</x:v>
+        <x:v>46093.1585185185</x:v>
       </x:c>
       <x:c r="J10" s="18" t="n">
-        <x:v>1511232</x:v>
+        <x:v>1511815</x:v>
       </x:c>
       <x:c r="K10" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L10" s="21">
-        <x:v>46097.1461689815</x:v>
+        <x:v>46093.159537037</x:v>
       </x:c>
       <x:c r="M10" s="17" t="s">
-        <x:v>121</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
@@ -3654,7 +3664,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C11" s="17" t="s">
-        <x:v>117</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D11" s="18" t="s">
         <x:v>34</x:v>
@@ -3669,22 +3679,22 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="H11" s="19">
-        <x:v>46083.2380439815</x:v>
+        <x:v>46080.4532523148</x:v>
       </x:c>
       <x:c r="I11" s="19">
         <x:v>46100</x:v>
       </x:c>
       <x:c r="J11" s="18" t="n">
-        <x:v>1511234</x:v>
+        <x:v>1511232</x:v>
       </x:c>
       <x:c r="K11" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L11" s="21">
-        <x:v>46097.1564351852</x:v>
+        <x:v>46097.1461689815</x:v>
       </x:c>
       <x:c r="M11" s="17" t="s">
-        <x:v>121</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
@@ -3692,7 +3702,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C12" s="17" t="s">
-        <x:v>125</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D12" s="18" t="s">
         <x:v>34</x:v>
@@ -3707,22 +3717,22 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="H12" s="19">
-        <x:v>46083.2599189815</x:v>
+        <x:v>46083.2380439815</x:v>
       </x:c>
       <x:c r="I12" s="19">
-        <x:v>46101</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J12" s="18" t="n">
-        <x:v>1511237</x:v>
+        <x:v>1511234</x:v>
       </x:c>
       <x:c r="K12" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L12" s="21">
-        <x:v>46097.1652314815</x:v>
+        <x:v>46097.1564351852</x:v>
       </x:c>
       <x:c r="M12" s="17" t="s">
-        <x:v>121</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
@@ -3745,22 +3755,22 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="H13" s="19">
-        <x:v>46084.0996759259</x:v>
+        <x:v>46083.2599189815</x:v>
       </x:c>
       <x:c r="I13" s="19">
-        <x:v>46094</x:v>
+        <x:v>46101</x:v>
       </x:c>
       <x:c r="J13" s="18" t="n">
-        <x:v>1511192</x:v>
+        <x:v>1511237</x:v>
       </x:c>
       <x:c r="K13" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="21">
-        <x:v>46097.2414583333</x:v>
+        <x:v>46097.1652314815</x:v>
       </x:c>
       <x:c r="M13" s="17" t="s">
-        <x:v>121</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
@@ -3768,19 +3778,19 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C14" s="17" t="s">
-        <x:v>129</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D14" s="18" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E14" s="17" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="F14" s="17" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="G14" s="17" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H14" s="19">
         <x:v>46084.0854513889</x:v>
@@ -3798,7 +3808,7 @@
         <x:v>46093.3956365741</x:v>
       </x:c>
       <x:c r="M14" s="17" t="s">
-        <x:v>121</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
@@ -3806,7 +3816,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C15" s="17" t="s">
-        <x:v>136</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D15" s="18" t="s">
         <x:v>34</x:v>
@@ -3821,22 +3831,22 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="H15" s="19">
-        <x:v>46069.1542013889</x:v>
+        <x:v>46084.0996759259</x:v>
       </x:c>
       <x:c r="I15" s="19">
-        <x:v>46035</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J15" s="18" t="n">
-        <x:v>1511206</x:v>
+        <x:v>1511192</x:v>
       </x:c>
       <x:c r="K15" s="20" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="21">
-        <x:v>46097.2466550926</x:v>
+        <x:v>46097.2414583333</x:v>
       </x:c>
       <x:c r="M15" s="17" t="s">
-        <x:v>121</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
@@ -3859,22 +3869,22 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="H16" s="19">
-        <x:v>46069.2178703704</x:v>
+        <x:v>46069.1542013889</x:v>
       </x:c>
       <x:c r="I16" s="19">
-        <x:v>46051</x:v>
+        <x:v>46035</x:v>
       </x:c>
       <x:c r="J16" s="18" t="n">
-        <x:v>1511196</x:v>
+        <x:v>1511206</x:v>
       </x:c>
       <x:c r="K16" s="20" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L16" s="21">
-        <x:v>46097.2456365741</x:v>
+        <x:v>46097.2466550926</x:v>
       </x:c>
       <x:c r="M16" s="17" t="s">
-        <x:v>121</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
@@ -3897,22 +3907,22 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="H17" s="19">
-        <x:v>46083.2443865741</x:v>
+        <x:v>46069.2178703704</x:v>
       </x:c>
       <x:c r="I17" s="19">
-        <x:v>46100</x:v>
+        <x:v>46051</x:v>
       </x:c>
       <x:c r="J17" s="18" t="n">
-        <x:v>1511235</x:v>
+        <x:v>1511196</x:v>
       </x:c>
       <x:c r="K17" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L17" s="21">
-        <x:v>46097.1600115741</x:v>
+        <x:v>46097.2456365741</x:v>
       </x:c>
       <x:c r="M17" s="17" t="s">
-        <x:v>121</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
@@ -3935,22 +3945,22 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="H18" s="19">
-        <x:v>46084.1225115741</x:v>
+        <x:v>46083.2443865741</x:v>
       </x:c>
       <x:c r="I18" s="19">
-        <x:v>46172</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J18" s="18" t="n">
-        <x:v>1511242</x:v>
+        <x:v>1511235</x:v>
       </x:c>
       <x:c r="K18" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L18" s="21">
-        <x:v>46097.3505092593</x:v>
+        <x:v>46097.1600115741</x:v>
       </x:c>
       <x:c r="M18" s="17" t="s">
-        <x:v>121</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
@@ -3973,22 +3983,22 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="H19" s="19">
-        <x:v>46083.2521064815</x:v>
+        <x:v>46084.1225115741</x:v>
       </x:c>
       <x:c r="I19" s="19">
-        <x:v>46100</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J19" s="18" t="n">
-        <x:v>1511236</x:v>
+        <x:v>1511242</x:v>
       </x:c>
       <x:c r="K19" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="21">
-        <x:v>46097.1628935185</x:v>
+        <x:v>46097.3505092593</x:v>
       </x:c>
       <x:c r="M19" s="17" t="s">
-        <x:v>121</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
@@ -4011,22 +4021,22 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="H20" s="19">
-        <x:v>46069.115150463</x:v>
+        <x:v>46083.2521064815</x:v>
       </x:c>
       <x:c r="I20" s="19">
-        <x:v>46172</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J20" s="18" t="n">
-        <x:v>1511241</x:v>
+        <x:v>1511236</x:v>
       </x:c>
       <x:c r="K20" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="21">
-        <x:v>46097.3433796296</x:v>
+        <x:v>46097.1628935185</x:v>
       </x:c>
       <x:c r="M20" s="17" t="s">
-        <x:v>121</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
@@ -4049,33 +4059,33 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="H21" s="19">
-        <x:v>46086.1064814815</x:v>
+        <x:v>46069.115150463</x:v>
       </x:c>
       <x:c r="I21" s="19">
-        <x:v>46095</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J21" s="18" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511241</x:v>
       </x:c>
       <x:c r="K21" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="21">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46097.3433796296</x:v>
       </x:c>
       <x:c r="M21" s="17" t="s">
-        <x:v>52</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B22" s="17" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C22" s="17" t="s">
         <x:v>164</x:v>
       </x:c>
       <x:c r="D22" s="18" t="s">
-        <x:v>27</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E22" s="17" t="s">
         <x:v>165</x:v>
@@ -4087,22 +4097,22 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="H22" s="19">
-        <x:v>46085.1709143519</x:v>
+        <x:v>46086.1064814815</x:v>
       </x:c>
       <x:c r="I22" s="19">
-        <x:v>46085.1709375</x:v>
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J22" s="18" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K22" s="20" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="21">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M22" s="17" t="s">
-        <x:v>168</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
@@ -4110,7 +4120,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C23" s="17" t="s">
-        <x:v>164</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="D23" s="18" t="s">
         <x:v>27</x:v>
@@ -4125,60 +4135,60 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="H23" s="19">
-        <x:v>46085.16625</x:v>
+        <x:v>46085.1709143519</x:v>
       </x:c>
       <x:c r="I23" s="19">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J23" s="18" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K23" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L23" s="21">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M23" s="17" t="s">
-        <x:v>168</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B24" s="17" t="s">
-        <x:v>57</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C24" s="17" t="s">
-        <x:v>129</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="D24" s="18" t="s">
-        <x:v>34</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E24" s="17" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="F24" s="17" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="G24" s="17" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="H24" s="19">
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I24" s="19">
+        <x:v>46085.1662615741</x:v>
+      </x:c>
+      <x:c r="J24" s="18" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K24" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L24" s="21">
+        <x:v>46090.3437268519</x:v>
+      </x:c>
+      <x:c r="M24" s="17" t="s">
         <x:v>172</x:v>
-      </x:c>
-      <x:c r="F24" s="17" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="G24" s="17" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="H24" s="19">
-        <x:v>46084.1080324074</x:v>
-      </x:c>
-      <x:c r="I24" s="19">
-        <x:v>46103</x:v>
-      </x:c>
-      <x:c r="J24" s="18" t="n">
-        <x:v>1511208</x:v>
-      </x:c>
-      <x:c r="K24" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L24" s="21">
-        <x:v>46097.2478125</x:v>
-      </x:c>
-      <x:c r="M24" s="17" t="s">
-        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
@@ -4186,7 +4196,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C25" s="17" t="s">
-        <x:v>175</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D25" s="18" t="s">
         <x:v>34</x:v>
@@ -4201,22 +4211,22 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="H25" s="19">
-        <x:v>46083.0787962963</x:v>
+        <x:v>46084.1080324074</x:v>
       </x:c>
       <x:c r="I25" s="19">
-        <x:v>46084</x:v>
+        <x:v>46103</x:v>
       </x:c>
       <x:c r="J25" s="18" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1511208</x:v>
       </x:c>
       <x:c r="K25" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L25" s="21">
-        <x:v>46083.104224537</x:v>
+        <x:v>46097.2478125</x:v>
       </x:c>
       <x:c r="M25" s="17" t="s">
-        <x:v>52</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
@@ -4224,34 +4234,34 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C26" s="17" t="s">
-        <x:v>160</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="D26" s="18" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E26" s="17" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="F26" s="17" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G26" s="17" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H26" s="19">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I26" s="19">
-        <x:v>46097</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J26" s="18" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1511639</x:v>
       </x:c>
       <x:c r="K26" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L26" s="21">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46083.104224537</x:v>
       </x:c>
       <x:c r="M26" s="17" t="s">
         <x:v>52</x:v>
@@ -4262,34 +4272,34 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C27" s="17" t="s">
-        <x:v>160</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="D27" s="18" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E27" s="17" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="F27" s="17" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="G27" s="17" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H27" s="19">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46086.0997916667</x:v>
       </x:c>
       <x:c r="I27" s="19">
-        <x:v>46104</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="J27" s="18" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511758</x:v>
       </x:c>
       <x:c r="K27" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L27" s="21">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46090.2691087963</x:v>
       </x:c>
       <x:c r="M27" s="17" t="s">
         <x:v>52</x:v>
@@ -4300,34 +4310,34 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C28" s="17" t="s">
-        <x:v>160</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="D28" s="18" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E28" s="17" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="F28" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="G28" s="17" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="H28" s="19">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46086.1144444444</x:v>
       </x:c>
       <x:c r="I28" s="19">
-        <x:v>46098</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="J28" s="18" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511759</x:v>
       </x:c>
       <x:c r="K28" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L28" s="21">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46090.2703703704</x:v>
       </x:c>
       <x:c r="M28" s="17" t="s">
         <x:v>52</x:v>
@@ -4335,10 +4345,10 @@
     </x:row>
     <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B29" s="17" t="s">
-        <x:v>99</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C29" s="17" t="s">
-        <x:v>188</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="D29" s="18" t="s">
         <x:v>34</x:v>
@@ -4353,113 +4363,150 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="H29" s="19">
-        <x:v>46098.2908796296</x:v>
+        <x:v>46087.1643287037</x:v>
       </x:c>
       <x:c r="I29" s="19">
-        <x:v>45997</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J29" s="18" t="n">
-        <x:v>1511858</x:v>
+        <x:v>1511760</x:v>
       </x:c>
       <x:c r="K29" s="20" t="n">
-        <x:v>2550</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L29" s="21">
-        <x:v>46098.3188657407</x:v>
+        <x:v>46090.2727777778</x:v>
       </x:c>
       <x:c r="M29" s="17" t="s">
         <x:v>52</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="17" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C30" s="17" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D30" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E30" s="17" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="F30" s="17" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="G30" s="17" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="H30" s="19">
+        <x:v>46098.2908796296</x:v>
+      </x:c>
+      <x:c r="I30" s="19">
+        <x:v>45997</x:v>
+      </x:c>
+      <x:c r="J30" s="18" t="n">
+        <x:v>1511858</x:v>
+      </x:c>
+      <x:c r="K30" s="20" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L30" s="21">
+        <x:v>46098.3188657407</x:v>
+      </x:c>
+      <x:c r="M30" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="32" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B32" s="22" t="s">
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B33" s="22" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="C32" s="23" t="s"/>
-      <x:c r="D32" s="23" t="s"/>
-      <x:c r="E32" s="24" t="s"/>
-      <x:c r="F32" s="24" t="s"/>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B33" s="25" t="s">
+      <x:c r="C33" s="23" t="s"/>
+      <x:c r="D33" s="23" t="s"/>
+      <x:c r="E33" s="24" t="s"/>
+      <x:c r="F33" s="24" t="s"/>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B34" s="25" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C33" s="26" t="s"/>
-      <x:c r="D33" s="26" t="s"/>
-      <x:c r="E33" s="26" t="s"/>
-      <x:c r="F33" s="27" t="s">
+      <x:c r="C34" s="26" t="s"/>
+      <x:c r="D34" s="26" t="s"/>
+      <x:c r="E34" s="26" t="s"/>
+      <x:c r="F34" s="27" t="s">
         <x:v>106</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C34" s="29" t="s"/>
-      <x:c r="D34" s="29" t="s"/>
-      <x:c r="E34" s="29" t="s"/>
-      <x:c r="F34" s="30" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
       <x:c r="B35" s="28" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C35" s="29" t="s"/>
       <x:c r="D35" s="29" t="s"/>
       <x:c r="E35" s="29" t="s"/>
       <x:c r="F35" s="30" t="n">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="18" customHeight="1">
       <x:c r="B36" s="28" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C36" s="29" t="s"/>
       <x:c r="D36" s="29" t="s"/>
       <x:c r="E36" s="29" t="s"/>
       <x:c r="F36" s="30" t="n">
-        <x:v>2</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="18" customHeight="1">
       <x:c r="B37" s="28" t="s">
-        <x:v>57</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C37" s="29" t="s"/>
       <x:c r="D37" s="29" t="s"/>
       <x:c r="E37" s="29" t="s"/>
       <x:c r="F37" s="30" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="18" customHeight="1">
       <x:c r="B38" s="28" t="s">
-        <x:v>99</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C38" s="29" t="s"/>
       <x:c r="D38" s="29" t="s"/>
       <x:c r="E38" s="29" t="s"/>
       <x:c r="F38" s="30" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B39" s="28" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C39" s="29" t="s"/>
+      <x:c r="D39" s="29" t="s"/>
+      <x:c r="E39" s="29" t="s"/>
+      <x:c r="F39" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B39" s="31" t="s">
+    <x:row r="40" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B40" s="31" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="C39" s="32" t="s"/>
-      <x:c r="D39" s="32" t="s"/>
-      <x:c r="E39" s="32" t="s"/>
-      <x:c r="F39" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C40" s="32" t="s"/>
+      <x:c r="D40" s="32" t="s"/>
+      <x:c r="E40" s="32" t="s"/>
+      <x:c r="F40" s="33" t="n">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
     <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5419,14 +5466,14 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B32:F32"/>
-    <x:mergeCell ref="B33:E33"/>
+    <x:mergeCell ref="B33:F33"/>
     <x:mergeCell ref="B34:E34"/>
     <x:mergeCell ref="B35:E35"/>
     <x:mergeCell ref="B36:E36"/>
     <x:mergeCell ref="B37:E37"/>
     <x:mergeCell ref="B38:E38"/>
     <x:mergeCell ref="B39:E39"/>
+    <x:mergeCell ref="B40:E40"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="209">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -424,6 +424,21 @@
     <x:t>43A-3-2026-1154-964</x:t>
   </x:si>
   <x:si>
+    <x:t>CELLBLITZ MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LG05 SM MARKETMALL, BUROL I, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-010R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1089-192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Caesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELLTY MOBILE INC</x:t>
   </x:si>
   <x:si>
@@ -469,6 +484,18 @@
     <x:t>43A-2-2026-1086-471</x:t>
   </x:si>
   <x:si>
+    <x:t>HLH GENTECH INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SM CENTER ILLUSTRE AVE, DISTRICT IV, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1097-702</x:t>
+  </x:si>
+  <x:si>
     <x:t>INTO GADGETS TOO INC.</x:t>
   </x:si>
   <x:si>
@@ -517,6 +544,18 @@
     <x:t>43A-2-2026-1083-282</x:t>
   </x:si>
   <x:si>
+    <x:t>TEQWARE PHONES AND ACCESSORIES INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYALA MALLS SERIN JUNCTION EAST, SILANG, Tagaytay City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-20-01-0883</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1087-228</x:t>
+  </x:si>
+  <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
   </x:si>
   <x:si>
@@ -532,6 +571,18 @@
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
+    <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2519</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1171-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ricardo Natividad</x:t>
+  </x:si>
+  <x:si>
     <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
   </x:si>
   <x:si>
@@ -541,18 +592,6 @@
     <x:t>43A-3-2026-1172-434</x:t>
   </x:si>
   <x:si>
-    <x:t>Ricardo Natividad</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-2519</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1171-081</x:t>
-  </x:si>
-  <x:si>
     <x:t>WALTERMART TANAUAN 225 WALTERMART JPL-HWAY, DARASA, City Of Tanauan, Batangas</x:t>
   </x:si>
   <x:si>
@@ -574,6 +613,15 @@
     <x:t>43A-3-2026-1146-031</x:t>
   </x:si>
   <x:si>
+    <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2106</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1176-385</x:t>
+  </x:si>
+  <x:si>
     <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -590,15 +638,6 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1175-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-18-02-2106</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1176-385</x:t>
   </x:si>
   <x:si>
     <x:t>CELLBOY INC.</x:t>
@@ -3793,22 +3832,22 @@
         <x:v>136</x:v>
       </x:c>
       <x:c r="H14" s="19">
-        <x:v>46084.0854513889</x:v>
+        <x:v>46069.2785648148</x:v>
       </x:c>
       <x:c r="I14" s="19">
-        <x:v>46144</x:v>
+        <x:v>46067</x:v>
       </x:c>
       <x:c r="J14" s="18" t="n">
-        <x:v>1511225</x:v>
+        <x:v>1511276</x:v>
       </x:c>
       <x:c r="K14" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L14" s="21">
-        <x:v>46093.3956365741</x:v>
+        <x:v>46100.3884027778</x:v>
       </x:c>
       <x:c r="M14" s="17" t="s">
-        <x:v>125</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
@@ -3816,34 +3855,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C15" s="17" t="s">
-        <x:v>133</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D15" s="18" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E15" s="17" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F15" s="17" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G15" s="17" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H15" s="19">
-        <x:v>46084.0996759259</x:v>
+        <x:v>46084.0854513889</x:v>
       </x:c>
       <x:c r="I15" s="19">
-        <x:v>46094</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J15" s="18" t="n">
-        <x:v>1511192</x:v>
+        <x:v>1511225</x:v>
       </x:c>
       <x:c r="K15" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="21">
-        <x:v>46097.2414583333</x:v>
+        <x:v>46093.3956365741</x:v>
       </x:c>
       <x:c r="M15" s="17" t="s">
         <x:v>125</x:v>
@@ -3854,34 +3893,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C16" s="17" t="s">
-        <x:v>140</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D16" s="18" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E16" s="17" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F16" s="17" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G16" s="17" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H16" s="19">
-        <x:v>46069.1542013889</x:v>
+        <x:v>46084.0996759259</x:v>
       </x:c>
       <x:c r="I16" s="19">
-        <x:v>46035</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J16" s="18" t="n">
-        <x:v>1511206</x:v>
+        <x:v>1511192</x:v>
       </x:c>
       <x:c r="K16" s="20" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="21">
-        <x:v>46097.2466550926</x:v>
+        <x:v>46097.2414583333</x:v>
       </x:c>
       <x:c r="M16" s="17" t="s">
         <x:v>125</x:v>
@@ -3892,34 +3931,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C17" s="17" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D17" s="18" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E17" s="17" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="F17" s="17" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G17" s="17" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="H17" s="19">
-        <x:v>46069.2178703704</x:v>
+        <x:v>46069.1542013889</x:v>
       </x:c>
       <x:c r="I17" s="19">
-        <x:v>46051</x:v>
+        <x:v>46035</x:v>
       </x:c>
       <x:c r="J17" s="18" t="n">
-        <x:v>1511196</x:v>
+        <x:v>1511206</x:v>
       </x:c>
       <x:c r="K17" s="20" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L17" s="21">
-        <x:v>46097.2456365741</x:v>
+        <x:v>46097.2466550926</x:v>
       </x:c>
       <x:c r="M17" s="17" t="s">
         <x:v>125</x:v>
@@ -3930,34 +3969,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C18" s="17" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D18" s="18" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E18" s="17" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="F18" s="17" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G18" s="17" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="H18" s="19">
-        <x:v>46083.2443865741</x:v>
+        <x:v>46069.2178703704</x:v>
       </x:c>
       <x:c r="I18" s="19">
-        <x:v>46100</x:v>
+        <x:v>46051</x:v>
       </x:c>
       <x:c r="J18" s="18" t="n">
-        <x:v>1511235</x:v>
+        <x:v>1511196</x:v>
       </x:c>
       <x:c r="K18" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L18" s="21">
-        <x:v>46097.1600115741</x:v>
+        <x:v>46097.2456365741</x:v>
       </x:c>
       <x:c r="M18" s="17" t="s">
         <x:v>125</x:v>
@@ -3968,37 +4007,37 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C19" s="17" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="D19" s="18" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E19" s="17" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="F19" s="17" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="G19" s="17" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H19" s="19">
-        <x:v>46084.1225115741</x:v>
+        <x:v>46069.3717592593</x:v>
       </x:c>
       <x:c r="I19" s="19">
-        <x:v>46172</x:v>
+        <x:v>46066</x:v>
       </x:c>
       <x:c r="J19" s="18" t="n">
-        <x:v>1511242</x:v>
+        <x:v>1511274</x:v>
       </x:c>
       <x:c r="K19" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L19" s="21">
-        <x:v>46097.3505092593</x:v>
+        <x:v>46100.3754861111</x:v>
       </x:c>
       <x:c r="M19" s="17" t="s">
-        <x:v>125</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
@@ -4006,34 +4045,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C20" s="17" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D20" s="18" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E20" s="17" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="F20" s="17" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="G20" s="17" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="H20" s="19">
-        <x:v>46083.2521064815</x:v>
+        <x:v>46083.2443865741</x:v>
       </x:c>
       <x:c r="I20" s="19">
         <x:v>46100</x:v>
       </x:c>
       <x:c r="J20" s="18" t="n">
-        <x:v>1511236</x:v>
+        <x:v>1511235</x:v>
       </x:c>
       <x:c r="K20" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="21">
-        <x:v>46097.1628935185</x:v>
+        <x:v>46097.1600115741</x:v>
       </x:c>
       <x:c r="M20" s="17" t="s">
         <x:v>125</x:v>
@@ -4044,34 +4083,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C21" s="17" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D21" s="18" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E21" s="17" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="F21" s="17" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G21" s="17" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="H21" s="19">
-        <x:v>46069.115150463</x:v>
+        <x:v>46084.1225115741</x:v>
       </x:c>
       <x:c r="I21" s="19">
         <x:v>46172</x:v>
       </x:c>
       <x:c r="J21" s="18" t="n">
-        <x:v>1511241</x:v>
+        <x:v>1511242</x:v>
       </x:c>
       <x:c r="K21" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="21">
-        <x:v>46097.3433796296</x:v>
+        <x:v>46097.3505092593</x:v>
       </x:c>
       <x:c r="M21" s="17" t="s">
         <x:v>125</x:v>
@@ -4082,227 +4121,227 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C22" s="17" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="D22" s="18" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E22" s="17" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="F22" s="17" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="G22" s="17" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H22" s="19">
-        <x:v>46086.1064814815</x:v>
+        <x:v>46083.2521064815</x:v>
       </x:c>
       <x:c r="I22" s="19">
-        <x:v>46095</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J22" s="18" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511236</x:v>
       </x:c>
       <x:c r="K22" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="21">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46097.1628935185</x:v>
       </x:c>
       <x:c r="M22" s="17" t="s">
-        <x:v>52</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B23" s="17" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C23" s="17" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D23" s="18" t="s">
-        <x:v>27</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E23" s="17" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="F23" s="17" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G23" s="17" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H23" s="19">
-        <x:v>46085.1709143519</x:v>
+        <x:v>46069.115150463</x:v>
       </x:c>
       <x:c r="I23" s="19">
-        <x:v>46085.1709375</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J23" s="18" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1511241</x:v>
       </x:c>
       <x:c r="K23" s="20" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="21">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46097.3433796296</x:v>
       </x:c>
       <x:c r="M23" s="17" t="s">
-        <x:v>172</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B24" s="17" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C24" s="17" t="s">
-        <x:v>168</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="D24" s="18" t="s">
-        <x:v>27</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E24" s="17" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="F24" s="17" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="G24" s="17" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="H24" s="19">
-        <x:v>46085.16625</x:v>
+        <x:v>46069.2327893519</x:v>
       </x:c>
       <x:c r="I24" s="19">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46049</x:v>
       </x:c>
       <x:c r="J24" s="18" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1511275</x:v>
       </x:c>
       <x:c r="K24" s="20" t="n">
-        <x:v>3530</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L24" s="21">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46100.3816782407</x:v>
       </x:c>
       <x:c r="M24" s="17" t="s">
-        <x:v>172</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B25" s="17" t="s">
-        <x:v>57</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C25" s="17" t="s">
-        <x:v>133</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="D25" s="18" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E25" s="17" t="s">
-        <x:v>176</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="F25" s="17" t="s">
-        <x:v>177</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="G25" s="17" t="s">
-        <x:v>178</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="H25" s="19">
-        <x:v>46084.1080324074</x:v>
+        <x:v>46086.1064814815</x:v>
       </x:c>
       <x:c r="I25" s="19">
-        <x:v>46103</x:v>
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J25" s="18" t="n">
-        <x:v>1511208</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K25" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L25" s="21">
-        <x:v>46097.2478125</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M25" s="17" t="s">
-        <x:v>125</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B26" s="17" t="s">
-        <x:v>57</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C26" s="17" t="s">
-        <x:v>179</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="D26" s="18" t="s">
-        <x:v>34</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E26" s="17" t="s">
-        <x:v>180</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="F26" s="17" t="s">
-        <x:v>181</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G26" s="17" t="s">
-        <x:v>182</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="H26" s="19">
-        <x:v>46083.0787962963</x:v>
+        <x:v>46085.16625</x:v>
       </x:c>
       <x:c r="I26" s="19">
-        <x:v>46084</x:v>
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J26" s="18" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K26" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L26" s="21">
-        <x:v>46083.104224537</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M26" s="17" t="s">
-        <x:v>52</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B27" s="17" t="s">
-        <x:v>57</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C27" s="17" t="s">
-        <x:v>164</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="D27" s="18" t="s">
-        <x:v>34</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E27" s="17" t="s">
-        <x:v>183</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="F27" s="17" t="s">
-        <x:v>184</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="G27" s="17" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="H27" s="19">
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I27" s="19">
+        <x:v>46085.1709375</x:v>
+      </x:c>
+      <x:c r="J27" s="18" t="n">
+        <x:v>1507965</x:v>
+      </x:c>
+      <x:c r="K27" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L27" s="21">
+        <x:v>46090.3336921296</x:v>
+      </x:c>
+      <x:c r="M27" s="17" t="s">
         <x:v>185</x:v>
-      </x:c>
-      <x:c r="H27" s="19">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I27" s="19">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="J27" s="18" t="n">
-        <x:v>1511758</x:v>
-      </x:c>
-      <x:c r="K27" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="21">
-        <x:v>46090.2691087963</x:v>
-      </x:c>
-      <x:c r="M27" s="17" t="s">
-        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
@@ -4310,37 +4349,37 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C28" s="17" t="s">
-        <x:v>164</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D28" s="18" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E28" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="F28" s="17" t="s">
-        <x:v>187</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G28" s="17" t="s">
-        <x:v>188</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="H28" s="19">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46084.1080324074</x:v>
       </x:c>
       <x:c r="I28" s="19">
-        <x:v>46097</x:v>
+        <x:v>46103</x:v>
       </x:c>
       <x:c r="J28" s="18" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1511208</x:v>
       </x:c>
       <x:c r="K28" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L28" s="21">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46097.2478125</x:v>
       </x:c>
       <x:c r="M28" s="17" t="s">
-        <x:v>52</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
@@ -4348,34 +4387,34 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C29" s="17" t="s">
-        <x:v>164</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D29" s="18" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E29" s="17" t="s">
-        <x:v>189</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="F29" s="17" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G29" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H29" s="19">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I29" s="19">
-        <x:v>46104</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J29" s="18" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511639</x:v>
       </x:c>
       <x:c r="K29" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L29" s="21">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46083.104224537</x:v>
       </x:c>
       <x:c r="M29" s="17" t="s">
         <x:v>52</x:v>
@@ -4383,133 +4422,244 @@
     </x:row>
     <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B30" s="17" t="s">
-        <x:v>99</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C30" s="17" t="s">
-        <x:v>192</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="D30" s="18" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E30" s="17" t="s">
-        <x:v>193</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="F30" s="17" t="s">
-        <x:v>194</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="G30" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="H30" s="19">
-        <x:v>46098.2908796296</x:v>
+        <x:v>46087.1643287037</x:v>
       </x:c>
       <x:c r="I30" s="19">
-        <x:v>45997</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J30" s="18" t="n">
-        <x:v>1511858</x:v>
+        <x:v>1511760</x:v>
       </x:c>
       <x:c r="K30" s="20" t="n">
-        <x:v>2550</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L30" s="21">
-        <x:v>46098.3188657407</x:v>
+        <x:v>46090.2727777778</x:v>
       </x:c>
       <x:c r="M30" s="17" t="s">
         <x:v>52</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="33" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B33" s="22" t="s">
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C31" s="17" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="D31" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E31" s="17" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="F31" s="17" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G31" s="17" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="H31" s="19">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I31" s="19">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J31" s="18" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K31" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="21">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M31" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C32" s="17" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="D32" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E32" s="17" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="F32" s="17" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G32" s="17" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="H32" s="19">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I32" s="19">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J32" s="18" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K32" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L32" s="21">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M32" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="17" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C33" s="17" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D33" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E33" s="17" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="F33" s="17" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G33" s="17" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="H33" s="19">
+        <x:v>46098.2908796296</x:v>
+      </x:c>
+      <x:c r="I33" s="19">
+        <x:v>45997</x:v>
+      </x:c>
+      <x:c r="J33" s="18" t="n">
+        <x:v>1511858</x:v>
+      </x:c>
+      <x:c r="K33" s="20" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L33" s="21">
+        <x:v>46098.3188657407</x:v>
+      </x:c>
+      <x:c r="M33" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B36" s="22" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="C33" s="23" t="s"/>
-      <x:c r="D33" s="23" t="s"/>
-      <x:c r="E33" s="24" t="s"/>
-      <x:c r="F33" s="24" t="s"/>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B34" s="25" t="s">
+      <x:c r="C36" s="23" t="s"/>
+      <x:c r="D36" s="23" t="s"/>
+      <x:c r="E36" s="24" t="s"/>
+      <x:c r="F36" s="24" t="s"/>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B37" s="25" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C34" s="26" t="s"/>
-      <x:c r="D34" s="26" t="s"/>
-      <x:c r="E34" s="26" t="s"/>
-      <x:c r="F34" s="27" t="s">
+      <x:c r="C37" s="26" t="s"/>
+      <x:c r="D37" s="26" t="s"/>
+      <x:c r="E37" s="26" t="s"/>
+      <x:c r="F37" s="27" t="s">
         <x:v>106</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C35" s="29" t="s"/>
-      <x:c r="D35" s="29" t="s"/>
-      <x:c r="E35" s="29" t="s"/>
-      <x:c r="F35" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="28" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C36" s="29" t="s"/>
-      <x:c r="D36" s="29" t="s"/>
-      <x:c r="E36" s="29" t="s"/>
-      <x:c r="F36" s="30" t="n">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B37" s="28" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C37" s="29" t="s"/>
-      <x:c r="D37" s="29" t="s"/>
-      <x:c r="E37" s="29" t="s"/>
-      <x:c r="F37" s="30" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="18" customHeight="1">
       <x:c r="B38" s="28" t="s">
-        <x:v>57</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C38" s="29" t="s"/>
       <x:c r="D38" s="29" t="s"/>
       <x:c r="E38" s="29" t="s"/>
       <x:c r="F38" s="30" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="18" customHeight="1">
       <x:c r="B39" s="28" t="s">
-        <x:v>99</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C39" s="29" t="s"/>
       <x:c r="D39" s="29" t="s"/>
       <x:c r="E39" s="29" t="s"/>
       <x:c r="F39" s="30" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B40" s="28" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C40" s="29" t="s"/>
+      <x:c r="D40" s="29" t="s"/>
+      <x:c r="E40" s="29" t="s"/>
+      <x:c r="F40" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B41" s="28" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C41" s="29" t="s"/>
+      <x:c r="D41" s="29" t="s"/>
+      <x:c r="E41" s="29" t="s"/>
+      <x:c r="F41" s="30" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B42" s="28" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C42" s="29" t="s"/>
+      <x:c r="D42" s="29" t="s"/>
+      <x:c r="E42" s="29" t="s"/>
+      <x:c r="F42" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B40" s="31" t="s">
+    <x:row r="43" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B43" s="31" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="C40" s="32" t="s"/>
-      <x:c r="D40" s="32" t="s"/>
-      <x:c r="E40" s="32" t="s"/>
-      <x:c r="F40" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C43" s="32" t="s"/>
+      <x:c r="D43" s="32" t="s"/>
+      <x:c r="E43" s="32" t="s"/>
+      <x:c r="F43" s="33" t="n">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5466,14 +5616,14 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B33:F33"/>
-    <x:mergeCell ref="B34:E34"/>
-    <x:mergeCell ref="B35:E35"/>
-    <x:mergeCell ref="B36:E36"/>
+    <x:mergeCell ref="B36:F36"/>
     <x:mergeCell ref="B37:E37"/>
     <x:mergeCell ref="B38:E38"/>
     <x:mergeCell ref="B39:E39"/>
     <x:mergeCell ref="B40:E40"/>
+    <x:mergeCell ref="B41:E41"/>
+    <x:mergeCell ref="B42:E42"/>
+    <x:mergeCell ref="B43:E43"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="209">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="252">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -85,6 +85,9 @@
     <x:t>43A-2-2026-1081-190</x:t>
   </x:si>
   <x:si>
+    <x:t>1506161</x:t>
+  </x:si>
+  <x:si>
     <x:t>Nerrisa Manalo</x:t>
   </x:si>
   <x:si>
@@ -100,6 +103,9 @@
     <x:t>43A-2-2026-1082-997</x:t>
   </x:si>
   <x:si>
+    <x:t>1506159</x:t>
+  </x:si>
+  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -118,6 +124,9 @@
     <x:t>43A-2-2026-1080-857</x:t>
   </x:si>
   <x:si>
+    <x:t>1505803</x:t>
+  </x:si>
+  <x:si>
     <x:t>Deniel Puyo</x:t>
   </x:si>
   <x:si>
@@ -139,6 +148,9 @@
     <x:t>43A-2-2026-1078-427</x:t>
   </x:si>
   <x:si>
+    <x:t>1505804</x:t>
+  </x:si>
+  <x:si>
     <x:t>MOBILETOOLS VENTURE INC</x:t>
   </x:si>
   <x:si>
@@ -151,6 +163,9 @@
     <x:t>43A-2-2026-1079-778</x:t>
   </x:si>
   <x:si>
+    <x:t>1505805</x:t>
+  </x:si>
+  <x:si>
     <x:t>TECHNOKID CELLPHONE CENTER INC.</x:t>
   </x:si>
   <x:si>
@@ -163,6 +178,9 @@
     <x:t>43A-2-2026-1070-812</x:t>
   </x:si>
   <x:si>
+    <x:t>1511010</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ceasar Allen Centeno</x:t>
   </x:si>
   <x:si>
@@ -181,6 +199,9 @@
     <x:t>43A-2-2026-1135-273</x:t>
   </x:si>
   <x:si>
+    <x:t>1511622</x:t>
+  </x:si>
+  <x:si>
     <x:t>Adora Mercado</x:t>
   </x:si>
   <x:si>
@@ -196,6 +217,9 @@
     <x:t>43A-2-2026-1134-784</x:t>
   </x:si>
   <x:si>
+    <x:t>1511627</x:t>
+  </x:si>
+  <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -211,6 +235,9 @@
     <x:t>43A-2-2026-1139-014</x:t>
   </x:si>
   <x:si>
+    <x:t>1511623</x:t>
+  </x:si>
+  <x:si>
     <x:t>GREENTELCOM CELLPHONE &amp; ACCESSORIES CENTER  (TECNO STORE)</x:t>
   </x:si>
   <x:si>
@@ -223,6 +250,9 @@
     <x:t>43A-2-2026-1129-801</x:t>
   </x:si>
   <x:si>
+    <x:t>1511631</x:t>
+  </x:si>
+  <x:si>
     <x:t>GREENTELCOM CELLPHONE AND ACCESSORIES CENTER (HONOR STORE )</x:t>
   </x:si>
   <x:si>
@@ -235,6 +265,9 @@
     <x:t>43A-2-2026-1128-999</x:t>
   </x:si>
   <x:si>
+    <x:t>1511630</x:t>
+  </x:si>
+  <x:si>
     <x:t>GREENTELCOMMUNICATIONS TRADING INC.</x:t>
   </x:si>
   <x:si>
@@ -247,6 +280,9 @@
     <x:t>43A-2-2026-1136-850</x:t>
   </x:si>
   <x:si>
+    <x:t>1511626</x:t>
+  </x:si>
+  <x:si>
     <x:t>GREENTELCOMMUNICATIONS TRADING INC. (GREENTELCOM STORE)</x:t>
   </x:si>
   <x:si>
@@ -259,6 +295,9 @@
     <x:t>43A-2-2026-1142-741</x:t>
   </x:si>
   <x:si>
+    <x:t>1511635</x:t>
+  </x:si>
+  <x:si>
     <x:t>GREENTELCOMMUNICATIONS TRADING INC. (HONOR STORE )</x:t>
   </x:si>
   <x:si>
@@ -298,6 +337,9 @@
     <x:t>43A-2-2026-1138-367</x:t>
   </x:si>
   <x:si>
+    <x:t>1511624</x:t>
+  </x:si>
+  <x:si>
     <x:t>GREENTELCOMMUNICATIONS TRADING INC.(GREENTELCOM STORE)</x:t>
   </x:si>
   <x:si>
@@ -307,6 +349,9 @@
     <x:t>43A-2-2026-1137-243</x:t>
   </x:si>
   <x:si>
+    <x:t>1511625</x:t>
+  </x:si>
+  <x:si>
     <x:t>Service Center Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -322,6 +367,9 @@
     <x:t>43A-2-2026-1067-112</x:t>
   </x:si>
   <x:si>
+    <x:t>1510925</x:t>
+  </x:si>
+  <x:si>
     <x:t>Service Center Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -337,6 +385,9 @@
     <x:t>43A-2-2026-1099-127</x:t>
   </x:si>
   <x:si>
+    <x:t>1511502</x:t>
+  </x:si>
+  <x:si>
     <x:t>SUMMARY</x:t>
   </x:si>
   <x:si>
@@ -364,6 +415,9 @@
     <x:t>43A-3-2026-1207-652</x:t>
   </x:si>
   <x:si>
+    <x:t>1511906</x:t>
+  </x:si>
+  <x:si>
     <x:t>HERALD BEBIS</x:t>
   </x:si>
   <x:si>
@@ -376,6 +430,9 @@
     <x:t>43A-3-2026-1189-403</x:t>
   </x:si>
   <x:si>
+    <x:t>1511778</x:t>
+  </x:si>
+  <x:si>
     <x:t>JAKE C. PASILAN</x:t>
   </x:si>
   <x:si>
@@ -388,6 +445,9 @@
     <x:t>43A-3-2026-1198-002</x:t>
   </x:si>
   <x:si>
+    <x:t>1511815</x:t>
+  </x:si>
+  <x:si>
     <x:t>BSD INTERNATIONAL MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -400,6 +460,9 @@
     <x:t>43A-2-2026-1144-933</x:t>
   </x:si>
   <x:si>
+    <x:t>1511232</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cesar Allen Centeno</x:t>
   </x:si>
   <x:si>
@@ -412,6 +475,9 @@
     <x:t>43A-3-2026-1151-716</x:t>
   </x:si>
   <x:si>
+    <x:t>1511234</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELL EVER MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -424,6 +490,9 @@
     <x:t>43A-3-2026-1154-964</x:t>
   </x:si>
   <x:si>
+    <x:t>1511237</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELLBLITZ MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -436,6 +505,9 @@
     <x:t>43A-2-2026-1089-192</x:t>
   </x:si>
   <x:si>
+    <x:t>1511276</x:t>
+  </x:si>
+  <x:si>
     <x:t>Caesar Allen Centeno</x:t>
   </x:si>
   <x:si>
@@ -451,6 +523,9 @@
     <x:t>43A-3-2026-1155-834</x:t>
   </x:si>
   <x:si>
+    <x:t>1511225</x:t>
+  </x:si>
+  <x:si>
     <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
   </x:si>
   <x:si>
@@ -460,6 +535,9 @@
     <x:t>43A-3-2026-1156-896</x:t>
   </x:si>
   <x:si>
+    <x:t>1511192</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -472,6 +550,9 @@
     <x:t>43A-2-2026-1085-453</x:t>
   </x:si>
   <x:si>
+    <x:t>1511206</x:t>
+  </x:si>
+  <x:si>
     <x:t>CLIXTEC INC.</x:t>
   </x:si>
   <x:si>
@@ -484,6 +565,9 @@
     <x:t>43A-2-2026-1086-471</x:t>
   </x:si>
   <x:si>
+    <x:t>1511196</x:t>
+  </x:si>
+  <x:si>
     <x:t>HLH GENTECH INC.</x:t>
   </x:si>
   <x:si>
@@ -496,6 +580,9 @@
     <x:t>43A-2-2026-1097-702</x:t>
   </x:si>
   <x:si>
+    <x:t>1511274</x:t>
+  </x:si>
+  <x:si>
     <x:t>INTO GADGETS TOO INC.</x:t>
   </x:si>
   <x:si>
@@ -508,6 +595,9 @@
     <x:t>43A-3-2026-1152-831</x:t>
   </x:si>
   <x:si>
+    <x:t>1511235</x:t>
+  </x:si>
+  <x:si>
     <x:t>MOBILECRAZE TELECOM INC</x:t>
   </x:si>
   <x:si>
@@ -520,6 +610,9 @@
     <x:t>43A-3-2026-1159-651</x:t>
   </x:si>
   <x:si>
+    <x:t>1511242</x:t>
+  </x:si>
+  <x:si>
     <x:t>ONE DOTCOM CELL INC.</x:t>
   </x:si>
   <x:si>
@@ -532,6 +625,9 @@
     <x:t>43A-3-2026-1153-796</x:t>
   </x:si>
   <x:si>
+    <x:t>1511236</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYNCNETIC INC.</x:t>
   </x:si>
   <x:si>
@@ -544,6 +640,9 @@
     <x:t>43A-2-2026-1083-282</x:t>
   </x:si>
   <x:si>
+    <x:t>1511241</x:t>
+  </x:si>
+  <x:si>
     <x:t>TEQWARE PHONES AND ACCESSORIES INC.</x:t>
   </x:si>
   <x:si>
@@ -556,6 +655,9 @@
     <x:t>43A-2-2026-1087-228</x:t>
   </x:si>
   <x:si>
+    <x:t>1511275</x:t>
+  </x:si>
+  <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
   </x:si>
   <x:si>
@@ -568,6 +670,9 @@
     <x:t>43A-3-2026-1174-419</x:t>
   </x:si>
   <x:si>
+    <x:t>1511761</x:t>
+  </x:si>
+  <x:si>
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
@@ -580,6 +685,9 @@
     <x:t>43A-3-2026-1171-081</x:t>
   </x:si>
   <x:si>
+    <x:t>1507966</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ricardo Natividad</x:t>
   </x:si>
   <x:si>
@@ -592,6 +700,9 @@
     <x:t>43A-3-2026-1172-434</x:t>
   </x:si>
   <x:si>
+    <x:t>1507965</x:t>
+  </x:si>
+  <x:si>
     <x:t>WALTERMART TANAUAN 225 WALTERMART JPL-HWAY, DARASA, City Of Tanauan, Batangas</x:t>
   </x:si>
   <x:si>
@@ -601,6 +712,9 @@
     <x:t>43A-3-2026-1157-256</x:t>
   </x:si>
   <x:si>
+    <x:t>1511208</x:t>
+  </x:si>
+  <x:si>
     <x:t>INNOVASIA MARKETING</x:t>
   </x:si>
   <x:si>
@@ -613,6 +727,9 @@
     <x:t>43A-3-2026-1146-031</x:t>
   </x:si>
   <x:si>
+    <x:t>1511639</x:t>
+  </x:si>
+  <x:si>
     <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
   </x:si>
   <x:si>
@@ -622,6 +739,9 @@
     <x:t>43A-3-2026-1176-385</x:t>
   </x:si>
   <x:si>
+    <x:t>1511760</x:t>
+  </x:si>
+  <x:si>
     <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -631,6 +751,9 @@
     <x:t>43A-3-2026-1173-016</x:t>
   </x:si>
   <x:si>
+    <x:t>1511758</x:t>
+  </x:si>
+  <x:si>
     <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
   </x:si>
   <x:si>
@@ -640,6 +763,9 @@
     <x:t>43A-3-2026-1175-710</x:t>
   </x:si>
   <x:si>
+    <x:t>1511759</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELLBOY INC.</x:t>
   </x:si>
   <x:si>
@@ -650,6 +776,9 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1205-403</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511858</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -661,7 +790,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -730,13 +859,6 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
@@ -988,7 +1110,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="28">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1029,50 +1151,41 @@
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1120,6 +1233,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1131,71 +1248,55 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1576,7 +1677,7 @@
       <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s"/>
+      <x:c r="D8" s="15" t="s"/>
       <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1586,23 +1687,23 @@
       <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46069.0835185185</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46069.1006712963</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1506161</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="H8" s="16">
+        <x:v>46069.0835222569</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46069.1006819792</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46069.1133333333</x:v>
+      <x:c r="L8" s="18">
+        <x:v>46069.1133347338</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -1610,828 +1711,828 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s"/>
+      <x:c r="E9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46069.0835757523</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46069.1000300231</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L9" s="18">
+        <x:v>46069.1128697454</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46069.0835648148</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46069.1000231481</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1506159</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46069.1128587963</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="E10" s="17" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="F10" s="17" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G10" s="17" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H10" s="19">
-        <x:v>46067.3600231481</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>46067.3600462963</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="F10" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46067.3600302778</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46067.3600485417</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>46079.2730092593</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>31</x:v>
+      <x:c r="L10" s="18">
+        <x:v>46079.273015787</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
+      <x:c r="B11" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46067.1596693866</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>46079.277259919</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E11" s="17" t="s">
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
+      <x:c r="C12" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="H11" s="19">
-        <x:v>46067.1596643518</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="E12" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46067.222213287</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46089</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>46079.2763165278</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>46063.1352781944</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="18">
+        <x:v>46063.2367775347</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46079.3584810995</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46079.3584983796</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L14" s="18">
+        <x:v>46080.2311256134</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>46079.3539738194</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46079.3539910417</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L15" s="18">
+        <x:v>46080.244091956</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>46079.3873177662</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1505804</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="J16" s="15" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>46079.2772569444</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E12" s="17" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>46067.2222106481</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>46089</x:v>
-      </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1505805</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
+      <x:c r="L16" s="18">
+        <x:v>46080.2360791898</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>46079.2523059375</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="21">
-        <x:v>46079.2763078704</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C13" s="17" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E13" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="H13" s="19">
-        <x:v>46063.1352777778</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J13" s="18" t="n">
-        <x:v>1511010</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
+      <x:c r="L17" s="18">
+        <x:v>46080.2925916204</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46079.2430618866</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="21">
-        <x:v>46063.2367708333</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="17" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C14" s="17" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E14" s="17" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F14" s="17" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H14" s="19">
-        <x:v>46079.3584722222</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
-        <x:v>46079.3584953704</x:v>
-      </x:c>
-      <x:c r="J14" s="18" t="n">
-        <x:v>1511622</x:v>
-      </x:c>
-      <x:c r="K14" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L14" s="21">
-        <x:v>46080.2311226852</x:v>
-      </x:c>
-      <x:c r="M14" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="17" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C15" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E15" s="17" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F15" s="17" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G15" s="17" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H15" s="19">
-        <x:v>46079.3539699074</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
-        <x:v>46079.3539814815</x:v>
-      </x:c>
-      <x:c r="J15" s="18" t="n">
-        <x:v>1511627</x:v>
-      </x:c>
-      <x:c r="K15" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L15" s="21">
-        <x:v>46080.2440856481</x:v>
-      </x:c>
-      <x:c r="M15" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C16" s="17" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D16" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E16" s="17" t="s">
+      <x:c r="L18" s="18">
+        <x:v>46080.2801283218</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="F16" s="17" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G16" s="17" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="H16" s="19">
-        <x:v>46079.3873148148</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46079.3652018403</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J16" s="18" t="n">
-        <x:v>1511623</x:v>
-      </x:c>
-      <x:c r="K16" s="20" t="n">
+      <x:c r="J19" s="15" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="21">
-        <x:v>46080.2360763889</x:v>
-      </x:c>
-      <x:c r="M16" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C17" s="17" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D17" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E17" s="17" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="F17" s="17" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G17" s="17" t="s">
+      <x:c r="L19" s="18">
+        <x:v>46080.2425555208</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="H17" s="19">
-        <x:v>46079.2523032407</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
+      <x:c r="C20" s="14" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46080.2923673264</x:v>
+      </x:c>
+      <x:c r="I20" s="16">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J17" s="18" t="n">
-        <x:v>1511631</x:v>
-      </x:c>
-      <x:c r="K17" s="20" t="n">
+      <x:c r="J20" s="15" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="21">
-        <x:v>46080.2925810185</x:v>
-      </x:c>
-      <x:c r="M17" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C18" s="17" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D18" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E18" s="17" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F18" s="17" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G18" s="17" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H18" s="19">
-        <x:v>46079.2430555556</x:v>
-      </x:c>
-      <x:c r="I18" s="19">
+      <x:c r="L20" s="18">
+        <x:v>46080.3208568171</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46079.3162545833</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J18" s="18" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K18" s="20" t="n">
+      <x:c r="J21" s="15" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="21">
-        <x:v>46080.2801273148</x:v>
-      </x:c>
-      <x:c r="M18" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C19" s="17" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D19" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E19" s="17" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="F19" s="17" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G19" s="17" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H19" s="19">
-        <x:v>46079.3651967593</x:v>
-      </x:c>
-      <x:c r="I19" s="19">
+      <x:c r="L21" s="18">
+        <x:v>46080.2883729977</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46079.3059443634</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J19" s="18" t="n">
-        <x:v>1511626</x:v>
-      </x:c>
-      <x:c r="K19" s="20" t="n">
+      <x:c r="J22" s="15" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L19" s="21">
-        <x:v>46080.2425462963</x:v>
-      </x:c>
-      <x:c r="M19" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C20" s="17" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D20" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E20" s="17" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F20" s="17" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G20" s="17" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="H20" s="19">
-        <x:v>46080.2923611111</x:v>
-      </x:c>
-      <x:c r="I20" s="19">
+      <x:c r="L22" s="18">
+        <x:v>46080.2896890278</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46079.2943998843</x:v>
+      </x:c>
+      <x:c r="I23" s="16">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J20" s="18" t="n">
-        <x:v>1511635</x:v>
-      </x:c>
-      <x:c r="K20" s="20" t="n">
+      <x:c r="J23" s="15" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L20" s="21">
-        <x:v>46080.3208564815</x:v>
-      </x:c>
-      <x:c r="M20" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C21" s="17" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D21" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E21" s="17" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F21" s="17" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="G21" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="H21" s="19">
-        <x:v>46079.31625</x:v>
-      </x:c>
-      <x:c r="I21" s="19">
+      <x:c r="L23" s="18">
+        <x:v>46080.2916823611</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>46079.3789042361</x:v>
+      </x:c>
+      <x:c r="I24" s="16">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J21" s="18" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K21" s="20" t="n">
+      <x:c r="J24" s="15" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L21" s="21">
-        <x:v>46080.2883680556</x:v>
-      </x:c>
-      <x:c r="M21" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C22" s="17" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D22" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E22" s="17" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F22" s="17" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="G22" s="17" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="H22" s="19">
-        <x:v>46079.3059375</x:v>
-      </x:c>
-      <x:c r="I22" s="19">
+      <x:c r="L24" s="18">
+        <x:v>46080.2376106713</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="H25" s="16">
+        <x:v>46079.3728295139</x:v>
+      </x:c>
+      <x:c r="I25" s="16">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J22" s="18" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K22" s="20" t="n">
+      <x:c r="J25" s="15" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="K25" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L22" s="21">
-        <x:v>46080.2896875</x:v>
-      </x:c>
-      <x:c r="M22" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C23" s="17" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D23" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E23" s="17" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F23" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="G23" s="17" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="H23" s="19">
-        <x:v>46079.2943981482</x:v>
-      </x:c>
-      <x:c r="I23" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J23" s="18" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K23" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="21">
-        <x:v>46080.2916782407</x:v>
-      </x:c>
-      <x:c r="M23" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C24" s="17" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="D24" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E24" s="17" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="F24" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="G24" s="17" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H24" s="19">
-        <x:v>46079.378900463</x:v>
-      </x:c>
-      <x:c r="I24" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J24" s="18" t="n">
-        <x:v>1511624</x:v>
-      </x:c>
-      <x:c r="K24" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L24" s="21">
-        <x:v>46080.2376041667</x:v>
-      </x:c>
-      <x:c r="M24" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C25" s="17" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D25" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E25" s="17" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="F25" s="17" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="G25" s="17" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="H25" s="19">
-        <x:v>46079.3728240741</x:v>
-      </x:c>
-      <x:c r="I25" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J25" s="18" t="n">
-        <x:v>1511625</x:v>
-      </x:c>
-      <x:c r="K25" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L25" s="21">
-        <x:v>46080.2394328704</x:v>
-      </x:c>
-      <x:c r="M25" s="17" t="s">
-        <x:v>52</x:v>
+      <x:c r="L25" s="18">
+        <x:v>46080.2394384722</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="s">
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C26" s="17" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D26" s="18" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E26" s="17" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="F26" s="17" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="G26" s="17" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="H26" s="19">
-        <x:v>46062.1590162037</x:v>
-      </x:c>
-      <x:c r="I26" s="19">
-        <x:v>46062.1590277778</x:v>
-      </x:c>
-      <x:c r="J26" s="18" t="n">
-        <x:v>1510925</x:v>
-      </x:c>
-      <x:c r="K26" s="20" t="n">
+      <x:c r="B26" s="14" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H26" s="16">
+        <x:v>46062.159017581</x:v>
+      </x:c>
+      <x:c r="I26" s="16">
+        <x:v>46062.1590321875</x:v>
+      </x:c>
+      <x:c r="J26" s="15" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="K26" s="17" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L26" s="21">
-        <x:v>46062.1863194444</x:v>
-      </x:c>
-      <x:c r="M26" s="17" t="s">
-        <x:v>52</x:v>
+      <x:c r="L26" s="18">
+        <x:v>46062.1863264931</x:v>
+      </x:c>
+      <x:c r="M26" s="14" t="s">
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="17" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C27" s="17" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D27" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E27" s="17" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="F27" s="17" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="G27" s="17" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="H27" s="19">
-        <x:v>46071.0492476852</x:v>
-      </x:c>
-      <x:c r="I27" s="19">
+      <x:c r="B27" s="14" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="H27" s="16">
+        <x:v>46071.0492490046</x:v>
+      </x:c>
+      <x:c r="I27" s="16">
         <x:v>46052</x:v>
       </x:c>
-      <x:c r="J27" s="18" t="n">
-        <x:v>1511502</x:v>
-      </x:c>
-      <x:c r="K27" s="20" t="n">
+      <x:c r="J27" s="15" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="K27" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L27" s="21">
-        <x:v>46071.0606134259</x:v>
-      </x:c>
-      <x:c r="M27" s="17" t="s">
-        <x:v>52</x:v>
+      <x:c r="L27" s="18">
+        <x:v>46071.0606162616</x:v>
+      </x:c>
+      <x:c r="M27" s="14" t="s">
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B30" s="22" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="C30" s="23" t="s"/>
-      <x:c r="D30" s="23" t="s"/>
-      <x:c r="E30" s="24" t="s"/>
-      <x:c r="F30" s="24" t="s"/>
+      <x:c r="B30" s="19" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C30" s="20" t="s"/>
+      <x:c r="D30" s="20" t="s"/>
+      <x:c r="E30" s="21" t="s"/>
+      <x:c r="F30" s="21" t="s"/>
     </x:row>
     <x:row r="31" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B31" s="25" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C31" s="26" t="s"/>
-      <x:c r="D31" s="26" t="s"/>
-      <x:c r="E31" s="26" t="s"/>
-      <x:c r="F31" s="27" t="s">
-        <x:v>106</x:v>
+      <x:c r="B31" s="22" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="C31" s="23" t="s"/>
+      <x:c r="D31" s="23" t="s"/>
+      <x:c r="E31" s="23" t="s"/>
+      <x:c r="F31" s="24" t="s">
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="28" t="s">
+      <x:c r="B32" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C32" s="29" t="s"/>
-      <x:c r="D32" s="29" t="s"/>
-      <x:c r="E32" s="29" t="s"/>
-      <x:c r="F32" s="30" t="n">
+      <x:c r="C32" s="26" t="s"/>
+      <x:c r="D32" s="26" t="s"/>
+      <x:c r="E32" s="26" t="s"/>
+      <x:c r="F32" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="28" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C33" s="29" t="s"/>
-      <x:c r="D33" s="29" t="s"/>
-      <x:c r="E33" s="29" t="s"/>
-      <x:c r="F33" s="30" t="n">
+      <x:c r="B33" s="25" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C33" s="26" t="s"/>
+      <x:c r="D33" s="26" t="s"/>
+      <x:c r="E33" s="26" t="s"/>
+      <x:c r="F33" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="28" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C34" s="29" t="s"/>
-      <x:c r="D34" s="29" t="s"/>
-      <x:c r="E34" s="29" t="s"/>
-      <x:c r="F34" s="30" t="n">
+      <x:c r="B34" s="25" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C34" s="26" t="s"/>
+      <x:c r="D34" s="26" t="s"/>
+      <x:c r="E34" s="26" t="s"/>
+      <x:c r="F34" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="28" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C35" s="29" t="s"/>
-      <x:c r="D35" s="29" t="s"/>
-      <x:c r="E35" s="29" t="s"/>
-      <x:c r="F35" s="30" t="n">
+      <x:c r="B35" s="25" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C35" s="26" t="s"/>
+      <x:c r="D35" s="26" t="s"/>
+      <x:c r="E35" s="26" t="s"/>
+      <x:c r="F35" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="28" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C36" s="29" t="s"/>
-      <x:c r="D36" s="29" t="s"/>
-      <x:c r="E36" s="29" t="s"/>
-      <x:c r="F36" s="30" t="n">
+      <x:c r="B36" s="25" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C36" s="26" t="s"/>
+      <x:c r="D36" s="26" t="s"/>
+      <x:c r="E36" s="26" t="s"/>
+      <x:c r="F36" s="27" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B37" s="28" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C37" s="29" t="s"/>
-      <x:c r="D37" s="29" t="s"/>
-      <x:c r="E37" s="29" t="s"/>
-      <x:c r="F37" s="30" t="n">
+      <x:c r="B37" s="25" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C37" s="26" t="s"/>
+      <x:c r="D37" s="26" t="s"/>
+      <x:c r="E37" s="26" t="s"/>
+      <x:c r="F37" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B38" s="28" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C38" s="29" t="s"/>
-      <x:c r="D38" s="29" t="s"/>
-      <x:c r="E38" s="29" t="s"/>
-      <x:c r="F38" s="30" t="n">
+      <x:c r="B38" s="25" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="C38" s="26" t="s"/>
+      <x:c r="D38" s="26" t="s"/>
+      <x:c r="E38" s="26" t="s"/>
+      <x:c r="F38" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B39" s="31" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="C39" s="32" t="s"/>
-      <x:c r="D39" s="32" t="s"/>
-      <x:c r="E39" s="32" t="s"/>
-      <x:c r="F39" s="33" t="n">
+      <x:c r="B39" s="28" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="C39" s="29" t="s"/>
+      <x:c r="D39" s="29" t="s"/>
+      <x:c r="E39" s="29" t="s"/>
+      <x:c r="F39" s="30" t="n">
         <x:v>20</x:v>
       </x:c>
     </x:row>
@@ -3516,7 +3617,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>108</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -3595,35 +3696,35 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s"/>
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s"/>
       <x:c r="E8" s="14" t="s">
-        <x:v>110</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>111</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46100.1144675926</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46100.1505092593</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1511906</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46100.1144765394</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46100.1505107292</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46100.1652777778</x:v>
+      <x:c r="L8" s="18">
+        <x:v>46100.1652817245</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -3631,1032 +3732,1032 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s"/>
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s"/>
       <x:c r="E9" s="14" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46091.3061033796</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46091.3108077083</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L9" s="18">
+        <x:v>46091.3131892477</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46093.1459465972</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46093.1585187731</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L10" s="18">
+        <x:v>46093.1595409143</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46080.4532551852</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>46097.1461728357</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46083.2380494329</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>46097.1564439468</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>46083.2599218056</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="18">
+        <x:v>46097.1652390856</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46069.278571956</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46067</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L14" s="18">
+        <x:v>46100.3884108912</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>161</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>46084.0854516898</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="18">
+        <x:v>46093.3956400694</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>46084.0996762384</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="18">
+        <x:v>46097.241468588</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>46069.1542109954</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
+        <x:v>46035</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L17" s="18">
+        <x:v>46097.2466610301</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46069.2178798032</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L18" s="18">
+        <x:v>46097.2456397685</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46069.3717699074</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L19" s="18">
+        <x:v>46100.3754893056</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>161</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46083.2443981019</x:v>
+      </x:c>
+      <x:c r="I20" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="18">
+        <x:v>46097.1600206018</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46084.1225139699</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="18">
+        <x:v>46097.3505144329</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46083.252116412</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L22" s="18">
+        <x:v>46097.1628986343</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46069.1151616435</x:v>
+      </x:c>
+      <x:c r="I23" s="16">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="18">
+        <x:v>46097.343386956</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>46069.2327997454</x:v>
+      </x:c>
+      <x:c r="I24" s="16">
+        <x:v>46049</x:v>
+      </x:c>
+      <x:c r="J24" s="15" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L24" s="18">
+        <x:v>46100.3816829514</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>161</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="H25" s="16">
+        <x:v>46086.106481875</x:v>
+      </x:c>
+      <x:c r="I25" s="16">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="J25" s="15" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="K25" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="18">
+        <x:v>46090.2765830324</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="H26" s="16">
+        <x:v>46085.1662527662</x:v>
+      </x:c>
+      <x:c r="I26" s="16">
+        <x:v>46085.1662689699</x:v>
+      </x:c>
+      <x:c r="J26" s="15" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="K26" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L26" s="18">
+        <x:v>46090.3437343634</x:v>
+      </x:c>
+      <x:c r="M26" s="14" t="s">
+        <x:v>221</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="H27" s="16">
+        <x:v>46085.1709247338</x:v>
+      </x:c>
+      <x:c r="I27" s="16">
+        <x:v>46085.1709419676</x:v>
+      </x:c>
+      <x:c r="J27" s="15" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="K27" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L27" s="18">
+        <x:v>46090.3337014815</x:v>
+      </x:c>
+      <x:c r="M27" s="14" t="s">
+        <x:v>221</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="D28" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E28" s="14" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="G28" s="14" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="H28" s="16">
+        <x:v>46084.1080380324</x:v>
+      </x:c>
+      <x:c r="I28" s="16">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J28" s="15" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="K28" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="18">
+        <x:v>46097.2478153472</x:v>
+      </x:c>
+      <x:c r="M28" s="14" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="D29" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="H29" s="16">
+        <x:v>46083.0788057755</x:v>
+      </x:c>
+      <x:c r="I29" s="16">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J29" s="15" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="K29" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="18">
+        <x:v>46083.1042250116</x:v>
+      </x:c>
+      <x:c r="M29" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C30" s="14" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="D30" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E30" s="14" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="G30" s="14" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="H30" s="16">
+        <x:v>46087.1643336806</x:v>
+      </x:c>
+      <x:c r="I30" s="16">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J30" s="15" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="K30" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="18">
+        <x:v>46090.2727784143</x:v>
+      </x:c>
+      <x:c r="M30" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C31" s="14" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="D31" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E31" s="14" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="G31" s="14" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="H31" s="16">
+        <x:v>46086.099798588</x:v>
+      </x:c>
+      <x:c r="I31" s="16">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J31" s="15" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="K31" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="18">
+        <x:v>46090.2691152778</x:v>
+      </x:c>
+      <x:c r="M31" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C32" s="14" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="D32" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E32" s="14" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="G32" s="14" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="H32" s="16">
+        <x:v>46086.1144463079</x:v>
+      </x:c>
+      <x:c r="I32" s="16">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J32" s="15" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="K32" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L32" s="18">
+        <x:v>46090.2703739352</x:v>
+      </x:c>
+      <x:c r="M32" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="14" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46091.306099537</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46091.3107986111</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1511778</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46091.3131828704</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="17" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>46093.1459375</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>46093.1585185185</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1511815</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L10" s="21">
-        <x:v>46093.159537037</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E11" s="17" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>46080.4532523148</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1511232</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L11" s="21">
-        <x:v>46097.1461689815</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>125</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E12" s="17" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>46083.2380439815</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1511234</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L12" s="21">
-        <x:v>46097.1564351852</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>125</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C13" s="17" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E13" s="17" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="H13" s="19">
-        <x:v>46083.2599189815</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
-        <x:v>46101</x:v>
-      </x:c>
-      <x:c r="J13" s="18" t="n">
-        <x:v>1511237</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="21">
-        <x:v>46097.1652314815</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="s">
-        <x:v>125</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C14" s="17" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E14" s="17" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="F14" s="17" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="H14" s="19">
-        <x:v>46069.2785648148</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
-        <x:v>46067</x:v>
-      </x:c>
-      <x:c r="J14" s="18" t="n">
-        <x:v>1511276</x:v>
-      </x:c>
-      <x:c r="K14" s="20" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L14" s="21">
-        <x:v>46100.3884027778</x:v>
-      </x:c>
-      <x:c r="M14" s="17" t="s">
-        <x:v>137</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C15" s="17" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E15" s="17" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="F15" s="17" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="G15" s="17" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="H15" s="19">
-        <x:v>46084.0854513889</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J15" s="18" t="n">
-        <x:v>1511225</x:v>
-      </x:c>
-      <x:c r="K15" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L15" s="21">
-        <x:v>46093.3956365741</x:v>
-      </x:c>
-      <x:c r="M15" s="17" t="s">
-        <x:v>125</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C16" s="17" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="D16" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E16" s="17" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="F16" s="17" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="G16" s="17" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="H16" s="19">
-        <x:v>46084.0996759259</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J16" s="18" t="n">
-        <x:v>1511192</x:v>
-      </x:c>
-      <x:c r="K16" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L16" s="21">
-        <x:v>46097.2414583333</x:v>
-      </x:c>
-      <x:c r="M16" s="17" t="s">
-        <x:v>125</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C17" s="17" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="D17" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E17" s="17" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="F17" s="17" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="G17" s="17" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="H17" s="19">
-        <x:v>46069.1542013889</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
-        <x:v>46035</x:v>
-      </x:c>
-      <x:c r="J17" s="18" t="n">
-        <x:v>1511206</x:v>
-      </x:c>
-      <x:c r="K17" s="20" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L17" s="21">
-        <x:v>46097.2466550926</x:v>
-      </x:c>
-      <x:c r="M17" s="17" t="s">
-        <x:v>125</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C18" s="17" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="D18" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E18" s="17" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="F18" s="17" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="G18" s="17" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="H18" s="19">
-        <x:v>46069.2178703704</x:v>
-      </x:c>
-      <x:c r="I18" s="19">
-        <x:v>46051</x:v>
-      </x:c>
-      <x:c r="J18" s="18" t="n">
-        <x:v>1511196</x:v>
-      </x:c>
-      <x:c r="K18" s="20" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L18" s="21">
-        <x:v>46097.2456365741</x:v>
-      </x:c>
-      <x:c r="M18" s="17" t="s">
-        <x:v>125</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C19" s="17" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="D19" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E19" s="17" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="F19" s="17" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="G19" s="17" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="H19" s="19">
-        <x:v>46069.3717592593</x:v>
-      </x:c>
-      <x:c r="I19" s="19">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J19" s="18" t="n">
-        <x:v>1511274</x:v>
-      </x:c>
-      <x:c r="K19" s="20" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L19" s="21">
-        <x:v>46100.3754861111</x:v>
-      </x:c>
-      <x:c r="M19" s="17" t="s">
-        <x:v>137</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C20" s="17" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="D20" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E20" s="17" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="F20" s="17" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="G20" s="17" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="H20" s="19">
-        <x:v>46083.2443865741</x:v>
-      </x:c>
-      <x:c r="I20" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J20" s="18" t="n">
-        <x:v>1511235</x:v>
-      </x:c>
-      <x:c r="K20" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="21">
-        <x:v>46097.1600115741</x:v>
-      </x:c>
-      <x:c r="M20" s="17" t="s">
-        <x:v>125</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C21" s="17" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="D21" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E21" s="17" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="F21" s="17" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="G21" s="17" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="H21" s="19">
-        <x:v>46084.1225115741</x:v>
-      </x:c>
-      <x:c r="I21" s="19">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J21" s="18" t="n">
-        <x:v>1511242</x:v>
-      </x:c>
-      <x:c r="K21" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="21">
-        <x:v>46097.3505092593</x:v>
-      </x:c>
-      <x:c r="M21" s="17" t="s">
-        <x:v>125</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C22" s="17" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="D22" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E22" s="17" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="F22" s="17" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="G22" s="17" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="H22" s="19">
-        <x:v>46083.2521064815</x:v>
-      </x:c>
-      <x:c r="I22" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J22" s="18" t="n">
-        <x:v>1511236</x:v>
-      </x:c>
-      <x:c r="K22" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="21">
-        <x:v>46097.1628935185</x:v>
-      </x:c>
-      <x:c r="M22" s="17" t="s">
-        <x:v>125</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C23" s="17" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="D23" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E23" s="17" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="F23" s="17" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="G23" s="17" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="H23" s="19">
-        <x:v>46069.115150463</x:v>
-      </x:c>
-      <x:c r="I23" s="19">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J23" s="18" t="n">
-        <x:v>1511241</x:v>
-      </x:c>
-      <x:c r="K23" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="21">
-        <x:v>46097.3433796296</x:v>
-      </x:c>
-      <x:c r="M23" s="17" t="s">
-        <x:v>125</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C24" s="17" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="D24" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E24" s="17" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="F24" s="17" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="G24" s="17" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="H24" s="19">
-        <x:v>46069.2327893519</x:v>
-      </x:c>
-      <x:c r="I24" s="19">
-        <x:v>46049</x:v>
-      </x:c>
-      <x:c r="J24" s="18" t="n">
-        <x:v>1511275</x:v>
-      </x:c>
-      <x:c r="K24" s="20" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L24" s="21">
-        <x:v>46100.3816782407</x:v>
-      </x:c>
-      <x:c r="M24" s="17" t="s">
-        <x:v>137</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C25" s="17" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="D25" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E25" s="17" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="F25" s="17" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="G25" s="17" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="H25" s="19">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I25" s="19">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="J25" s="18" t="n">
-        <x:v>1511761</x:v>
-      </x:c>
-      <x:c r="K25" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L25" s="21">
-        <x:v>46090.2765740741</x:v>
-      </x:c>
-      <x:c r="M25" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="17" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C26" s="17" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="D26" s="18" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E26" s="17" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="F26" s="17" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="G26" s="17" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="H26" s="19">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I26" s="19">
-        <x:v>46085.1662615741</x:v>
-      </x:c>
-      <x:c r="J26" s="18" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K26" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L26" s="21">
-        <x:v>46090.3437268519</x:v>
-      </x:c>
-      <x:c r="M26" s="17" t="s">
-        <x:v>185</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="17" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C27" s="17" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="D27" s="18" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E27" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="F27" s="17" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="G27" s="17" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="H27" s="19">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I27" s="19">
-        <x:v>46085.1709375</x:v>
-      </x:c>
-      <x:c r="J27" s="18" t="n">
-        <x:v>1507965</x:v>
-      </x:c>
-      <x:c r="K27" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L27" s="21">
-        <x:v>46090.3336921296</x:v>
-      </x:c>
-      <x:c r="M27" s="17" t="s">
-        <x:v>185</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C28" s="17" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="D28" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E28" s="17" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="F28" s="17" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="G28" s="17" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="H28" s="19">
-        <x:v>46084.1080324074</x:v>
-      </x:c>
-      <x:c r="I28" s="19">
-        <x:v>46103</x:v>
-      </x:c>
-      <x:c r="J28" s="18" t="n">
-        <x:v>1511208</x:v>
-      </x:c>
-      <x:c r="K28" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="21">
-        <x:v>46097.2478125</x:v>
-      </x:c>
-      <x:c r="M28" s="17" t="s">
-        <x:v>125</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C29" s="17" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="D29" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E29" s="17" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="F29" s="17" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="G29" s="17" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="H29" s="19">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I29" s="19">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J29" s="18" t="n">
-        <x:v>1511639</x:v>
-      </x:c>
-      <x:c r="K29" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="21">
-        <x:v>46083.104224537</x:v>
-      </x:c>
-      <x:c r="M29" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C30" s="17" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="D30" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E30" s="17" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="F30" s="17" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="G30" s="17" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="H30" s="19">
-        <x:v>46087.1643287037</x:v>
-      </x:c>
-      <x:c r="I30" s="19">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="J30" s="18" t="n">
-        <x:v>1511760</x:v>
-      </x:c>
-      <x:c r="K30" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="21">
-        <x:v>46090.2727777778</x:v>
-      </x:c>
-      <x:c r="M30" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C31" s="17" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="D31" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E31" s="17" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="F31" s="17" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="G31" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="H31" s="19">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I31" s="19">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="J31" s="18" t="n">
-        <x:v>1511758</x:v>
-      </x:c>
-      <x:c r="K31" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L31" s="21">
-        <x:v>46090.2691087963</x:v>
-      </x:c>
-      <x:c r="M31" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C32" s="17" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="D32" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E32" s="17" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="F32" s="17" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="G32" s="17" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="H32" s="19">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I32" s="19">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J32" s="18" t="n">
-        <x:v>1511759</x:v>
-      </x:c>
-      <x:c r="K32" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L32" s="21">
-        <x:v>46090.2703703704</x:v>
-      </x:c>
-      <x:c r="M32" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="17" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C33" s="17" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="D33" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E33" s="17" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="F33" s="17" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="G33" s="17" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="H33" s="19">
-        <x:v>46098.2908796296</x:v>
-      </x:c>
-      <x:c r="I33" s="19">
+      <x:c r="C33" s="14" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="D33" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E33" s="14" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="G33" s="14" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="H33" s="16">
+        <x:v>46098.290884375</x:v>
+      </x:c>
+      <x:c r="I33" s="16">
         <x:v>45997</x:v>
       </x:c>
-      <x:c r="J33" s="18" t="n">
-        <x:v>1511858</x:v>
-      </x:c>
-      <x:c r="K33" s="20" t="n">
+      <x:c r="J33" s="15" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="K33" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L33" s="21">
-        <x:v>46098.3188657407</x:v>
-      </x:c>
-      <x:c r="M33" s="17" t="s">
-        <x:v>52</x:v>
+      <x:c r="L33" s="18">
+        <x:v>46098.3188767824</x:v>
+      </x:c>
+      <x:c r="M33" s="14" t="s">
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="36" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B36" s="22" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="C36" s="23" t="s"/>
-      <x:c r="D36" s="23" t="s"/>
-      <x:c r="E36" s="24" t="s"/>
-      <x:c r="F36" s="24" t="s"/>
+      <x:c r="B36" s="19" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C36" s="20" t="s"/>
+      <x:c r="D36" s="20" t="s"/>
+      <x:c r="E36" s="21" t="s"/>
+      <x:c r="F36" s="21" t="s"/>
     </x:row>
     <x:row r="37" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B37" s="25" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C37" s="26" t="s"/>
-      <x:c r="D37" s="26" t="s"/>
-      <x:c r="E37" s="26" t="s"/>
-      <x:c r="F37" s="27" t="s">
-        <x:v>106</x:v>
+      <x:c r="B37" s="22" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="C37" s="23" t="s"/>
+      <x:c r="D37" s="23" t="s"/>
+      <x:c r="E37" s="23" t="s"/>
+      <x:c r="F37" s="24" t="s">
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B38" s="28" t="s">
+      <x:c r="B38" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C38" s="29" t="s"/>
-      <x:c r="D38" s="29" t="s"/>
-      <x:c r="E38" s="29" t="s"/>
-      <x:c r="F38" s="30" t="n">
+      <x:c r="C38" s="26" t="s"/>
+      <x:c r="D38" s="26" t="s"/>
+      <x:c r="E38" s="26" t="s"/>
+      <x:c r="F38" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B39" s="28" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C39" s="29" t="s"/>
-      <x:c r="D39" s="29" t="s"/>
-      <x:c r="E39" s="29" t="s"/>
-      <x:c r="F39" s="30" t="n">
+      <x:c r="B39" s="25" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C39" s="26" t="s"/>
+      <x:c r="D39" s="26" t="s"/>
+      <x:c r="E39" s="26" t="s"/>
+      <x:c r="F39" s="27" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B40" s="28" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C40" s="29" t="s"/>
-      <x:c r="D40" s="29" t="s"/>
-      <x:c r="E40" s="29" t="s"/>
-      <x:c r="F40" s="30" t="n">
+      <x:c r="B40" s="25" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C40" s="26" t="s"/>
+      <x:c r="D40" s="26" t="s"/>
+      <x:c r="E40" s="26" t="s"/>
+      <x:c r="F40" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B41" s="28" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C41" s="29" t="s"/>
-      <x:c r="D41" s="29" t="s"/>
-      <x:c r="E41" s="29" t="s"/>
-      <x:c r="F41" s="30" t="n">
+      <x:c r="B41" s="25" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C41" s="26" t="s"/>
+      <x:c r="D41" s="26" t="s"/>
+      <x:c r="E41" s="26" t="s"/>
+      <x:c r="F41" s="27" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B42" s="28" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C42" s="29" t="s"/>
-      <x:c r="D42" s="29" t="s"/>
-      <x:c r="E42" s="29" t="s"/>
-      <x:c r="F42" s="30" t="n">
+      <x:c r="B42" s="25" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="C42" s="26" t="s"/>
+      <x:c r="D42" s="26" t="s"/>
+      <x:c r="E42" s="26" t="s"/>
+      <x:c r="F42" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B43" s="31" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="C43" s="32" t="s"/>
-      <x:c r="D43" s="32" t="s"/>
-      <x:c r="E43" s="32" t="s"/>
-      <x:c r="F43" s="33" t="n">
+      <x:c r="B43" s="28" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="C43" s="29" t="s"/>
+      <x:c r="D43" s="29" t="s"/>
+      <x:c r="E43" s="29" t="s"/>
+      <x:c r="F43" s="30" t="n">
         <x:v>26</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -23,9 +23,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="252">
-  <x:si>
-    <x:t>EVALUATOR SUMMARY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="290">
+  <x:si>
+    <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>ENGR. GALELEO MENDOZA</x:t>
@@ -181,7 +181,7 @@
     <x:t>1511010</x:t>
   </x:si>
   <x:si>
-    <x:t>Ceasar Allen Centeno</x:t>
+    <x:t>Caesar Allen Centeno</x:t>
   </x:si>
   <x:si>
     <x:t>Retailer/Reseller Permit (NEW)</x:t>
@@ -418,6 +418,36 @@
     <x:t>1511906</x:t>
   </x:si>
   <x:si>
+    <x:t>ARIEL PASAHOL ASILO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vallega Compound 4th., Palola, Lucban, Quezon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-2026-03-0004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1236-376</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511955</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDEN ENRIQUEZ LUNETA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Purok 2, Gulod Itaas, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03016-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1241-783</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511992</x:t>
+  </x:si>
+  <x:si>
     <x:t>HERALD BEBIS</x:t>
   </x:si>
   <x:si>
@@ -448,6 +478,51 @@
     <x:t>1511815</x:t>
   </x:si>
   <x:si>
+    <x:t>JOMAR BACSAL MONDRAGON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Purok 7B, Magnetic hills, Timugan, Los Baños, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-2026-03-003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1232-952</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511954</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REX FAJARDO VIDAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guiho Guiho st, Quipot, Tiaong, Quezon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-2026-03-0002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1231-664</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511953</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RONALD BRYAN C. DERIQUITO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>246 Sitio ibaba, Santisimo rosario, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03-0001ML</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1230-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511940</x:t>
+  </x:si>
+  <x:si>
     <x:t>BSD INTERNATIONAL MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -463,9 +538,6 @@
     <x:t>1511232</x:t>
   </x:si>
   <x:si>
-    <x:t>Cesar Allen Centeno</x:t>
-  </x:si>
-  <x:si>
     <x:t>CZ 248-3 SM City San Pablo, Brgy. San Rafael, San Pablo City, Laguna</x:t>
   </x:si>
   <x:si>
@@ -508,9 +580,6 @@
     <x:t>1511276</x:t>
   </x:si>
   <x:si>
-    <x:t>Caesar Allen Centeno</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELLTY MOBILE INC</x:t>
   </x:si>
   <x:si>
@@ -628,6 +697,21 @@
     <x:t>1511236</x:t>
   </x:si>
   <x:si>
+    <x:t>RULLS CELLPHONES AND ACCESSORIES INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SM CITY STO. TOMAS CZ-5 MAHARLIKA HIGHWAY, SAN BARTOLOME, Santo Tomas, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 24-466R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1158-087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511302</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYNCNETIC INC.</x:t>
   </x:si>
   <x:si>
@@ -643,6 +727,21 @@
     <x:t>1511241</x:t>
   </x:si>
   <x:si>
+    <x:t>TECH101 TECHNOLOGIES INC. - BR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ-248-15 2f SM CITY SAN PABLO, BRGY SAN RAFAEL, SAN PABLO San rafael, San rafael, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-21-11-0934</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1240-025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511971</x:t>
+  </x:si>
+  <x:si>
     <x:t>TEQWARE PHONES AND ACCESSORIES INC.</x:t>
   </x:si>
   <x:si>
@@ -676,6 +775,21 @@
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
+    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2518</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1172-434</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1507965</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ricardo Natividad</x:t>
+  </x:si>
+  <x:si>
     <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
   </x:si>
   <x:si>
@@ -688,19 +802,19 @@
     <x:t>1507966</x:t>
   </x:si>
   <x:si>
-    <x:t>Ricardo Natividad</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-2518</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1172-434</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1507965</x:t>
+    <x:t>SELECT GOODS OPC (VIVO)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SM City San Pablo , 2nd floor , Cyberzone, San Rafael, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03001ML</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1239-893</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511970</x:t>
   </x:si>
   <x:si>
     <x:t>WALTERMART TANAUAN 225 WALTERMART JPL-HWAY, DARASA, City Of Tanauan, Batangas</x:t>
@@ -730,6 +844,30 @@
     <x:t>1511639</x:t>
   </x:si>
   <x:si>
+    <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-17-03-2015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1173-016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511758</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1175-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511759</x:t>
+  </x:si>
+  <x:si>
     <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
   </x:si>
   <x:si>
@@ -740,30 +878,6 @@
   </x:si>
   <x:si>
     <x:t>1511760</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-17-03-2015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1173-016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511758</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-18-02-2017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1175-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511759</x:t>
   </x:si>
   <x:si>
     <x:t>CELLBOY INC.</x:t>
@@ -1629,7 +1743,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1669,7 +1783,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -1706,7 +1820,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -1742,7 +1856,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
@@ -1780,7 +1894,7 @@
         <x:v>34</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
@@ -1818,7 +1932,7 @@
         <x:v>34</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
@@ -1856,7 +1970,7 @@
         <x:v>34</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
@@ -1894,7 +2008,7 @@
         <x:v>52</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
@@ -1932,7 +2046,7 @@
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
@@ -1970,7 +2084,7 @@
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
@@ -2008,7 +2122,7 @@
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
@@ -2046,7 +2160,7 @@
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
@@ -2084,7 +2198,7 @@
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
@@ -2122,7 +2236,7 @@
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
@@ -2160,7 +2274,7 @@
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
@@ -2198,7 +2312,7 @@
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
@@ -2236,7 +2350,7 @@
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
@@ -2274,7 +2388,7 @@
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
@@ -2312,7 +2426,7 @@
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
@@ -2350,7 +2464,7 @@
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
       <x:c r="B26" s="14" t="s">
         <x:v>109</x:v>
       </x:c>
@@ -2388,7 +2502,7 @@
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
       <x:c r="B27" s="14" t="s">
         <x:v>115</x:v>
       </x:c>
@@ -3650,7 +3764,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -3690,7 +3804,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -3727,7 +3841,7 @@
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -3745,10 +3859,10 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46091.3061033796</x:v>
+        <x:v>46107.1401251852</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46091.3108077083</x:v>
+        <x:v>46107.1653469792</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
         <x:v>135</x:v>
@@ -3757,13 +3871,13 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46091.3131892477</x:v>
+        <x:v>46107.1722420255</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -3781,10 +3895,10 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46093.1459465972</x:v>
+        <x:v>46111.14459375</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>46093.1585187731</x:v>
+        <x:v>46111.1542258102</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
         <x:v>140</x:v>
@@ -3793,22 +3907,20 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46093.1595409143</x:v>
+        <x:v>46111.1662193056</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
+      <x:c r="D11" s="15" t="s"/>
       <x:c r="E11" s="14" t="s">
         <x:v>142</x:v>
       </x:c>
@@ -3819,34 +3931,32 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46080.4532551852</x:v>
+        <x:v>46091.3061033796</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>46100</x:v>
+        <x:v>46091.3108077083</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
         <x:v>145</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46097.1461728357</x:v>
+        <x:v>46091.3131892477</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
         <x:v>146</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
+      <x:c r="D12" s="15" t="s"/>
       <x:c r="E12" s="14" t="s">
         <x:v>147</x:v>
       </x:c>
@@ -3857,34 +3967,32 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46083.2380494329</x:v>
+        <x:v>46093.1459465972</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>46100</x:v>
+        <x:v>46093.1585187731</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
         <x:v>150</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46097.1564439468</x:v>
+        <x:v>46093.1595409143</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
-        <x:v>146</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
+      <x:c r="D13" s="15" t="s"/>
       <x:c r="E13" s="14" t="s">
         <x:v>152</x:v>
       </x:c>
@@ -3895,34 +4003,32 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46083.2599218056</x:v>
+        <x:v>46107.1079779977</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>46101</x:v>
+        <x:v>46107.1569821643</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
         <x:v>155</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46097.1652390856</x:v>
+        <x:v>46107.1713369444</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
-        <x:v>146</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
+      <x:c r="D14" s="15" t="s"/>
       <x:c r="E14" s="14" t="s">
         <x:v>157</x:v>
       </x:c>
@@ -3933,68 +4039,66 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46069.278571956</x:v>
+        <x:v>46107.1074963889</x:v>
       </x:c>
       <x:c r="I14" s="16">
-        <x:v>46067</x:v>
+        <x:v>46107.1512672454</x:v>
       </x:c>
       <x:c r="J14" s="15" t="s">
         <x:v>160</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46100.3884108912</x:v>
+        <x:v>46107.1672093287</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
         <x:v>161</x:v>
       </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
+      <x:c r="D15" s="15" t="s"/>
+      <x:c r="E15" s="14" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="H15" s="16">
+        <x:v>46106.2628248843</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46106.2706934954</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46084.0854516898</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
-        <x:v>166</x:v>
-      </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46093.3956400694</x:v>
+        <x:v>46106.2922441319</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
-        <x:v>146</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>37</x:v>
@@ -4009,10 +4113,10 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46084.0996762384</x:v>
+        <x:v>46080.4532551852</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>46094</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J16" s="15" t="s">
         <x:v>170</x:v>
@@ -4021,512 +4125,512 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46097.241468588</x:v>
+        <x:v>46097.1461728357</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
-        <x:v>146</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>171</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E17" s="14" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="F17" s="14" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="G17" s="14" t="s">
+      <x:c r="H17" s="16">
+        <x:v>46083.2380494329</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46069.1542109954</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>46035</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="s">
-        <x:v>175</x:v>
-      </x:c>
       <x:c r="K17" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46097.2466610301</x:v>
+        <x:v>46097.1564439468</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
-        <x:v>146</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D18" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E18" s="14" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="G18" s="14" t="s">
+      <x:c r="H18" s="16">
+        <x:v>46083.2599218056</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46069.2178798032</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>46051</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="s">
-        <x:v>180</x:v>
-      </x:c>
       <x:c r="K18" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46097.2456397685</x:v>
+        <x:v>46097.1652390856</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
-        <x:v>146</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
-        <x:v>181</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D19" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E19" s="14" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="F19" s="14" t="s">
+      <x:c r="G19" s="14" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="G19" s="14" t="s">
+      <x:c r="H19" s="16">
+        <x:v>46069.278571956</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
+        <x:v>46067</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46069.3717699074</x:v>
-      </x:c>
-      <x:c r="I19" s="16">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="s">
-        <x:v>185</x:v>
       </x:c>
       <x:c r="K19" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46100.3754893056</x:v>
+        <x:v>46100.3884108912</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
-        <x:v>161</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="C20" s="14" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="D20" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E20" s="14" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="F20" s="14" t="s">
+      <x:c r="G20" s="14" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="G20" s="14" t="s">
+      <x:c r="H20" s="16">
+        <x:v>46084.0854516898</x:v>
+      </x:c>
+      <x:c r="I20" s="16">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="s">
         <x:v>189</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46083.2443981019</x:v>
-      </x:c>
-      <x:c r="I20" s="16">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="s">
-        <x:v>190</x:v>
       </x:c>
       <x:c r="K20" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46097.1600206018</x:v>
+        <x:v>46093.3956400694</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
-        <x:v>146</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="C21" s="14" t="s">
-        <x:v>191</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="D21" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E21" s="14" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="F21" s="14" t="s">
+      <x:c r="H21" s="16">
+        <x:v>46084.0996762384</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="s">
         <x:v>193</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46084.1225139699</x:v>
-      </x:c>
-      <x:c r="I21" s="16">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="s">
-        <x:v>195</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46097.3505144329</x:v>
+        <x:v>46097.241468588</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
-        <x:v>146</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>196</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="D22" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E22" s="14" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="F22" s="14" t="s">
+      <x:c r="H22" s="16">
+        <x:v>46069.1542109954</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
+        <x:v>46035</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46083.252116412</x:v>
-      </x:c>
-      <x:c r="I22" s="16">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="s">
-        <x:v>200</x:v>
-      </x:c>
       <x:c r="K22" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46097.1628986343</x:v>
+        <x:v>46097.2466610301</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
-        <x:v>146</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
-        <x:v>201</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="D23" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E23" s="14" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="F23" s="14" t="s">
+      <x:c r="H23" s="16">
+        <x:v>46069.2178798032</x:v>
+      </x:c>
+      <x:c r="I23" s="16">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46069.1151616435</x:v>
-      </x:c>
-      <x:c r="I23" s="16">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="s">
-        <x:v>205</x:v>
-      </x:c>
       <x:c r="K23" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46097.343386956</x:v>
+        <x:v>46097.2456397685</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
-        <x:v>146</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="C24" s="14" t="s">
-        <x:v>206</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="D24" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E24" s="14" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="F24" s="14" t="s">
+      <x:c r="H24" s="16">
+        <x:v>46069.3717699074</x:v>
+      </x:c>
+      <x:c r="I24" s="16">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J24" s="15" t="s">
         <x:v>208</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="H24" s="16">
-        <x:v>46069.2327997454</x:v>
-      </x:c>
-      <x:c r="I24" s="16">
-        <x:v>46049</x:v>
-      </x:c>
-      <x:c r="J24" s="15" t="s">
-        <x:v>210</x:v>
       </x:c>
       <x:c r="K24" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L24" s="18">
-        <x:v>46100.3816829514</x:v>
+        <x:v>46100.3754893056</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
-        <x:v>161</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="C25" s="14" t="s">
-        <x:v>211</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D25" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E25" s="14" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="F25" s="14" t="s">
+      <x:c r="H25" s="16">
+        <x:v>46083.2443981019</x:v>
+      </x:c>
+      <x:c r="I25" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J25" s="15" t="s">
         <x:v>213</x:v>
-      </x:c>
-      <x:c r="G25" s="14" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="H25" s="16">
-        <x:v>46086.106481875</x:v>
-      </x:c>
-      <x:c r="I25" s="16">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="J25" s="15" t="s">
-        <x:v>215</x:v>
       </x:c>
       <x:c r="K25" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L25" s="18">
-        <x:v>46090.2765830324</x:v>
+        <x:v>46097.1600206018</x:v>
       </x:c>
       <x:c r="M25" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
       <x:c r="B26" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C26" s="14" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="D26" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E26" s="14" t="s">
+      <x:c r="G26" s="14" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="F26" s="14" t="s">
+      <x:c r="H26" s="16">
+        <x:v>46084.1225139699</x:v>
+      </x:c>
+      <x:c r="I26" s="16">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J26" s="15" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="G26" s="14" t="s">
+      <x:c r="K26" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="18">
+        <x:v>46097.3505144329</x:v>
+      </x:c>
+      <x:c r="M26" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B27" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="H26" s="16">
-        <x:v>46085.1662527662</x:v>
-      </x:c>
-      <x:c r="I26" s="16">
-        <x:v>46085.1662689699</x:v>
-      </x:c>
-      <x:c r="J26" s="15" t="s">
+      <x:c r="D27" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="K26" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L26" s="18">
-        <x:v>46090.3437343634</x:v>
-      </x:c>
-      <x:c r="M26" s="14" t="s">
+      <x:c r="F27" s="14" t="s">
         <x:v>221</x:v>
       </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C27" s="14" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="D27" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E27" s="14" t="s">
+      <x:c r="G27" s="14" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="F27" s="14" t="s">
+      <x:c r="H27" s="16">
+        <x:v>46083.252116412</x:v>
+      </x:c>
+      <x:c r="I27" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J27" s="15" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="G27" s="14" t="s">
+      <x:c r="K27" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L27" s="18">
+        <x:v>46097.1628986343</x:v>
+      </x:c>
+      <x:c r="M27" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B28" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="s">
         <x:v>224</x:v>
-      </x:c>
-      <x:c r="H27" s="16">
-        <x:v>46085.1709247338</x:v>
-      </x:c>
-      <x:c r="I27" s="16">
-        <x:v>46085.1709419676</x:v>
-      </x:c>
-      <x:c r="J27" s="15" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="K27" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L27" s="18">
-        <x:v>46090.3337014815</x:v>
-      </x:c>
-      <x:c r="M27" s="14" t="s">
-        <x:v>221</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C28" s="14" t="s">
-        <x:v>162</x:v>
       </x:c>
       <x:c r="D28" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E28" s="14" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="F28" s="14" t="s">
+      <x:c r="G28" s="14" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="G28" s="14" t="s">
+      <x:c r="H28" s="16">
+        <x:v>46084.1157546528</x:v>
+      </x:c>
+      <x:c r="I28" s="16">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J28" s="15" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="H28" s="16">
-        <x:v>46084.1080380324</x:v>
-      </x:c>
-      <x:c r="I28" s="16">
-        <x:v>46103</x:v>
-      </x:c>
-      <x:c r="J28" s="15" t="s">
+      <x:c r="K28" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L28" s="18">
+        <x:v>46105.3755915741</x:v>
+      </x:c>
+      <x:c r="M28" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B29" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="s">
         <x:v>229</x:v>
-      </x:c>
-      <x:c r="K28" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="18">
-        <x:v>46097.2478153472</x:v>
-      </x:c>
-      <x:c r="M28" s="14" t="s">
-        <x:v>146</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C29" s="14" t="s">
-        <x:v>230</x:v>
       </x:c>
       <x:c r="D29" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E29" s="14" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="F29" s="14" t="s">
+      <x:c r="G29" s="14" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="G29" s="14" t="s">
+      <x:c r="H29" s="16">
+        <x:v>46069.1151616435</x:v>
+      </x:c>
+      <x:c r="I29" s="16">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J29" s="15" t="s">
         <x:v>233</x:v>
-      </x:c>
-      <x:c r="H29" s="16">
-        <x:v>46083.0788057755</x:v>
-      </x:c>
-      <x:c r="I29" s="16">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J29" s="15" t="s">
-        <x:v>234</x:v>
       </x:c>
       <x:c r="K29" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L29" s="18">
-        <x:v>46083.1042250116</x:v>
+        <x:v>46097.343386956</x:v>
       </x:c>
       <x:c r="M29" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="30" customHeight="1">
       <x:c r="B30" s="14" t="s">
-        <x:v>65</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C30" s="14" t="s">
-        <x:v>211</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="D30" s="15" t="s">
         <x:v>37</x:v>
@@ -4541,10 +4645,10 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="H30" s="16">
-        <x:v>46087.1643336806</x:v>
+        <x:v>46107.3381444213</x:v>
       </x:c>
       <x:c r="I30" s="16">
-        <x:v>46104</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="J30" s="15" t="s">
         <x:v>238</x:v>
@@ -4553,222 +4657,518 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L30" s="18">
-        <x:v>46090.2727784143</x:v>
+        <x:v>46107.3506854282</x:v>
       </x:c>
       <x:c r="M30" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="31" spans="1:28" ht="30" customHeight="1">
       <x:c r="B31" s="14" t="s">
-        <x:v>65</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C31" s="14" t="s">
-        <x:v>211</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="D31" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E31" s="14" t="s">
-        <x:v>239</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="F31" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="G31" s="14" t="s">
-        <x:v>241</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="H31" s="16">
-        <x:v>46086.099798588</x:v>
+        <x:v>46069.2327997454</x:v>
       </x:c>
       <x:c r="I31" s="16">
-        <x:v>46098</x:v>
+        <x:v>46049</x:v>
       </x:c>
       <x:c r="J31" s="15" t="s">
-        <x:v>242</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="K31" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L31" s="18">
-        <x:v>46090.2691152778</x:v>
+        <x:v>46100.3816829514</x:v>
       </x:c>
       <x:c r="M31" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="30" customHeight="1">
       <x:c r="B32" s="14" t="s">
-        <x:v>65</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C32" s="14" t="s">
-        <x:v>211</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D32" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E32" s="14" t="s">
-        <x:v>243</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="F32" s="14" t="s">
-        <x:v>244</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="G32" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="H32" s="16">
-        <x:v>46086.1144463079</x:v>
+        <x:v>46086.106481875</x:v>
       </x:c>
       <x:c r="I32" s="16">
-        <x:v>46097</x:v>
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J32" s="15" t="s">
-        <x:v>246</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="K32" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L32" s="18">
-        <x:v>46090.2703739352</x:v>
+        <x:v>46090.2765830324</x:v>
       </x:c>
       <x:c r="M32" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="33" spans="1:28" ht="30" customHeight="1">
       <x:c r="B33" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C33" s="14" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="D33" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E33" s="14" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="G33" s="14" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="H33" s="16">
+        <x:v>46085.1709247338</x:v>
+      </x:c>
+      <x:c r="I33" s="16">
+        <x:v>46085.1709419676</x:v>
+      </x:c>
+      <x:c r="J33" s="15" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="K33" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L33" s="18">
+        <x:v>46090.3337014815</x:v>
+      </x:c>
+      <x:c r="M33" s="14" t="s">
+        <x:v>254</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B34" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C34" s="14" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="D34" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E34" s="14" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G34" s="14" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="H34" s="16">
+        <x:v>46085.1662527662</x:v>
+      </x:c>
+      <x:c r="I34" s="16">
+        <x:v>46085.1662689699</x:v>
+      </x:c>
+      <x:c r="J34" s="15" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="K34" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L34" s="18">
+        <x:v>46090.3437343634</x:v>
+      </x:c>
+      <x:c r="M34" s="14" t="s">
+        <x:v>254</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B35" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C35" s="14" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="D35" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E35" s="14" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="F35" s="14" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="G35" s="14" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="H35" s="16">
+        <x:v>46107.2716210185</x:v>
+      </x:c>
+      <x:c r="I35" s="16">
+        <x:v>46107.2716387731</x:v>
+      </x:c>
+      <x:c r="J35" s="15" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="K35" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L35" s="18">
+        <x:v>46107.3352773843</x:v>
+      </x:c>
+      <x:c r="M35" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B36" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C36" s="14" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="D36" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E36" s="14" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="G36" s="14" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="H36" s="16">
+        <x:v>46084.1080380324</x:v>
+      </x:c>
+      <x:c r="I36" s="16">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J36" s="15" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="K36" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L36" s="18">
+        <x:v>46097.2478153472</x:v>
+      </x:c>
+      <x:c r="M36" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B37" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C37" s="14" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="D37" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E37" s="14" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="F37" s="14" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="G37" s="14" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="H37" s="16">
+        <x:v>46083.0788057755</x:v>
+      </x:c>
+      <x:c r="I37" s="16">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J37" s="15" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="K37" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L37" s="18">
+        <x:v>46083.1042250116</x:v>
+      </x:c>
+      <x:c r="M37" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B38" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C38" s="14" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="D38" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E38" s="14" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="F38" s="14" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="G38" s="14" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="H38" s="16">
+        <x:v>46086.099798588</x:v>
+      </x:c>
+      <x:c r="I38" s="16">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J38" s="15" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="K38" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L38" s="18">
+        <x:v>46090.2691152778</x:v>
+      </x:c>
+      <x:c r="M38" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B39" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C39" s="14" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="D39" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E39" s="14" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="F39" s="14" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="G39" s="14" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="H39" s="16">
+        <x:v>46086.1144463079</x:v>
+      </x:c>
+      <x:c r="I39" s="16">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J39" s="15" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="K39" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L39" s="18">
+        <x:v>46090.2703739352</x:v>
+      </x:c>
+      <x:c r="M39" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B40" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C40" s="14" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="D40" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E40" s="14" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="F40" s="14" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="G40" s="14" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="H40" s="16">
+        <x:v>46087.1643336806</x:v>
+      </x:c>
+      <x:c r="I40" s="16">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J40" s="15" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="K40" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L40" s="18">
+        <x:v>46090.2727784143</x:v>
+      </x:c>
+      <x:c r="M40" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B41" s="14" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="C33" s="14" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="D33" s="15" t="s">
+      <x:c r="C41" s="14" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="D41" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E33" s="14" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="F33" s="14" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="G33" s="14" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="H33" s="16">
+      <x:c r="E41" s="14" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="F41" s="14" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="G41" s="14" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="H41" s="16">
         <x:v>46098.290884375</x:v>
       </x:c>
-      <x:c r="I33" s="16">
+      <x:c r="I41" s="16">
         <x:v>45997</x:v>
       </x:c>
-      <x:c r="J33" s="15" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="K33" s="17" t="n">
+      <x:c r="J41" s="15" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="K41" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L33" s="18">
+      <x:c r="L41" s="18">
         <x:v>46098.3188767824</x:v>
       </x:c>
-      <x:c r="M33" s="14" t="s">
+      <x:c r="M41" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="36" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B36" s="19" t="s">
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B44" s="19" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="C36" s="20" t="s"/>
-      <x:c r="D36" s="20" t="s"/>
-      <x:c r="E36" s="21" t="s"/>
-      <x:c r="F36" s="21" t="s"/>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B37" s="22" t="s">
+      <x:c r="C44" s="20" t="s"/>
+      <x:c r="D44" s="20" t="s"/>
+      <x:c r="E44" s="21" t="s"/>
+      <x:c r="F44" s="21" t="s"/>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B45" s="22" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="C37" s="23" t="s"/>
-      <x:c r="D37" s="23" t="s"/>
-      <x:c r="E37" s="23" t="s"/>
-      <x:c r="F37" s="24" t="s">
+      <x:c r="C45" s="23" t="s"/>
+      <x:c r="D45" s="23" t="s"/>
+      <x:c r="E45" s="23" t="s"/>
+      <x:c r="F45" s="24" t="s">
         <x:v>123</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B38" s="25" t="s">
+    <x:row r="46" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B46" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C38" s="26" t="s"/>
-      <x:c r="D38" s="26" t="s"/>
-      <x:c r="E38" s="26" t="s"/>
-      <x:c r="F38" s="27" t="n">
+      <x:c r="C46" s="26" t="s"/>
+      <x:c r="D46" s="26" t="s"/>
+      <x:c r="E46" s="26" t="s"/>
+      <x:c r="F46" s="27" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B47" s="25" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C47" s="26" t="s"/>
+      <x:c r="D47" s="26" t="s"/>
+      <x:c r="E47" s="26" t="s"/>
+      <x:c r="F47" s="27" t="n">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B48" s="25" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C48" s="26" t="s"/>
+      <x:c r="D48" s="26" t="s"/>
+      <x:c r="E48" s="26" t="s"/>
+      <x:c r="F48" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B39" s="25" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C39" s="26" t="s"/>
-      <x:c r="D39" s="26" t="s"/>
-      <x:c r="E39" s="26" t="s"/>
-      <x:c r="F39" s="27" t="n">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B40" s="25" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C40" s="26" t="s"/>
-      <x:c r="D40" s="26" t="s"/>
-      <x:c r="E40" s="26" t="s"/>
-      <x:c r="F40" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B41" s="25" t="s">
+    <x:row r="49" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B49" s="25" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="C41" s="26" t="s"/>
-      <x:c r="D41" s="26" t="s"/>
-      <x:c r="E41" s="26" t="s"/>
-      <x:c r="F41" s="27" t="n">
+      <x:c r="C49" s="26" t="s"/>
+      <x:c r="D49" s="26" t="s"/>
+      <x:c r="E49" s="26" t="s"/>
+      <x:c r="F49" s="27" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B42" s="25" t="s">
+    <x:row r="50" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B50" s="25" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="C42" s="26" t="s"/>
-      <x:c r="D42" s="26" t="s"/>
-      <x:c r="E42" s="26" t="s"/>
-      <x:c r="F42" s="27" t="n">
+      <x:c r="C50" s="26" t="s"/>
+      <x:c r="D50" s="26" t="s"/>
+      <x:c r="E50" s="26" t="s"/>
+      <x:c r="F50" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B43" s="28" t="s">
+    <x:row r="51" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B51" s="28" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="C43" s="29" t="s"/>
-      <x:c r="D43" s="29" t="s"/>
-      <x:c r="E43" s="29" t="s"/>
-      <x:c r="F43" s="30" t="n">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C51" s="29" t="s"/>
+      <x:c r="D51" s="29" t="s"/>
+      <x:c r="E51" s="29" t="s"/>
+      <x:c r="F51" s="30" t="n">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
     <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5717,14 +6117,14 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B36:F36"/>
-    <x:mergeCell ref="B37:E37"/>
-    <x:mergeCell ref="B38:E38"/>
-    <x:mergeCell ref="B39:E39"/>
-    <x:mergeCell ref="B40:E40"/>
-    <x:mergeCell ref="B41:E41"/>
-    <x:mergeCell ref="B42:E42"/>
-    <x:mergeCell ref="B43:E43"/>
+    <x:mergeCell ref="B44:F44"/>
+    <x:mergeCell ref="B45:E45"/>
+    <x:mergeCell ref="B46:E46"/>
+    <x:mergeCell ref="B47:E47"/>
+    <x:mergeCell ref="B48:E48"/>
+    <x:mergeCell ref="B49:E49"/>
+    <x:mergeCell ref="B50:E50"/>
+    <x:mergeCell ref="B51:E51"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="290">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="288">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -31,9 +31,6 @@
     <x:t>ENGR. GALELEO MENDOZA</x:t>
   </x:si>
   <x:si>
-    <x:t>IV-A | February 2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>Application Type</x:t>
   </x:si>
   <x:si>
@@ -398,9 +395,6 @@
   </x:si>
   <x:si>
     <x:t>TOTAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IV-A | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>ALCALA, GLENN GUIBAO</x:t>
@@ -1224,7 +1218,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1239,6 +1233,9 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1299,7 +1296,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1335,6 +1332,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1709,20 +1710,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46054</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1745,908 +1746,908 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="D8" s="16" t="s"/>
+      <x:c r="E8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>46069.0835222569</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46069.1006819792</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46069.0835222569</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46069.1006819792</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46069.1133347338</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s"/>
+      <x:c r="E9" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H9" s="17">
+        <x:v>46069.0835757523</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46069.1000300231</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46069.1133347338</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46069.0835757523</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46069.1000300231</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
+      <x:c r="L9" s="19">
+        <x:v>46069.1128697454</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46069.1128697454</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="C10" s="15" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="D10" s="16" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
+      <x:c r="E10" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="H10" s="17">
+        <x:v>46067.3600302778</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46067.3600485417</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46067.3600302778</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46067.3600485417</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
+      <x:c r="K10" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>46079.273015787</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46067.1596693866</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>46079.277259919</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46067.222213287</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46089</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>46079.2763165278</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>46063.1352781944</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>46063.2367775347</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>46079.3584810995</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>46079.3584983796</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46079.273015787</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
+      <x:c r="L14" s="19">
+        <x:v>46080.2311256134</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>46079.3539738194</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>46079.3539910417</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L15" s="19">
+        <x:v>46080.244091956</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46067.1596693866</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
+      <x:c r="E16" s="15" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>46079.3873177662</x:v>
+      </x:c>
+      <x:c r="I16" s="17">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="J16" s="16" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46079.277259919</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46067.222213287</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46089</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="L16" s="19">
+        <x:v>46080.2360791898</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
+        <x:v>46079.2523059375</x:v>
+      </x:c>
+      <x:c r="I17" s="17">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J17" s="16" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46079.2763165278</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46063.1352781944</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
+      <x:c r="L17" s="19">
+        <x:v>46080.2925916204</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H18" s="17">
+        <x:v>46079.2430618866</x:v>
+      </x:c>
+      <x:c r="I18" s="17">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="K18" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46063.2367775347</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46079.3584810995</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46079.3584983796</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
+      <x:c r="L18" s="19">
+        <x:v>46080.2801283218</x:v>
+      </x:c>
+      <x:c r="M18" s="15" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46080.2311256134</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46079.3539738194</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46079.3539910417</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
+    </x:row>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="15" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46080.244091956</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46079.3873177662</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
+      <x:c r="C19" s="15" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H19" s="17">
+        <x:v>46079.3652018403</x:v>
+      </x:c>
+      <x:c r="I19" s="17">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J16" s="15" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
+      <x:c r="J19" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="18">
-        <x:v>46080.2360791898</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46079.2523059375</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
+      <x:c r="L19" s="19">
+        <x:v>46080.2425555208</x:v>
+      </x:c>
+      <x:c r="M19" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H20" s="17">
+        <x:v>46080.2923673264</x:v>
+      </x:c>
+      <x:c r="I20" s="17">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J17" s="15" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
+      <x:c r="J20" s="16" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K20" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46080.2925916204</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
+      <x:c r="L20" s="19">
+        <x:v>46080.3208568171</x:v>
+      </x:c>
+      <x:c r="M20" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F21" s="15" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H21" s="17">
+        <x:v>46079.3162545833</x:v>
+      </x:c>
+      <x:c r="I21" s="17">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J21" s="16" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46079.2430618866</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
+      <x:c r="K21" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="19">
+        <x:v>46080.2883729977</x:v>
+      </x:c>
+      <x:c r="M21" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D22" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E22" s="15" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H22" s="17">
+        <x:v>46079.3059443634</x:v>
+      </x:c>
+      <x:c r="I22" s="17">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J18" s="15" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
+      <x:c r="J22" s="16" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="K22" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="18">
-        <x:v>46080.2801283218</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46079.3652018403</x:v>
-      </x:c>
-      <x:c r="I19" s="16">
+      <x:c r="L22" s="19">
+        <x:v>46080.2896890278</x:v>
+      </x:c>
+      <x:c r="M22" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B23" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C23" s="15" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D23" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E23" s="15" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F23" s="15" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G23" s="15" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H23" s="17">
+        <x:v>46079.2943998843</x:v>
+      </x:c>
+      <x:c r="I23" s="17">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J19" s="15" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
+      <x:c r="J23" s="16" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="K23" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L19" s="18">
-        <x:v>46080.2425555208</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46080.2923673264</x:v>
-      </x:c>
-      <x:c r="I20" s="16">
+      <x:c r="L23" s="19">
+        <x:v>46080.2916823611</x:v>
+      </x:c>
+      <x:c r="M23" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B24" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C24" s="15" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D24" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E24" s="15" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F24" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G24" s="15" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H24" s="17">
+        <x:v>46079.3789042361</x:v>
+      </x:c>
+      <x:c r="I24" s="17">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J20" s="15" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="n">
+      <x:c r="J24" s="16" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="K24" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L20" s="18">
-        <x:v>46080.3208568171</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46079.3162545833</x:v>
-      </x:c>
-      <x:c r="I21" s="16">
+      <x:c r="L24" s="19">
+        <x:v>46080.2376106713</x:v>
+      </x:c>
+      <x:c r="M24" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B25" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C25" s="15" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D25" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E25" s="15" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F25" s="15" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="G25" s="15" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="H25" s="17">
+        <x:v>46079.3728295139</x:v>
+      </x:c>
+      <x:c r="I25" s="17">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J21" s="15" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="K21" s="17" t="n">
+      <x:c r="J25" s="16" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="K25" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L21" s="18">
-        <x:v>46080.2883729977</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46079.3059443634</x:v>
-      </x:c>
-      <x:c r="I22" s="16">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="K22" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="18">
-        <x:v>46080.2896890278</x:v>
-      </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46079.2943998843</x:v>
-      </x:c>
-      <x:c r="I23" s="16">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="K23" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="18">
-        <x:v>46080.2916823611</x:v>
-      </x:c>
-      <x:c r="M23" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="H24" s="16">
-        <x:v>46079.3789042361</x:v>
-      </x:c>
-      <x:c r="I24" s="16">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J24" s="15" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="K24" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L24" s="18">
-        <x:v>46080.2376106713</x:v>
-      </x:c>
-      <x:c r="M24" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C25" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="D25" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E25" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="F25" s="14" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G25" s="14" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="H25" s="16">
-        <x:v>46079.3728295139</x:v>
-      </x:c>
-      <x:c r="I25" s="16">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J25" s="15" t="s">
+      <x:c r="L25" s="19">
+        <x:v>46080.2394384722</x:v>
+      </x:c>
+      <x:c r="M25" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B26" s="15" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="K25" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L25" s="18">
-        <x:v>46080.2394384722</x:v>
-      </x:c>
-      <x:c r="M25" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="14" t="s">
+      <x:c r="C26" s="15" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="C26" s="14" t="s">
+      <x:c r="D26" s="16" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E26" s="15" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="D26" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E26" s="14" t="s">
+      <x:c r="F26" s="15" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="F26" s="14" t="s">
+      <x:c r="G26" s="15" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G26" s="14" t="s">
+      <x:c r="H26" s="17">
+        <x:v>46062.159017581</x:v>
+      </x:c>
+      <x:c r="I26" s="17">
+        <x:v>46062.1590321875</x:v>
+      </x:c>
+      <x:c r="J26" s="16" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="H26" s="16">
-        <x:v>46062.159017581</x:v>
-      </x:c>
-      <x:c r="I26" s="16">
-        <x:v>46062.1590321875</x:v>
-      </x:c>
-      <x:c r="J26" s="15" t="s">
+      <x:c r="K26" s="18" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L26" s="19">
+        <x:v>46062.1863264931</x:v>
+      </x:c>
+      <x:c r="M26" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B27" s="15" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="K26" s="17" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L26" s="18">
-        <x:v>46062.1863264931</x:v>
-      </x:c>
-      <x:c r="M26" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="14" t="s">
+      <x:c r="C27" s="15" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="C27" s="14" t="s">
+      <x:c r="D27" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E27" s="15" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="D27" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E27" s="14" t="s">
+      <x:c r="F27" s="15" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="F27" s="14" t="s">
+      <x:c r="G27" s="15" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="G27" s="14" t="s">
+      <x:c r="H27" s="17">
+        <x:v>46071.0492490046</x:v>
+      </x:c>
+      <x:c r="I27" s="17">
+        <x:v>46052</x:v>
+      </x:c>
+      <x:c r="J27" s="16" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="H27" s="16">
-        <x:v>46071.0492490046</x:v>
-      </x:c>
-      <x:c r="I27" s="16">
-        <x:v>46052</x:v>
-      </x:c>
-      <x:c r="J27" s="15" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="K27" s="17" t="n">
+      <x:c r="K27" s="18" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L27" s="18">
+      <x:c r="L27" s="19">
         <x:v>46071.0606162616</x:v>
       </x:c>
-      <x:c r="M27" s="14" t="s">
-        <x:v>59</x:v>
+      <x:c r="M27" s="15" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B30" s="19" t="s">
+      <x:c r="B30" s="20" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C30" s="21" t="s"/>
+      <x:c r="D30" s="21" t="s"/>
+      <x:c r="E30" s="22" t="s"/>
+      <x:c r="F30" s="22" t="s"/>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B31" s="23" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="C30" s="20" t="s"/>
-      <x:c r="D30" s="20" t="s"/>
-      <x:c r="E30" s="21" t="s"/>
-      <x:c r="F30" s="21" t="s"/>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B31" s="22" t="s">
+      <x:c r="C31" s="24" t="s"/>
+      <x:c r="D31" s="24" t="s"/>
+      <x:c r="E31" s="24" t="s"/>
+      <x:c r="F31" s="25" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="C31" s="23" t="s"/>
-      <x:c r="D31" s="23" t="s"/>
-      <x:c r="E31" s="23" t="s"/>
-      <x:c r="F31" s="24" t="s">
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C32" s="27" t="s"/>
+      <x:c r="D32" s="27" t="s"/>
+      <x:c r="E32" s="27" t="s"/>
+      <x:c r="F32" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="26" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C33" s="27" t="s"/>
+      <x:c r="D33" s="27" t="s"/>
+      <x:c r="E33" s="27" t="s"/>
+      <x:c r="F33" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="26" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C34" s="27" t="s"/>
+      <x:c r="D34" s="27" t="s"/>
+      <x:c r="E34" s="27" t="s"/>
+      <x:c r="F34" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="26" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C35" s="27" t="s"/>
+      <x:c r="D35" s="27" t="s"/>
+      <x:c r="E35" s="27" t="s"/>
+      <x:c r="F35" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="26" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C36" s="27" t="s"/>
+      <x:c r="D36" s="27" t="s"/>
+      <x:c r="E36" s="27" t="s"/>
+      <x:c r="F36" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B37" s="26" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C37" s="27" t="s"/>
+      <x:c r="D37" s="27" t="s"/>
+      <x:c r="E37" s="27" t="s"/>
+      <x:c r="F37" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B38" s="26" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C38" s="27" t="s"/>
+      <x:c r="D38" s="27" t="s"/>
+      <x:c r="E38" s="27" t="s"/>
+      <x:c r="F38" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B39" s="29" t="s">
         <x:v>123</x:v>
       </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C32" s="26" t="s"/>
-      <x:c r="D32" s="26" t="s"/>
-      <x:c r="E32" s="26" t="s"/>
-      <x:c r="F32" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="25" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C33" s="26" t="s"/>
-      <x:c r="D33" s="26" t="s"/>
-      <x:c r="E33" s="26" t="s"/>
-      <x:c r="F33" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="25" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C34" s="26" t="s"/>
-      <x:c r="D34" s="26" t="s"/>
-      <x:c r="E34" s="26" t="s"/>
-      <x:c r="F34" s="27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="25" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C35" s="26" t="s"/>
-      <x:c r="D35" s="26" t="s"/>
-      <x:c r="E35" s="26" t="s"/>
-      <x:c r="F35" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="25" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C36" s="26" t="s"/>
-      <x:c r="D36" s="26" t="s"/>
-      <x:c r="E36" s="26" t="s"/>
-      <x:c r="F36" s="27" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B37" s="25" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="C37" s="26" t="s"/>
-      <x:c r="D37" s="26" t="s"/>
-      <x:c r="E37" s="26" t="s"/>
-      <x:c r="F37" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B38" s="25" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="C38" s="26" t="s"/>
-      <x:c r="D38" s="26" t="s"/>
-      <x:c r="E38" s="26" t="s"/>
-      <x:c r="F38" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B39" s="28" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="C39" s="29" t="s"/>
-      <x:c r="D39" s="29" t="s"/>
-      <x:c r="E39" s="29" t="s"/>
-      <x:c r="F39" s="30" t="n">
+      <x:c r="C39" s="30" t="s"/>
+      <x:c r="D39" s="30" t="s"/>
+      <x:c r="E39" s="30" t="s"/>
+      <x:c r="F39" s="31" t="n">
         <x:v>20</x:v>
       </x:c>
     </x:row>
@@ -3730,20 +3731,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3766,1406 +3767,1406 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s"/>
+      <x:c r="E8" s="15" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>46100.1144765394</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46100.1505107292</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46100.1652817245</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46100.1144765394</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46100.1505107292</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="D9" s="16" t="s"/>
+      <x:c r="E9" s="15" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="F9" s="15" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H9" s="17">
+        <x:v>46107.1401251852</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46107.1653469792</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46100.1652817245</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="14" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="L9" s="19">
+        <x:v>46107.1722420255</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46107.1401251852</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46107.1653469792</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="F10" s="15" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>46111.14459375</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46111.1542258102</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46107.1722420255</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s"/>
-      <x:c r="E10" s="14" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="L10" s="19">
+        <x:v>46111.1662193056</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46111.14459375</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46111.1542258102</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="15" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="F11" s="15" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46091.3061033796</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46091.3108077083</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46111.1662193056</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="14" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="L11" s="19">
+        <x:v>46091.3131892477</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46091.3061033796</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46091.3108077083</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
+      <x:c r="D12" s="16" t="s"/>
+      <x:c r="E12" s="15" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="F12" s="15" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46093.1459465972</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46093.1585187731</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46091.3131892477</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s"/>
-      <x:c r="E12" s="14" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="L12" s="19">
+        <x:v>46093.1595409143</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46093.1459465972</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46093.1585187731</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
+      <x:c r="D13" s="16" t="s"/>
+      <x:c r="E13" s="15" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="F13" s="15" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>46107.1079779977</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46107.1569821643</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>46107.1713369444</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s"/>
+      <x:c r="E14" s="15" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>46107.1074963889</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>46107.1512672454</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L14" s="19">
+        <x:v>46107.1672093287</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s"/>
+      <x:c r="E15" s="15" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>46106.2628248843</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>46106.2706934954</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46093.1595409143</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s"/>
-      <x:c r="E13" s="14" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46107.1079779977</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46107.1569821643</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46107.1713369444</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s"/>
-      <x:c r="E14" s="14" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46107.1074963889</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46107.1512672454</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46107.1672093287</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s"/>
-      <x:c r="E15" s="14" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="L15" s="19">
+        <x:v>46106.2922441319</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46106.2628248843</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46106.2706934954</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
+      <x:c r="D16" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="K15" s="17" t="n">
+      <x:c r="F16" s="15" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>46080.4532551852</x:v>
+      </x:c>
+      <x:c r="I16" s="17">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="19">
+        <x:v>46097.1461728357</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
+        <x:v>46083.2380494329</x:v>
+      </x:c>
+      <x:c r="I17" s="17">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J17" s="16" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="19">
+        <x:v>46097.1564439468</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="H18" s="17">
+        <x:v>46083.2599218056</x:v>
+      </x:c>
+      <x:c r="I18" s="17">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="K18" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="19">
+        <x:v>46097.1652390856</x:v>
+      </x:c>
+      <x:c r="M18" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="H19" s="17">
+        <x:v>46069.278571956</x:v>
+      </x:c>
+      <x:c r="I19" s="17">
+        <x:v>46067</x:v>
+      </x:c>
+      <x:c r="J19" s="16" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L19" s="19">
+        <x:v>46100.3884108912</x:v>
+      </x:c>
+      <x:c r="M19" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="H20" s="17">
+        <x:v>46084.0854516898</x:v>
+      </x:c>
+      <x:c r="I20" s="17">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J20" s="16" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="K20" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="19">
+        <x:v>46093.3956400694</x:v>
+      </x:c>
+      <x:c r="M20" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="F21" s="15" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="H21" s="17">
+        <x:v>46084.0996762384</x:v>
+      </x:c>
+      <x:c r="I21" s="17">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J21" s="16" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="K21" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="19">
+        <x:v>46097.241468588</x:v>
+      </x:c>
+      <x:c r="M21" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D22" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E22" s="15" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="H22" s="17">
+        <x:v>46069.1542109954</x:v>
+      </x:c>
+      <x:c r="I22" s="17">
+        <x:v>46035</x:v>
+      </x:c>
+      <x:c r="J22" s="16" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="K22" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L22" s="19">
+        <x:v>46097.2466610301</x:v>
+      </x:c>
+      <x:c r="M22" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B23" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C23" s="15" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="D23" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E23" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="F23" s="15" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G23" s="15" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H23" s="17">
+        <x:v>46069.2178798032</x:v>
+      </x:c>
+      <x:c r="I23" s="17">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J23" s="16" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="K23" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L23" s="19">
+        <x:v>46097.2456397685</x:v>
+      </x:c>
+      <x:c r="M23" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B24" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C24" s="15" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D24" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E24" s="15" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="F24" s="15" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G24" s="15" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="H24" s="17">
+        <x:v>46069.3717699074</x:v>
+      </x:c>
+      <x:c r="I24" s="17">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J24" s="16" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="K24" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L24" s="19">
+        <x:v>46100.3754893056</x:v>
+      </x:c>
+      <x:c r="M24" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B25" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C25" s="15" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="D25" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E25" s="15" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="F25" s="15" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="G25" s="15" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="H25" s="17">
+        <x:v>46083.2443981019</x:v>
+      </x:c>
+      <x:c r="I25" s="17">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J25" s="16" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="K25" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="19">
+        <x:v>46097.1600206018</x:v>
+      </x:c>
+      <x:c r="M25" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B26" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C26" s="15" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D26" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E26" s="15" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="F26" s="15" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G26" s="15" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="H26" s="17">
+        <x:v>46084.1225139699</x:v>
+      </x:c>
+      <x:c r="I26" s="17">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J26" s="16" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="K26" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="19">
+        <x:v>46097.3505144329</x:v>
+      </x:c>
+      <x:c r="M26" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B27" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C27" s="15" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="D27" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E27" s="15" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="F27" s="15" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="G27" s="15" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="H27" s="17">
+        <x:v>46083.252116412</x:v>
+      </x:c>
+      <x:c r="I27" s="17">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J27" s="16" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="K27" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L27" s="19">
+        <x:v>46097.1628986343</x:v>
+      </x:c>
+      <x:c r="M27" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B28" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C28" s="15" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="D28" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E28" s="15" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="F28" s="15" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="G28" s="15" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="H28" s="17">
+        <x:v>46084.1157546528</x:v>
+      </x:c>
+      <x:c r="I28" s="17">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J28" s="16" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="K28" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L28" s="19">
+        <x:v>46105.3755915741</x:v>
+      </x:c>
+      <x:c r="M28" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B29" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C29" s="15" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="D29" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E29" s="15" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="F29" s="15" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="G29" s="15" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46106.2922441319</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46080.4532551852</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
+      <x:c r="H29" s="17">
+        <x:v>46069.1151616435</x:v>
+      </x:c>
+      <x:c r="I29" s="17">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J29" s="16" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="K29" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="18">
-        <x:v>46097.1461728357</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
+      <x:c r="L29" s="19">
+        <x:v>46097.343386956</x:v>
+      </x:c>
+      <x:c r="M29" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B30" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C30" s="15" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="D30" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E30" s="15" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="F30" s="15" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="G30" s="15" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="H30" s="17">
+        <x:v>46107.3381444213</x:v>
+      </x:c>
+      <x:c r="I30" s="17">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J30" s="16" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="K30" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="19">
+        <x:v>46107.3506854282</x:v>
+      </x:c>
+      <x:c r="M30" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B31" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C31" s="15" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="D31" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E31" s="15" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="F31" s="15" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="G31" s="15" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="H31" s="17">
+        <x:v>46069.2327997454</x:v>
+      </x:c>
+      <x:c r="I31" s="17">
+        <x:v>46049</x:v>
+      </x:c>
+      <x:c r="J31" s="16" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="K31" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L31" s="19">
+        <x:v>46100.3816829514</x:v>
+      </x:c>
+      <x:c r="M31" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B32" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C32" s="15" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="D32" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E32" s="15" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="F32" s="15" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="G32" s="15" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="H32" s="17">
+        <x:v>46086.106481875</x:v>
+      </x:c>
+      <x:c r="I32" s="17">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="J32" s="16" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="K32" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L32" s="19">
+        <x:v>46090.2765830324</x:v>
+      </x:c>
+      <x:c r="M32" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B33" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46083.2380494329</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
+      <x:c r="C33" s="15" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="D33" s="16" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E33" s="15" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="F33" s="15" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="G33" s="15" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="H33" s="17">
+        <x:v>46085.1709247338</x:v>
+      </x:c>
+      <x:c r="I33" s="17">
+        <x:v>46085.1709419676</x:v>
+      </x:c>
+      <x:c r="J33" s="16" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="K33" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L33" s="19">
+        <x:v>46090.3337014815</x:v>
+      </x:c>
+      <x:c r="M33" s="15" t="s">
+        <x:v>252</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B34" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C34" s="15" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="D34" s="16" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E34" s="15" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="F34" s="15" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="G34" s="15" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="H34" s="17">
+        <x:v>46085.1662527662</x:v>
+      </x:c>
+      <x:c r="I34" s="17">
+        <x:v>46085.1662689699</x:v>
+      </x:c>
+      <x:c r="J34" s="16" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="K34" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L34" s="19">
+        <x:v>46090.3437343634</x:v>
+      </x:c>
+      <x:c r="M34" s="15" t="s">
+        <x:v>252</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B35" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C35" s="15" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="D35" s="16" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E35" s="15" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="F35" s="15" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="G35" s="15" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="H35" s="17">
+        <x:v>46107.2716210185</x:v>
+      </x:c>
+      <x:c r="I35" s="17">
+        <x:v>46107.2716387731</x:v>
+      </x:c>
+      <x:c r="J35" s="16" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="K35" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L35" s="19">
+        <x:v>46107.3352773843</x:v>
+      </x:c>
+      <x:c r="M35" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B36" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C36" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="D36" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E36" s="15" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="F36" s="15" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="G36" s="15" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="H36" s="17">
+        <x:v>46084.1080380324</x:v>
+      </x:c>
+      <x:c r="I36" s="17">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J36" s="16" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="K36" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46097.1564439468</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46083.2599218056</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>46101</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
+      <x:c r="L36" s="19">
+        <x:v>46097.2478153472</x:v>
+      </x:c>
+      <x:c r="M36" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B37" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C37" s="15" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="D37" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E37" s="15" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="F37" s="15" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="G37" s="15" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="H37" s="17">
+        <x:v>46083.0788057755</x:v>
+      </x:c>
+      <x:c r="I37" s="17">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J37" s="16" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="K37" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="18">
-        <x:v>46097.1652390856</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46069.278571956</x:v>
-      </x:c>
-      <x:c r="I19" s="16">
-        <x:v>46067</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L19" s="18">
-        <x:v>46100.3884108912</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46084.0854516898</x:v>
-      </x:c>
-      <x:c r="I20" s="16">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="n">
+      <x:c r="L37" s="19">
+        <x:v>46083.1042250116</x:v>
+      </x:c>
+      <x:c r="M37" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B38" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C38" s="15" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="D38" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E38" s="15" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F38" s="15" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="G38" s="15" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="H38" s="17">
+        <x:v>46086.099798588</x:v>
+      </x:c>
+      <x:c r="I38" s="17">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J38" s="16" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="K38" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L20" s="18">
-        <x:v>46093.3956400694</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46084.0996762384</x:v>
-      </x:c>
-      <x:c r="I21" s="16">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="K21" s="17" t="n">
+      <x:c r="L38" s="19">
+        <x:v>46090.2691152778</x:v>
+      </x:c>
+      <x:c r="M38" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B39" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C39" s="15" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="D39" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E39" s="15" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="F39" s="15" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="G39" s="15" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="H39" s="17">
+        <x:v>46086.1144463079</x:v>
+      </x:c>
+      <x:c r="I39" s="17">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J39" s="16" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="K39" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L21" s="18">
-        <x:v>46097.241468588</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46069.1542109954</x:v>
-      </x:c>
-      <x:c r="I22" s="16">
-        <x:v>46035</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="K22" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L22" s="18">
-        <x:v>46097.2466610301</x:v>
-      </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46069.2178798032</x:v>
-      </x:c>
-      <x:c r="I23" s="16">
-        <x:v>46051</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="K23" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L23" s="18">
-        <x:v>46097.2456397685</x:v>
-      </x:c>
-      <x:c r="M23" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="H24" s="16">
-        <x:v>46069.3717699074</x:v>
-      </x:c>
-      <x:c r="I24" s="16">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J24" s="15" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="K24" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L24" s="18">
-        <x:v>46100.3754893056</x:v>
-      </x:c>
-      <x:c r="M24" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C25" s="14" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="D25" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E25" s="14" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="F25" s="14" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="G25" s="14" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="H25" s="16">
-        <x:v>46083.2443981019</x:v>
-      </x:c>
-      <x:c r="I25" s="16">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J25" s="15" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="K25" s="17" t="n">
+      <x:c r="L39" s="19">
+        <x:v>46090.2703739352</x:v>
+      </x:c>
+      <x:c r="M39" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B40" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C40" s="15" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="D40" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E40" s="15" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="F40" s="15" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="G40" s="15" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="H40" s="17">
+        <x:v>46087.1643336806</x:v>
+      </x:c>
+      <x:c r="I40" s="17">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J40" s="16" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K40" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L25" s="18">
-        <x:v>46097.1600206018</x:v>
-      </x:c>
-      <x:c r="M25" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C26" s="14" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="D26" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E26" s="14" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="F26" s="14" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="G26" s="14" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="H26" s="16">
-        <x:v>46084.1225139699</x:v>
-      </x:c>
-      <x:c r="I26" s="16">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J26" s="15" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="K26" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="18">
-        <x:v>46097.3505144329</x:v>
-      </x:c>
-      <x:c r="M26" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C27" s="14" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="D27" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E27" s="14" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="F27" s="14" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="G27" s="14" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="H27" s="16">
-        <x:v>46083.252116412</x:v>
-      </x:c>
-      <x:c r="I27" s="16">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J27" s="15" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="K27" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="18">
-        <x:v>46097.1628986343</x:v>
-      </x:c>
-      <x:c r="M27" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C28" s="14" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="D28" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E28" s="14" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="F28" s="14" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="G28" s="14" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="H28" s="16">
-        <x:v>46084.1157546528</x:v>
-      </x:c>
-      <x:c r="I28" s="16">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J28" s="15" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="K28" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L28" s="18">
-        <x:v>46105.3755915741</x:v>
-      </x:c>
-      <x:c r="M28" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B29" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C29" s="14" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="D29" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E29" s="14" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="F29" s="14" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="G29" s="14" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="H29" s="16">
-        <x:v>46069.1151616435</x:v>
-      </x:c>
-      <x:c r="I29" s="16">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J29" s="15" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="K29" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="18">
-        <x:v>46097.343386956</x:v>
-      </x:c>
-      <x:c r="M29" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B30" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C30" s="14" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="D30" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E30" s="14" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="F30" s="14" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="G30" s="14" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="H30" s="16">
-        <x:v>46107.3381444213</x:v>
-      </x:c>
-      <x:c r="I30" s="16">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J30" s="15" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="K30" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="18">
-        <x:v>46107.3506854282</x:v>
-      </x:c>
-      <x:c r="M30" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B31" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C31" s="14" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="D31" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E31" s="14" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="F31" s="14" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="G31" s="14" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="H31" s="16">
-        <x:v>46069.2327997454</x:v>
-      </x:c>
-      <x:c r="I31" s="16">
-        <x:v>46049</x:v>
-      </x:c>
-      <x:c r="J31" s="15" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="K31" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L31" s="18">
-        <x:v>46100.3816829514</x:v>
-      </x:c>
-      <x:c r="M31" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B32" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C32" s="14" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="D32" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E32" s="14" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="F32" s="14" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="G32" s="14" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="H32" s="16">
-        <x:v>46086.106481875</x:v>
-      </x:c>
-      <x:c r="I32" s="16">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="J32" s="15" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="K32" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L32" s="18">
-        <x:v>46090.2765830324</x:v>
-      </x:c>
-      <x:c r="M32" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B33" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C33" s="14" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="D33" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E33" s="14" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="F33" s="14" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="G33" s="14" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="H33" s="16">
-        <x:v>46085.1709247338</x:v>
-      </x:c>
-      <x:c r="I33" s="16">
-        <x:v>46085.1709419676</x:v>
-      </x:c>
-      <x:c r="J33" s="15" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="K33" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L33" s="18">
-        <x:v>46090.3337014815</x:v>
-      </x:c>
-      <x:c r="M33" s="14" t="s">
-        <x:v>254</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B34" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C34" s="14" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="D34" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E34" s="14" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="F34" s="14" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="G34" s="14" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="H34" s="16">
-        <x:v>46085.1662527662</x:v>
-      </x:c>
-      <x:c r="I34" s="16">
-        <x:v>46085.1662689699</x:v>
-      </x:c>
-      <x:c r="J34" s="15" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="K34" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L34" s="18">
-        <x:v>46090.3437343634</x:v>
-      </x:c>
-      <x:c r="M34" s="14" t="s">
-        <x:v>254</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B35" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C35" s="14" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="D35" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E35" s="14" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="F35" s="14" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="G35" s="14" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="H35" s="16">
-        <x:v>46107.2716210185</x:v>
-      </x:c>
-      <x:c r="I35" s="16">
-        <x:v>46107.2716387731</x:v>
-      </x:c>
-      <x:c r="J35" s="15" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="K35" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L35" s="18">
-        <x:v>46107.3352773843</x:v>
-      </x:c>
-      <x:c r="M35" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B36" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C36" s="14" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="D36" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E36" s="14" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="F36" s="14" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="G36" s="14" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="H36" s="16">
-        <x:v>46084.1080380324</x:v>
-      </x:c>
-      <x:c r="I36" s="16">
-        <x:v>46103</x:v>
-      </x:c>
-      <x:c r="J36" s="15" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="K36" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L36" s="18">
-        <x:v>46097.2478153472</x:v>
-      </x:c>
-      <x:c r="M36" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B37" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C37" s="14" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="D37" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E37" s="14" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="F37" s="14" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="G37" s="14" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="H37" s="16">
-        <x:v>46083.0788057755</x:v>
-      </x:c>
-      <x:c r="I37" s="16">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J37" s="15" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="K37" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L37" s="18">
-        <x:v>46083.1042250116</x:v>
-      </x:c>
-      <x:c r="M37" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B38" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C38" s="14" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="D38" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E38" s="14" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="F38" s="14" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="G38" s="14" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="H38" s="16">
-        <x:v>46086.099798588</x:v>
-      </x:c>
-      <x:c r="I38" s="16">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="J38" s="15" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="K38" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L38" s="18">
-        <x:v>46090.2691152778</x:v>
-      </x:c>
-      <x:c r="M38" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B39" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C39" s="14" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="D39" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E39" s="14" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="F39" s="14" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="G39" s="14" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="H39" s="16">
-        <x:v>46086.1144463079</x:v>
-      </x:c>
-      <x:c r="I39" s="16">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J39" s="15" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="K39" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L39" s="18">
-        <x:v>46090.2703739352</x:v>
-      </x:c>
-      <x:c r="M39" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B40" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C40" s="14" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="D40" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E40" s="14" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="F40" s="14" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="G40" s="14" t="s">
+      <x:c r="L40" s="19">
+        <x:v>46090.2727784143</x:v>
+      </x:c>
+      <x:c r="M40" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B41" s="15" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C41" s="15" t="s">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="H40" s="16">
-        <x:v>46087.1643336806</x:v>
-      </x:c>
-      <x:c r="I40" s="16">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="J40" s="15" t="s">
+      <x:c r="D41" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E41" s="15" t="s">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="K40" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L40" s="18">
-        <x:v>46090.2727784143</x:v>
-      </x:c>
-      <x:c r="M40" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B41" s="14" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="C41" s="14" t="s">
+      <x:c r="F41" s="15" t="s">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="D41" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E41" s="14" t="s">
+      <x:c r="G41" s="15" t="s">
         <x:v>286</x:v>
       </x:c>
-      <x:c r="F41" s="14" t="s">
+      <x:c r="H41" s="17">
+        <x:v>46098.290884375</x:v>
+      </x:c>
+      <x:c r="I41" s="17">
+        <x:v>45997</x:v>
+      </x:c>
+      <x:c r="J41" s="16" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="G41" s="14" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="H41" s="16">
-        <x:v>46098.290884375</x:v>
-      </x:c>
-      <x:c r="I41" s="16">
-        <x:v>45997</x:v>
-      </x:c>
-      <x:c r="J41" s="15" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="K41" s="17" t="n">
+      <x:c r="K41" s="18" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L41" s="18">
+      <x:c r="L41" s="19">
         <x:v>46098.3188767824</x:v>
       </x:c>
-      <x:c r="M41" s="14" t="s">
-        <x:v>59</x:v>
+      <x:c r="M41" s="15" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="44" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B44" s="19" t="s">
+      <x:c r="B44" s="20" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C44" s="21" t="s"/>
+      <x:c r="D44" s="21" t="s"/>
+      <x:c r="E44" s="22" t="s"/>
+      <x:c r="F44" s="22" t="s"/>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B45" s="23" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="C44" s="20" t="s"/>
-      <x:c r="D44" s="20" t="s"/>
-      <x:c r="E44" s="21" t="s"/>
-      <x:c r="F44" s="21" t="s"/>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B45" s="22" t="s">
+      <x:c r="C45" s="24" t="s"/>
+      <x:c r="D45" s="24" t="s"/>
+      <x:c r="E45" s="24" t="s"/>
+      <x:c r="F45" s="25" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="C45" s="23" t="s"/>
-      <x:c r="D45" s="23" t="s"/>
-      <x:c r="E45" s="23" t="s"/>
-      <x:c r="F45" s="24" t="s">
+    </x:row>
+    <x:row r="46" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B46" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C46" s="27" t="s"/>
+      <x:c r="D46" s="27" t="s"/>
+      <x:c r="E46" s="27" t="s"/>
+      <x:c r="F46" s="28" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B47" s="26" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C47" s="27" t="s"/>
+      <x:c r="D47" s="27" t="s"/>
+      <x:c r="E47" s="27" t="s"/>
+      <x:c r="F47" s="28" t="n">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B48" s="26" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C48" s="27" t="s"/>
+      <x:c r="D48" s="27" t="s"/>
+      <x:c r="E48" s="27" t="s"/>
+      <x:c r="F48" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B49" s="26" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C49" s="27" t="s"/>
+      <x:c r="D49" s="27" t="s"/>
+      <x:c r="E49" s="27" t="s"/>
+      <x:c r="F49" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B50" s="26" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C50" s="27" t="s"/>
+      <x:c r="D50" s="27" t="s"/>
+      <x:c r="E50" s="27" t="s"/>
+      <x:c r="F50" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B51" s="29" t="s">
         <x:v>123</x:v>
       </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B46" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C46" s="26" t="s"/>
-      <x:c r="D46" s="26" t="s"/>
-      <x:c r="E46" s="26" t="s"/>
-      <x:c r="F46" s="27" t="n">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B47" s="25" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C47" s="26" t="s"/>
-      <x:c r="D47" s="26" t="s"/>
-      <x:c r="E47" s="26" t="s"/>
-      <x:c r="F47" s="27" t="n">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="25" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C48" s="26" t="s"/>
-      <x:c r="D48" s="26" t="s"/>
-      <x:c r="E48" s="26" t="s"/>
-      <x:c r="F48" s="27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="25" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C49" s="26" t="s"/>
-      <x:c r="D49" s="26" t="s"/>
-      <x:c r="E49" s="26" t="s"/>
-      <x:c r="F49" s="27" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="25" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="C50" s="26" t="s"/>
-      <x:c r="D50" s="26" t="s"/>
-      <x:c r="E50" s="26" t="s"/>
-      <x:c r="F50" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B51" s="28" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="C51" s="29" t="s"/>
-      <x:c r="D51" s="29" t="s"/>
-      <x:c r="E51" s="29" t="s"/>
-      <x:c r="F51" s="30" t="n">
+      <x:c r="C51" s="30" t="s"/>
+      <x:c r="D51" s="30" t="s"/>
+      <x:c r="E51" s="30" t="s"/>
+      <x:c r="F51" s="31" t="n">
         <x:v>34</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -8,6 +8,7 @@
   <x:sheets>
     <x:sheet name="February 2026" sheetId="7" r:id="rId7"/>
     <x:sheet name="March 2026" sheetId="8" r:id="rId8"/>
+    <x:sheet name="April 2026" sheetId="9" r:id="rId9"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="288">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="292">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -887,6 +888,18 @@
   </x:si>
   <x:si>
     <x:t>1511858</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2F SM CYBERZONE, SM CITY CALAMBA, BRGY. REAL, City Of Calamba, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-24-01-1081(REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1260-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1530589</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -898,7 +911,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -984,6 +997,13 @@
       <x:sz val="14"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
   </x:fonts>
@@ -1218,7 +1238,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1295,8 +1315,20 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1413,6 +1445,18 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -6140,4 +6184,1273 @@
   </x:headerFooter>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="0" summaryRight="0"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:AB993"/>
+  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
+    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
+    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A1" s="1" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="14" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="14" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="14" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="14" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="14" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="32" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C8" s="32" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E8" s="32" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="F8" s="32" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="G8" s="32" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="H8" s="33">
+        <x:v>46120.2370111574</x:v>
+      </x:c>
+      <x:c r="I8" s="33">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J8" s="32" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="K8" s="34" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L8" s="33">
+        <x:v>46120.2952031944</x:v>
+      </x:c>
+      <x:c r="M8" s="32" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="20" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C11" s="21" t="s"/>
+      <x:c r="D11" s="21" t="s"/>
+      <x:c r="E11" s="22" t="s"/>
+      <x:c r="F11" s="22" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="23" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C12" s="24" t="s"/>
+      <x:c r="D12" s="24" t="s"/>
+      <x:c r="E12" s="24" t="s"/>
+      <x:c r="F12" s="25" t="s">
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="26" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s"/>
+      <x:c r="D13" s="27" t="s"/>
+      <x:c r="E13" s="27" t="s"/>
+      <x:c r="F13" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="29" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="C14" s="30" t="s"/>
+      <x:c r="D14" s="30" t="s"/>
+      <x:c r="E14" s="30" t="s"/>
+      <x:c r="F14" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
+  </x:sheetData>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="292">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="302">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -888,6 +888,36 @@
   </x:si>
   <x:si>
     <x:t>1511858</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JAYRON G CALABIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>House 104 Leonor 1 Compound, 3, City Of Calamba, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-04017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1267-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1530643</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JAYRON G. CALABIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>104 104 Leonor 1 Compound, 3, City Of Calamba, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-04018-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1271-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1530645</x:t>
   </x:si>
   <x:si>
     <x:t>2F SM CYBERZONE, SM CITY CALAMBA, BRGY. REAL, City Of Calamba, Laguna</x:t>
@@ -911,7 +941,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -997,13 +1027,6 @@
       <x:sz val="14"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
   </x:fonts>
@@ -1238,7 +1261,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="30">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1315,20 +1338,8 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1445,18 +1456,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -6356,103 +6355,170 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="32" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s"/>
+      <x:c r="E8" s="15" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>46126.3445514815</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46126.3505074537</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46126.3564094097</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s"/>
+      <x:c r="E9" s="15" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="H9" s="17">
+        <x:v>46126.3584514236</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46126.3611957755</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>46126.3662729282</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="C8" s="32" t="s">
+      <x:c r="C10" s="15" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="D8" s="32" t="s">
+      <x:c r="D10" s="16" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E8" s="32" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="G8" s="32" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="H8" s="33">
+      <x:c r="E10" s="15" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>46120.2370111574</x:v>
       </x:c>
-      <x:c r="I8" s="33">
+      <x:c r="I10" s="17">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="J8" s="32" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="K8" s="34" t="n">
+      <x:c r="J10" s="16" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L8" s="33">
+      <x:c r="L10" s="19">
         <x:v>46120.2952031944</x:v>
       </x:c>
-      <x:c r="M8" s="32" t="s">
+      <x:c r="M10" s="15" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="20" t="s">
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="20" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="C11" s="21" t="s"/>
-      <x:c r="D11" s="21" t="s"/>
-      <x:c r="E11" s="22" t="s"/>
-      <x:c r="F11" s="22" t="s"/>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="23" t="s">
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="25" t="s">
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
         <x:v>122</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="26" t="s">
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="26" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="C13" s="27" t="s"/>
-      <x:c r="D13" s="27" t="s"/>
-      <x:c r="E13" s="27" t="s"/>
-      <x:c r="F13" s="28" t="n">
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="29" t="s">
+    <x:row r="17" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B17" s="29" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="C14" s="30" t="s"/>
-      <x:c r="D14" s="30" t="s"/>
-      <x:c r="E14" s="30" t="s"/>
-      <x:c r="F14" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C17" s="30" t="s"/>
+      <x:c r="D17" s="30" t="s"/>
+      <x:c r="E17" s="30" t="s"/>
+      <x:c r="F17" s="31" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7430,15 +7496,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
+  <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -941,7 +941,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -981,14 +981,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -1261,7 +1253,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1272,16 +1264,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1293,53 +1282,53 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1374,87 +1363,83 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1756,17 +1741,17 @@
       <x:c r="B5" s="12">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1789,908 +1774,908 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s"/>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="D8" s="15" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46069.0835222569</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46069.1006819792</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46069.1133347338</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s"/>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="D9" s="15" t="s"/>
+      <x:c r="E9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46069.0835757523</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46069.1000300231</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46069.1128697454</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46067.3600302778</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>46067.3600485417</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46079.273015787</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46067.1596693866</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46079.277259919</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>46067.222213287</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>46089</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>46079.2763165278</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>46063.1352781944</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>46066</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>46063.2367775347</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>46079.3584810995</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>46079.3584983796</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>46080.2311256134</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>46079.3539738194</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>46079.3539910417</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>46080.244091956</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="s">
+      <x:c r="C16" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="s">
+      <x:c r="D16" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="E16" s="14" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="F16" s="14" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="H16" s="17">
+      <x:c r="H16" s="16">
         <x:v>46079.3873177662</x:v>
       </x:c>
-      <x:c r="I16" s="17">
+      <x:c r="I16" s="16">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="s">
+      <x:c r="J16" s="15" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="19">
+      <x:c r="L16" s="18">
         <x:v>46080.2360791898</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
+      <x:c r="M16" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="15" t="s">
+      <x:c r="B17" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="s">
+      <x:c r="C17" s="14" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="s">
+      <x:c r="D17" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="s">
+      <x:c r="E17" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="s">
+      <x:c r="F17" s="14" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="H17" s="17">
+      <x:c r="H17" s="16">
         <x:v>46079.2523059375</x:v>
       </x:c>
-      <x:c r="I17" s="17">
+      <x:c r="I17" s="16">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="s">
+      <x:c r="J17" s="15" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="K17" s="18" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="19">
+      <x:c r="L17" s="18">
         <x:v>46080.2925916204</x:v>
       </x:c>
-      <x:c r="M17" s="15" t="s">
+      <x:c r="M17" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="15" t="s">
+      <x:c r="B18" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="s">
+      <x:c r="C18" s="14" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="D18" s="16" t="s">
+      <x:c r="D18" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="s">
+      <x:c r="E18" s="14" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="s">
+      <x:c r="F18" s="14" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="G18" s="15" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="H18" s="17">
+      <x:c r="H18" s="16">
         <x:v>46079.2430618866</x:v>
       </x:c>
-      <x:c r="I18" s="17">
+      <x:c r="I18" s="16">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="s">
+      <x:c r="J18" s="15" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="K18" s="18" t="n">
+      <x:c r="K18" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="19">
+      <x:c r="L18" s="18">
         <x:v>46080.2801283218</x:v>
       </x:c>
-      <x:c r="M18" s="15" t="s">
+      <x:c r="M18" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="15" t="s">
+      <x:c r="B19" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C19" s="15" t="s">
+      <x:c r="C19" s="14" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D19" s="16" t="s">
+      <x:c r="D19" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="s">
+      <x:c r="E19" s="14" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="F19" s="15" t="s">
+      <x:c r="F19" s="14" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G19" s="15" t="s">
+      <x:c r="G19" s="14" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="H19" s="17">
+      <x:c r="H19" s="16">
         <x:v>46079.3652018403</x:v>
       </x:c>
-      <x:c r="I19" s="17">
+      <x:c r="I19" s="16">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J19" s="16" t="s">
+      <x:c r="J19" s="15" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="K19" s="18" t="n">
+      <x:c r="K19" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L19" s="19">
+      <x:c r="L19" s="18">
         <x:v>46080.2425555208</x:v>
       </x:c>
-      <x:c r="M19" s="15" t="s">
+      <x:c r="M19" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="15" t="s">
+      <x:c r="B20" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C20" s="15" t="s">
+      <x:c r="C20" s="14" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D20" s="16" t="s">
+      <x:c r="D20" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E20" s="15" t="s">
+      <x:c r="E20" s="14" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="F20" s="15" t="s">
+      <x:c r="F20" s="14" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="G20" s="15" t="s">
+      <x:c r="G20" s="14" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="H20" s="17">
+      <x:c r="H20" s="16">
         <x:v>46080.2923673264</x:v>
       </x:c>
-      <x:c r="I20" s="17">
+      <x:c r="I20" s="16">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J20" s="16" t="s">
+      <x:c r="J20" s="15" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="K20" s="18" t="n">
+      <x:c r="K20" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L20" s="19">
+      <x:c r="L20" s="18">
         <x:v>46080.3208568171</x:v>
       </x:c>
-      <x:c r="M20" s="15" t="s">
+      <x:c r="M20" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="15" t="s">
+      <x:c r="B21" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C21" s="15" t="s">
+      <x:c r="C21" s="14" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="D21" s="16" t="s">
+      <x:c r="D21" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E21" s="15" t="s">
+      <x:c r="E21" s="14" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="F21" s="15" t="s">
+      <x:c r="F21" s="14" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="G21" s="15" t="s">
+      <x:c r="G21" s="14" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="H21" s="17">
+      <x:c r="H21" s="16">
         <x:v>46079.3162545833</x:v>
       </x:c>
-      <x:c r="I21" s="17">
+      <x:c r="I21" s="16">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J21" s="16" t="s">
+      <x:c r="J21" s="15" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="K21" s="18" t="n">
+      <x:c r="K21" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L21" s="19">
+      <x:c r="L21" s="18">
         <x:v>46080.2883729977</x:v>
       </x:c>
-      <x:c r="M21" s="15" t="s">
+      <x:c r="M21" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="15" t="s">
+      <x:c r="B22" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C22" s="15" t="s">
+      <x:c r="C22" s="14" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D22" s="16" t="s">
+      <x:c r="D22" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E22" s="15" t="s">
+      <x:c r="E22" s="14" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="F22" s="15" t="s">
+      <x:c r="F22" s="14" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G22" s="15" t="s">
+      <x:c r="G22" s="14" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="H22" s="17">
+      <x:c r="H22" s="16">
         <x:v>46079.3059443634</x:v>
       </x:c>
-      <x:c r="I22" s="17">
+      <x:c r="I22" s="16">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J22" s="16" t="s">
+      <x:c r="J22" s="15" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="K22" s="18" t="n">
+      <x:c r="K22" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L22" s="19">
+      <x:c r="L22" s="18">
         <x:v>46080.2896890278</x:v>
       </x:c>
-      <x:c r="M22" s="15" t="s">
+      <x:c r="M22" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="15" t="s">
+      <x:c r="B23" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C23" s="15" t="s">
+      <x:c r="C23" s="14" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="D23" s="16" t="s">
+      <x:c r="D23" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E23" s="15" t="s">
+      <x:c r="E23" s="14" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="F23" s="15" t="s">
+      <x:c r="F23" s="14" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="G23" s="15" t="s">
+      <x:c r="G23" s="14" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="H23" s="17">
+      <x:c r="H23" s="16">
         <x:v>46079.2943998843</x:v>
       </x:c>
-      <x:c r="I23" s="17">
+      <x:c r="I23" s="16">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J23" s="16" t="s">
+      <x:c r="J23" s="15" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="K23" s="18" t="n">
+      <x:c r="K23" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L23" s="19">
+      <x:c r="L23" s="18">
         <x:v>46080.2916823611</x:v>
       </x:c>
-      <x:c r="M23" s="15" t="s">
+      <x:c r="M23" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="15" t="s">
+      <x:c r="B24" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C24" s="15" t="s">
+      <x:c r="C24" s="14" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="D24" s="16" t="s">
+      <x:c r="D24" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E24" s="15" t="s">
+      <x:c r="E24" s="14" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F24" s="15" t="s">
+      <x:c r="F24" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="G24" s="15" t="s">
+      <x:c r="G24" s="14" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="H24" s="17">
+      <x:c r="H24" s="16">
         <x:v>46079.3789042361</x:v>
       </x:c>
-      <x:c r="I24" s="17">
+      <x:c r="I24" s="16">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J24" s="16" t="s">
+      <x:c r="J24" s="15" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="K24" s="18" t="n">
+      <x:c r="K24" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L24" s="19">
+      <x:c r="L24" s="18">
         <x:v>46080.2376106713</x:v>
       </x:c>
-      <x:c r="M24" s="15" t="s">
+      <x:c r="M24" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="15" t="s">
+      <x:c r="B25" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C25" s="15" t="s">
+      <x:c r="C25" s="14" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="D25" s="16" t="s">
+      <x:c r="D25" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E25" s="15" t="s">
+      <x:c r="E25" s="14" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F25" s="15" t="s">
+      <x:c r="F25" s="14" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="G25" s="15" t="s">
+      <x:c r="G25" s="14" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="H25" s="17">
+      <x:c r="H25" s="16">
         <x:v>46079.3728295139</x:v>
       </x:c>
-      <x:c r="I25" s="17">
+      <x:c r="I25" s="16">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J25" s="16" t="s">
+      <x:c r="J25" s="15" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="K25" s="18" t="n">
+      <x:c r="K25" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L25" s="19">
+      <x:c r="L25" s="18">
         <x:v>46080.2394384722</x:v>
       </x:c>
-      <x:c r="M25" s="15" t="s">
+      <x:c r="M25" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="15" t="s">
+      <x:c r="B26" s="14" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="C26" s="15" t="s">
+      <x:c r="C26" s="14" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="D26" s="16" t="s">
+      <x:c r="D26" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E26" s="15" t="s">
+      <x:c r="E26" s="14" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="F26" s="15" t="s">
+      <x:c r="F26" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="G26" s="15" t="s">
+      <x:c r="G26" s="14" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H26" s="17">
+      <x:c r="H26" s="16">
         <x:v>46062.159017581</x:v>
       </x:c>
-      <x:c r="I26" s="17">
+      <x:c r="I26" s="16">
         <x:v>46062.1590321875</x:v>
       </x:c>
-      <x:c r="J26" s="16" t="s">
+      <x:c r="J26" s="15" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="K26" s="18" t="n">
+      <x:c r="K26" s="17" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L26" s="19">
+      <x:c r="L26" s="18">
         <x:v>46062.1863264931</x:v>
       </x:c>
-      <x:c r="M26" s="15" t="s">
+      <x:c r="M26" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="15" t="s">
+      <x:c r="B27" s="14" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="C27" s="15" t="s">
+      <x:c r="C27" s="14" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="D27" s="16" t="s">
+      <x:c r="D27" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E27" s="15" t="s">
+      <x:c r="E27" s="14" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="F27" s="15" t="s">
+      <x:c r="F27" s="14" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="G27" s="15" t="s">
+      <x:c r="G27" s="14" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="H27" s="17">
+      <x:c r="H27" s="16">
         <x:v>46071.0492490046</x:v>
       </x:c>
-      <x:c r="I27" s="17">
+      <x:c r="I27" s="16">
         <x:v>46052</x:v>
       </x:c>
-      <x:c r="J27" s="16" t="s">
+      <x:c r="J27" s="15" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="K27" s="18" t="n">
+      <x:c r="K27" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L27" s="19">
+      <x:c r="L27" s="18">
         <x:v>46071.0606162616</x:v>
       </x:c>
-      <x:c r="M27" s="15" t="s">
+      <x:c r="M27" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B30" s="20" t="s">
+      <x:c r="B30" s="19" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="C30" s="21" t="s"/>
-      <x:c r="D30" s="21" t="s"/>
-      <x:c r="E30" s="22" t="s"/>
-      <x:c r="F30" s="22" t="s"/>
+      <x:c r="C30" s="20" t="s"/>
+      <x:c r="D30" s="20" t="s"/>
+      <x:c r="E30" s="21" t="s"/>
+      <x:c r="F30" s="21" t="s"/>
     </x:row>
     <x:row r="31" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B31" s="23" t="s">
+      <x:c r="B31" s="22" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="C31" s="24" t="s"/>
-      <x:c r="D31" s="24" t="s"/>
-      <x:c r="E31" s="24" t="s"/>
-      <x:c r="F31" s="25" t="s">
+      <x:c r="C31" s="23" t="s"/>
+      <x:c r="D31" s="23" t="s"/>
+      <x:c r="E31" s="23" t="s"/>
+      <x:c r="F31" s="24" t="s">
         <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="26" t="s">
+      <x:c r="B32" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C32" s="27" t="s"/>
-      <x:c r="D32" s="27" t="s"/>
-      <x:c r="E32" s="27" t="s"/>
-      <x:c r="F32" s="28" t="n">
+      <x:c r="C32" s="26" t="s"/>
+      <x:c r="D32" s="26" t="s"/>
+      <x:c r="E32" s="26" t="s"/>
+      <x:c r="F32" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="26" t="s">
+      <x:c r="B33" s="25" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C33" s="27" t="s"/>
-      <x:c r="D33" s="27" t="s"/>
-      <x:c r="E33" s="27" t="s"/>
-      <x:c r="F33" s="28" t="n">
+      <x:c r="C33" s="26" t="s"/>
+      <x:c r="D33" s="26" t="s"/>
+      <x:c r="E33" s="26" t="s"/>
+      <x:c r="F33" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="26" t="s">
+      <x:c r="B34" s="25" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C34" s="27" t="s"/>
-      <x:c r="D34" s="27" t="s"/>
-      <x:c r="E34" s="27" t="s"/>
-      <x:c r="F34" s="28" t="n">
+      <x:c r="C34" s="26" t="s"/>
+      <x:c r="D34" s="26" t="s"/>
+      <x:c r="E34" s="26" t="s"/>
+      <x:c r="F34" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="26" t="s">
+      <x:c r="B35" s="25" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C35" s="27" t="s"/>
-      <x:c r="D35" s="27" t="s"/>
-      <x:c r="E35" s="27" t="s"/>
-      <x:c r="F35" s="28" t="n">
+      <x:c r="C35" s="26" t="s"/>
+      <x:c r="D35" s="26" t="s"/>
+      <x:c r="E35" s="26" t="s"/>
+      <x:c r="F35" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="26" t="s">
+      <x:c r="B36" s="25" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C36" s="27" t="s"/>
-      <x:c r="D36" s="27" t="s"/>
-      <x:c r="E36" s="27" t="s"/>
-      <x:c r="F36" s="28" t="n">
+      <x:c r="C36" s="26" t="s"/>
+      <x:c r="D36" s="26" t="s"/>
+      <x:c r="E36" s="26" t="s"/>
+      <x:c r="F36" s="27" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B37" s="26" t="s">
+      <x:c r="B37" s="25" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="C37" s="27" t="s"/>
-      <x:c r="D37" s="27" t="s"/>
-      <x:c r="E37" s="27" t="s"/>
-      <x:c r="F37" s="28" t="n">
+      <x:c r="C37" s="26" t="s"/>
+      <x:c r="D37" s="26" t="s"/>
+      <x:c r="E37" s="26" t="s"/>
+      <x:c r="F37" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B38" s="26" t="s">
+      <x:c r="B38" s="25" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="C38" s="27" t="s"/>
-      <x:c r="D38" s="27" t="s"/>
-      <x:c r="E38" s="27" t="s"/>
-      <x:c r="F38" s="28" t="n">
+      <x:c r="C38" s="26" t="s"/>
+      <x:c r="D38" s="26" t="s"/>
+      <x:c r="E38" s="26" t="s"/>
+      <x:c r="F38" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B39" s="29" t="s">
+      <x:c r="B39" s="28" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="C39" s="30" t="s"/>
-      <x:c r="D39" s="30" t="s"/>
-      <x:c r="E39" s="30" t="s"/>
-      <x:c r="F39" s="31" t="n">
+      <x:c r="C39" s="29" t="s"/>
+      <x:c r="D39" s="29" t="s"/>
+      <x:c r="E39" s="29" t="s"/>
+      <x:c r="F39" s="30" t="n">
         <x:v>20</x:v>
       </x:c>
     </x:row>
@@ -3777,17 +3762,17 @@
       <x:c r="B5" s="12">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3810,1406 +3795,1406 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s"/>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="D8" s="15" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46100.1144765394</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46100.1505107292</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46100.1652817245</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s"/>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="D9" s="15" t="s"/>
+      <x:c r="E9" s="14" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46107.1401251852</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46107.1653469792</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46107.1722420255</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46111.14459375</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>46111.1542258102</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46111.1662193056</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46091.3061033796</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>46091.3108077083</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46091.3131892477</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="D12" s="15" t="s"/>
+      <x:c r="E12" s="14" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>46093.1459465972</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>46093.1585187731</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>46093.1595409143</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s"/>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="D13" s="15" t="s"/>
+      <x:c r="E13" s="14" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>46107.1079779977</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>46107.1569821643</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>46107.1713369444</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s"/>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="D14" s="15" t="s"/>
+      <x:c r="E14" s="14" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>46107.1074963889</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>46107.1512672454</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>46107.1672093287</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s"/>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="D15" s="15" t="s"/>
+      <x:c r="E15" s="14" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>46106.2628248843</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>46106.2706934954</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>46106.2922441319</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="s">
+      <x:c r="C16" s="14" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="s">
+      <x:c r="D16" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="E16" s="14" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="F16" s="14" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="H16" s="17">
+      <x:c r="H16" s="16">
         <x:v>46080.4532551852</x:v>
       </x:c>
-      <x:c r="I16" s="17">
+      <x:c r="I16" s="16">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="s">
+      <x:c r="J16" s="15" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="19">
+      <x:c r="L16" s="18">
         <x:v>46097.1461728357</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
+      <x:c r="M16" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="15" t="s">
+      <x:c r="B17" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="s">
+      <x:c r="C17" s="14" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="s">
+      <x:c r="D17" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="s">
+      <x:c r="E17" s="14" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="s">
+      <x:c r="F17" s="14" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="H17" s="17">
+      <x:c r="H17" s="16">
         <x:v>46083.2380494329</x:v>
       </x:c>
-      <x:c r="I17" s="17">
+      <x:c r="I17" s="16">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="s">
+      <x:c r="J17" s="15" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="K17" s="18" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="19">
+      <x:c r="L17" s="18">
         <x:v>46097.1564439468</x:v>
       </x:c>
-      <x:c r="M17" s="15" t="s">
+      <x:c r="M17" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="15" t="s">
+      <x:c r="B18" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="s">
+      <x:c r="C18" s="14" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="D18" s="16" t="s">
+      <x:c r="D18" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="s">
+      <x:c r="E18" s="14" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="s">
+      <x:c r="F18" s="14" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="G18" s="15" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="H18" s="17">
+      <x:c r="H18" s="16">
         <x:v>46083.2599218056</x:v>
       </x:c>
-      <x:c r="I18" s="17">
+      <x:c r="I18" s="16">
         <x:v>46101</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="s">
+      <x:c r="J18" s="15" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="K18" s="18" t="n">
+      <x:c r="K18" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="19">
+      <x:c r="L18" s="18">
         <x:v>46097.1652390856</x:v>
       </x:c>
-      <x:c r="M18" s="15" t="s">
+      <x:c r="M18" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="15" t="s">
+      <x:c r="B19" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C19" s="15" t="s">
+      <x:c r="C19" s="14" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="D19" s="16" t="s">
+      <x:c r="D19" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="s">
+      <x:c r="E19" s="14" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="F19" s="15" t="s">
+      <x:c r="F19" s="14" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="G19" s="15" t="s">
+      <x:c r="G19" s="14" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="H19" s="17">
+      <x:c r="H19" s="16">
         <x:v>46069.278571956</x:v>
       </x:c>
-      <x:c r="I19" s="17">
+      <x:c r="I19" s="16">
         <x:v>46067</x:v>
       </x:c>
-      <x:c r="J19" s="16" t="s">
+      <x:c r="J19" s="15" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="K19" s="18" t="n">
+      <x:c r="K19" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L19" s="19">
+      <x:c r="L19" s="18">
         <x:v>46100.3884108912</x:v>
       </x:c>
-      <x:c r="M19" s="15" t="s">
+      <x:c r="M19" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="15" t="s">
+      <x:c r="B20" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C20" s="15" t="s">
+      <x:c r="C20" s="14" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="D20" s="16" t="s">
+      <x:c r="D20" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E20" s="15" t="s">
+      <x:c r="E20" s="14" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="F20" s="15" t="s">
+      <x:c r="F20" s="14" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="G20" s="15" t="s">
+      <x:c r="G20" s="14" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="H20" s="17">
+      <x:c r="H20" s="16">
         <x:v>46084.0854516898</x:v>
       </x:c>
-      <x:c r="I20" s="17">
+      <x:c r="I20" s="16">
         <x:v>46144</x:v>
       </x:c>
-      <x:c r="J20" s="16" t="s">
+      <x:c r="J20" s="15" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="K20" s="18" t="n">
+      <x:c r="K20" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L20" s="19">
+      <x:c r="L20" s="18">
         <x:v>46093.3956400694</x:v>
       </x:c>
-      <x:c r="M20" s="15" t="s">
+      <x:c r="M20" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="15" t="s">
+      <x:c r="B21" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C21" s="15" t="s">
+      <x:c r="C21" s="14" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="D21" s="16" t="s">
+      <x:c r="D21" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E21" s="15" t="s">
+      <x:c r="E21" s="14" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="F21" s="15" t="s">
+      <x:c r="F21" s="14" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="G21" s="15" t="s">
+      <x:c r="G21" s="14" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="H21" s="17">
+      <x:c r="H21" s="16">
         <x:v>46084.0996762384</x:v>
       </x:c>
-      <x:c r="I21" s="17">
+      <x:c r="I21" s="16">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J21" s="16" t="s">
+      <x:c r="J21" s="15" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="K21" s="18" t="n">
+      <x:c r="K21" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L21" s="19">
+      <x:c r="L21" s="18">
         <x:v>46097.241468588</x:v>
       </x:c>
-      <x:c r="M21" s="15" t="s">
+      <x:c r="M21" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="15" t="s">
+      <x:c r="B22" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C22" s="15" t="s">
+      <x:c r="C22" s="14" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="D22" s="16" t="s">
+      <x:c r="D22" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E22" s="15" t="s">
+      <x:c r="E22" s="14" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="F22" s="15" t="s">
+      <x:c r="F22" s="14" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="G22" s="15" t="s">
+      <x:c r="G22" s="14" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="H22" s="17">
+      <x:c r="H22" s="16">
         <x:v>46069.1542109954</x:v>
       </x:c>
-      <x:c r="I22" s="17">
+      <x:c r="I22" s="16">
         <x:v>46035</x:v>
       </x:c>
-      <x:c r="J22" s="16" t="s">
+      <x:c r="J22" s="15" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="K22" s="18" t="n">
+      <x:c r="K22" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L22" s="19">
+      <x:c r="L22" s="18">
         <x:v>46097.2466610301</x:v>
       </x:c>
-      <x:c r="M22" s="15" t="s">
+      <x:c r="M22" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="15" t="s">
+      <x:c r="B23" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C23" s="15" t="s">
+      <x:c r="C23" s="14" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="D23" s="16" t="s">
+      <x:c r="D23" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E23" s="15" t="s">
+      <x:c r="E23" s="14" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="F23" s="15" t="s">
+      <x:c r="F23" s="14" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="G23" s="15" t="s">
+      <x:c r="G23" s="14" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="H23" s="17">
+      <x:c r="H23" s="16">
         <x:v>46069.2178798032</x:v>
       </x:c>
-      <x:c r="I23" s="17">
+      <x:c r="I23" s="16">
         <x:v>46051</x:v>
       </x:c>
-      <x:c r="J23" s="16" t="s">
+      <x:c r="J23" s="15" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="K23" s="18" t="n">
+      <x:c r="K23" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L23" s="19">
+      <x:c r="L23" s="18">
         <x:v>46097.2456397685</x:v>
       </x:c>
-      <x:c r="M23" s="15" t="s">
+      <x:c r="M23" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="15" t="s">
+      <x:c r="B24" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C24" s="15" t="s">
+      <x:c r="C24" s="14" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="D24" s="16" t="s">
+      <x:c r="D24" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E24" s="15" t="s">
+      <x:c r="E24" s="14" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="F24" s="15" t="s">
+      <x:c r="F24" s="14" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="G24" s="15" t="s">
+      <x:c r="G24" s="14" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="H24" s="17">
+      <x:c r="H24" s="16">
         <x:v>46069.3717699074</x:v>
       </x:c>
-      <x:c r="I24" s="17">
+      <x:c r="I24" s="16">
         <x:v>46066</x:v>
       </x:c>
-      <x:c r="J24" s="16" t="s">
+      <x:c r="J24" s="15" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="K24" s="18" t="n">
+      <x:c r="K24" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L24" s="19">
+      <x:c r="L24" s="18">
         <x:v>46100.3754893056</x:v>
       </x:c>
-      <x:c r="M24" s="15" t="s">
+      <x:c r="M24" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="15" t="s">
+      <x:c r="B25" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C25" s="15" t="s">
+      <x:c r="C25" s="14" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="D25" s="16" t="s">
+      <x:c r="D25" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E25" s="15" t="s">
+      <x:c r="E25" s="14" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="F25" s="15" t="s">
+      <x:c r="F25" s="14" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="G25" s="15" t="s">
+      <x:c r="G25" s="14" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="H25" s="17">
+      <x:c r="H25" s="16">
         <x:v>46083.2443981019</x:v>
       </x:c>
-      <x:c r="I25" s="17">
+      <x:c r="I25" s="16">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J25" s="16" t="s">
+      <x:c r="J25" s="15" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="K25" s="18" t="n">
+      <x:c r="K25" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L25" s="19">
+      <x:c r="L25" s="18">
         <x:v>46097.1600206018</x:v>
       </x:c>
-      <x:c r="M25" s="15" t="s">
+      <x:c r="M25" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="15" t="s">
+      <x:c r="B26" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C26" s="15" t="s">
+      <x:c r="C26" s="14" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="D26" s="16" t="s">
+      <x:c r="D26" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E26" s="15" t="s">
+      <x:c r="E26" s="14" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="F26" s="15" t="s">
+      <x:c r="F26" s="14" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="G26" s="15" t="s">
+      <x:c r="G26" s="14" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="H26" s="17">
+      <x:c r="H26" s="16">
         <x:v>46084.1225139699</x:v>
       </x:c>
-      <x:c r="I26" s="17">
+      <x:c r="I26" s="16">
         <x:v>46172</x:v>
       </x:c>
-      <x:c r="J26" s="16" t="s">
+      <x:c r="J26" s="15" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="K26" s="18" t="n">
+      <x:c r="K26" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L26" s="19">
+      <x:c r="L26" s="18">
         <x:v>46097.3505144329</x:v>
       </x:c>
-      <x:c r="M26" s="15" t="s">
+      <x:c r="M26" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="15" t="s">
+      <x:c r="B27" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C27" s="15" t="s">
+      <x:c r="C27" s="14" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="D27" s="16" t="s">
+      <x:c r="D27" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E27" s="15" t="s">
+      <x:c r="E27" s="14" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="F27" s="15" t="s">
+      <x:c r="F27" s="14" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="G27" s="15" t="s">
+      <x:c r="G27" s="14" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="H27" s="17">
+      <x:c r="H27" s="16">
         <x:v>46083.252116412</x:v>
       </x:c>
-      <x:c r="I27" s="17">
+      <x:c r="I27" s="16">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J27" s="16" t="s">
+      <x:c r="J27" s="15" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="K27" s="18" t="n">
+      <x:c r="K27" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L27" s="19">
+      <x:c r="L27" s="18">
         <x:v>46097.1628986343</x:v>
       </x:c>
-      <x:c r="M27" s="15" t="s">
+      <x:c r="M27" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="15" t="s">
+      <x:c r="B28" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C28" s="15" t="s">
+      <x:c r="C28" s="14" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="D28" s="16" t="s">
+      <x:c r="D28" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E28" s="15" t="s">
+      <x:c r="E28" s="14" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="F28" s="15" t="s">
+      <x:c r="F28" s="14" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="G28" s="15" t="s">
+      <x:c r="G28" s="14" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="H28" s="17">
+      <x:c r="H28" s="16">
         <x:v>46084.1157546528</x:v>
       </x:c>
-      <x:c r="I28" s="17">
+      <x:c r="I28" s="16">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J28" s="16" t="s">
+      <x:c r="J28" s="15" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="K28" s="18" t="n">
+      <x:c r="K28" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L28" s="19">
+      <x:c r="L28" s="18">
         <x:v>46105.3755915741</x:v>
       </x:c>
-      <x:c r="M28" s="15" t="s">
+      <x:c r="M28" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B29" s="15" t="s">
+      <x:c r="B29" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C29" s="15" t="s">
+      <x:c r="C29" s="14" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="D29" s="16" t="s">
+      <x:c r="D29" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E29" s="15" t="s">
+      <x:c r="E29" s="14" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="F29" s="15" t="s">
+      <x:c r="F29" s="14" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="G29" s="15" t="s">
+      <x:c r="G29" s="14" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="H29" s="17">
+      <x:c r="H29" s="16">
         <x:v>46069.1151616435</x:v>
       </x:c>
-      <x:c r="I29" s="17">
+      <x:c r="I29" s="16">
         <x:v>46172</x:v>
       </x:c>
-      <x:c r="J29" s="16" t="s">
+      <x:c r="J29" s="15" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="K29" s="18" t="n">
+      <x:c r="K29" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L29" s="19">
+      <x:c r="L29" s="18">
         <x:v>46097.343386956</x:v>
       </x:c>
-      <x:c r="M29" s="15" t="s">
+      <x:c r="M29" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B30" s="15" t="s">
+      <x:c r="B30" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C30" s="15" t="s">
+      <x:c r="C30" s="14" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="D30" s="16" t="s">
+      <x:c r="D30" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E30" s="15" t="s">
+      <x:c r="E30" s="14" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="F30" s="15" t="s">
+      <x:c r="F30" s="14" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="G30" s="15" t="s">
+      <x:c r="G30" s="14" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="H30" s="17">
+      <x:c r="H30" s="16">
         <x:v>46107.3381444213</x:v>
       </x:c>
-      <x:c r="I30" s="17">
+      <x:c r="I30" s="16">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J30" s="16" t="s">
+      <x:c r="J30" s="15" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="K30" s="18" t="n">
+      <x:c r="K30" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L30" s="19">
+      <x:c r="L30" s="18">
         <x:v>46107.3506854282</x:v>
       </x:c>
-      <x:c r="M30" s="15" t="s">
+      <x:c r="M30" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B31" s="15" t="s">
+      <x:c r="B31" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C31" s="15" t="s">
+      <x:c r="C31" s="14" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="D31" s="16" t="s">
+      <x:c r="D31" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E31" s="15" t="s">
+      <x:c r="E31" s="14" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="F31" s="15" t="s">
+      <x:c r="F31" s="14" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="G31" s="15" t="s">
+      <x:c r="G31" s="14" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="H31" s="17">
+      <x:c r="H31" s="16">
         <x:v>46069.2327997454</x:v>
       </x:c>
-      <x:c r="I31" s="17">
+      <x:c r="I31" s="16">
         <x:v>46049</x:v>
       </x:c>
-      <x:c r="J31" s="16" t="s">
+      <x:c r="J31" s="15" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="K31" s="18" t="n">
+      <x:c r="K31" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L31" s="19">
+      <x:c r="L31" s="18">
         <x:v>46100.3816829514</x:v>
       </x:c>
-      <x:c r="M31" s="15" t="s">
+      <x:c r="M31" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B32" s="15" t="s">
+      <x:c r="B32" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C32" s="15" t="s">
+      <x:c r="C32" s="14" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="D32" s="16" t="s">
+      <x:c r="D32" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E32" s="15" t="s">
+      <x:c r="E32" s="14" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="F32" s="15" t="s">
+      <x:c r="F32" s="14" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="G32" s="15" t="s">
+      <x:c r="G32" s="14" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="H32" s="17">
+      <x:c r="H32" s="16">
         <x:v>46086.106481875</x:v>
       </x:c>
-      <x:c r="I32" s="17">
+      <x:c r="I32" s="16">
         <x:v>46095</x:v>
       </x:c>
-      <x:c r="J32" s="16" t="s">
+      <x:c r="J32" s="15" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="K32" s="18" t="n">
+      <x:c r="K32" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L32" s="19">
+      <x:c r="L32" s="18">
         <x:v>46090.2765830324</x:v>
       </x:c>
-      <x:c r="M32" s="15" t="s">
+      <x:c r="M32" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B33" s="15" t="s">
+      <x:c r="B33" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C33" s="15" t="s">
+      <x:c r="C33" s="14" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="D33" s="16" t="s">
+      <x:c r="D33" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E33" s="15" t="s">
+      <x:c r="E33" s="14" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="F33" s="15" t="s">
+      <x:c r="F33" s="14" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="G33" s="15" t="s">
+      <x:c r="G33" s="14" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="H33" s="17">
+      <x:c r="H33" s="16">
         <x:v>46085.1709247338</x:v>
       </x:c>
-      <x:c r="I33" s="17">
+      <x:c r="I33" s="16">
         <x:v>46085.1709419676</x:v>
       </x:c>
-      <x:c r="J33" s="16" t="s">
+      <x:c r="J33" s="15" t="s">
         <x:v>251</x:v>
       </x:c>
-      <x:c r="K33" s="18" t="n">
+      <x:c r="K33" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L33" s="19">
+      <x:c r="L33" s="18">
         <x:v>46090.3337014815</x:v>
       </x:c>
-      <x:c r="M33" s="15" t="s">
+      <x:c r="M33" s="14" t="s">
         <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B34" s="15" t="s">
+      <x:c r="B34" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C34" s="15" t="s">
+      <x:c r="C34" s="14" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="D34" s="16" t="s">
+      <x:c r="D34" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E34" s="15" t="s">
+      <x:c r="E34" s="14" t="s">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="F34" s="15" t="s">
+      <x:c r="F34" s="14" t="s">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="G34" s="15" t="s">
+      <x:c r="G34" s="14" t="s">
         <x:v>255</x:v>
       </x:c>
-      <x:c r="H34" s="17">
+      <x:c r="H34" s="16">
         <x:v>46085.1662527662</x:v>
       </x:c>
-      <x:c r="I34" s="17">
+      <x:c r="I34" s="16">
         <x:v>46085.1662689699</x:v>
       </x:c>
-      <x:c r="J34" s="16" t="s">
+      <x:c r="J34" s="15" t="s">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="K34" s="18" t="n">
+      <x:c r="K34" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L34" s="19">
+      <x:c r="L34" s="18">
         <x:v>46090.3437343634</x:v>
       </x:c>
-      <x:c r="M34" s="15" t="s">
+      <x:c r="M34" s="14" t="s">
         <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B35" s="15" t="s">
+      <x:c r="B35" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C35" s="15" t="s">
+      <x:c r="C35" s="14" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="D35" s="16" t="s">
+      <x:c r="D35" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E35" s="15" t="s">
+      <x:c r="E35" s="14" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="F35" s="15" t="s">
+      <x:c r="F35" s="14" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="G35" s="15" t="s">
+      <x:c r="G35" s="14" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="H35" s="17">
+      <x:c r="H35" s="16">
         <x:v>46107.2716210185</x:v>
       </x:c>
-      <x:c r="I35" s="17">
+      <x:c r="I35" s="16">
         <x:v>46107.2716387731</x:v>
       </x:c>
-      <x:c r="J35" s="16" t="s">
+      <x:c r="J35" s="15" t="s">
         <x:v>261</x:v>
       </x:c>
-      <x:c r="K35" s="18" t="n">
+      <x:c r="K35" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L35" s="19">
+      <x:c r="L35" s="18">
         <x:v>46107.3352773843</x:v>
       </x:c>
-      <x:c r="M35" s="15" t="s">
+      <x:c r="M35" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B36" s="15" t="s">
+      <x:c r="B36" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C36" s="15" t="s">
+      <x:c r="C36" s="14" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="D36" s="16" t="s">
+      <x:c r="D36" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E36" s="15" t="s">
+      <x:c r="E36" s="14" t="s">
         <x:v>262</x:v>
       </x:c>
-      <x:c r="F36" s="15" t="s">
+      <x:c r="F36" s="14" t="s">
         <x:v>263</x:v>
       </x:c>
-      <x:c r="G36" s="15" t="s">
+      <x:c r="G36" s="14" t="s">
         <x:v>264</x:v>
       </x:c>
-      <x:c r="H36" s="17">
+      <x:c r="H36" s="16">
         <x:v>46084.1080380324</x:v>
       </x:c>
-      <x:c r="I36" s="17">
+      <x:c r="I36" s="16">
         <x:v>46103</x:v>
       </x:c>
-      <x:c r="J36" s="16" t="s">
+      <x:c r="J36" s="15" t="s">
         <x:v>265</x:v>
       </x:c>
-      <x:c r="K36" s="18" t="n">
+      <x:c r="K36" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L36" s="19">
+      <x:c r="L36" s="18">
         <x:v>46097.2478153472</x:v>
       </x:c>
-      <x:c r="M36" s="15" t="s">
+      <x:c r="M36" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B37" s="15" t="s">
+      <x:c r="B37" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C37" s="15" t="s">
+      <x:c r="C37" s="14" t="s">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="D37" s="16" t="s">
+      <x:c r="D37" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E37" s="15" t="s">
+      <x:c r="E37" s="14" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="F37" s="15" t="s">
+      <x:c r="F37" s="14" t="s">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="G37" s="15" t="s">
+      <x:c r="G37" s="14" t="s">
         <x:v>269</x:v>
       </x:c>
-      <x:c r="H37" s="17">
+      <x:c r="H37" s="16">
         <x:v>46083.0788057755</x:v>
       </x:c>
-      <x:c r="I37" s="17">
+      <x:c r="I37" s="16">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J37" s="16" t="s">
+      <x:c r="J37" s="15" t="s">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="K37" s="18" t="n">
+      <x:c r="K37" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L37" s="19">
+      <x:c r="L37" s="18">
         <x:v>46083.1042250116</x:v>
       </x:c>
-      <x:c r="M37" s="15" t="s">
+      <x:c r="M37" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B38" s="15" t="s">
+      <x:c r="B38" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C38" s="15" t="s">
+      <x:c r="C38" s="14" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="D38" s="16" t="s">
+      <x:c r="D38" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E38" s="15" t="s">
+      <x:c r="E38" s="14" t="s">
         <x:v>271</x:v>
       </x:c>
-      <x:c r="F38" s="15" t="s">
+      <x:c r="F38" s="14" t="s">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="G38" s="15" t="s">
+      <x:c r="G38" s="14" t="s">
         <x:v>273</x:v>
       </x:c>
-      <x:c r="H38" s="17">
+      <x:c r="H38" s="16">
         <x:v>46086.099798588</x:v>
       </x:c>
-      <x:c r="I38" s="17">
+      <x:c r="I38" s="16">
         <x:v>46098</x:v>
       </x:c>
-      <x:c r="J38" s="16" t="s">
+      <x:c r="J38" s="15" t="s">
         <x:v>274</x:v>
       </x:c>
-      <x:c r="K38" s="18" t="n">
+      <x:c r="K38" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L38" s="19">
+      <x:c r="L38" s="18">
         <x:v>46090.2691152778</x:v>
       </x:c>
-      <x:c r="M38" s="15" t="s">
+      <x:c r="M38" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B39" s="15" t="s">
+      <x:c r="B39" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C39" s="15" t="s">
+      <x:c r="C39" s="14" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="D39" s="16" t="s">
+      <x:c r="D39" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E39" s="15" t="s">
+      <x:c r="E39" s="14" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="F39" s="15" t="s">
+      <x:c r="F39" s="14" t="s">
         <x:v>276</x:v>
       </x:c>
-      <x:c r="G39" s="15" t="s">
+      <x:c r="G39" s="14" t="s">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="H39" s="17">
+      <x:c r="H39" s="16">
         <x:v>46086.1144463079</x:v>
       </x:c>
-      <x:c r="I39" s="17">
+      <x:c r="I39" s="16">
         <x:v>46097</x:v>
       </x:c>
-      <x:c r="J39" s="16" t="s">
+      <x:c r="J39" s="15" t="s">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="K39" s="18" t="n">
+      <x:c r="K39" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L39" s="19">
+      <x:c r="L39" s="18">
         <x:v>46090.2703739352</x:v>
       </x:c>
-      <x:c r="M39" s="15" t="s">
+      <x:c r="M39" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B40" s="15" t="s">
+      <x:c r="B40" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C40" s="15" t="s">
+      <x:c r="C40" s="14" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="D40" s="16" t="s">
+      <x:c r="D40" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E40" s="15" t="s">
+      <x:c r="E40" s="14" t="s">
         <x:v>279</x:v>
       </x:c>
-      <x:c r="F40" s="15" t="s">
+      <x:c r="F40" s="14" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="G40" s="15" t="s">
+      <x:c r="G40" s="14" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="H40" s="17">
+      <x:c r="H40" s="16">
         <x:v>46087.1643336806</x:v>
       </x:c>
-      <x:c r="I40" s="17">
+      <x:c r="I40" s="16">
         <x:v>46104</x:v>
       </x:c>
-      <x:c r="J40" s="16" t="s">
+      <x:c r="J40" s="15" t="s">
         <x:v>282</x:v>
       </x:c>
-      <x:c r="K40" s="18" t="n">
+      <x:c r="K40" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L40" s="19">
+      <x:c r="L40" s="18">
         <x:v>46090.2727784143</x:v>
       </x:c>
-      <x:c r="M40" s="15" t="s">
+      <x:c r="M40" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B41" s="15" t="s">
+      <x:c r="B41" s="14" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="C41" s="15" t="s">
+      <x:c r="C41" s="14" t="s">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="D41" s="16" t="s">
+      <x:c r="D41" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E41" s="15" t="s">
+      <x:c r="E41" s="14" t="s">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="F41" s="15" t="s">
+      <x:c r="F41" s="14" t="s">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="G41" s="15" t="s">
+      <x:c r="G41" s="14" t="s">
         <x:v>286</x:v>
       </x:c>
-      <x:c r="H41" s="17">
+      <x:c r="H41" s="16">
         <x:v>46098.290884375</x:v>
       </x:c>
-      <x:c r="I41" s="17">
+      <x:c r="I41" s="16">
         <x:v>45997</x:v>
       </x:c>
-      <x:c r="J41" s="16" t="s">
+      <x:c r="J41" s="15" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="K41" s="18" t="n">
+      <x:c r="K41" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L41" s="19">
+      <x:c r="L41" s="18">
         <x:v>46098.3188767824</x:v>
       </x:c>
-      <x:c r="M41" s="15" t="s">
+      <x:c r="M41" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="44" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B44" s="20" t="s">
+      <x:c r="B44" s="19" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="C44" s="21" t="s"/>
-      <x:c r="D44" s="21" t="s"/>
-      <x:c r="E44" s="22" t="s"/>
-      <x:c r="F44" s="22" t="s"/>
+      <x:c r="C44" s="20" t="s"/>
+      <x:c r="D44" s="20" t="s"/>
+      <x:c r="E44" s="21" t="s"/>
+      <x:c r="F44" s="21" t="s"/>
     </x:row>
     <x:row r="45" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B45" s="23" t="s">
+      <x:c r="B45" s="22" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="C45" s="24" t="s"/>
-      <x:c r="D45" s="24" t="s"/>
-      <x:c r="E45" s="24" t="s"/>
-      <x:c r="F45" s="25" t="s">
+      <x:c r="C45" s="23" t="s"/>
+      <x:c r="D45" s="23" t="s"/>
+      <x:c r="E45" s="23" t="s"/>
+      <x:c r="F45" s="24" t="s">
         <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B46" s="26" t="s">
+      <x:c r="B46" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C46" s="27" t="s"/>
-      <x:c r="D46" s="27" t="s"/>
-      <x:c r="E46" s="27" t="s"/>
-      <x:c r="F46" s="28" t="n">
+      <x:c r="C46" s="26" t="s"/>
+      <x:c r="D46" s="26" t="s"/>
+      <x:c r="E46" s="26" t="s"/>
+      <x:c r="F46" s="27" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B47" s="26" t="s">
+      <x:c r="B47" s="25" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C47" s="27" t="s"/>
-      <x:c r="D47" s="27" t="s"/>
-      <x:c r="E47" s="27" t="s"/>
-      <x:c r="F47" s="28" t="n">
+      <x:c r="C47" s="26" t="s"/>
+      <x:c r="D47" s="26" t="s"/>
+      <x:c r="E47" s="26" t="s"/>
+      <x:c r="F47" s="27" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="26" t="s">
+      <x:c r="B48" s="25" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C48" s="27" t="s"/>
-      <x:c r="D48" s="27" t="s"/>
-      <x:c r="E48" s="27" t="s"/>
-      <x:c r="F48" s="28" t="n">
+      <x:c r="C48" s="26" t="s"/>
+      <x:c r="D48" s="26" t="s"/>
+      <x:c r="E48" s="26" t="s"/>
+      <x:c r="F48" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="26" t="s">
+      <x:c r="B49" s="25" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C49" s="27" t="s"/>
-      <x:c r="D49" s="27" t="s"/>
-      <x:c r="E49" s="27" t="s"/>
-      <x:c r="F49" s="28" t="n">
+      <x:c r="C49" s="26" t="s"/>
+      <x:c r="D49" s="26" t="s"/>
+      <x:c r="E49" s="26" t="s"/>
+      <x:c r="F49" s="27" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="26" t="s">
+      <x:c r="B50" s="25" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="C50" s="27" t="s"/>
-      <x:c r="D50" s="27" t="s"/>
-      <x:c r="E50" s="27" t="s"/>
-      <x:c r="F50" s="28" t="n">
+      <x:c r="C50" s="26" t="s"/>
+      <x:c r="D50" s="26" t="s"/>
+      <x:c r="E50" s="26" t="s"/>
+      <x:c r="F50" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B51" s="29" t="s">
+      <x:c r="B51" s="28" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="C51" s="30" t="s"/>
-      <x:c r="D51" s="30" t="s"/>
-      <x:c r="E51" s="30" t="s"/>
-      <x:c r="F51" s="31" t="n">
+      <x:c r="C51" s="29" t="s"/>
+      <x:c r="D51" s="29" t="s"/>
+      <x:c r="E51" s="29" t="s"/>
+      <x:c r="F51" s="30" t="n">
         <x:v>34</x:v>
       </x:c>
     </x:row>
@@ -6282,17 +6267,17 @@
       <x:c r="B5" s="12">
         <x:v>46113</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -6315,207 +6300,207 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>288</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s"/>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="D8" s="15" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>289</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>290</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>291</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46126.3445514815</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46126.3505074537</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>292</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46126.3564094097</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>293</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s"/>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="D9" s="15" t="s"/>
+      <x:c r="E9" s="14" t="s">
         <x:v>294</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>295</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>296</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46126.3584514236</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46126.3611957755</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>297</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46126.3662729282</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>298</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>299</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46120.2370111574</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>301</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46120.2952031944</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
+      <x:c r="B13" s="19" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
+      <x:c r="C13" s="20" t="s"/>
+      <x:c r="D13" s="20" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="21" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
+      <x:c r="B14" s="22" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="24" t="s">
         <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
+      <x:c r="B15" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="29" t="s">
+      <x:c r="B17" s="28" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="C17" s="30" t="s"/>
-      <x:c r="D17" s="30" t="s"/>
-      <x:c r="E17" s="30" t="s"/>
-      <x:c r="F17" s="31" t="n">
+      <x:c r="C17" s="29" t="s"/>
+      <x:c r="D17" s="29" t="s"/>
+      <x:c r="E17" s="29" t="s"/>
+      <x:c r="F17" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="302">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="307">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -918,6 +918,21 @@
   </x:si>
   <x:si>
     <x:t>1530645</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MELANIE C. UMALI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Velasco Subd., Concepción I, Sariaya, Quezon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-04019-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1282-403</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1530708</x:t>
   </x:si>
   <x:si>
     <x:t>2F SM CYBERZONE, SM CITY CALAMBA, BRGY. REAL, City Of Calamba, Laguna</x:t>
@@ -6413,98 +6428,133 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
-        <x:v>114</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s"/>
       <x:c r="E10" s="14" t="s">
-        <x:v>298</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
-        <x:v>299</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="G10" s="14" t="s">
-        <x:v>300</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46120.2370111574</x:v>
+        <x:v>46133.1256989236</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>46023</x:v>
+        <x:v>46133.1306981713</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
-        <x:v>301</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
-        <x:v>2550</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46120.2952031944</x:v>
+        <x:v>46133.1352517477</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46120.2370111574</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>46120.2952031944</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="19" t="s">
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="19" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="C13" s="20" t="s"/>
-      <x:c r="D13" s="20" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="21" t="s"/>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="22" t="s">
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="21" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="22" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="24" t="s">
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="s">
         <x:v>122</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
       <x:c r="B16" s="25" t="s">
-        <x:v>114</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C16" s="26" t="s"/>
       <x:c r="D16" s="26" t="s"/>
       <x:c r="E16" s="26" t="s"/>
       <x:c r="F16" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="25" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="28" t="s">
+    <x:row r="18" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B18" s="28" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="C17" s="29" t="s"/>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7486,11 +7536,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B13:F13"/>
-    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B14:F14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="307">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="312">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -933,6 +933,21 @@
   </x:si>
   <x:si>
     <x:t>1530708</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEFORE ANYTHING ELSE CORP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNIT NOS. 214-215, 2ND FLR SM CITY ROSARIO, GENERAL TRIAS DRIVE COR. COSTA VERDE ACCESS ROAD, TEJEROS CONVENTION, Rosario, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-24-05-0975</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1283-664</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1530725</x:t>
   </x:si>
   <x:si>
     <x:t>2F SM CYBERZONE, SM CITY CALAMBA, BRGY. REAL, City Of Calamba, Laguna</x:t>
@@ -6464,99 +6479,146 @@
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>114</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>115</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="E11" s="14" t="s">
-        <x:v>303</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="F11" s="14" t="s">
-        <x:v>304</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="G11" s="14" t="s">
-        <x:v>305</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46120.2370111574</x:v>
+        <x:v>46134.0392876852</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>46023</x:v>
+        <x:v>46154</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
-        <x:v>306</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
-        <x:v>2550</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46120.2952031944</x:v>
+        <x:v>46134.0609597569</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46120.2370111574</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>46120.2952031944</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="19" t="s">
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="19" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="C14" s="20" t="s"/>
-      <x:c r="D14" s="20" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="21" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="22" t="s">
+      <x:c r="C15" s="20" t="s"/>
+      <x:c r="D15" s="20" t="s"/>
+      <x:c r="E15" s="21" t="s"/>
+      <x:c r="F15" s="21" t="s"/>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B16" s="22" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="24" t="s">
+      <x:c r="C16" s="23" t="s"/>
+      <x:c r="D16" s="23" t="s"/>
+      <x:c r="E16" s="23" t="s"/>
+      <x:c r="F16" s="24" t="s">
         <x:v>122</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
-        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
       <x:c r="B17" s="25" t="s">
-        <x:v>114</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C17" s="26" t="s"/>
       <x:c r="D17" s="26" t="s"/>
       <x:c r="E17" s="26" t="s"/>
       <x:c r="F17" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="25" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="28" t="s">
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="25" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="26" t="s"/>
+      <x:c r="F19" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B20" s="28" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C20" s="29" t="s"/>
+      <x:c r="D20" s="29" t="s"/>
+      <x:c r="E20" s="29" t="s"/>
+      <x:c r="F20" s="30" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7531,16 +7593,17 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="9">
+  <x:mergeCells count="10">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B14:F14"/>
-    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B15:F15"/>
     <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="312">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="317">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -948,6 +948,21 @@
   </x:si>
   <x:si>
     <x:t>1530725</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WYNSCELL MOBILE PHONES AND ACCESSORIES STORE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZK215 CYBERZONE SM CITY LIPA PRESIDENT JOSE P. LAUREL HIGHWAY, BALINTAWAK, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-04-2520</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1298-134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1530781</x:t>
   </x:si>
   <x:si>
     <x:t>2F SM CYBERZONE, SM CITY CALAMBA, BRGY. REAL, City Of Calamba, Laguna</x:t>
@@ -6517,89 +6532,116 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>114</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>115</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
-        <x:v>308</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="F12" s="14" t="s">
-        <x:v>309</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="G12" s="14" t="s">
-        <x:v>310</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46120.2370111574</x:v>
+        <x:v>46140.22664875</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>46023</x:v>
+        <x:v>46140.2266724884</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
-        <x:v>311</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>2550</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46120.2952031944</x:v>
+        <x:v>46140.2614984259</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>46120.2370111574</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L13" s="18">
+        <x:v>46120.2952031944</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="19" t="s">
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="19" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="C15" s="20" t="s"/>
-      <x:c r="D15" s="20" t="s"/>
-      <x:c r="E15" s="21" t="s"/>
-      <x:c r="F15" s="21" t="s"/>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="22" t="s">
+      <x:c r="C16" s="20" t="s"/>
+      <x:c r="D16" s="20" t="s"/>
+      <x:c r="E16" s="21" t="s"/>
+      <x:c r="F16" s="21" t="s"/>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B17" s="22" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="C16" s="23" t="s"/>
-      <x:c r="D16" s="23" t="s"/>
-      <x:c r="E16" s="23" t="s"/>
-      <x:c r="F16" s="24" t="s">
+      <x:c r="C17" s="23" t="s"/>
+      <x:c r="D17" s="23" t="s"/>
+      <x:c r="E17" s="23" t="s"/>
+      <x:c r="F17" s="24" t="s">
         <x:v>122</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
-        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
       <x:c r="B18" s="25" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C18" s="26" t="s"/>
       <x:c r="D18" s="26" t="s"/>
       <x:c r="E18" s="26" t="s"/>
       <x:c r="F18" s="27" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
       <x:c r="B19" s="25" t="s">
-        <x:v>114</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C19" s="26" t="s"/>
       <x:c r="D19" s="26" t="s"/>
@@ -6608,19 +6650,39 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="28" t="s">
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="25" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C20" s="26" t="s"/>
+      <x:c r="D20" s="26" t="s"/>
+      <x:c r="E20" s="26" t="s"/>
+      <x:c r="F20" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="25" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C21" s="26" t="s"/>
+      <x:c r="D21" s="26" t="s"/>
+      <x:c r="E21" s="26" t="s"/>
+      <x:c r="F21" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B22" s="28" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="C20" s="29" t="s"/>
-      <x:c r="D20" s="29" t="s"/>
-      <x:c r="E20" s="29" t="s"/>
-      <x:c r="F20" s="30" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C22" s="29" t="s"/>
+      <x:c r="D22" s="29" t="s"/>
+      <x:c r="E22" s="29" t="s"/>
+      <x:c r="F22" s="30" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7593,17 +7655,18 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="10">
+  <x:mergeCells count="11">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B15:F15"/>
-    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B16:F16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="317">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="327">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -950,6 +950,21 @@
     <x:t>1530725</x:t>
   </x:si>
   <x:si>
+    <x:t>MACMC GADGETS &amp; ACESSORIES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4F BAY CITY MALL D. SILANG ST., BRGY. 14, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DP-MP-24-47R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1301-459</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1530788</x:t>
+  </x:si>
+  <x:si>
     <x:t>WYNSCELL MOBILE PHONES AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
@@ -963,6 +978,21 @@
   </x:si>
   <x:si>
     <x:t>1530781</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACMC GADGETS &amp; ACCESSORIES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2/F, PACIFIC MALL M.L. TAGARAO ST., Barangay III, Lucena City (Capital), Quezon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-24-467R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1300-827</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1530787</x:t>
   </x:si>
   <x:si>
     <x:t>2F SM CYBERZONE, SM CITY CALAMBA, BRGY. REAL, City Of Calamba, Laguna</x:t>
@@ -6532,13 +6562,13 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
         <x:v>308</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
-        <x:v>28</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
         <x:v>309</x:v>
@@ -6550,19 +6580,19 @@
         <x:v>311</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46140.22664875</x:v>
+        <x:v>46141.2837138079</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>46140.2266724884</x:v>
+        <x:v>45814</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
         <x:v>312</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>7530</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46140.2614984259</x:v>
+        <x:v>46141.3129605787</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>58</x:v>
@@ -6570,122 +6600,206 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>114</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>115</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
-        <x:v>313</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>314</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="G13" s="14" t="s">
-        <x:v>315</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46120.2370111574</x:v>
+        <x:v>46140.22664875</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>46023</x:v>
+        <x:v>46140.2266724884</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
-        <x:v>316</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>2550</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46120.2952031944</x:v>
+        <x:v>46140.2614984259</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="19" t="s">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46141.2802576736</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>45814</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L14" s="18">
+        <x:v>46141.3116617361</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>46120.2370111574</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L15" s="18">
+        <x:v>46120.2952031944</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="19" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="C16" s="20" t="s"/>
-      <x:c r="D16" s="20" t="s"/>
-      <x:c r="E16" s="21" t="s"/>
-      <x:c r="F16" s="21" t="s"/>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="22" t="s">
+      <x:c r="C18" s="20" t="s"/>
+      <x:c r="D18" s="20" t="s"/>
+      <x:c r="E18" s="21" t="s"/>
+      <x:c r="F18" s="21" t="s"/>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B19" s="22" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="C17" s="23" t="s"/>
-      <x:c r="D17" s="23" t="s"/>
-      <x:c r="E17" s="23" t="s"/>
-      <x:c r="F17" s="24" t="s">
+      <x:c r="C19" s="23" t="s"/>
+      <x:c r="D19" s="23" t="s"/>
+      <x:c r="E19" s="23" t="s"/>
+      <x:c r="F19" s="24" t="s">
         <x:v>122</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="25" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="25" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C19" s="26" t="s"/>
-      <x:c r="D19" s="26" t="s"/>
-      <x:c r="E19" s="26" t="s"/>
-      <x:c r="F19" s="27" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
       <x:c r="B20" s="25" t="s">
-        <x:v>52</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="26" t="s"/>
       <x:c r="D20" s="26" t="s"/>
       <x:c r="E20" s="26" t="s"/>
       <x:c r="F20" s="27" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
       <x:c r="B21" s="25" t="s">
-        <x:v>114</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C21" s="26" t="s"/>
       <x:c r="D21" s="26" t="s"/>
       <x:c r="E21" s="26" t="s"/>
       <x:c r="F21" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="25" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C22" s="26" t="s"/>
+      <x:c r="D22" s="26" t="s"/>
+      <x:c r="E22" s="26" t="s"/>
+      <x:c r="F22" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="28" t="s">
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="25" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C23" s="26" t="s"/>
+      <x:c r="D23" s="26" t="s"/>
+      <x:c r="E23" s="26" t="s"/>
+      <x:c r="F23" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="25" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C24" s="26" t="s"/>
+      <x:c r="D24" s="26" t="s"/>
+      <x:c r="E24" s="26" t="s"/>
+      <x:c r="F24" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B25" s="28" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="C22" s="29" t="s"/>
-      <x:c r="D22" s="29" t="s"/>
-      <x:c r="E22" s="29" t="s"/>
-      <x:c r="F22" s="30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C25" s="29" t="s"/>
+      <x:c r="D25" s="29" t="s"/>
+      <x:c r="E25" s="29" t="s"/>
+      <x:c r="F25" s="30" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7655,18 +7769,19 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="11">
+  <x:mergeCells count="12">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B16:F16"/>
-    <x:mergeCell ref="B17:E17"/>
-    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B18:F18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B25:E25"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-ENGR-GALELEO-MENDOZA-evaluator-cache-serviceTracking-ENGR-GALELEO-MENDOZA-IV-A-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="327">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="299">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -68,9 +68,75 @@
     <x:t>BY</x:t>
   </x:si>
   <x:si>
+    <x:t>Service Center Permit (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JAZZY TECHNICAL SERVICES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNIT 5 BALETE DRIVE LIPA GOVERNOR LEVISTE HIGHWAY, BULACNIN, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-26-02-1102(NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1067-112</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1510925</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Adora Mercado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dealer Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TECHNOKID CELLPHONE CENTER INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2nd Flr. Cyberzone SM City Calamba, Real, City Of Calamba, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-008R (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1070-812</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Caesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
   </x:si>
   <x:si>
+    <x:t>JOHN PAUL ORIBELLO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>San miguel, Santo Tomas, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-02007-2026E</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1082-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1506159</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nerrisa Manalo</x:t>
+  </x:si>
+  <x:si>
     <x:t>CHESTER JUDE  QUILITIS</x:t>
   </x:si>
   <x:si>
@@ -86,22 +152,22 @@
     <x:t>1506161</x:t>
   </x:si>
   <x:si>
-    <x:t>Nerrisa Manalo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JOHN PAUL ORIBELLO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>San miguel, Santo Tomas, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-AT-02007-2026E</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1082-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1506159</x:t>
+    <x:t>Service Center Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIZMOTECH CORPORATION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DALAHICAN ROAD, IBABANG DUPAY RED V, Lucena City (Capital), Quezon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-23-11-1065</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1099-127</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511502</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -110,10 +176,7 @@
     <x:t>POLARIS LINKING INC</x:t>
   </x:si>
   <x:si>
-    <x:t>NEW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2F 2106 SM CITY LIPA JP LAUREL, San Antonio, Lipa City, Batangas</x:t>
+    <x:t>UG MASSWAY SHOPPING CENTER F.T Catapusan, Plaza Almeda, Tanay, Rizal</x:t>
   </x:si>
   <x:si>
     <x:t>DD-MP-26-02-0981</x:t>
@@ -128,18 +191,21 @@
     <x:t>Deniel Puyo</x:t>
   </x:si>
   <x:si>
-    <x:t>Dealer Permit (RENEWAL)</x:t>
+    <x:t>MOBILETOOLS VENTURE INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-22-009R(REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1079-778</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1505805</x:t>
   </x:si>
   <x:si>
     <x:t>MOBILESTYLE DISTRIBUTION INC</x:t>
   </x:si>
   <x:si>
-    <x:t>REN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ21 2F SM CITY ROSARIO GEN TRIAS, San Antonio, Rosario, Cavite</x:t>
-  </x:si>
-  <x:si>
     <x:t>DD-MP-19-03-0772(REN)</x:t>
   </x:si>
   <x:si>
@@ -149,46 +215,13 @@
     <x:t>1505804</x:t>
   </x:si>
   <x:si>
-    <x:t>MOBILETOOLS VENTURE INC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ-15 3F SM CITY LUCENA Maharlika Highway, Ibabang Dupay, Lucena City (Capital), Quezon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-22-009R(REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1079-778</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1505805</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TECHNOKID CELLPHONE CENTER INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ 248 05 SM City San pablo, San Rafael, San Pablo City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-008R (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1070-812</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Caesar Allen Centeno</x:t>
-  </x:si>
-  <x:si>
     <x:t>Retailer/Reseller Permit (NEW)</x:t>
   </x:si>
   <x:si>
     <x:t>GREENTELCOMMUNICATIONS TRADING INC. (HONOR)</x:t>
   </x:si>
   <x:si>
-    <x:t>WALTERMART, BANLIC, Cabuyao City, Laguna</x:t>
+    <x:t>CZ SM TRECE MARTIRES S.A PROPER, SAN AGUSTIN, Trece Martires City (Capital), Cavite</x:t>
   </x:si>
   <x:si>
     <x:t>DD-RR-26-02-2516(NEW)</x:t>
@@ -200,15 +233,60 @@
     <x:t>1511622</x:t>
   </x:si>
   <x:si>
-    <x:t>Adora Mercado</x:t>
+    <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREENTELCOM CELLPHONE &amp; ACCESSORIES CENTER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-25-03-2472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1139-014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511623</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREENTELCOMMUNICATIONS TRADING INC. (SAMSUNG STORE )</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-25-03-2480</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1138-367</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511624</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREENTELCOMMUNICATIONS TRADING INC.(GREENTELCOM STORE)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-25-03-2481</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1137-243</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511625</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREENTELCOMMUNICATIONS TRADING INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-25-03-2479</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1136-850</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511626</x:t>
   </x:si>
   <x:si>
     <x:t>GREENTELCOMMUNICATIONS TRADING INC. (SAMSUNG)</x:t>
   </x:si>
   <x:si>
-    <x:t>G/F WALTERMART CABUYAO KM47 NATIONAL HIGHWAY, BANLIC, Cabuyao City, Laguna</x:t>
-  </x:si>
-  <x:si>
     <x:t>DD-RR-26-02-2517 (NEW)</x:t>
   </x:si>
   <x:si>
@@ -218,30 +296,48 @@
     <x:t>1511627</x:t>
   </x:si>
   <x:si>
-    <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GREENTELCOM CELLPHONE &amp; ACCESSORIES CENTER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GF WALTERMART NAIC GOV. DRIVE, SABANG, Naic, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-25-03-2472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1139-014</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511623</x:t>
+    <x:t>GREENTELCOM CELLPHONE AND ACCESSORIES CENTER (HONOR STORE )</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-25-03-2475</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1128-999</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511630</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREENTELCOMMUNICATIONS TRADING INC. (HONOR STORE )</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-25-03-2477</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1132-580</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREENTELCOMMUNICATIONS TRADING INC. (HUAWEI STORE )</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-25-03-2474</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1131-730</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREENTELCOMMUNICATIONS TRADING INC. (OPPO STORE)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-25-03-2476</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1130-950</x:t>
   </x:si>
   <x:si>
     <x:t>GREENTELCOM CELLPHONE &amp; ACCESSORIES CENTER  (TECNO STORE)</x:t>
   </x:si>
   <x:si>
-    <x:t>WNAI K025 WALTERMART NAIC GOV. DRIVE, SABANG, Naic, Cavite</x:t>
-  </x:si>
-  <x:si>
     <x:t>DD-RR-25-03-2473</x:t>
   </x:si>
   <x:si>
@@ -251,42 +347,9 @@
     <x:t>1511631</x:t>
   </x:si>
   <x:si>
-    <x:t>GREENTELCOM CELLPHONE AND ACCESSORIES CENTER (HONOR STORE )</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WNAI K026 WALTERMART NAIC GOV. DRIVE, SABANG, Naic, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-25-03-2475</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1128-999</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511630</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GREENTELCOMMUNICATIONS TRADING INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3/F ROBINSONS PLACE IMUS AGUINALDO HIGHWAY, TANZANG LUMA V, Imus City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-25-03-2479</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1136-850</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511626</x:t>
-  </x:si>
-  <x:si>
     <x:t>GREENTELCOMMUNICATIONS TRADING INC. (GREENTELCOM STORE)</x:t>
   </x:si>
   <x:si>
-    <x:t>CZ SM TRECE MARTIRES S.A PROPER, SAN AGUSTIN, Trece Martires City (Capital), Cavite</x:t>
-  </x:si>
-  <x:si>
     <x:t>DD-RR-25-03-2478</x:t>
   </x:si>
   <x:si>
@@ -296,96 +359,6 @@
     <x:t>1511635</x:t>
   </x:si>
   <x:si>
-    <x:t>GREENTELCOMMUNICATIONS TRADING INC. (HONOR STORE )</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-25-03-2477</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1132-580</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GREENTELCOMMUNICATIONS TRADING INC. (HUAWEI STORE )</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-25-03-2474</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1131-730</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GREENTELCOMMUNICATIONS TRADING INC. (OPPO STORE)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-25-03-2476</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1130-950</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GREENTELCOMMUNICATIONS TRADING INC. (SAMSUNG STORE )</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SM CENTER IMUS NIA ROAD, ALAPAN 1C, Imus City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-25-03-2480</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1138-367</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511624</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GREENTELCOMMUNICATIONS TRADING INC.(GREENTELCOM STORE)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-25-03-2481</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1137-243</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511625</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Service Center Permit (NEW)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JAZZY TECHNICAL SERVICES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNIT 5 BALETE DRIVE LIPA GOVERNOR LEVISTE HIGHWAY, BULACNIN, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-SC-26-02-1102(NEW)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1067-112</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1510925</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Service Center Permit (RENEWAL)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIZMOTECH CORPORATION</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DALAHICAN ROAD, IBABANG DUPAY RED V, Lucena City (Capital), Quezon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-SC-23-11-1065</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1099-127</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511502</x:t>
-  </x:si>
-  <x:si>
     <x:t>SUMMARY</x:t>
   </x:si>
   <x:si>
@@ -398,6 +371,273 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>INNOVASIA MARKETING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>41 RIZAL AVENUE, BARANGAY 17, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-08-03-0517(REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1146-031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UPSON INTERNATIONAL CORP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-17-03-2015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1173-016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511758</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1175-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511759</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2106</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1176-385</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511760</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-03-03-0771</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1174-419</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511761</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2518</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1172-434</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1507965</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ricardo Natividad</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2519</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1171-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1507966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERALD BEBIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>94 Magsaysay, Poblacion, Cavinti, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03009-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1189-403</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511778</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JAKE C. PASILAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>103, Banlic, Cabuyao City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03010-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1198-002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511815</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELLTY MOBILE INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNIT 008 G/F WALTERMART BACOOR WALTERMART BACOOR BLVD., MAMBOG IV, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0762</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1155-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511225</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSD INTERNATIONAL MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0781 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1144-933</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0780 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1151-716</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511234</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTO GADGETS TOO INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0773 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1152-831</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511235</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONE DOTCOM CELL INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0778 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1153-796</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511236</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELL EVER MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-456b-22R (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1154-964</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511237</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-020R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1156-896</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLIXTEC INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-01-25-456R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1086-471</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511196</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELLTY MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-01-25-453R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1085-453</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511206</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-21-03-2265</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1157-256</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511208</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYNCNETIC INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-18-05-0718</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1083-282</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511241</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBILECRAZE TELECOM INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-06-0809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1159-651</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511242</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELLBOY INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLOOR CYBERZONE SM CALAMBA NATIONAL HIGHWAY, REAL, City Of Calamba, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-16-12-0951</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1205-403</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511858</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALCALA, GLENN GUIBAO</x:t>
   </x:si>
   <x:si>
@@ -413,6 +653,99 @@
     <x:t>1511906</x:t>
   </x:si>
   <x:si>
+    <x:t>HLH GENTECH INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1097-702</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511274</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEQWARE PHONES AND ACCESSORIES INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-20-01-0883</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1087-228</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511275</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELLBLITZ MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-010R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1089-192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511276</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RULLS CELLPHONES AND ACCESSORIES INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 24-466R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1158-087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RONALD BRYAN C. DERIQUITO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>246 Sitio ibaba, Santisimo rosario, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03-0001ML</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1230-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511940</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REX FAJARDO VIDAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guiho Guiho st, Quipot, Tiaong, Quezon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-2026-03-0002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1231-664</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511953</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOMAR BACSAL MONDRAGON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Purok 7B, Magnetic hills, Timugan, Los Baños, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-2026-03-003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1232-952</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511954</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARIEL PASAHOL ASILO</x:t>
   </x:si>
   <x:si>
@@ -428,6 +761,36 @@
     <x:t>1511955</x:t>
   </x:si>
   <x:si>
+    <x:t>SELECT GOODS OPC (VIVO)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SM City San Pablo , 2nd floor , Cyberzone, San Rafael, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03001ML</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1239-893</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511970</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TECH101 TECHNOLOGIES INC. - BR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ-248-15 2f SM CITY SAN PABLO, BRGY SAN RAFAEL, SAN PABLO San rafael, San rafael, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-21-11-0934</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1240-025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511971</x:t>
+  </x:si>
+  <x:si>
     <x:t>EDEN ENRIQUEZ LUNETA</x:t>
   </x:si>
   <x:si>
@@ -443,451 +806,16 @@
     <x:t>1511992</x:t>
   </x:si>
   <x:si>
-    <x:t>HERALD BEBIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>94 Magsaysay, Poblacion, Cavinti, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-AT-03009-2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1189-403</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511778</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JAKE C. PASILAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>103, Banlic, Cabuyao City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-AT-03010-2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1198-002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511815</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JOMAR BACSAL MONDRAGON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Purok 7B, Magnetic hills, Timugan, Los Baños, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-AT-2026-03-003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1232-952</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511954</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REX FAJARDO VIDAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Guiho Guiho st, Quipot, Tiaong, Quezon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-AT-2026-03-0002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1231-664</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511953</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RONALD BRYAN C. DERIQUITO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>246 Sitio ibaba, Santisimo rosario, San Pablo City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-AT-03-0001ML</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1230-591</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511940</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSD INTERNATIONAL MOBILE INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C-24 SM City Rosario, Gen. Trias Dr.,, Tejeros Convention,, Rosario, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-03-0781 (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1144-933</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511232</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ 248-3 SM City San Pablo, Brgy. San Rafael, San Pablo City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-03-0780 (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1151-716</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511234</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELL EVER MOBILE INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ 424 Cyberzone 4th flr., SM City Bacoor, Habay II, Bacoor City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-456b-22R (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1154-964</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511237</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELLBLITZ MOBILE INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LG05 SM MARKETMALL, BUROL I, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-010R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1089-192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511276</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELLTY MOBILE INC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SM CITY BACOOR CZ430, HABAY II, Bacoor City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-03-0762</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1155-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511225</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-020R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1156-896</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELLTY MOBILE INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-01-25-453R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1085-453</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511206</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLIXTEC INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3/F BLDG. D DAANG HARI ROAD, PASONG BUAYA I, Imus City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-01-25-456R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1086-471</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511196</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLH GENTECH INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SM CENTER ILLUSTRE AVE, DISTRICT IV, Lemery, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-18-02-2111</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1097-702</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511274</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTO GADGETS TOO INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ 440 SM City Bacoor, Habay II,, Bacoor City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-03-0773 (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1152-831</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511235</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBILECRAZE TELECOM INC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLA MALL PAGSANJAN NATIONAL ROAD, PAGSANJAN, City Of Biñan, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-06-0809</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1159-651</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511242</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONE DOTCOM CELL INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ SM City Bacoor, Habay II,, Bacoor City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-03-0778 (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1153-796</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511236</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RULLS CELLPHONES AND ACCESSORIES INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SM CITY STO. TOMAS CZ-5 MAHARLIKA HIGHWAY, SAN BARTOLOME, Santo Tomas, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 24-466R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1158-087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511302</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SYNCNETIC INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LEVEL 3 0118, SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-18-05-0718</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1083-282</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511241</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TECH101 TECHNOLOGIES INC. - BR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ-248-15 2f SM CITY SAN PABLO, BRGY SAN RAFAEL, SAN PABLO San rafael, San rafael, San Pablo City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-21-11-0934</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1240-025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511971</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEQWARE PHONES AND ACCESSORIES INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYALA MALLS SERIN JUNCTION EAST, SILANG, Tagaytay City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-20-01-0883</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1087-228</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511275</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UPSON INTERNATIONAL CORP.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2nd floor SM Cyberzone SM City Sta. Rosa, Tagapo, City Of Santa Rosa, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-03-03-0771</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1174-419</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511761</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-2518</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1172-434</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1507965</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ricardo Natividad</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-2519</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1171-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1507966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELECT GOODS OPC (VIVO)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SM City San Pablo , 2nd floor , Cyberzone, San Rafael, San Pablo City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03001ML</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1239-893</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511970</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALTERMART TANAUAN 225 WALTERMART JPL-HWAY, DARASA, City Of Tanauan, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-21-03-2265</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1157-256</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511208</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INNOVASIA MARKETING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>41 RIZAL AVENUE, BARANGAY 17, Batangas City (Capital), Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-08-03-0517(REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1146-031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-17-03-2015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1173-016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511758</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-18-02-2017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1175-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511759</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-18-02-2106</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1176-385</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511760</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELLBOY INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2ND FLOOR CYBERZONE SM CALAMBA NATIONAL HIGHWAY, REAL, City Of Calamba, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-SC-16-12-0951</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1205-403</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511858</x:t>
+    <x:t>2F SM CYBERZONE, SM CITY CALAMBA, BRGY. REAL, City Of Calamba, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-24-01-1081(REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1260-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1530589</x:t>
   </x:si>
   <x:si>
     <x:t>JAYRON G CALABIA</x:t>
@@ -950,6 +878,36 @@
     <x:t>1530725</x:t>
   </x:si>
   <x:si>
+    <x:t>WYNSCELL MOBILE PHONES AND ACCESSORIES STORE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZK215 CYBERZONE SM CITY LIPA PRESIDENT JOSE P. LAUREL HIGHWAY, BALINTAWAK, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-04-2520</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1298-134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1530781</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACMC GADGETS &amp; ACCESSORIES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2/F, PACIFIC MALL M.L. TAGARAO ST., Barangay III, Lucena City (Capital), Quezon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-24-467R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1300-827</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1530787</x:t>
+  </x:si>
+  <x:si>
     <x:t>MACMC GADGETS &amp; ACESSORIES</x:t>
   </x:si>
   <x:si>
@@ -963,48 +921,6 @@
   </x:si>
   <x:si>
     <x:t>1530788</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WYNSCELL MOBILE PHONES AND ACCESSORIES STORE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZK215 CYBERZONE SM CITY LIPA PRESIDENT JOSE P. LAUREL HIGHWAY, BALINTAWAK, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-04-2520</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-4-2026-1298-134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1530781</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACMC GADGETS &amp; ACCESSORIES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2/F, PACIFIC MALL M.L. TAGARAO ST., Barangay III, Lucena City (Capital), Quezon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-24-467R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-4-2026-1300-827</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1530787</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2F SM CYBERZONE, SM CITY CALAMBA, BRGY. REAL, City Of Calamba, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-SC-24-01-1081(REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-4-2026-1260-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1530589</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1895,760 +1811,760 @@
       <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s"/>
+      <x:c r="D8" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46069.0835222569</x:v>
+        <x:v>46062.159017581</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>46069.1006819792</x:v>
+        <x:v>46062.1590321875</x:v>
       </x:c>
       <x:c r="J8" s="15" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
-        <x:v>130</x:v>
+        <x:v>2130</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46069.1133347338</x:v>
+        <x:v>46062.1863264931</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s"/>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46069.0835757523</x:v>
+        <x:v>46063.1352781944</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46069.1000300231</x:v>
+        <x:v>46066</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
-        <x:v>130</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46069.1128697454</x:v>
+        <x:v>46063.2367775347</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s"/>
       <x:c r="E10" s="14" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G10" s="14" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46067.3600302778</x:v>
+        <x:v>46069.0835757523</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>46067.3600485417</x:v>
+        <x:v>46069.1000300231</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46079.273015787</x:v>
+        <x:v>46069.1128697454</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46069.0835222569</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46069.1006819792</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>46069.1133347338</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46067.1596693866</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46079.277259919</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F12" s="14" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G12" s="14" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46067.222213287</x:v>
+        <x:v>46071.0492490046</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>46089</x:v>
+        <x:v>46052</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46079.2763165278</x:v>
+        <x:v>46071.0606162616</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
-        <x:v>33</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G13" s="14" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46063.1352781944</x:v>
+        <x:v>46067.3600302778</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>46066</x:v>
+        <x:v>46067.3600485417</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46063.2367775347</x:v>
+        <x:v>46079.273015787</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46067.222213287</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46089</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="18">
+        <x:v>46079.2763165278</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46079.3584810995</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46079.3584983796</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46080.2311256134</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="H15" s="16">
+        <x:v>46067.1596693866</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46079.3539738194</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46079.3539910417</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46080.244091956</x:v>
+        <x:v>46079.277259919</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C16" s="14" t="s">
+      <x:c r="D16" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
+      <x:c r="F16" s="14" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="G16" s="14" t="s">
+      <x:c r="H16" s="16">
+        <x:v>46079.3584810995</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46079.3584983796</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46079.3873177662</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="K16" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46080.2360791898</x:v>
+        <x:v>46080.2311256134</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E17" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="F17" s="14" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
       <x:c r="H17" s="16">
-        <x:v>46079.2523059375</x:v>
+        <x:v>46079.3873177662</x:v>
       </x:c>
       <x:c r="I17" s="16">
         <x:v>46092</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46080.2925916204</x:v>
+        <x:v>46080.2360791898</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
       <x:c r="H18" s="16">
-        <x:v>46079.2430618866</x:v>
+        <x:v>46079.3789042361</x:v>
       </x:c>
       <x:c r="I18" s="16">
         <x:v>46092</x:v>
       </x:c>
       <x:c r="J18" s="15" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46080.2801283218</x:v>
+        <x:v>46080.2376106713</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
       <x:c r="H19" s="16">
-        <x:v>46079.3652018403</x:v>
+        <x:v>46079.3728295139</x:v>
       </x:c>
       <x:c r="I19" s="16">
         <x:v>46092</x:v>
       </x:c>
       <x:c r="J19" s="15" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="K19" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46080.2425555208</x:v>
+        <x:v>46080.2394384722</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C20" s="14" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D20" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E20" s="14" t="s">
-        <x:v>86</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F20" s="14" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G20" s="14" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H20" s="16">
-        <x:v>46080.2923673264</x:v>
+        <x:v>46079.3652018403</x:v>
       </x:c>
       <x:c r="I20" s="16">
         <x:v>46092</x:v>
       </x:c>
       <x:c r="J20" s="15" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K20" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46080.3208568171</x:v>
+        <x:v>46080.2425555208</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C21" s="14" t="s">
-        <x:v>90</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D21" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E21" s="14" t="s">
-        <x:v>86</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F21" s="14" t="s">
-        <x:v>91</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G21" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H21" s="16">
-        <x:v>46079.3162545833</x:v>
+        <x:v>46079.3539738194</x:v>
       </x:c>
       <x:c r="I21" s="16">
-        <x:v>46092</x:v>
+        <x:v>46079.3539910417</x:v>
       </x:c>
       <x:c r="J21" s="15" t="s">
-        <x:v>79</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46080.2883729977</x:v>
+        <x:v>46080.244091956</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D22" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E22" s="14" t="s">
-        <x:v>86</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F22" s="14" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G22" s="14" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H22" s="16">
-        <x:v>46079.3059443634</x:v>
+        <x:v>46079.2430618866</x:v>
       </x:c>
       <x:c r="I22" s="16">
         <x:v>46092</x:v>
       </x:c>
       <x:c r="J22" s="15" t="s">
-        <x:v>79</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="K22" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46080.2896890278</x:v>
+        <x:v>46080.2801283218</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="H23" s="16">
-        <x:v>46079.2943998843</x:v>
+        <x:v>46079.3162545833</x:v>
       </x:c>
       <x:c r="I23" s="16">
         <x:v>46092</x:v>
       </x:c>
       <x:c r="J23" s="15" t="s">
-        <x:v>79</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="K23" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46080.2916823611</x:v>
+        <x:v>46080.2883729977</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C24" s="14" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>102</x:v>
-      </x:c>
       <x:c r="H24" s="16">
-        <x:v>46079.3789042361</x:v>
+        <x:v>46079.3059443634</x:v>
       </x:c>
       <x:c r="I24" s="16">
         <x:v>46092</x:v>
       </x:c>
       <x:c r="J24" s="15" t="s">
-        <x:v>103</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="K24" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="18">
-        <x:v>46080.2376106713</x:v>
+        <x:v>46080.2896890278</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C25" s="14" t="s">
-        <x:v>104</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D25" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E25" s="14" t="s">
-        <x:v>100</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F25" s="14" t="s">
-        <x:v>105</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G25" s="14" t="s">
-        <x:v>106</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H25" s="16">
-        <x:v>46079.3728295139</x:v>
+        <x:v>46079.2943998843</x:v>
       </x:c>
       <x:c r="I25" s="16">
         <x:v>46092</x:v>
       </x:c>
       <x:c r="J25" s="15" t="s">
-        <x:v>107</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="K25" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L25" s="18">
-        <x:v>46080.2394384722</x:v>
+        <x:v>46080.2916823611</x:v>
       </x:c>
       <x:c r="M25" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="30" customHeight="1">
       <x:c r="B26" s="14" t="s">
-        <x:v>108</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C26" s="14" t="s">
-        <x:v>109</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D26" s="15" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E26" s="14" t="s">
-        <x:v>110</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F26" s="14" t="s">
-        <x:v>111</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G26" s="14" t="s">
-        <x:v>112</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H26" s="16">
-        <x:v>46062.159017581</x:v>
+        <x:v>46079.2523059375</x:v>
       </x:c>
       <x:c r="I26" s="16">
-        <x:v>46062.1590321875</x:v>
+        <x:v>46092</x:v>
       </x:c>
       <x:c r="J26" s="15" t="s">
-        <x:v>113</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="K26" s="17" t="n">
-        <x:v>2130</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L26" s="18">
-        <x:v>46062.1863264931</x:v>
+        <x:v>46080.2925916204</x:v>
       </x:c>
       <x:c r="M26" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
       <x:c r="B27" s="14" t="s">
-        <x:v>114</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C27" s="14" t="s">
-        <x:v>115</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D27" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E27" s="14" t="s">
-        <x:v>116</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F27" s="14" t="s">
-        <x:v>117</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G27" s="14" t="s">
-        <x:v>118</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H27" s="16">
-        <x:v>46071.0492490046</x:v>
+        <x:v>46080.2923673264</x:v>
       </x:c>
       <x:c r="I27" s="16">
-        <x:v>46052</x:v>
+        <x:v>46092</x:v>
       </x:c>
       <x:c r="J27" s="15" t="s">
-        <x:v>119</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="K27" s="17" t="n">
-        <x:v>2550</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L27" s="18">
-        <x:v>46071.0606162616</x:v>
+        <x:v>46080.3208568171</x:v>
       </x:c>
       <x:c r="M27" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
       <x:c r="B30" s="19" t="s">
-        <x:v>120</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C30" s="20" t="s"/>
       <x:c r="D30" s="20" t="s"/>
@@ -2657,18 +2573,18 @@
     </x:row>
     <x:row r="31" spans="1:28" ht="22" customHeight="1">
       <x:c r="B31" s="22" t="s">
-        <x:v>121</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C31" s="23" t="s"/>
       <x:c r="D31" s="23" t="s"/>
       <x:c r="E31" s="23" t="s"/>
       <x:c r="F31" s="24" t="s">
-        <x:v>122</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
       <x:c r="B32" s="25" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C32" s="26" t="s"/>
       <x:c r="D32" s="26" t="s"/>
@@ -2679,7 +2595,7 @@
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
       <x:c r="B33" s="25" t="s">
-        <x:v>26</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C33" s="26" t="s"/>
       <x:c r="D33" s="26" t="s"/>
@@ -2690,7 +2606,7 @@
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
       <x:c r="B34" s="25" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C34" s="26" t="s"/>
       <x:c r="D34" s="26" t="s"/>
@@ -2701,7 +2617,7 @@
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
       <x:c r="B35" s="25" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C35" s="26" t="s"/>
       <x:c r="D35" s="26" t="s"/>
@@ -2712,7 +2628,7 @@
     </x:row>
     <x:row r="36" spans="1:28" ht="18" customHeight="1">
       <x:c r="B36" s="25" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C36" s="26" t="s"/>
       <x:c r="D36" s="26" t="s"/>
@@ -2723,7 +2639,7 @@
     </x:row>
     <x:row r="37" spans="1:28" ht="18" customHeight="1">
       <x:c r="B37" s="25" t="s">
-        <x:v>108</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C37" s="26" t="s"/>
       <x:c r="D37" s="26" t="s"/>
@@ -2734,7 +2650,7 @@
     </x:row>
     <x:row r="38" spans="1:28" ht="18" customHeight="1">
       <x:c r="B38" s="25" t="s">
-        <x:v>114</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C38" s="26" t="s"/>
       <x:c r="D38" s="26" t="s"/>
@@ -2745,7 +2661,7 @@
     </x:row>
     <x:row r="39" spans="1:28" ht="28" customHeight="1">
       <x:c r="B39" s="28" t="s">
-        <x:v>123</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C39" s="29" t="s"/>
       <x:c r="D39" s="29" t="s"/>
@@ -3911,1285 +3827,1285 @@
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="D8" s="15" t="s"/>
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>125</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>127</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46100.1144765394</x:v>
+        <x:v>46083.0788057755</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>46100.1505107292</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J8" s="15" t="s">
-        <x:v>128</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
-        <x:v>230</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46100.1652817245</x:v>
+        <x:v>46083.1042250116</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s"/>
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>131</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>132</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46107.1401251852</x:v>
+        <x:v>46086.099798588</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46107.1653469792</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
-        <x:v>133</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
-        <x:v>230</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46107.1722420255</x:v>
+        <x:v>46090.2691152778</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s"/>
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
       <x:c r="E10" s="14" t="s">
-        <x:v>135</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
-        <x:v>136</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G10" s="14" t="s">
-        <x:v>137</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46111.14459375</x:v>
+        <x:v>46086.1144463079</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>46111.1542258102</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
-        <x:v>138</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
-        <x:v>230</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46111.1662193056</x:v>
+        <x:v>46090.2703739352</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s"/>
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
       <x:c r="E11" s="14" t="s">
-        <x:v>140</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F11" s="14" t="s">
-        <x:v>141</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G11" s="14" t="s">
-        <x:v>142</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46091.3061033796</x:v>
+        <x:v>46087.1643336806</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>46091.3108077083</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
-        <x:v>143</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
-        <x:v>230</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46091.3131892477</x:v>
+        <x:v>46090.2727784143</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s"/>
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
       <x:c r="E12" s="14" t="s">
-        <x:v>145</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F12" s="14" t="s">
-        <x:v>146</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G12" s="14" t="s">
-        <x:v>147</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46093.1459465972</x:v>
+        <x:v>46086.106481875</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>46093.1585187731</x:v>
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
-        <x:v>148</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>230</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46093.1595409143</x:v>
+        <x:v>46090.2765830324</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s"/>
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="E13" s="14" t="s">
-        <x:v>150</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>151</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G13" s="14" t="s">
-        <x:v>152</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46107.1079779977</x:v>
+        <x:v>46085.1709247338</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>46107.1569821643</x:v>
+        <x:v>46085.1709419676</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
-        <x:v>153</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>130</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46107.1713369444</x:v>
+        <x:v>46090.3337014815</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s"/>
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="E14" s="14" t="s">
-        <x:v>155</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F14" s="14" t="s">
-        <x:v>156</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G14" s="14" t="s">
-        <x:v>157</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46107.1074963889</x:v>
+        <x:v>46085.1662527662</x:v>
       </x:c>
       <x:c r="I14" s="16">
-        <x:v>46107.1512672454</x:v>
+        <x:v>46085.1662689699</x:v>
       </x:c>
       <x:c r="J14" s="15" t="s">
-        <x:v>158</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
-        <x:v>130</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46107.1672093287</x:v>
+        <x:v>46090.3437343634</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>159</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s"/>
       <x:c r="E15" s="14" t="s">
-        <x:v>160</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
-        <x:v>161</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G15" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46106.2628248843</x:v>
+        <x:v>46091.3061033796</x:v>
       </x:c>
       <x:c r="I15" s="16">
-        <x:v>46106.2706934954</x:v>
+        <x:v>46091.3108077083</x:v>
       </x:c>
       <x:c r="J15" s="15" t="s">
-        <x:v>163</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
         <x:v>230</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46106.2922441319</x:v>
+        <x:v>46091.3131892477</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s"/>
       <x:c r="E16" s="14" t="s">
-        <x:v>165</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="F16" s="14" t="s">
-        <x:v>166</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G16" s="14" t="s">
-        <x:v>167</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46080.4532551852</x:v>
+        <x:v>46093.1459465972</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>46100</x:v>
+        <x:v>46093.1585187731</x:v>
       </x:c>
       <x:c r="J16" s="15" t="s">
-        <x:v>168</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46097.1461728357</x:v>
+        <x:v>46093.1595409143</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>164</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E17" s="14" t="s">
-        <x:v>169</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="F17" s="14" t="s">
-        <x:v>170</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="G17" s="14" t="s">
-        <x:v>171</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46083.2380494329</x:v>
+        <x:v>46084.0854516898</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46100</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
-        <x:v>172</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46097.1564439468</x:v>
+        <x:v>46093.3956400694</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>173</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D18" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E18" s="14" t="s">
-        <x:v>174</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F18" s="14" t="s">
-        <x:v>175</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="G18" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46083.2599218056</x:v>
+        <x:v>46080.4532551852</x:v>
       </x:c>
       <x:c r="I18" s="16">
-        <x:v>46101</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J18" s="15" t="s">
-        <x:v>177</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46097.1652390856</x:v>
+        <x:v>46097.1461728357</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
-        <x:v>178</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D19" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E19" s="14" t="s">
-        <x:v>179</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F19" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="G19" s="14" t="s">
-        <x:v>181</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H19" s="16">
-        <x:v>46069.278571956</x:v>
+        <x:v>46083.2380494329</x:v>
       </x:c>
       <x:c r="I19" s="16">
-        <x:v>46067</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J19" s="15" t="s">
-        <x:v>182</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="K19" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46100.3884108912</x:v>
+        <x:v>46097.1564439468</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C20" s="14" t="s">
-        <x:v>183</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="D20" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E20" s="14" t="s">
-        <x:v>184</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F20" s="14" t="s">
-        <x:v>185</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G20" s="14" t="s">
-        <x:v>186</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="H20" s="16">
-        <x:v>46084.0854516898</x:v>
+        <x:v>46083.2443981019</x:v>
       </x:c>
       <x:c r="I20" s="16">
-        <x:v>46144</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J20" s="15" t="s">
-        <x:v>187</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="K20" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46093.3956400694</x:v>
+        <x:v>46097.1600206018</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C21" s="14" t="s">
-        <x:v>183</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D21" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E21" s="14" t="s">
-        <x:v>188</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F21" s="14" t="s">
-        <x:v>189</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G21" s="14" t="s">
-        <x:v>190</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="H21" s="16">
-        <x:v>46084.0996762384</x:v>
+        <x:v>46083.252116412</x:v>
       </x:c>
       <x:c r="I21" s="16">
-        <x:v>46094</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J21" s="15" t="s">
-        <x:v>191</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46097.241468588</x:v>
+        <x:v>46097.1628986343</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>192</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="D22" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E22" s="14" t="s">
-        <x:v>193</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F22" s="14" t="s">
-        <x:v>194</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G22" s="14" t="s">
-        <x:v>195</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H22" s="16">
-        <x:v>46069.1542109954</x:v>
+        <x:v>46083.2599218056</x:v>
       </x:c>
       <x:c r="I22" s="16">
-        <x:v>46035</x:v>
+        <x:v>46101</x:v>
       </x:c>
       <x:c r="J22" s="15" t="s">
-        <x:v>196</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K22" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46097.2466610301</x:v>
+        <x:v>46097.1652390856</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
-        <x:v>197</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="D23" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E23" s="14" t="s">
-        <x:v>198</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="F23" s="14" t="s">
-        <x:v>199</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G23" s="14" t="s">
-        <x:v>200</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46069.2178798032</x:v>
+        <x:v>46084.0996762384</x:v>
       </x:c>
       <x:c r="I23" s="16">
-        <x:v>46051</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J23" s="15" t="s">
-        <x:v>201</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="K23" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46097.2456397685</x:v>
+        <x:v>46097.241468588</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C24" s="14" t="s">
-        <x:v>202</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D24" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E24" s="14" t="s">
-        <x:v>203</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="F24" s="14" t="s">
-        <x:v>204</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G24" s="14" t="s">
-        <x:v>205</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H24" s="16">
-        <x:v>46069.3717699074</x:v>
+        <x:v>46069.2178798032</x:v>
       </x:c>
       <x:c r="I24" s="16">
-        <x:v>46066</x:v>
+        <x:v>46051</x:v>
       </x:c>
       <x:c r="J24" s="15" t="s">
-        <x:v>206</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="K24" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L24" s="18">
-        <x:v>46100.3754893056</x:v>
+        <x:v>46097.2456397685</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C25" s="14" t="s">
-        <x:v>207</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D25" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E25" s="14" t="s">
-        <x:v>208</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="F25" s="14" t="s">
-        <x:v>209</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G25" s="14" t="s">
-        <x:v>210</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H25" s="16">
-        <x:v>46083.2443981019</x:v>
+        <x:v>46069.1542109954</x:v>
       </x:c>
       <x:c r="I25" s="16">
-        <x:v>46100</x:v>
+        <x:v>46035</x:v>
       </x:c>
       <x:c r="J25" s="15" t="s">
-        <x:v>211</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="K25" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L25" s="18">
-        <x:v>46097.1600206018</x:v>
+        <x:v>46097.2466610301</x:v>
       </x:c>
       <x:c r="M25" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="30" customHeight="1">
       <x:c r="B26" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C26" s="14" t="s">
-        <x:v>212</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="D26" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E26" s="14" t="s">
-        <x:v>213</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="F26" s="14" t="s">
-        <x:v>214</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="G26" s="14" t="s">
-        <x:v>215</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="H26" s="16">
-        <x:v>46084.1225139699</x:v>
+        <x:v>46084.1080380324</x:v>
       </x:c>
       <x:c r="I26" s="16">
-        <x:v>46172</x:v>
+        <x:v>46103</x:v>
       </x:c>
       <x:c r="J26" s="15" t="s">
-        <x:v>216</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="K26" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L26" s="18">
-        <x:v>46097.3505144329</x:v>
+        <x:v>46097.2478153472</x:v>
       </x:c>
       <x:c r="M26" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
       <x:c r="B27" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C27" s="14" t="s">
-        <x:v>217</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="D27" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E27" s="14" t="s">
-        <x:v>218</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="F27" s="14" t="s">
-        <x:v>219</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="G27" s="14" t="s">
-        <x:v>220</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H27" s="16">
-        <x:v>46083.252116412</x:v>
+        <x:v>46069.1151616435</x:v>
       </x:c>
       <x:c r="I27" s="16">
-        <x:v>46100</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J27" s="15" t="s">
-        <x:v>221</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="K27" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L27" s="18">
-        <x:v>46097.1628986343</x:v>
+        <x:v>46097.343386956</x:v>
       </x:c>
       <x:c r="M27" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
       <x:c r="B28" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C28" s="14" t="s">
-        <x:v>222</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="D28" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E28" s="14" t="s">
-        <x:v>223</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="F28" s="14" t="s">
-        <x:v>224</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="G28" s="14" t="s">
-        <x:v>225</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="H28" s="16">
-        <x:v>46084.1157546528</x:v>
+        <x:v>46084.1225139699</x:v>
       </x:c>
       <x:c r="I28" s="16">
-        <x:v>46084</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J28" s="15" t="s">
-        <x:v>226</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="K28" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L28" s="18">
-        <x:v>46105.3755915741</x:v>
+        <x:v>46097.3505144329</x:v>
       </x:c>
       <x:c r="M28" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="30" customHeight="1">
       <x:c r="B29" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C29" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="D29" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E29" s="14" t="s">
-        <x:v>228</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="F29" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G29" s="14" t="s">
-        <x:v>230</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H29" s="16">
-        <x:v>46069.1151616435</x:v>
+        <x:v>46098.290884375</x:v>
       </x:c>
       <x:c r="I29" s="16">
-        <x:v>46172</x:v>
+        <x:v>45997</x:v>
       </x:c>
       <x:c r="J29" s="15" t="s">
-        <x:v>231</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="K29" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="L29" s="18">
-        <x:v>46097.343386956</x:v>
+        <x:v>46098.3188767824</x:v>
       </x:c>
       <x:c r="M29" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
       <x:c r="B30" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C30" s="14" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="D30" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="D30" s="15" t="s"/>
       <x:c r="E30" s="14" t="s">
-        <x:v>233</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="F30" s="14" t="s">
-        <x:v>234</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="G30" s="14" t="s">
-        <x:v>235</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="H30" s="16">
-        <x:v>46107.3381444213</x:v>
+        <x:v>46100.1144765394</x:v>
       </x:c>
       <x:c r="I30" s="16">
-        <x:v>46112</x:v>
+        <x:v>46100.1505107292</x:v>
       </x:c>
       <x:c r="J30" s="15" t="s">
-        <x:v>236</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="K30" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L30" s="18">
-        <x:v>46107.3506854282</x:v>
+        <x:v>46100.1652817245</x:v>
       </x:c>
       <x:c r="M30" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="30" customHeight="1">
       <x:c r="B31" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C31" s="14" t="s">
-        <x:v>237</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D31" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E31" s="14" t="s">
-        <x:v>238</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="F31" s="14" t="s">
-        <x:v>239</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="G31" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="H31" s="16">
-        <x:v>46069.2327997454</x:v>
+        <x:v>46069.3717699074</x:v>
       </x:c>
       <x:c r="I31" s="16">
-        <x:v>46049</x:v>
+        <x:v>46066</x:v>
       </x:c>
       <x:c r="J31" s="15" t="s">
-        <x:v>241</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="K31" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L31" s="18">
-        <x:v>46100.3816829514</x:v>
+        <x:v>46100.3754893056</x:v>
       </x:c>
       <x:c r="M31" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="30" customHeight="1">
       <x:c r="B32" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C32" s="14" t="s">
-        <x:v>242</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="D32" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E32" s="14" t="s">
-        <x:v>243</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="F32" s="14" t="s">
-        <x:v>244</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="G32" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="H32" s="16">
-        <x:v>46086.106481875</x:v>
+        <x:v>46069.2327997454</x:v>
       </x:c>
       <x:c r="I32" s="16">
-        <x:v>46095</x:v>
+        <x:v>46049</x:v>
       </x:c>
       <x:c r="J32" s="15" t="s">
-        <x:v>246</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="K32" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L32" s="18">
-        <x:v>46090.2765830324</x:v>
+        <x:v>46100.3816829514</x:v>
       </x:c>
       <x:c r="M32" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="30" customHeight="1">
       <x:c r="B33" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C33" s="14" t="s">
-        <x:v>247</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="D33" s="15" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E33" s="14" t="s">
-        <x:v>248</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="F33" s="14" t="s">
-        <x:v>249</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="G33" s="14" t="s">
-        <x:v>250</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="H33" s="16">
-        <x:v>46085.1709247338</x:v>
+        <x:v>46069.278571956</x:v>
       </x:c>
       <x:c r="I33" s="16">
-        <x:v>46085.1709419676</x:v>
+        <x:v>46067</x:v>
       </x:c>
       <x:c r="J33" s="15" t="s">
-        <x:v>251</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="K33" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L33" s="18">
-        <x:v>46090.3337014815</x:v>
+        <x:v>46100.3884108912</x:v>
       </x:c>
       <x:c r="M33" s="14" t="s">
-        <x:v>252</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="30" customHeight="1">
       <x:c r="B34" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C34" s="14" t="s">
-        <x:v>247</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="D34" s="15" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E34" s="14" t="s">
-        <x:v>253</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="F34" s="14" t="s">
-        <x:v>254</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="G34" s="14" t="s">
-        <x:v>255</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="H34" s="16">
-        <x:v>46085.1662527662</x:v>
+        <x:v>46084.1157546528</x:v>
       </x:c>
       <x:c r="I34" s="16">
-        <x:v>46085.1662689699</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J34" s="15" t="s">
-        <x:v>256</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="K34" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L34" s="18">
-        <x:v>46090.3437343634</x:v>
+        <x:v>46105.3755915741</x:v>
       </x:c>
       <x:c r="M34" s="14" t="s">
-        <x:v>252</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="30" customHeight="1">
       <x:c r="B35" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C35" s="14" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="D35" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D35" s="15" t="s"/>
       <x:c r="E35" s="14" t="s">
-        <x:v>258</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="F35" s="14" t="s">
-        <x:v>259</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="G35" s="14" t="s">
-        <x:v>260</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H35" s="16">
-        <x:v>46107.2716210185</x:v>
+        <x:v>46106.2628248843</x:v>
       </x:c>
       <x:c r="I35" s="16">
-        <x:v>46107.2716387731</x:v>
+        <x:v>46106.2706934954</x:v>
       </x:c>
       <x:c r="J35" s="15" t="s">
-        <x:v>261</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="K35" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L35" s="18">
-        <x:v>46107.3352773843</x:v>
+        <x:v>46106.2922441319</x:v>
       </x:c>
       <x:c r="M35" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="30" customHeight="1">
       <x:c r="B36" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C36" s="14" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="D36" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="D36" s="15" t="s"/>
       <x:c r="E36" s="14" t="s">
-        <x:v>262</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="F36" s="14" t="s">
-        <x:v>263</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="G36" s="14" t="s">
-        <x:v>264</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="H36" s="16">
-        <x:v>46084.1080380324</x:v>
+        <x:v>46107.1074963889</x:v>
       </x:c>
       <x:c r="I36" s="16">
-        <x:v>46103</x:v>
+        <x:v>46107.1512672454</x:v>
       </x:c>
       <x:c r="J36" s="15" t="s">
-        <x:v>265</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="K36" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L36" s="18">
-        <x:v>46097.2478153472</x:v>
+        <x:v>46107.1672093287</x:v>
       </x:c>
       <x:c r="M36" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="30" customHeight="1">
       <x:c r="B37" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C37" s="14" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="D37" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="D37" s="15" t="s"/>
       <x:c r="E37" s="14" t="s">
-        <x:v>267</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="F37" s="14" t="s">
-        <x:v>268</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="G37" s="14" t="s">
-        <x:v>269</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="H37" s="16">
-        <x:v>46083.0788057755</x:v>
+        <x:v>46107.1079779977</x:v>
       </x:c>
       <x:c r="I37" s="16">
-        <x:v>46084</x:v>
+        <x:v>46107.1569821643</x:v>
       </x:c>
       <x:c r="J37" s="15" t="s">
-        <x:v>270</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K37" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L37" s="18">
-        <x:v>46083.1042250116</x:v>
+        <x:v>46107.1713369444</x:v>
       </x:c>
       <x:c r="M37" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="30" customHeight="1">
       <x:c r="B38" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C38" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="D38" s="15" t="s"/>
+      <x:c r="E38" s="14" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="F38" s="14" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="D38" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E38" s="14" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="F38" s="14" t="s">
-        <x:v>272</x:v>
-      </x:c>
       <x:c r="G38" s="14" t="s">
-        <x:v>273</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="H38" s="16">
-        <x:v>46086.099798588</x:v>
+        <x:v>46107.1401251852</x:v>
       </x:c>
       <x:c r="I38" s="16">
-        <x:v>46098</x:v>
+        <x:v>46107.1653469792</x:v>
       </x:c>
       <x:c r="J38" s="15" t="s">
-        <x:v>274</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="K38" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L38" s="18">
-        <x:v>46090.2691152778</x:v>
+        <x:v>46107.1722420255</x:v>
       </x:c>
       <x:c r="M38" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="30" customHeight="1">
       <x:c r="B39" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C39" s="14" t="s">
-        <x:v>242</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="D39" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E39" s="14" t="s">
-        <x:v>275</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="F39" s="14" t="s">
-        <x:v>276</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="G39" s="14" t="s">
-        <x:v>277</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="H39" s="16">
-        <x:v>46086.1144463079</x:v>
+        <x:v>46107.2716210185</x:v>
       </x:c>
       <x:c r="I39" s="16">
-        <x:v>46097</x:v>
+        <x:v>46107.2716387731</x:v>
       </x:c>
       <x:c r="J39" s="15" t="s">
-        <x:v>278</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="K39" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L39" s="18">
-        <x:v>46090.2703739352</x:v>
+        <x:v>46107.3352773843</x:v>
       </x:c>
       <x:c r="M39" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="30" customHeight="1">
       <x:c r="B40" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C40" s="14" t="s">
-        <x:v>242</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D40" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E40" s="14" t="s">
-        <x:v>279</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="F40" s="14" t="s">
-        <x:v>280</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="G40" s="14" t="s">
-        <x:v>281</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="H40" s="16">
-        <x:v>46087.1643336806</x:v>
+        <x:v>46107.3381444213</x:v>
       </x:c>
       <x:c r="I40" s="16">
-        <x:v>46104</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="J40" s="15" t="s">
-        <x:v>282</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="K40" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L40" s="18">
-        <x:v>46090.2727784143</x:v>
+        <x:v>46107.3506854282</x:v>
       </x:c>
       <x:c r="M40" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="30" customHeight="1">
       <x:c r="B41" s="14" t="s">
-        <x:v>114</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C41" s="14" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="D41" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D41" s="15" t="s"/>
       <x:c r="E41" s="14" t="s">
-        <x:v>284</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="F41" s="14" t="s">
-        <x:v>285</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="G41" s="14" t="s">
-        <x:v>286</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="H41" s="16">
-        <x:v>46098.290884375</x:v>
+        <x:v>46111.14459375</x:v>
       </x:c>
       <x:c r="I41" s="16">
-        <x:v>45997</x:v>
+        <x:v>46111.1542258102</x:v>
       </x:c>
       <x:c r="J41" s="15" t="s">
-        <x:v>287</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="K41" s="17" t="n">
-        <x:v>2550</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L41" s="18">
-        <x:v>46098.3188767824</x:v>
+        <x:v>46111.1662193056</x:v>
       </x:c>
       <x:c r="M41" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="44" spans="1:28" ht="30" customHeight="1">
       <x:c r="B44" s="19" t="s">
-        <x:v>120</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C44" s="20" t="s"/>
       <x:c r="D44" s="20" t="s"/>
@@ -5198,18 +5114,18 @@
     </x:row>
     <x:row r="45" spans="1:28" ht="22" customHeight="1">
       <x:c r="B45" s="22" t="s">
-        <x:v>121</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C45" s="23" t="s"/>
       <x:c r="D45" s="23" t="s"/>
       <x:c r="E45" s="23" t="s"/>
       <x:c r="F45" s="24" t="s">
-        <x:v>122</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:28" ht="18" customHeight="1">
       <x:c r="B46" s="25" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C46" s="26" t="s"/>
       <x:c r="D46" s="26" t="s"/>
@@ -5220,7 +5136,7 @@
     </x:row>
     <x:row r="47" spans="1:28" ht="18" customHeight="1">
       <x:c r="B47" s="25" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C47" s="26" t="s"/>
       <x:c r="D47" s="26" t="s"/>
@@ -5231,7 +5147,7 @@
     </x:row>
     <x:row r="48" spans="1:28" ht="18" customHeight="1">
       <x:c r="B48" s="25" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C48" s="26" t="s"/>
       <x:c r="D48" s="26" t="s"/>
@@ -5242,7 +5158,7 @@
     </x:row>
     <x:row r="49" spans="1:28" ht="18" customHeight="1">
       <x:c r="B49" s="25" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C49" s="26" t="s"/>
       <x:c r="D49" s="26" t="s"/>
@@ -5253,7 +5169,7 @@
     </x:row>
     <x:row r="50" spans="1:28" ht="18" customHeight="1">
       <x:c r="B50" s="25" t="s">
-        <x:v>114</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C50" s="26" t="s"/>
       <x:c r="D50" s="26" t="s"/>
@@ -5264,7 +5180,7 @@
     </x:row>
     <x:row r="51" spans="1:28" ht="28" customHeight="1">
       <x:c r="B51" s="28" t="s">
-        <x:v>123</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C51" s="29" t="s"/>
       <x:c r="D51" s="29" t="s"/>
@@ -6416,206 +6332,206 @@
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="D8" s="15" t="s"/>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>289</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>290</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>291</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46126.3445514815</x:v>
+        <x:v>46120.2370111574</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>46126.3505074537</x:v>
+        <x:v>46023</x:v>
       </x:c>
       <x:c r="J8" s="15" t="s">
-        <x:v>292</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
-        <x:v>130</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46126.3564094097</x:v>
+        <x:v>46120.2952031944</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>293</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s"/>
       <x:c r="E9" s="14" t="s">
-        <x:v>294</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>295</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>296</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46126.3584514236</x:v>
+        <x:v>46126.3445514815</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46126.3611957755</x:v>
+        <x:v>46126.3505074537</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
-        <x:v>297</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46126.3662729282</x:v>
+        <x:v>46126.3564094097</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>298</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s"/>
       <x:c r="E10" s="14" t="s">
-        <x:v>299</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
-        <x:v>300</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="G10" s="14" t="s">
-        <x:v>301</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46133.1256989236</x:v>
+        <x:v>46126.3584514236</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>46133.1306981713</x:v>
+        <x:v>46126.3611957755</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
-        <x:v>302</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46133.1352517477</x:v>
+        <x:v>46126.3662729282</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s"/>
       <x:c r="E11" s="14" t="s">
-        <x:v>304</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="F11" s="14" t="s">
-        <x:v>305</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="G11" s="14" t="s">
-        <x:v>306</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46134.0392876852</x:v>
+        <x:v>46133.1256989236</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>46154</x:v>
+        <x:v>46133.1306981713</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
-        <x:v>307</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46134.0609597569</x:v>
+        <x:v>46133.1352517477</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>308</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
-        <x:v>309</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="F12" s="14" t="s">
-        <x:v>310</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="G12" s="14" t="s">
-        <x:v>311</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46141.2837138079</x:v>
+        <x:v>46134.0392876852</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>45814</x:v>
+        <x:v>46154</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
-        <x:v>312</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>7530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46141.3129605787</x:v>
+        <x:v>46134.0609597569</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>313</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
-        <x:v>314</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>315</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="G13" s="14" t="s">
-        <x:v>316</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="H13" s="16">
         <x:v>46140.22664875</x:v>
@@ -6624,7 +6540,7 @@
         <x:v>46140.2266724884</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
-        <x:v>317</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
         <x:v>3530</x:v>
@@ -6633,27 +6549,27 @@
         <x:v>46140.2614984259</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>318</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
-        <x:v>319</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F14" s="14" t="s">
-        <x:v>320</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="G14" s="14" t="s">
-        <x:v>321</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="H14" s="16">
         <x:v>46141.2802576736</x:v>
@@ -6662,7 +6578,7 @@
         <x:v>45814</x:v>
       </x:c>
       <x:c r="J14" s="15" t="s">
-        <x:v>322</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
         <x:v>7530</x:v>
@@ -6671,52 +6587,52 @@
         <x:v>46141.3116617361</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>114</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>115</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
-        <x:v>323</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
-        <x:v>324</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="G15" s="14" t="s">
-        <x:v>325</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46120.2370111574</x:v>
+        <x:v>46141.2837138079</x:v>
       </x:c>
       <x:c r="I15" s="16">
-        <x:v>46023</x:v>
+        <x:v>45814</x:v>
       </x:c>
       <x:c r="J15" s="15" t="s">
-        <x:v>326</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>2550</x:v>
+        <x:v>7530</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46120.2952031944</x:v>
+        <x:v>46141.3129605787</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="19" t="s">
-        <x:v>120</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C18" s="20" t="s"/>
       <x:c r="D18" s="20" t="s"/>
@@ -6725,18 +6641,18 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
       <x:c r="B19" s="22" t="s">
-        <x:v>121</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C19" s="23" t="s"/>
       <x:c r="D19" s="23" t="s"/>
       <x:c r="E19" s="23" t="s"/>
       <x:c r="F19" s="24" t="s">
-        <x:v>122</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
       <x:c r="B20" s="25" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C20" s="26" t="s"/>
       <x:c r="D20" s="26" t="s"/>
@@ -6747,7 +6663,7 @@
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
       <x:c r="B21" s="25" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C21" s="26" t="s"/>
       <x:c r="D21" s="26" t="s"/>
@@ -6758,7 +6674,7 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
       <x:c r="B22" s="25" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C22" s="26" t="s"/>
       <x:c r="D22" s="26" t="s"/>
@@ -6769,7 +6685,7 @@
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
       <x:c r="B23" s="25" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C23" s="26" t="s"/>
       <x:c r="D23" s="26" t="s"/>
@@ -6780,7 +6696,7 @@
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
       <x:c r="B24" s="25" t="s">
-        <x:v>114</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C24" s="26" t="s"/>
       <x:c r="D24" s="26" t="s"/>
@@ -6791,7 +6707,7 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="28" customHeight="1">
       <x:c r="B25" s="28" t="s">
-        <x:v>123</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C25" s="29" t="s"/>
       <x:c r="D25" s="29" t="s"/>
